--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -934,6 +934,5846 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126192244</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98257</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>720876</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6382945</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126192356</v>
+      </c>
+      <c r="B5" t="n">
+        <v>95942</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>720868</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6382908</v>
+      </c>
+      <c r="S5" t="n">
+        <v>7</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126192233</v>
+      </c>
+      <c r="B6" t="n">
+        <v>110419</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>720895</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6382925</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126192220</v>
+      </c>
+      <c r="B7" t="n">
+        <v>105363</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>720869</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6382918</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126192192</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98317</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>720755</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6382837</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126192215</v>
+      </c>
+      <c r="B9" t="n">
+        <v>109152</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>720838</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6382930</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126192274</v>
+      </c>
+      <c r="B10" t="n">
+        <v>105363</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>720757</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6383073</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126192209</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99014</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222322</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ängsstarr</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>720818</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6382895</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126192246</v>
+      </c>
+      <c r="B12" t="n">
+        <v>110419</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>720876</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6382953</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126192224</v>
+      </c>
+      <c r="B13" t="n">
+        <v>105363</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>720878</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6382913</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126192228</v>
+      </c>
+      <c r="B14" t="n">
+        <v>105363</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>720883</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6382912</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126192259</v>
+      </c>
+      <c r="B15" t="n">
+        <v>105363</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>720844</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6383011</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Barrblandskog, mossrik, vaierande ålder på träd, bara enstak död.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126192229</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>720883</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6382912</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126192258</v>
+      </c>
+      <c r="B17" t="n">
+        <v>105363</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>720841</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6382998</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ett ex i blom.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126192248</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98257</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>720869</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6382960</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126192243</v>
+      </c>
+      <c r="B19" t="n">
+        <v>110419</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>720876</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6382945</v>
+      </c>
+      <c r="S19" t="n">
+        <v>7</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126192227</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98317</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>720883</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6382912</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126192216</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98317</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>720838</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6382930</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126192241</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>720883</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6382951</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126192238</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98317</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>720883</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6382941</v>
+      </c>
+      <c r="S23" t="n">
+        <v>7</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126192240</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98362</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>720883</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6382951</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126192211</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>223572</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blodnycklar</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata var. cruenta</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(O F.Müll.) Hyl.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>720818</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6382895</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126192239</v>
+      </c>
+      <c r="B26" t="n">
+        <v>105363</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>720883</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6382941</v>
+      </c>
+      <c r="S26" t="n">
+        <v>7</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126192250</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98317</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>720876</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6382966</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126192221</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>720865</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6382912</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126192194</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98257</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>720755</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6382837</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126192210</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99380</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222662</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Axag</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Schoenus ferrugineus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>720818</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6382895</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126192237</v>
+      </c>
+      <c r="B31" t="n">
+        <v>105363</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>720884</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6382932</v>
+      </c>
+      <c r="S31" t="n">
+        <v>6</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126192230</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>720895</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6382925</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126192271</v>
+      </c>
+      <c r="B33" t="n">
+        <v>105363</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>720797</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6383069</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126192304</v>
+      </c>
+      <c r="B34" t="n">
+        <v>105923</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>720765</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6382808</v>
+      </c>
+      <c r="S34" t="n">
+        <v>7</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126192257</v>
+      </c>
+      <c r="B35" t="n">
+        <v>110419</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>720869</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6382986</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126192198</v>
+      </c>
+      <c r="B36" t="n">
+        <v>109152</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>720774</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6382882</v>
+      </c>
+      <c r="S36" t="n">
+        <v>7</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126192231</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98362</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>720895</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6382925</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126192203</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>720789</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6382884</v>
+      </c>
+      <c r="S38" t="n">
+        <v>8</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126192253</v>
+      </c>
+      <c r="B39" t="n">
+        <v>110419</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>720863</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6382976</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126192200</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98362</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>720774</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6382882</v>
+      </c>
+      <c r="S40" t="n">
+        <v>7</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126192252</v>
+      </c>
+      <c r="B41" t="n">
+        <v>109152</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>720863</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6382976</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126192249</v>
+      </c>
+      <c r="B42" t="n">
+        <v>109152</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>720876</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6382966</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126192331</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98362</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>720772</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6382868</v>
+      </c>
+      <c r="S43" t="n">
+        <v>6</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126192214</v>
+      </c>
+      <c r="B44" t="n">
+        <v>109152</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>720826</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6382935</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126192242</v>
+      </c>
+      <c r="B45" t="n">
+        <v>109152</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>720876</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6382945</v>
+      </c>
+      <c r="S45" t="n">
+        <v>7</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126192202</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98317</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>720782</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6382877</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126192254</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98317</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>720863</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6382976</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126192219</v>
+      </c>
+      <c r="B48" t="n">
+        <v>105363</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>720858</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6382930</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126192199</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98317</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>720774</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6382882</v>
+      </c>
+      <c r="S49" t="n">
+        <v>7</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126192330</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98367</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>720772</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6382868</v>
+      </c>
+      <c r="S50" t="n">
+        <v>6</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126192207</v>
+      </c>
+      <c r="B51" t="n">
+        <v>105261</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>720818</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6382895</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126192195</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98362</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>720755</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6382837</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>126192213</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98362</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>720826</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6382935</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>126192260</v>
+      </c>
+      <c r="B54" t="n">
+        <v>105363</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>720835</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6383025</v>
+      </c>
+      <c r="S54" t="n">
+        <v>3</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Yngre skog mot N, nyröjt?</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126192222</v>
+      </c>
+      <c r="B55" t="n">
+        <v>105363</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>720868</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6382908</v>
+      </c>
+      <c r="S55" t="n">
+        <v>7</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126192268</v>
+      </c>
+      <c r="B56" t="n">
+        <v>109152</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>720800</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6383077</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -936,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126192244</v>
+        <v>126192356</v>
       </c>
       <c r="B4" t="n">
-        <v>98257</v>
+        <v>95944</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,31 +947,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223591</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720876</v>
+        <v>720868</v>
       </c>
       <c r="R4" t="n">
-        <v>6382945</v>
+        <v>6382908</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
@@ -1026,11 +1026,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1047,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126192356</v>
+        <v>126192244</v>
       </c>
       <c r="B5" t="n">
-        <v>95942</v>
+        <v>98259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,31 +1053,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>223591</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1091,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720868</v>
+        <v>720876</v>
       </c>
       <c r="R5" t="n">
-        <v>6382908</v>
+        <v>6382945</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
@@ -1137,6 +1132,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1156,7 +1156,7 @@
         <v>126192233</v>
       </c>
       <c r="B6" t="n">
-        <v>110419</v>
+        <v>110421</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>126192220</v>
       </c>
       <c r="B7" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>126192192</v>
       </c>
       <c r="B8" t="n">
-        <v>98317</v>
+        <v>98319</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>126192215</v>
       </c>
       <c r="B9" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>126192274</v>
       </c>
       <c r="B10" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>126192209</v>
       </c>
       <c r="B11" t="n">
-        <v>99014</v>
+        <v>99016</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126192246</v>
+        <v>126192224</v>
       </c>
       <c r="B12" t="n">
-        <v>110419</v>
+        <v>105365</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,37 +1813,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219711</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720876</v>
+        <v>720878</v>
       </c>
       <c r="R12" t="n">
-        <v>6382953</v>
+        <v>6382913</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1904,10 +1913,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126192224</v>
+        <v>126192228</v>
       </c>
       <c r="B13" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1943,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1948,13 +1957,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720878</v>
+        <v>720883</v>
       </c>
       <c r="R13" t="n">
-        <v>6382913</v>
+        <v>6382912</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2015,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126192228</v>
+        <v>126192246</v>
       </c>
       <c r="B14" t="n">
-        <v>105363</v>
+        <v>110421</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2026,43 +2035,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>219711</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720883</v>
+        <v>720876</v>
       </c>
       <c r="R14" t="n">
-        <v>6382912</v>
+        <v>6382953</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126192259</v>
+        <v>126192229</v>
       </c>
       <c r="B15" t="n">
-        <v>105363</v>
+        <v>98363</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2137,21 +2137,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>219862</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2164,21 +2164,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720844</v>
+        <v>720883</v>
       </c>
       <c r="R15" t="n">
-        <v>6383011</v>
+        <v>6382912</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2211,11 +2206,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Barrblandskog, mossrik, vaierande ålder på träd, bara enstak död.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126192229</v>
+        <v>126192259</v>
       </c>
       <c r="B16" t="n">
-        <v>98361</v>
+        <v>105365</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,21 +2248,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219862</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2285,16 +2275,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720883</v>
+        <v>720844</v>
       </c>
       <c r="R16" t="n">
-        <v>6382912</v>
+        <v>6383011</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2327,6 +2322,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Barrblandskog, mossrik, vaierande ålder på träd, bara enstak död.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2361,7 +2361,7 @@
         <v>126192258</v>
       </c>
       <c r="B17" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>126192248</v>
       </c>
       <c r="B18" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>126192243</v>
       </c>
       <c r="B19" t="n">
-        <v>110419</v>
+        <v>110421</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>126192227</v>
       </c>
       <c r="B20" t="n">
-        <v>98317</v>
+        <v>98319</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>126192216</v>
       </c>
       <c r="B21" t="n">
-        <v>98317</v>
+        <v>98319</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>126192241</v>
       </c>
       <c r="B22" t="n">
-        <v>98361</v>
+        <v>98363</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>126192238</v>
       </c>
       <c r="B23" t="n">
-        <v>98317</v>
+        <v>98319</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>126192240</v>
       </c>
       <c r="B24" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>126192211</v>
       </c>
       <c r="B25" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3367,10 +3367,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126192239</v>
+        <v>126192250</v>
       </c>
       <c r="B26" t="n">
-        <v>105363</v>
+        <v>98319</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3378,26 +3378,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3405,19 +3405,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>720883</v>
+        <v>720876</v>
       </c>
       <c r="R26" t="n">
-        <v>6382941</v>
+        <v>6382966</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3478,10 +3483,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126192250</v>
+        <v>126192239</v>
       </c>
       <c r="B27" t="n">
-        <v>98317</v>
+        <v>105365</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,26 +3494,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3516,24 +3521,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720876</v>
+        <v>720883</v>
       </c>
       <c r="R27" t="n">
-        <v>6382966</v>
+        <v>6382941</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>126192221</v>
       </c>
       <c r="B28" t="n">
-        <v>98361</v>
+        <v>98363</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126192194</v>
+        <v>126192210</v>
       </c>
       <c r="B29" t="n">
-        <v>98257</v>
+        <v>99382</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3716,46 +3716,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>223591</v>
+        <v>222662</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720755</v>
+        <v>720818</v>
       </c>
       <c r="R29" t="n">
-        <v>6382837</v>
+        <v>6382895</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3798,7 +3789,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3816,10 +3807,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126192210</v>
+        <v>126192237</v>
       </c>
       <c r="B30" t="n">
-        <v>99380</v>
+        <v>105365</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3827,37 +3818,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222662</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720818</v>
+        <v>720884</v>
       </c>
       <c r="R30" t="n">
-        <v>6382895</v>
+        <v>6382932</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3918,10 +3918,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126192237</v>
+        <v>126192194</v>
       </c>
       <c r="B31" t="n">
-        <v>105363</v>
+        <v>98259</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3929,26 +3929,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221144</v>
+        <v>223591</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3962,13 +3962,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720884</v>
+        <v>720755</v>
       </c>
       <c r="R31" t="n">
-        <v>6382932</v>
+        <v>6382837</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>126192230</v>
       </c>
       <c r="B32" t="n">
-        <v>98361</v>
+        <v>98363</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>126192271</v>
       </c>
       <c r="B33" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,27 +4256,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126192304</v>
+        <v>126192198</v>
       </c>
       <c r="B34" t="n">
-        <v>105923</v>
+        <v>109154</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720765</v>
+        <v>720774</v>
       </c>
       <c r="R34" t="n">
-        <v>6382808</v>
+        <v>6382882</v>
       </c>
       <c r="S34" t="n">
         <v>7</v>
@@ -4358,10 +4358,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126192257</v>
+        <v>126192231</v>
       </c>
       <c r="B35" t="n">
-        <v>110419</v>
+        <v>98364</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4369,26 +4369,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4396,21 +4396,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720869</v>
+        <v>720895</v>
       </c>
       <c r="R35" t="n">
-        <v>6382986</v>
+        <v>6382925</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4474,27 +4469,27 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126192198</v>
+        <v>126192257</v>
       </c>
       <c r="B36" t="n">
-        <v>109152</v>
+        <v>110421</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>219711</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4502,20 +4497,34 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720774</v>
+        <v>720869</v>
       </c>
       <c r="R36" t="n">
-        <v>6382882</v>
+        <v>6382986</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4576,57 +4585,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126192231</v>
+        <v>126192304</v>
       </c>
       <c r="B37" t="n">
-        <v>98362</v>
+        <v>105925</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720895</v>
+        <v>720765</v>
       </c>
       <c r="R37" t="n">
-        <v>6382925</v>
+        <v>6382808</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>126192203</v>
       </c>
       <c r="B38" t="n">
-        <v>98361</v>
+        <v>98363</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4798,10 +4798,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126192253</v>
+        <v>126192331</v>
       </c>
       <c r="B39" t="n">
-        <v>110419</v>
+        <v>98364</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4809,26 +4809,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4836,24 +4836,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720863</v>
+        <v>720772</v>
       </c>
       <c r="R39" t="n">
-        <v>6382976</v>
+        <v>6382868</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4914,57 +4909,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126192200</v>
+        <v>126192252</v>
       </c>
       <c r="B40" t="n">
-        <v>98362</v>
+        <v>109154</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>720774</v>
+        <v>720863</v>
       </c>
       <c r="R40" t="n">
-        <v>6382882</v>
+        <v>6382976</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5025,10 +5011,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126192252</v>
+        <v>126192249</v>
       </c>
       <c r="B41" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5053,20 +5039,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>720863</v>
+        <v>720876</v>
       </c>
       <c r="R41" t="n">
-        <v>6382976</v>
+        <v>6382966</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5127,37 +5122,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126192249</v>
+        <v>126192200</v>
       </c>
       <c r="B42" t="n">
-        <v>109152</v>
+        <v>98364</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5171,13 +5166,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>720876</v>
+        <v>720774</v>
       </c>
       <c r="R42" t="n">
-        <v>6382966</v>
+        <v>6382882</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5238,10 +5233,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126192331</v>
+        <v>126192253</v>
       </c>
       <c r="B43" t="n">
-        <v>98362</v>
+        <v>110421</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5249,26 +5244,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5276,19 +5271,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720772</v>
+        <v>720863</v>
       </c>
       <c r="R43" t="n">
-        <v>6382868</v>
+        <v>6382976</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>126192214</v>
       </c>
       <c r="B44" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5451,32 +5451,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126192242</v>
+        <v>126192202</v>
       </c>
       <c r="B45" t="n">
-        <v>109152</v>
+        <v>98319</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5486,13 +5486,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720876</v>
+        <v>720782</v>
       </c>
       <c r="R45" t="n">
-        <v>6382945</v>
+        <v>6382877</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5553,32 +5553,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126192202</v>
+        <v>126192242</v>
       </c>
       <c r="B46" t="n">
-        <v>98317</v>
+        <v>109154</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5588,13 +5588,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720782</v>
+        <v>720876</v>
       </c>
       <c r="R46" t="n">
-        <v>6382877</v>
+        <v>6382945</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5655,10 +5655,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126192254</v>
+        <v>126192199</v>
       </c>
       <c r="B47" t="n">
-        <v>98317</v>
+        <v>98319</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5693,24 +5693,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720863</v>
+        <v>720774</v>
       </c>
       <c r="R47" t="n">
-        <v>6382976</v>
+        <v>6382882</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5771,10 +5766,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126192219</v>
+        <v>126192254</v>
       </c>
       <c r="B48" t="n">
-        <v>105363</v>
+        <v>98319</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5782,26 +5777,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5809,16 +5804,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720858</v>
+        <v>720863</v>
       </c>
       <c r="R48" t="n">
-        <v>6382930</v>
+        <v>6382976</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -5882,10 +5882,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126192199</v>
+        <v>126192330</v>
       </c>
       <c r="B49" t="n">
-        <v>98317</v>
+        <v>98369</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5893,26 +5893,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219798</v>
+        <v>219864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5926,13 +5926,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>720774</v>
+        <v>720772</v>
       </c>
       <c r="R49" t="n">
-        <v>6382882</v>
+        <v>6382868</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5993,10 +5993,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126192330</v>
+        <v>126192219</v>
       </c>
       <c r="B50" t="n">
-        <v>98367</v>
+        <v>105365</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6004,26 +6004,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219864</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6037,13 +6037,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>720772</v>
+        <v>720858</v>
       </c>
       <c r="R50" t="n">
-        <v>6382868</v>
+        <v>6382930</v>
       </c>
       <c r="S50" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6104,37 +6104,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126192207</v>
+        <v>126192195</v>
       </c>
       <c r="B51" t="n">
-        <v>105261</v>
+        <v>98364</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221137</v>
+        <v>219847</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6148,13 +6148,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>720818</v>
+        <v>720755</v>
       </c>
       <c r="R51" t="n">
-        <v>6382895</v>
+        <v>6382837</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6186,11 +6186,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6202,7 +6197,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6220,37 +6215,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126192195</v>
+        <v>126192207</v>
       </c>
       <c r="B52" t="n">
-        <v>98362</v>
+        <v>105263</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219847</v>
+        <v>221137</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6264,13 +6259,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>720755</v>
+        <v>720818</v>
       </c>
       <c r="R52" t="n">
-        <v>6382837</v>
+        <v>6382895</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6302,6 +6297,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6334,7 +6334,7 @@
         <v>126192213</v>
       </c>
       <c r="B53" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6442,62 +6442,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126192260</v>
+        <v>126192268</v>
       </c>
       <c r="B54" t="n">
-        <v>105363</v>
+        <v>109154</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221144</v>
+        <v>220299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>720835</v>
+        <v>720800</v>
       </c>
       <c r="R54" t="n">
-        <v>6383025</v>
+        <v>6383077</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6527,11 +6513,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Yngre skog mot N, nyröjt?</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6563,10 +6544,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126192222</v>
+        <v>126192260</v>
       </c>
       <c r="B55" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6593,7 +6574,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6601,19 +6582,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>720868</v>
+        <v>720835</v>
       </c>
       <c r="R55" t="n">
-        <v>6382908</v>
+        <v>6383025</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6643,6 +6629,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Yngre skog mot N, nyröjt?</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6674,48 +6665,57 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126192268</v>
+        <v>126192222</v>
       </c>
       <c r="B56" t="n">
-        <v>109152</v>
+        <v>105365</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220299</v>
+        <v>221144</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>720800</v>
+        <v>720868</v>
       </c>
       <c r="R56" t="n">
-        <v>6383077</v>
+        <v>6382908</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -936,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126192356</v>
+        <v>126192244</v>
       </c>
       <c r="B4" t="n">
-        <v>95944</v>
+        <v>98259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,31 +947,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>223591</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720868</v>
+        <v>720876</v>
       </c>
       <c r="R4" t="n">
-        <v>6382908</v>
+        <v>6382945</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
@@ -1026,6 +1026,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1042,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126192244</v>
+        <v>126192356</v>
       </c>
       <c r="B5" t="n">
-        <v>98259</v>
+        <v>95944</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1053,31 +1058,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223591</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1086,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720876</v>
+        <v>720868</v>
       </c>
       <c r="R5" t="n">
-        <v>6382945</v>
+        <v>6382908</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
@@ -1132,11 +1137,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -5655,10 +5655,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126192199</v>
+        <v>126192330</v>
       </c>
       <c r="B47" t="n">
-        <v>98319</v>
+        <v>98369</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5666,26 +5666,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219798</v>
+        <v>219864</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5699,13 +5699,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720774</v>
+        <v>720772</v>
       </c>
       <c r="R47" t="n">
-        <v>6382882</v>
+        <v>6382868</v>
       </c>
       <c r="S47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5766,10 +5766,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126192254</v>
+        <v>126192219</v>
       </c>
       <c r="B48" t="n">
-        <v>98319</v>
+        <v>105365</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5777,26 +5777,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5804,21 +5804,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720863</v>
+        <v>720858</v>
       </c>
       <c r="R48" t="n">
-        <v>6382976</v>
+        <v>6382930</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -5882,10 +5877,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126192330</v>
+        <v>126192199</v>
       </c>
       <c r="B49" t="n">
-        <v>98369</v>
+        <v>98319</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5893,26 +5888,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219864</v>
+        <v>219798</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5926,13 +5921,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>720772</v>
+        <v>720774</v>
       </c>
       <c r="R49" t="n">
-        <v>6382868</v>
+        <v>6382882</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5993,10 +5988,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126192219</v>
+        <v>126192254</v>
       </c>
       <c r="B50" t="n">
-        <v>105365</v>
+        <v>98319</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6004,26 +5999,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6031,16 +6026,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>720858</v>
+        <v>720863</v>
       </c>
       <c r="R50" t="n">
-        <v>6382930</v>
+        <v>6382976</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -939,7 +939,7 @@
         <v>126192244</v>
       </c>
       <c r="B4" t="n">
-        <v>98259</v>
+        <v>98261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>126192356</v>
       </c>
       <c r="B5" t="n">
-        <v>95944</v>
+        <v>95946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126192233</v>
+        <v>126192220</v>
       </c>
       <c r="B6" t="n">
-        <v>110421</v>
+        <v>105367</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,37 +1164,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219711</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720895</v>
+        <v>720869</v>
       </c>
       <c r="R6" t="n">
-        <v>6382925</v>
+        <v>6382918</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1255,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126192220</v>
+        <v>126192233</v>
       </c>
       <c r="B7" t="n">
-        <v>105365</v>
+        <v>110423</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,46 +1275,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>219711</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720869</v>
+        <v>720895</v>
       </c>
       <c r="R7" t="n">
-        <v>6382918</v>
+        <v>6382925</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1366,54 +1366,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126192192</v>
+        <v>126192215</v>
       </c>
       <c r="B8" t="n">
-        <v>98319</v>
+        <v>109156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720755</v>
+        <v>720838</v>
       </c>
       <c r="R8" t="n">
-        <v>6382837</v>
+        <v>6382930</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,45 +1468,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126192215</v>
+        <v>126192192</v>
       </c>
       <c r="B9" t="n">
-        <v>109154</v>
+        <v>98321</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720838</v>
+        <v>720755</v>
       </c>
       <c r="R9" t="n">
-        <v>6382930</v>
+        <v>6382837</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1582,7 +1582,7 @@
         <v>126192274</v>
       </c>
       <c r="B10" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,48 +1695,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126192209</v>
+        <v>126192224</v>
       </c>
       <c r="B11" t="n">
-        <v>99016</v>
+        <v>105367</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222322</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720818</v>
+        <v>720878</v>
       </c>
       <c r="R11" t="n">
-        <v>6382895</v>
+        <v>6382913</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,11 +1777,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1784,7 +1788,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1802,10 +1806,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126192224</v>
+        <v>126192228</v>
       </c>
       <c r="B12" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1836,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1846,13 +1850,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720878</v>
+        <v>720883</v>
       </c>
       <c r="R12" t="n">
-        <v>6382913</v>
+        <v>6382912</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1913,57 +1917,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126192228</v>
+        <v>126192209</v>
       </c>
       <c r="B13" t="n">
-        <v>105365</v>
+        <v>99018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>222322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720883</v>
+        <v>720818</v>
       </c>
       <c r="R13" t="n">
-        <v>6382912</v>
+        <v>6382895</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,6 +1990,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2027,7 +2027,7 @@
         <v>126192246</v>
       </c>
       <c r="B14" t="n">
-        <v>110421</v>
+        <v>110423</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>126192229</v>
       </c>
       <c r="B15" t="n">
-        <v>98363</v>
+        <v>98365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>126192259</v>
       </c>
       <c r="B16" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>126192258</v>
       </c>
       <c r="B17" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>126192248</v>
       </c>
       <c r="B18" t="n">
-        <v>98259</v>
+        <v>98261</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,10 +2590,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126192243</v>
+        <v>126192227</v>
       </c>
       <c r="B19" t="n">
-        <v>110421</v>
+        <v>98321</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,26 +2601,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2634,13 +2634,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720876</v>
+        <v>720883</v>
       </c>
       <c r="R19" t="n">
-        <v>6382945</v>
+        <v>6382912</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126192227</v>
+        <v>126192243</v>
       </c>
       <c r="B20" t="n">
-        <v>98319</v>
+        <v>110423</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,26 +2712,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2745,13 +2745,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720883</v>
+        <v>720876</v>
       </c>
       <c r="R20" t="n">
-        <v>6382912</v>
+        <v>6382945</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>126192216</v>
       </c>
       <c r="B21" t="n">
-        <v>98319</v>
+        <v>98321</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>126192241</v>
       </c>
       <c r="B22" t="n">
-        <v>98363</v>
+        <v>98365</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126192238</v>
+        <v>126192240</v>
       </c>
       <c r="B23" t="n">
-        <v>98319</v>
+        <v>98366</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3081,10 +3081,10 @@
         <v>720883</v>
       </c>
       <c r="R23" t="n">
-        <v>6382941</v>
+        <v>6382951</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3145,10 +3145,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126192240</v>
+        <v>126192238</v>
       </c>
       <c r="B24" t="n">
-        <v>98364</v>
+        <v>98321</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3156,21 +3156,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3192,10 +3192,10 @@
         <v>720883</v>
       </c>
       <c r="R24" t="n">
-        <v>6382951</v>
+        <v>6382941</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>126192211</v>
       </c>
       <c r="B25" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3367,10 +3367,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126192250</v>
+        <v>126192221</v>
       </c>
       <c r="B26" t="n">
-        <v>98319</v>
+        <v>98365</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3378,26 +3378,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3405,24 +3405,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>720876</v>
+        <v>720865</v>
       </c>
       <c r="R26" t="n">
-        <v>6382966</v>
+        <v>6382912</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3483,10 +3478,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126192239</v>
+        <v>126192250</v>
       </c>
       <c r="B27" t="n">
-        <v>105365</v>
+        <v>98321</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3494,26 +3489,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3521,19 +3516,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720883</v>
+        <v>720876</v>
       </c>
       <c r="R27" t="n">
-        <v>6382941</v>
+        <v>6382966</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3594,10 +3594,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126192221</v>
+        <v>126192239</v>
       </c>
       <c r="B28" t="n">
-        <v>98363</v>
+        <v>105367</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3605,21 +3605,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219862</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3638,13 +3638,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720865</v>
+        <v>720883</v>
       </c>
       <c r="R28" t="n">
-        <v>6382912</v>
+        <v>6382941</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126192210</v>
+        <v>126192194</v>
       </c>
       <c r="B29" t="n">
-        <v>99382</v>
+        <v>98261</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3716,37 +3716,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222662</v>
+        <v>223591</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720818</v>
+        <v>720755</v>
       </c>
       <c r="R29" t="n">
-        <v>6382895</v>
+        <v>6382837</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3789,7 +3798,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3810,7 +3819,7 @@
         <v>126192237</v>
       </c>
       <c r="B30" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3918,10 +3927,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126192194</v>
+        <v>126192210</v>
       </c>
       <c r="B31" t="n">
-        <v>98259</v>
+        <v>99384</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3929,46 +3938,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223591</v>
+        <v>222662</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720755</v>
+        <v>720818</v>
       </c>
       <c r="R31" t="n">
-        <v>6382837</v>
+        <v>6382895</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4032,7 +4032,7 @@
         <v>126192230</v>
       </c>
       <c r="B32" t="n">
-        <v>98363</v>
+        <v>98365</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>126192271</v>
       </c>
       <c r="B33" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,27 +4256,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126192198</v>
+        <v>126192257</v>
       </c>
       <c r="B34" t="n">
-        <v>109154</v>
+        <v>110423</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220299</v>
+        <v>219711</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4284,20 +4284,34 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720774</v>
+        <v>720869</v>
       </c>
       <c r="R34" t="n">
-        <v>6382882</v>
+        <v>6382986</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4358,57 +4372,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126192231</v>
+        <v>126192198</v>
       </c>
       <c r="B35" t="n">
-        <v>98364</v>
+        <v>109156</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720895</v>
+        <v>720774</v>
       </c>
       <c r="R35" t="n">
-        <v>6382925</v>
+        <v>6382882</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4469,10 +4474,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126192257</v>
+        <v>126192231</v>
       </c>
       <c r="B36" t="n">
-        <v>110421</v>
+        <v>98366</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4480,26 +4485,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4507,21 +4512,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720869</v>
+        <v>720895</v>
       </c>
       <c r="R36" t="n">
-        <v>6382986</v>
+        <v>6382925</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4588,7 +4588,7 @@
         <v>126192304</v>
       </c>
       <c r="B37" t="n">
-        <v>105925</v>
+        <v>105927</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>126192203</v>
       </c>
       <c r="B38" t="n">
-        <v>98363</v>
+        <v>98365</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>126192331</v>
       </c>
       <c r="B39" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>126192252</v>
       </c>
       <c r="B40" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>126192249</v>
       </c>
       <c r="B41" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>126192200</v>
       </c>
       <c r="B42" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>126192253</v>
       </c>
       <c r="B43" t="n">
-        <v>110421</v>
+        <v>110423</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>126192214</v>
       </c>
       <c r="B44" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>126192202</v>
       </c>
       <c r="B45" t="n">
-        <v>98319</v>
+        <v>98321</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>126192242</v>
       </c>
       <c r="B46" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>126192330</v>
       </c>
       <c r="B47" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5766,10 +5766,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126192219</v>
+        <v>126192199</v>
       </c>
       <c r="B48" t="n">
-        <v>105365</v>
+        <v>98321</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5777,26 +5777,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5810,13 +5810,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720858</v>
+        <v>720774</v>
       </c>
       <c r="R48" t="n">
-        <v>6382930</v>
+        <v>6382882</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5877,10 +5877,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126192199</v>
+        <v>126192254</v>
       </c>
       <c r="B49" t="n">
-        <v>98319</v>
+        <v>98321</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5915,19 +5915,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>720774</v>
+        <v>720863</v>
       </c>
       <c r="R49" t="n">
-        <v>6382882</v>
+        <v>6382976</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5988,10 +5993,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126192254</v>
+        <v>126192219</v>
       </c>
       <c r="B50" t="n">
-        <v>98319</v>
+        <v>105367</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5999,26 +6004,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6026,21 +6031,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>720863</v>
+        <v>720858</v>
       </c>
       <c r="R50" t="n">
-        <v>6382976</v>
+        <v>6382930</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -6107,7 +6107,7 @@
         <v>126192195</v>
       </c>
       <c r="B51" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>126192207</v>
       </c>
       <c r="B52" t="n">
-        <v>105263</v>
+        <v>105265</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>126192213</v>
       </c>
       <c r="B53" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6442,48 +6442,62 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126192268</v>
+        <v>126192260</v>
       </c>
       <c r="B54" t="n">
-        <v>109154</v>
+        <v>105367</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220299</v>
+        <v>221144</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>720800</v>
+        <v>720835</v>
       </c>
       <c r="R54" t="n">
-        <v>6383077</v>
+        <v>6383025</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6513,6 +6527,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Yngre skog mot N, nyröjt?</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6544,10 +6563,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126192260</v>
+        <v>126192222</v>
       </c>
       <c r="B55" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6574,7 +6593,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6582,24 +6601,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>720835</v>
+        <v>720868</v>
       </c>
       <c r="R55" t="n">
-        <v>6383025</v>
+        <v>6382908</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6629,11 +6643,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Yngre skog mot N, nyröjt?</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6665,57 +6674,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126192222</v>
+        <v>126192268</v>
       </c>
       <c r="B56" t="n">
-        <v>105365</v>
+        <v>109156</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>220299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>720868</v>
+        <v>720800</v>
       </c>
       <c r="R56" t="n">
-        <v>6382908</v>
+        <v>6383077</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -1153,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126192220</v>
+        <v>126192233</v>
       </c>
       <c r="B6" t="n">
-        <v>105367</v>
+        <v>110423</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,46 +1164,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>219711</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720869</v>
+        <v>720895</v>
       </c>
       <c r="R6" t="n">
-        <v>6382918</v>
+        <v>6382925</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1264,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126192233</v>
+        <v>126192220</v>
       </c>
       <c r="B7" t="n">
-        <v>110423</v>
+        <v>105367</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,37 +1266,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219711</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720895</v>
+        <v>720869</v>
       </c>
       <c r="R7" t="n">
-        <v>6382925</v>
+        <v>6382918</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2479,10 +2479,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126192248</v>
+        <v>126192227</v>
       </c>
       <c r="B18" t="n">
-        <v>98261</v>
+        <v>98321</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2490,26 +2490,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720869</v>
+        <v>720883</v>
       </c>
       <c r="R18" t="n">
-        <v>6382960</v>
+        <v>6382912</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2590,10 +2590,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126192227</v>
+        <v>126192243</v>
       </c>
       <c r="B19" t="n">
-        <v>98321</v>
+        <v>110423</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,26 +2601,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2634,13 +2634,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720883</v>
+        <v>720876</v>
       </c>
       <c r="R19" t="n">
-        <v>6382912</v>
+        <v>6382945</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126192243</v>
+        <v>126192248</v>
       </c>
       <c r="B20" t="n">
-        <v>110423</v>
+        <v>98261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,26 +2712,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219711</v>
+        <v>223591</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2745,13 +2745,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720876</v>
+        <v>720869</v>
       </c>
       <c r="R20" t="n">
-        <v>6382945</v>
+        <v>6382960</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -4256,27 +4256,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126192257</v>
+        <v>126192198</v>
       </c>
       <c r="B34" t="n">
-        <v>110423</v>
+        <v>109156</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219711</v>
+        <v>220299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4284,34 +4284,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720869</v>
+        <v>720774</v>
       </c>
       <c r="R34" t="n">
-        <v>6382986</v>
+        <v>6382882</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4372,48 +4358,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126192198</v>
+        <v>126192231</v>
       </c>
       <c r="B35" t="n">
-        <v>109156</v>
+        <v>98366</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720774</v>
+        <v>720895</v>
       </c>
       <c r="R35" t="n">
-        <v>6382882</v>
+        <v>6382925</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4474,57 +4469,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126192231</v>
+        <v>126192304</v>
       </c>
       <c r="B36" t="n">
-        <v>98366</v>
+        <v>105927</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720895</v>
+        <v>720765</v>
       </c>
       <c r="R36" t="n">
-        <v>6382925</v>
+        <v>6382808</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4585,27 +4571,27 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126192304</v>
+        <v>126192257</v>
       </c>
       <c r="B37" t="n">
-        <v>105927</v>
+        <v>110423</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220785</v>
+        <v>219711</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4613,20 +4599,34 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720765</v>
+        <v>720869</v>
       </c>
       <c r="R37" t="n">
-        <v>6382808</v>
+        <v>6382986</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -936,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126192244</v>
+        <v>126192356</v>
       </c>
       <c r="B4" t="n">
-        <v>98261</v>
+        <v>95948</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,31 +947,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223591</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720876</v>
+        <v>720868</v>
       </c>
       <c r="R4" t="n">
-        <v>6382945</v>
+        <v>6382908</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
@@ -1026,11 +1026,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1047,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126192356</v>
+        <v>126192244</v>
       </c>
       <c r="B5" t="n">
-        <v>95946</v>
+        <v>98263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,31 +1053,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>223591</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1091,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720868</v>
+        <v>720876</v>
       </c>
       <c r="R5" t="n">
-        <v>6382908</v>
+        <v>6382945</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
@@ -1137,6 +1132,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1156,7 +1156,7 @@
         <v>126192233</v>
       </c>
       <c r="B6" t="n">
-        <v>110423</v>
+        <v>110427</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>126192220</v>
       </c>
       <c r="B7" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,45 +1366,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126192215</v>
+        <v>126192192</v>
       </c>
       <c r="B8" t="n">
-        <v>109156</v>
+        <v>98323</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720838</v>
+        <v>720755</v>
       </c>
       <c r="R8" t="n">
-        <v>6382930</v>
+        <v>6382837</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1468,54 +1477,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126192192</v>
+        <v>126192215</v>
       </c>
       <c r="B9" t="n">
-        <v>98321</v>
+        <v>109160</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720755</v>
+        <v>720838</v>
       </c>
       <c r="R9" t="n">
-        <v>6382837</v>
+        <v>6382930</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1582,7 +1582,7 @@
         <v>126192274</v>
       </c>
       <c r="B10" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126192224</v>
+        <v>126192246</v>
       </c>
       <c r="B11" t="n">
-        <v>105367</v>
+        <v>110427</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,46 +1706,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>219711</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720878</v>
+        <v>720876</v>
       </c>
       <c r="R11" t="n">
-        <v>6382913</v>
+        <v>6382953</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1806,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126192228</v>
+        <v>126192224</v>
       </c>
       <c r="B12" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,7 +1827,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1850,13 +1841,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720883</v>
+        <v>720878</v>
       </c>
       <c r="R12" t="n">
-        <v>6382912</v>
+        <v>6382913</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1917,48 +1908,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126192209</v>
+        <v>126192228</v>
       </c>
       <c r="B13" t="n">
-        <v>99018</v>
+        <v>105371</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222322</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720818</v>
+        <v>720883</v>
       </c>
       <c r="R13" t="n">
-        <v>6382895</v>
+        <v>6382912</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1990,11 +1990,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2006,7 +2001,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2024,32 +2019,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126192246</v>
+        <v>126192209</v>
       </c>
       <c r="B14" t="n">
-        <v>110423</v>
+        <v>99020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219711</v>
+        <v>222322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,13 +2054,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720876</v>
+        <v>720818</v>
       </c>
       <c r="R14" t="n">
-        <v>6382953</v>
+        <v>6382895</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,6 +2092,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2129,7 +2129,7 @@
         <v>126192229</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>126192259</v>
       </c>
       <c r="B16" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>126192258</v>
       </c>
       <c r="B17" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>126192227</v>
       </c>
       <c r="B18" t="n">
-        <v>98321</v>
+        <v>98323</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>126192243</v>
       </c>
       <c r="B19" t="n">
-        <v>110423</v>
+        <v>110427</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>126192248</v>
       </c>
       <c r="B20" t="n">
-        <v>98261</v>
+        <v>98263</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>126192216</v>
       </c>
       <c r="B21" t="n">
-        <v>98321</v>
+        <v>98323</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>126192241</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126192240</v>
+        <v>126192211</v>
       </c>
       <c r="B23" t="n">
-        <v>98366</v>
+        <v>98255</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>223572</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3078,13 +3078,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720883</v>
+        <v>720818</v>
       </c>
       <c r="R23" t="n">
-        <v>6382951</v>
+        <v>6382895</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3145,10 +3145,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126192238</v>
+        <v>126192240</v>
       </c>
       <c r="B24" t="n">
-        <v>98321</v>
+        <v>98368</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3156,21 +3156,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3192,10 +3192,10 @@
         <v>720883</v>
       </c>
       <c r="R24" t="n">
-        <v>6382941</v>
+        <v>6382951</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126192211</v>
+        <v>126192238</v>
       </c>
       <c r="B25" t="n">
-        <v>98253</v>
+        <v>98323</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3267,21 +3267,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223572</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3300,13 +3300,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720818</v>
+        <v>720883</v>
       </c>
       <c r="R25" t="n">
-        <v>6382895</v>
+        <v>6382941</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126192221</v>
+        <v>126192239</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
+        <v>105371</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3378,21 +3378,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219862</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3411,13 +3411,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>720865</v>
+        <v>720883</v>
       </c>
       <c r="R26" t="n">
-        <v>6382912</v>
+        <v>6382941</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3478,10 +3478,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126192250</v>
+        <v>126192221</v>
       </c>
       <c r="B27" t="n">
-        <v>98321</v>
+        <v>98367</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,26 +3489,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3516,24 +3516,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720876</v>
+        <v>720865</v>
       </c>
       <c r="R27" t="n">
-        <v>6382966</v>
+        <v>6382912</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3594,10 +3589,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126192239</v>
+        <v>126192250</v>
       </c>
       <c r="B28" t="n">
-        <v>105367</v>
+        <v>98323</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3605,26 +3600,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3632,19 +3627,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720883</v>
+        <v>720876</v>
       </c>
       <c r="R28" t="n">
-        <v>6382941</v>
+        <v>6382966</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126192194</v>
+        <v>126192210</v>
       </c>
       <c r="B29" t="n">
-        <v>98261</v>
+        <v>99386</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3716,46 +3716,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>223591</v>
+        <v>222662</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720755</v>
+        <v>720818</v>
       </c>
       <c r="R29" t="n">
-        <v>6382837</v>
+        <v>6382895</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3798,7 +3789,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3819,7 +3810,7 @@
         <v>126192237</v>
       </c>
       <c r="B30" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3927,10 +3918,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126192210</v>
+        <v>126192194</v>
       </c>
       <c r="B31" t="n">
-        <v>99384</v>
+        <v>98263</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3938,37 +3929,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222662</v>
+        <v>223591</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720818</v>
+        <v>720755</v>
       </c>
       <c r="R31" t="n">
-        <v>6382895</v>
+        <v>6382837</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4032,7 +4032,7 @@
         <v>126192230</v>
       </c>
       <c r="B32" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>126192271</v>
       </c>
       <c r="B33" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,48 +4256,57 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126192198</v>
+        <v>126192231</v>
       </c>
       <c r="B34" t="n">
-        <v>109156</v>
+        <v>98368</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720774</v>
+        <v>720895</v>
       </c>
       <c r="R34" t="n">
-        <v>6382882</v>
+        <v>6382925</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4358,10 +4367,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126192231</v>
+        <v>126192257</v>
       </c>
       <c r="B35" t="n">
-        <v>98366</v>
+        <v>110427</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4369,26 +4378,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4396,16 +4405,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720895</v>
+        <v>720869</v>
       </c>
       <c r="R35" t="n">
-        <v>6382925</v>
+        <v>6382986</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4469,27 +4483,27 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126192304</v>
+        <v>126192198</v>
       </c>
       <c r="B36" t="n">
-        <v>105927</v>
+        <v>109160</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4504,10 +4518,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720765</v>
+        <v>720774</v>
       </c>
       <c r="R36" t="n">
-        <v>6382808</v>
+        <v>6382882</v>
       </c>
       <c r="S36" t="n">
         <v>7</v>
@@ -4571,27 +4585,27 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126192257</v>
+        <v>126192304</v>
       </c>
       <c r="B37" t="n">
-        <v>110423</v>
+        <v>105931</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219711</v>
+        <v>220785</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4599,34 +4613,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720869</v>
+        <v>720765</v>
       </c>
       <c r="R37" t="n">
-        <v>6382986</v>
+        <v>6382808</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>126192203</v>
       </c>
       <c r="B38" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4798,57 +4798,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126192331</v>
+        <v>126192252</v>
       </c>
       <c r="B39" t="n">
-        <v>98366</v>
+        <v>109160</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720772</v>
+        <v>720863</v>
       </c>
       <c r="R39" t="n">
-        <v>6382868</v>
+        <v>6382976</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4909,10 +4900,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126192252</v>
+        <v>126192249</v>
       </c>
       <c r="B40" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4937,20 +4928,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>720863</v>
+        <v>720876</v>
       </c>
       <c r="R40" t="n">
-        <v>6382976</v>
+        <v>6382966</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5011,37 +5011,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126192249</v>
+        <v>126192331</v>
       </c>
       <c r="B41" t="n">
-        <v>109156</v>
+        <v>98368</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>720876</v>
+        <v>720772</v>
       </c>
       <c r="R41" t="n">
-        <v>6382966</v>
+        <v>6382868</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>126192200</v>
       </c>
       <c r="B42" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>126192253</v>
       </c>
       <c r="B43" t="n">
-        <v>110423</v>
+        <v>110427</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>126192214</v>
       </c>
       <c r="B44" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>126192202</v>
       </c>
       <c r="B45" t="n">
-        <v>98321</v>
+        <v>98323</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>126192242</v>
       </c>
       <c r="B46" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>126192330</v>
       </c>
       <c r="B47" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>126192199</v>
       </c>
       <c r="B48" t="n">
-        <v>98321</v>
+        <v>98323</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>126192254</v>
       </c>
       <c r="B49" t="n">
-        <v>98321</v>
+        <v>98323</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>126192219</v>
       </c>
       <c r="B50" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>126192195</v>
       </c>
       <c r="B51" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>126192207</v>
       </c>
       <c r="B52" t="n">
-        <v>105265</v>
+        <v>105269</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>126192213</v>
       </c>
       <c r="B53" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6442,62 +6442,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126192260</v>
+        <v>126192268</v>
       </c>
       <c r="B54" t="n">
-        <v>105367</v>
+        <v>109160</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221144</v>
+        <v>220299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>720835</v>
+        <v>720800</v>
       </c>
       <c r="R54" t="n">
-        <v>6383025</v>
+        <v>6383077</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6527,11 +6513,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Yngre skog mot N, nyröjt?</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6566,7 +6547,7 @@
         <v>126192222</v>
       </c>
       <c r="B55" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6674,48 +6655,62 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126192268</v>
+        <v>126192260</v>
       </c>
       <c r="B56" t="n">
-        <v>109156</v>
+        <v>105371</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220299</v>
+        <v>221144</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>720800</v>
+        <v>720835</v>
       </c>
       <c r="R56" t="n">
-        <v>6383077</v>
+        <v>6383025</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6745,6 +6740,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Yngre skog mot N, nyröjt?</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -1695,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126192246</v>
+        <v>126192224</v>
       </c>
       <c r="B11" t="n">
-        <v>110427</v>
+        <v>105371</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,37 +1706,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219711</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720876</v>
+        <v>720878</v>
       </c>
       <c r="R11" t="n">
-        <v>6382953</v>
+        <v>6382913</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1797,7 +1806,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126192224</v>
+        <v>126192228</v>
       </c>
       <c r="B12" t="n">
         <v>105371</v>
@@ -1827,7 +1836,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1841,13 +1850,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720878</v>
+        <v>720883</v>
       </c>
       <c r="R12" t="n">
-        <v>6382913</v>
+        <v>6382912</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1908,57 +1917,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126192228</v>
+        <v>126192209</v>
       </c>
       <c r="B13" t="n">
-        <v>105371</v>
+        <v>99020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>222322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720883</v>
+        <v>720818</v>
       </c>
       <c r="R13" t="n">
-        <v>6382912</v>
+        <v>6382895</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1990,6 +1990,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2001,7 +2006,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2019,32 +2024,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126192209</v>
+        <v>126192246</v>
       </c>
       <c r="B14" t="n">
-        <v>99020</v>
+        <v>110427</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222322</v>
+        <v>219711</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,13 +2059,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720818</v>
+        <v>720876</v>
       </c>
       <c r="R14" t="n">
-        <v>6382895</v>
+        <v>6382953</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2092,11 +2097,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -4798,48 +4798,57 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126192252</v>
+        <v>126192331</v>
       </c>
       <c r="B39" t="n">
-        <v>109160</v>
+        <v>98368</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720863</v>
+        <v>720772</v>
       </c>
       <c r="R39" t="n">
-        <v>6382976</v>
+        <v>6382868</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4900,37 +4909,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126192249</v>
+        <v>126192200</v>
       </c>
       <c r="B40" t="n">
-        <v>109160</v>
+        <v>98368</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4944,13 +4953,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>720876</v>
+        <v>720774</v>
       </c>
       <c r="R40" t="n">
-        <v>6382966</v>
+        <v>6382882</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5011,10 +5020,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126192331</v>
+        <v>126192253</v>
       </c>
       <c r="B41" t="n">
-        <v>98368</v>
+        <v>110427</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5022,26 +5031,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5049,19 +5058,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>720772</v>
+        <v>720863</v>
       </c>
       <c r="R41" t="n">
-        <v>6382868</v>
+        <v>6382976</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5122,57 +5136,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126192200</v>
+        <v>126192252</v>
       </c>
       <c r="B42" t="n">
-        <v>98368</v>
+        <v>109160</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>720774</v>
+        <v>720863</v>
       </c>
       <c r="R42" t="n">
-        <v>6382882</v>
+        <v>6382976</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5233,27 +5238,27 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126192253</v>
+        <v>126192249</v>
       </c>
       <c r="B43" t="n">
-        <v>110427</v>
+        <v>109160</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219711</v>
+        <v>220299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5263,7 +5268,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5271,21 +5276,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720863</v>
+        <v>720876</v>
       </c>
       <c r="R43" t="n">
-        <v>6382976</v>
+        <v>6382966</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -6442,48 +6442,57 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126192268</v>
+        <v>126192222</v>
       </c>
       <c r="B54" t="n">
-        <v>109160</v>
+        <v>105371</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220299</v>
+        <v>221144</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>720800</v>
+        <v>720868</v>
       </c>
       <c r="R54" t="n">
-        <v>6383077</v>
+        <v>6382908</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6544,7 +6553,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126192222</v>
+        <v>126192260</v>
       </c>
       <c r="B55" t="n">
         <v>105371</v>
@@ -6574,7 +6583,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6582,19 +6591,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>720868</v>
+        <v>720835</v>
       </c>
       <c r="R55" t="n">
-        <v>6382908</v>
+        <v>6383025</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6624,6 +6638,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Yngre skog mot N, nyröjt?</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6655,62 +6674,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126192260</v>
+        <v>126192268</v>
       </c>
       <c r="B56" t="n">
-        <v>105371</v>
+        <v>109160</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>220299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>720835</v>
+        <v>720800</v>
       </c>
       <c r="R56" t="n">
-        <v>6383025</v>
+        <v>6383077</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6740,11 +6745,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Yngre skog mot N, nyröjt?</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -936,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126192356</v>
+        <v>126192244</v>
       </c>
       <c r="B4" t="n">
-        <v>95948</v>
+        <v>98267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,31 +947,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>223591</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720868</v>
+        <v>720876</v>
       </c>
       <c r="R4" t="n">
-        <v>6382908</v>
+        <v>6382945</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
@@ -1026,6 +1026,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1042,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126192244</v>
+        <v>126192356</v>
       </c>
       <c r="B5" t="n">
-        <v>98263</v>
+        <v>95952</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1053,31 +1058,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223591</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1086,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720876</v>
+        <v>720868</v>
       </c>
       <c r="R5" t="n">
-        <v>6382945</v>
+        <v>6382908</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
@@ -1132,11 +1137,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1153,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126192233</v>
+        <v>126192220</v>
       </c>
       <c r="B6" t="n">
-        <v>110427</v>
+        <v>105384</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,37 +1164,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219711</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720895</v>
+        <v>720869</v>
       </c>
       <c r="R6" t="n">
-        <v>6382925</v>
+        <v>6382918</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1255,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126192220</v>
+        <v>126192233</v>
       </c>
       <c r="B7" t="n">
-        <v>105371</v>
+        <v>110440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,46 +1275,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>219711</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720869</v>
+        <v>720895</v>
       </c>
       <c r="R7" t="n">
-        <v>6382918</v>
+        <v>6382925</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1366,54 +1366,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126192192</v>
+        <v>126192215</v>
       </c>
       <c r="B8" t="n">
-        <v>98323</v>
+        <v>109173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720755</v>
+        <v>720838</v>
       </c>
       <c r="R8" t="n">
-        <v>6382837</v>
+        <v>6382930</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,48 +1468,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126192215</v>
+        <v>126192274</v>
       </c>
       <c r="B9" t="n">
-        <v>109160</v>
+        <v>105384</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720838</v>
+        <v>720757</v>
       </c>
       <c r="R9" t="n">
-        <v>6382930</v>
+        <v>6383073</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1579,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126192274</v>
+        <v>126192192</v>
       </c>
       <c r="B10" t="n">
-        <v>105371</v>
+        <v>98327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1590,26 +1595,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1617,24 +1622,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720757</v>
+        <v>720755</v>
       </c>
       <c r="R10" t="n">
-        <v>6383073</v>
+        <v>6382837</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>126192224</v>
       </c>
       <c r="B11" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>126192228</v>
       </c>
       <c r="B12" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,32 +1917,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126192209</v>
+        <v>126192246</v>
       </c>
       <c r="B13" t="n">
-        <v>99020</v>
+        <v>110440</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222322</v>
+        <v>219711</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,13 +1952,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720818</v>
+        <v>720876</v>
       </c>
       <c r="R13" t="n">
-        <v>6382895</v>
+        <v>6382953</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1990,11 +1990,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2006,7 +2001,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2024,32 +2019,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126192246</v>
+        <v>126192209</v>
       </c>
       <c r="B14" t="n">
-        <v>110427</v>
+        <v>99024</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219711</v>
+        <v>222322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,13 +2054,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720876</v>
+        <v>720818</v>
       </c>
       <c r="R14" t="n">
-        <v>6382953</v>
+        <v>6382895</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,6 +2092,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2129,7 +2129,7 @@
         <v>126192229</v>
       </c>
       <c r="B15" t="n">
-        <v>98367</v>
+        <v>98371</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>126192259</v>
       </c>
       <c r="B16" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>126192258</v>
       </c>
       <c r="B17" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,10 +2479,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126192227</v>
+        <v>126192243</v>
       </c>
       <c r="B18" t="n">
-        <v>98323</v>
+        <v>110440</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2490,26 +2490,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720883</v>
+        <v>720876</v>
       </c>
       <c r="R18" t="n">
-        <v>6382912</v>
+        <v>6382945</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2590,10 +2590,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126192243</v>
+        <v>126192227</v>
       </c>
       <c r="B19" t="n">
-        <v>110427</v>
+        <v>98327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,26 +2601,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2634,13 +2634,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720876</v>
+        <v>720883</v>
       </c>
       <c r="R19" t="n">
-        <v>6382945</v>
+        <v>6382912</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>126192248</v>
       </c>
       <c r="B20" t="n">
-        <v>98263</v>
+        <v>98267</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>126192216</v>
       </c>
       <c r="B21" t="n">
-        <v>98323</v>
+        <v>98327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>126192241</v>
       </c>
       <c r="B22" t="n">
-        <v>98367</v>
+        <v>98371</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>126192211</v>
       </c>
       <c r="B23" t="n">
-        <v>98255</v>
+        <v>98259</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>126192240</v>
       </c>
       <c r="B24" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>126192238</v>
       </c>
       <c r="B25" t="n">
-        <v>98323</v>
+        <v>98327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>126192239</v>
       </c>
       <c r="B26" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>126192221</v>
       </c>
       <c r="B27" t="n">
-        <v>98367</v>
+        <v>98371</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>126192250</v>
       </c>
       <c r="B28" t="n">
-        <v>98323</v>
+        <v>98327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126192210</v>
+        <v>126192237</v>
       </c>
       <c r="B29" t="n">
-        <v>99386</v>
+        <v>105384</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3716,37 +3716,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222662</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720818</v>
+        <v>720884</v>
       </c>
       <c r="R29" t="n">
-        <v>6382895</v>
+        <v>6382932</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3789,7 +3798,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3807,10 +3816,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126192237</v>
+        <v>126192210</v>
       </c>
       <c r="B30" t="n">
-        <v>105371</v>
+        <v>99390</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3818,46 +3827,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>222662</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720884</v>
+        <v>720818</v>
       </c>
       <c r="R30" t="n">
-        <v>6382932</v>
+        <v>6382895</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3921,7 +3921,7 @@
         <v>126192194</v>
       </c>
       <c r="B31" t="n">
-        <v>98263</v>
+        <v>98267</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4029,10 +4029,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126192230</v>
+        <v>126192271</v>
       </c>
       <c r="B32" t="n">
-        <v>98367</v>
+        <v>105384</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4040,26 +4040,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219862</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4067,19 +4067,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>720895</v>
+        <v>720797</v>
       </c>
       <c r="R32" t="n">
-        <v>6382925</v>
+        <v>6383069</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4140,10 +4145,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126192271</v>
+        <v>126192230</v>
       </c>
       <c r="B33" t="n">
-        <v>105371</v>
+        <v>98371</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4151,26 +4156,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>219862</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4178,24 +4183,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>720797</v>
+        <v>720895</v>
       </c>
       <c r="R33" t="n">
-        <v>6383069</v>
+        <v>6382925</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126192231</v>
+        <v>126192257</v>
       </c>
       <c r="B34" t="n">
-        <v>98368</v>
+        <v>110440</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4267,26 +4267,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4294,16 +4294,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720895</v>
+        <v>720869</v>
       </c>
       <c r="R34" t="n">
-        <v>6382925</v>
+        <v>6382986</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -4367,10 +4372,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126192257</v>
+        <v>126192231</v>
       </c>
       <c r="B35" t="n">
-        <v>110427</v>
+        <v>98372</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4378,26 +4383,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4405,21 +4410,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720869</v>
+        <v>720895</v>
       </c>
       <c r="R35" t="n">
-        <v>6382986</v>
+        <v>6382925</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4486,7 +4486,7 @@
         <v>126192198</v>
       </c>
       <c r="B36" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>126192304</v>
       </c>
       <c r="B37" t="n">
-        <v>105931</v>
+        <v>105944</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>126192203</v>
       </c>
       <c r="B38" t="n">
-        <v>98367</v>
+        <v>98371</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4798,57 +4798,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126192331</v>
+        <v>126192252</v>
       </c>
       <c r="B39" t="n">
-        <v>98368</v>
+        <v>109173</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720772</v>
+        <v>720863</v>
       </c>
       <c r="R39" t="n">
-        <v>6382868</v>
+        <v>6382976</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4909,37 +4900,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126192200</v>
+        <v>126192249</v>
       </c>
       <c r="B40" t="n">
-        <v>98368</v>
+        <v>109173</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4953,13 +4944,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>720774</v>
+        <v>720876</v>
       </c>
       <c r="R40" t="n">
-        <v>6382882</v>
+        <v>6382966</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5020,10 +5011,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126192253</v>
+        <v>126192331</v>
       </c>
       <c r="B41" t="n">
-        <v>110427</v>
+        <v>98372</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5031,26 +5022,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5058,24 +5049,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>720863</v>
+        <v>720772</v>
       </c>
       <c r="R41" t="n">
-        <v>6382976</v>
+        <v>6382868</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5136,27 +5122,27 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126192252</v>
+        <v>126192253</v>
       </c>
       <c r="B42" t="n">
-        <v>109160</v>
+        <v>110440</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220299</v>
+        <v>219711</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5164,7 +5150,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
@@ -5177,7 +5177,7 @@
         <v>6382976</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5238,37 +5238,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126192249</v>
+        <v>126192200</v>
       </c>
       <c r="B43" t="n">
-        <v>109160</v>
+        <v>98372</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5282,13 +5282,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720876</v>
+        <v>720774</v>
       </c>
       <c r="R43" t="n">
-        <v>6382966</v>
+        <v>6382882</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>126192214</v>
       </c>
       <c r="B44" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5451,32 +5451,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126192202</v>
+        <v>126192242</v>
       </c>
       <c r="B45" t="n">
-        <v>98323</v>
+        <v>109173</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5486,13 +5486,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720782</v>
+        <v>720876</v>
       </c>
       <c r="R45" t="n">
-        <v>6382877</v>
+        <v>6382945</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5553,32 +5553,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126192242</v>
+        <v>126192202</v>
       </c>
       <c r="B46" t="n">
-        <v>109160</v>
+        <v>98327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5588,13 +5588,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720876</v>
+        <v>720782</v>
       </c>
       <c r="R46" t="n">
-        <v>6382945</v>
+        <v>6382877</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5655,10 +5655,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126192330</v>
+        <v>126192219</v>
       </c>
       <c r="B47" t="n">
-        <v>98373</v>
+        <v>105384</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5666,26 +5666,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219864</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5699,13 +5699,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720772</v>
+        <v>720858</v>
       </c>
       <c r="R47" t="n">
-        <v>6382868</v>
+        <v>6382930</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5766,10 +5766,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126192199</v>
+        <v>126192330</v>
       </c>
       <c r="B48" t="n">
-        <v>98323</v>
+        <v>98377</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5777,26 +5777,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219798</v>
+        <v>219864</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5810,13 +5810,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720774</v>
+        <v>720772</v>
       </c>
       <c r="R48" t="n">
-        <v>6382882</v>
+        <v>6382868</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5877,10 +5877,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126192254</v>
+        <v>126192199</v>
       </c>
       <c r="B49" t="n">
-        <v>98323</v>
+        <v>98327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5915,24 +5915,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>720863</v>
+        <v>720774</v>
       </c>
       <c r="R49" t="n">
-        <v>6382976</v>
+        <v>6382882</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5993,10 +5988,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126192219</v>
+        <v>126192254</v>
       </c>
       <c r="B50" t="n">
-        <v>105371</v>
+        <v>98327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6004,26 +5999,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6031,16 +6026,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>720858</v>
+        <v>720863</v>
       </c>
       <c r="R50" t="n">
-        <v>6382930</v>
+        <v>6382976</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -6107,7 +6107,7 @@
         <v>126192195</v>
       </c>
       <c r="B51" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>126192207</v>
       </c>
       <c r="B52" t="n">
-        <v>105269</v>
+        <v>105282</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>126192213</v>
       </c>
       <c r="B53" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6442,57 +6442,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126192222</v>
+        <v>126192268</v>
       </c>
       <c r="B54" t="n">
-        <v>105371</v>
+        <v>109173</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221144</v>
+        <v>220299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>720868</v>
+        <v>720800</v>
       </c>
       <c r="R54" t="n">
-        <v>6382908</v>
+        <v>6383077</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6556,7 +6547,7 @@
         <v>126192260</v>
       </c>
       <c r="B55" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6674,48 +6665,57 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126192268</v>
+        <v>126192222</v>
       </c>
       <c r="B56" t="n">
-        <v>109160</v>
+        <v>105384</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220299</v>
+        <v>221144</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>720800</v>
+        <v>720868</v>
       </c>
       <c r="R56" t="n">
-        <v>6383077</v>
+        <v>6382908</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126192229</v>
+        <v>126192259</v>
       </c>
       <c r="B15" t="n">
-        <v>98371</v>
+        <v>105384</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2137,21 +2137,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219862</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2164,16 +2164,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720883</v>
+        <v>720844</v>
       </c>
       <c r="R15" t="n">
-        <v>6382912</v>
+        <v>6383011</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2206,6 +2211,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Barrblandskog, mossrik, vaierande ålder på träd, bara enstak död.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,7 +2247,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126192259</v>
+        <v>126192258</v>
       </c>
       <c r="B16" t="n">
         <v>105384</v>
@@ -2267,7 +2277,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2286,13 +2296,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720844</v>
+        <v>720841</v>
       </c>
       <c r="R16" t="n">
-        <v>6383011</v>
+        <v>6382998</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2326,7 +2336,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Barrblandskog, mossrik, vaierande ålder på träd, bara enstak död.</t>
+          <t>Ett ex i blom.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,10 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126192258</v>
+        <v>126192229</v>
       </c>
       <c r="B17" t="n">
-        <v>105384</v>
+        <v>98371</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,26 +2379,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>219862</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2396,24 +2406,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720841</v>
+        <v>720883</v>
       </c>
       <c r="R17" t="n">
-        <v>6382998</v>
+        <v>6382912</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2443,11 +2448,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ett ex i blom.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3367,10 +3367,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126192239</v>
+        <v>126192221</v>
       </c>
       <c r="B26" t="n">
-        <v>105384</v>
+        <v>98371</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3378,21 +3378,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>219862</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3411,13 +3411,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>720883</v>
+        <v>720865</v>
       </c>
       <c r="R26" t="n">
-        <v>6382941</v>
+        <v>6382912</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3478,10 +3478,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126192221</v>
+        <v>126192250</v>
       </c>
       <c r="B27" t="n">
-        <v>98371</v>
+        <v>98327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,26 +3489,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3516,19 +3516,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720865</v>
+        <v>720876</v>
       </c>
       <c r="R27" t="n">
-        <v>6382912</v>
+        <v>6382966</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3589,10 +3594,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126192250</v>
+        <v>126192239</v>
       </c>
       <c r="B28" t="n">
-        <v>98327</v>
+        <v>105384</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3600,26 +3605,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3627,24 +3632,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720876</v>
+        <v>720883</v>
       </c>
       <c r="R28" t="n">
-        <v>6382966</v>
+        <v>6382941</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -936,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126192244</v>
+        <v>126192356</v>
       </c>
       <c r="B4" t="n">
-        <v>98267</v>
+        <v>95955</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,31 +947,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223591</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720876</v>
+        <v>720868</v>
       </c>
       <c r="R4" t="n">
-        <v>6382945</v>
+        <v>6382908</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
@@ -1026,11 +1026,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1047,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126192356</v>
+        <v>126192244</v>
       </c>
       <c r="B5" t="n">
-        <v>95952</v>
+        <v>98270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,31 +1053,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>223591</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1091,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720868</v>
+        <v>720876</v>
       </c>
       <c r="R5" t="n">
-        <v>6382908</v>
+        <v>6382945</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
@@ -1137,6 +1132,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1156,7 +1156,7 @@
         <v>126192220</v>
       </c>
       <c r="B6" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>126192233</v>
       </c>
       <c r="B7" t="n">
-        <v>110440</v>
+        <v>110443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,45 +1366,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126192215</v>
+        <v>126192192</v>
       </c>
       <c r="B8" t="n">
-        <v>109173</v>
+        <v>98330</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720838</v>
+        <v>720755</v>
       </c>
       <c r="R8" t="n">
-        <v>6382930</v>
+        <v>6382837</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1468,62 +1477,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126192274</v>
+        <v>126192215</v>
       </c>
       <c r="B9" t="n">
-        <v>105384</v>
+        <v>109176</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720757</v>
+        <v>720838</v>
       </c>
       <c r="R9" t="n">
-        <v>6383073</v>
+        <v>6382930</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1584,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126192192</v>
+        <v>126192274</v>
       </c>
       <c r="B10" t="n">
-        <v>98327</v>
+        <v>105387</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,26 +1590,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1622,19 +1617,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720755</v>
+        <v>720757</v>
       </c>
       <c r="R10" t="n">
-        <v>6382837</v>
+        <v>6383073</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1695,57 +1695,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126192224</v>
+        <v>126192209</v>
       </c>
       <c r="B11" t="n">
-        <v>105384</v>
+        <v>99027</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>222322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720878</v>
+        <v>720818</v>
       </c>
       <c r="R11" t="n">
-        <v>6382913</v>
+        <v>6382895</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1777,6 +1768,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1788,7 +1784,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1806,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126192228</v>
+        <v>126192246</v>
       </c>
       <c r="B12" t="n">
-        <v>105384</v>
+        <v>110443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1817,43 +1813,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>219711</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720883</v>
+        <v>720876</v>
       </c>
       <c r="R12" t="n">
-        <v>6382912</v>
+        <v>6382953</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1917,10 +1904,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126192246</v>
+        <v>126192224</v>
       </c>
       <c r="B13" t="n">
-        <v>110440</v>
+        <v>105387</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,37 +1915,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219711</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720876</v>
+        <v>720878</v>
       </c>
       <c r="R13" t="n">
-        <v>6382953</v>
+        <v>6382913</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2019,48 +2015,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126192209</v>
+        <v>126192228</v>
       </c>
       <c r="B14" t="n">
-        <v>99024</v>
+        <v>105387</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222322</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720818</v>
+        <v>720883</v>
       </c>
       <c r="R14" t="n">
-        <v>6382895</v>
+        <v>6382912</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2092,11 +2097,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2129,7 +2129,7 @@
         <v>126192259</v>
       </c>
       <c r="B15" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>126192258</v>
       </c>
       <c r="B16" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>126192229</v>
       </c>
       <c r="B17" t="n">
-        <v>98371</v>
+        <v>98374</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,10 +2479,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126192243</v>
+        <v>126192248</v>
       </c>
       <c r="B18" t="n">
-        <v>110440</v>
+        <v>98270</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2490,26 +2490,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219711</v>
+        <v>223591</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720876</v>
+        <v>720869</v>
       </c>
       <c r="R18" t="n">
-        <v>6382945</v>
+        <v>6382960</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2590,10 +2590,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126192227</v>
+        <v>126192243</v>
       </c>
       <c r="B19" t="n">
-        <v>98327</v>
+        <v>110443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,26 +2601,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2634,13 +2634,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720883</v>
+        <v>720876</v>
       </c>
       <c r="R19" t="n">
-        <v>6382912</v>
+        <v>6382945</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126192248</v>
+        <v>126192227</v>
       </c>
       <c r="B20" t="n">
-        <v>98267</v>
+        <v>98330</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,26 +2712,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2745,13 +2745,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720869</v>
+        <v>720883</v>
       </c>
       <c r="R20" t="n">
-        <v>6382960</v>
+        <v>6382912</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>126192216</v>
       </c>
       <c r="B21" t="n">
-        <v>98327</v>
+        <v>98330</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>126192241</v>
       </c>
       <c r="B22" t="n">
-        <v>98371</v>
+        <v>98374</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>126192211</v>
       </c>
       <c r="B23" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>126192240</v>
       </c>
       <c r="B24" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>126192238</v>
       </c>
       <c r="B25" t="n">
-        <v>98327</v>
+        <v>98330</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>126192221</v>
       </c>
       <c r="B26" t="n">
-        <v>98371</v>
+        <v>98374</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>126192250</v>
       </c>
       <c r="B27" t="n">
-        <v>98327</v>
+        <v>98330</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>126192239</v>
       </c>
       <c r="B28" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126192237</v>
+        <v>126192194</v>
       </c>
       <c r="B29" t="n">
-        <v>105384</v>
+        <v>98270</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3716,26 +3716,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>223591</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3749,13 +3749,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720884</v>
+        <v>720755</v>
       </c>
       <c r="R29" t="n">
-        <v>6382932</v>
+        <v>6382837</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126192210</v>
+        <v>126192237</v>
       </c>
       <c r="B30" t="n">
-        <v>99390</v>
+        <v>105387</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3827,37 +3827,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222662</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720818</v>
+        <v>720884</v>
       </c>
       <c r="R30" t="n">
-        <v>6382895</v>
+        <v>6382932</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3900,7 +3909,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3918,10 +3927,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126192194</v>
+        <v>126192210</v>
       </c>
       <c r="B31" t="n">
-        <v>98267</v>
+        <v>99393</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3929,46 +3938,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223591</v>
+        <v>222662</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720755</v>
+        <v>720818</v>
       </c>
       <c r="R31" t="n">
-        <v>6382837</v>
+        <v>6382895</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126192271</v>
+        <v>126192230</v>
       </c>
       <c r="B32" t="n">
-        <v>105384</v>
+        <v>98374</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4040,26 +4040,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>219862</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4067,24 +4067,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>720797</v>
+        <v>720895</v>
       </c>
       <c r="R32" t="n">
-        <v>6383069</v>
+        <v>6382925</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4145,10 +4140,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126192230</v>
+        <v>126192271</v>
       </c>
       <c r="B33" t="n">
-        <v>98371</v>
+        <v>105387</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4156,26 +4151,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219862</v>
+        <v>221144</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4183,19 +4178,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>720895</v>
+        <v>720797</v>
       </c>
       <c r="R33" t="n">
-        <v>6382925</v>
+        <v>6383069</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>126192257</v>
       </c>
       <c r="B34" t="n">
-        <v>110440</v>
+        <v>110443</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>126192231</v>
       </c>
       <c r="B35" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>126192198</v>
       </c>
       <c r="B36" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>126192304</v>
       </c>
       <c r="B37" t="n">
-        <v>105944</v>
+        <v>105947</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>126192203</v>
       </c>
       <c r="B38" t="n">
-        <v>98371</v>
+        <v>98374</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4798,10 +4798,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126192252</v>
+        <v>126192249</v>
       </c>
       <c r="B39" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4826,20 +4826,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720863</v>
+        <v>720876</v>
       </c>
       <c r="R39" t="n">
-        <v>6382976</v>
+        <v>6382966</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4900,10 +4909,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126192249</v>
+        <v>126192252</v>
       </c>
       <c r="B40" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4928,29 +4937,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>720876</v>
+        <v>720863</v>
       </c>
       <c r="R40" t="n">
-        <v>6382966</v>
+        <v>6382976</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>126192331</v>
       </c>
       <c r="B41" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>126192253</v>
       </c>
       <c r="B42" t="n">
-        <v>110440</v>
+        <v>110443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>126192200</v>
       </c>
       <c r="B43" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>126192214</v>
       </c>
       <c r="B44" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5451,32 +5451,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126192242</v>
+        <v>126192202</v>
       </c>
       <c r="B45" t="n">
-        <v>109173</v>
+        <v>98330</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5486,13 +5486,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720876</v>
+        <v>720782</v>
       </c>
       <c r="R45" t="n">
-        <v>6382945</v>
+        <v>6382877</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5553,32 +5553,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126192202</v>
+        <v>126192242</v>
       </c>
       <c r="B46" t="n">
-        <v>98327</v>
+        <v>109176</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5588,13 +5588,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720782</v>
+        <v>720876</v>
       </c>
       <c r="R46" t="n">
-        <v>6382877</v>
+        <v>6382945</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5655,10 +5655,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126192219</v>
+        <v>126192330</v>
       </c>
       <c r="B47" t="n">
-        <v>105384</v>
+        <v>98380</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5666,26 +5666,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>219864</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5699,13 +5699,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720858</v>
+        <v>720772</v>
       </c>
       <c r="R47" t="n">
-        <v>6382930</v>
+        <v>6382868</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5766,10 +5766,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126192330</v>
+        <v>126192254</v>
       </c>
       <c r="B48" t="n">
-        <v>98377</v>
+        <v>98330</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5777,21 +5777,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219864</v>
+        <v>219798</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5804,19 +5804,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720772</v>
+        <v>720863</v>
       </c>
       <c r="R48" t="n">
-        <v>6382868</v>
+        <v>6382976</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5880,7 +5885,7 @@
         <v>126192199</v>
       </c>
       <c r="B49" t="n">
-        <v>98327</v>
+        <v>98330</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5988,10 +5993,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126192254</v>
+        <v>126192219</v>
       </c>
       <c r="B50" t="n">
-        <v>98327</v>
+        <v>105387</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5999,26 +6004,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6026,21 +6031,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>720863</v>
+        <v>720858</v>
       </c>
       <c r="R50" t="n">
-        <v>6382976</v>
+        <v>6382930</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -6107,7 +6107,7 @@
         <v>126192195</v>
       </c>
       <c r="B51" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>126192207</v>
       </c>
       <c r="B52" t="n">
-        <v>105282</v>
+        <v>105285</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>126192213</v>
       </c>
       <c r="B53" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>126192268</v>
       </c>
       <c r="B54" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>126192260</v>
       </c>
       <c r="B55" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>126192222</v>
       </c>
       <c r="B56" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -936,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126192356</v>
+        <v>126192244</v>
       </c>
       <c r="B4" t="n">
-        <v>95955</v>
+        <v>98270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,31 +947,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>223591</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720868</v>
+        <v>720876</v>
       </c>
       <c r="R4" t="n">
-        <v>6382908</v>
+        <v>6382945</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
@@ -1026,6 +1026,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1042,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126192244</v>
+        <v>126192356</v>
       </c>
       <c r="B5" t="n">
-        <v>98270</v>
+        <v>95955</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1053,31 +1058,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223591</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1086,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720876</v>
+        <v>720868</v>
       </c>
       <c r="R5" t="n">
-        <v>6382945</v>
+        <v>6382908</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
@@ -1132,11 +1137,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1366,54 +1366,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126192192</v>
+        <v>126192215</v>
       </c>
       <c r="B8" t="n">
-        <v>98330</v>
+        <v>109176</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720755</v>
+        <v>720838</v>
       </c>
       <c r="R8" t="n">
-        <v>6382837</v>
+        <v>6382930</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,48 +1468,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126192215</v>
+        <v>126192274</v>
       </c>
       <c r="B9" t="n">
-        <v>109176</v>
+        <v>105387</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720838</v>
+        <v>720757</v>
       </c>
       <c r="R9" t="n">
-        <v>6382930</v>
+        <v>6383073</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1579,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126192274</v>
+        <v>126192192</v>
       </c>
       <c r="B10" t="n">
-        <v>105387</v>
+        <v>98330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1590,26 +1595,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1617,24 +1622,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720757</v>
+        <v>720755</v>
       </c>
       <c r="R10" t="n">
-        <v>6383073</v>
+        <v>6382837</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2479,10 +2479,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126192248</v>
+        <v>126192243</v>
       </c>
       <c r="B18" t="n">
-        <v>98270</v>
+        <v>110443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2490,26 +2490,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>223591</v>
+        <v>219711</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720869</v>
+        <v>720876</v>
       </c>
       <c r="R18" t="n">
-        <v>6382960</v>
+        <v>6382945</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2590,10 +2590,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126192243</v>
+        <v>126192227</v>
       </c>
       <c r="B19" t="n">
-        <v>110443</v>
+        <v>98330</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,26 +2601,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2634,13 +2634,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720876</v>
+        <v>720883</v>
       </c>
       <c r="R19" t="n">
-        <v>6382945</v>
+        <v>6382912</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126192227</v>
+        <v>126192248</v>
       </c>
       <c r="B20" t="n">
-        <v>98330</v>
+        <v>98270</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,26 +2712,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2745,13 +2745,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720883</v>
+        <v>720869</v>
       </c>
       <c r="R20" t="n">
-        <v>6382912</v>
+        <v>6382960</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -4798,37 +4798,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126192249</v>
+        <v>126192331</v>
       </c>
       <c r="B39" t="n">
-        <v>109176</v>
+        <v>98375</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4842,13 +4842,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720876</v>
+        <v>720772</v>
       </c>
       <c r="R39" t="n">
-        <v>6382966</v>
+        <v>6382868</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4909,27 +4909,27 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126192252</v>
+        <v>126192253</v>
       </c>
       <c r="B40" t="n">
-        <v>109176</v>
+        <v>110443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220299</v>
+        <v>219711</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4937,7 +4937,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
@@ -4950,7 +4964,7 @@
         <v>6382976</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5011,7 +5025,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126192331</v>
+        <v>126192200</v>
       </c>
       <c r="B41" t="n">
         <v>98375</v>
@@ -5041,7 +5055,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5055,13 +5069,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>720772</v>
+        <v>720774</v>
       </c>
       <c r="R41" t="n">
-        <v>6382868</v>
+        <v>6382882</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5122,27 +5136,27 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126192253</v>
+        <v>126192249</v>
       </c>
       <c r="B42" t="n">
-        <v>110443</v>
+        <v>109176</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219711</v>
+        <v>220299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5152,7 +5166,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5160,21 +5174,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>720863</v>
+        <v>720876</v>
       </c>
       <c r="R42" t="n">
-        <v>6382976</v>
+        <v>6382966</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -5238,57 +5247,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126192200</v>
+        <v>126192252</v>
       </c>
       <c r="B43" t="n">
-        <v>98375</v>
+        <v>109176</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720774</v>
+        <v>720863</v>
       </c>
       <c r="R43" t="n">
-        <v>6382882</v>
+        <v>6382976</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5655,10 +5655,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126192330</v>
+        <v>126192199</v>
       </c>
       <c r="B47" t="n">
-        <v>98380</v>
+        <v>98330</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5666,26 +5666,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219864</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5699,13 +5699,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720772</v>
+        <v>720774</v>
       </c>
       <c r="R47" t="n">
-        <v>6382868</v>
+        <v>6382882</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5766,10 +5766,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126192254</v>
+        <v>126192219</v>
       </c>
       <c r="B48" t="n">
-        <v>98330</v>
+        <v>105387</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5777,26 +5777,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5804,21 +5804,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720863</v>
+        <v>720858</v>
       </c>
       <c r="R48" t="n">
-        <v>6382976</v>
+        <v>6382930</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -5882,10 +5877,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126192199</v>
+        <v>126192330</v>
       </c>
       <c r="B49" t="n">
-        <v>98330</v>
+        <v>98380</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5893,26 +5888,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219798</v>
+        <v>219864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5926,13 +5921,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>720774</v>
+        <v>720772</v>
       </c>
       <c r="R49" t="n">
-        <v>6382882</v>
+        <v>6382868</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5993,10 +5988,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126192219</v>
+        <v>126192254</v>
       </c>
       <c r="B50" t="n">
-        <v>105387</v>
+        <v>98330</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6004,26 +5999,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6031,16 +6026,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>720858</v>
+        <v>720863</v>
       </c>
       <c r="R50" t="n">
-        <v>6382930</v>
+        <v>6382976</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -936,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126192244</v>
+        <v>126192356</v>
       </c>
       <c r="B4" t="n">
-        <v>98270</v>
+        <v>95955</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,31 +947,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223591</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720876</v>
+        <v>720868</v>
       </c>
       <c r="R4" t="n">
-        <v>6382945</v>
+        <v>6382908</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
@@ -1026,11 +1026,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1047,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126192356</v>
+        <v>126192244</v>
       </c>
       <c r="B5" t="n">
-        <v>95955</v>
+        <v>98270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,31 +1053,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>223591</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1091,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720868</v>
+        <v>720876</v>
       </c>
       <c r="R5" t="n">
-        <v>6382908</v>
+        <v>6382945</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
@@ -1137,6 +1132,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1153,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126192220</v>
+        <v>126192233</v>
       </c>
       <c r="B6" t="n">
-        <v>105387</v>
+        <v>110443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,46 +1164,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>219711</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720869</v>
+        <v>720895</v>
       </c>
       <c r="R6" t="n">
-        <v>6382918</v>
+        <v>6382925</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1264,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126192233</v>
+        <v>126192220</v>
       </c>
       <c r="B7" t="n">
-        <v>110443</v>
+        <v>105387</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,37 +1266,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219711</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720895</v>
+        <v>720869</v>
       </c>
       <c r="R7" t="n">
-        <v>6382925</v>
+        <v>6382918</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1468,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126192274</v>
+        <v>126192192</v>
       </c>
       <c r="B9" t="n">
-        <v>105387</v>
+        <v>98330</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,26 +1479,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1506,24 +1506,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720757</v>
+        <v>720755</v>
       </c>
       <c r="R9" t="n">
-        <v>6383073</v>
+        <v>6382837</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1584,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126192192</v>
+        <v>126192274</v>
       </c>
       <c r="B10" t="n">
-        <v>98330</v>
+        <v>105387</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,26 +1590,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1622,19 +1617,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720755</v>
+        <v>720757</v>
       </c>
       <c r="R10" t="n">
-        <v>6382837</v>
+        <v>6383073</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126192259</v>
+        <v>126192229</v>
       </c>
       <c r="B15" t="n">
-        <v>105387</v>
+        <v>98374</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2137,21 +2137,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>219862</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2164,21 +2164,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720844</v>
+        <v>720883</v>
       </c>
       <c r="R15" t="n">
-        <v>6383011</v>
+        <v>6382912</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2211,11 +2206,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Barrblandskog, mossrik, vaierande ålder på träd, bara enstak död.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,7 +2237,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126192258</v>
+        <v>126192259</v>
       </c>
       <c r="B16" t="n">
         <v>105387</v>
@@ -2277,7 +2267,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2296,13 +2286,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720841</v>
+        <v>720844</v>
       </c>
       <c r="R16" t="n">
-        <v>6382998</v>
+        <v>6383011</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2336,7 +2326,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ett ex i blom.</t>
+          <t>Barrblandskog, mossrik, vaierande ålder på träd, bara enstak död.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126192229</v>
+        <v>126192258</v>
       </c>
       <c r="B17" t="n">
-        <v>98374</v>
+        <v>105387</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,26 +2369,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219862</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2406,19 +2396,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720883</v>
+        <v>720841</v>
       </c>
       <c r="R17" t="n">
-        <v>6382912</v>
+        <v>6382998</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2448,6 +2443,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ett ex i blom.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2590,10 +2590,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126192227</v>
+        <v>126192248</v>
       </c>
       <c r="B19" t="n">
-        <v>98330</v>
+        <v>98270</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,26 +2601,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2634,13 +2634,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720883</v>
+        <v>720869</v>
       </c>
       <c r="R19" t="n">
-        <v>6382912</v>
+        <v>6382960</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126192248</v>
+        <v>126192227</v>
       </c>
       <c r="B20" t="n">
-        <v>98270</v>
+        <v>98330</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,26 +2712,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2745,13 +2745,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720869</v>
+        <v>720883</v>
       </c>
       <c r="R20" t="n">
-        <v>6382960</v>
+        <v>6382912</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126192211</v>
+        <v>126192240</v>
       </c>
       <c r="B23" t="n">
-        <v>98262</v>
+        <v>98375</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>223572</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3078,13 +3078,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720818</v>
+        <v>720883</v>
       </c>
       <c r="R23" t="n">
-        <v>6382895</v>
+        <v>6382951</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3145,10 +3145,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126192240</v>
+        <v>126192238</v>
       </c>
       <c r="B24" t="n">
-        <v>98375</v>
+        <v>98330</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3156,21 +3156,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3192,10 +3192,10 @@
         <v>720883</v>
       </c>
       <c r="R24" t="n">
-        <v>6382951</v>
+        <v>6382941</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126192238</v>
+        <v>126192211</v>
       </c>
       <c r="B25" t="n">
-        <v>98330</v>
+        <v>98262</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3267,21 +3267,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>223572</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3300,13 +3300,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720883</v>
+        <v>720818</v>
       </c>
       <c r="R25" t="n">
-        <v>6382941</v>
+        <v>6382895</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126192221</v>
+        <v>126192239</v>
       </c>
       <c r="B26" t="n">
-        <v>98374</v>
+        <v>105387</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3378,21 +3378,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219862</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3411,13 +3411,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>720865</v>
+        <v>720883</v>
       </c>
       <c r="R26" t="n">
-        <v>6382912</v>
+        <v>6382941</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3478,10 +3478,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126192250</v>
+        <v>126192221</v>
       </c>
       <c r="B27" t="n">
-        <v>98330</v>
+        <v>98374</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,26 +3489,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3516,24 +3516,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720876</v>
+        <v>720865</v>
       </c>
       <c r="R27" t="n">
-        <v>6382966</v>
+        <v>6382912</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3594,10 +3589,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126192239</v>
+        <v>126192250</v>
       </c>
       <c r="B28" t="n">
-        <v>105387</v>
+        <v>98330</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3605,26 +3600,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3632,19 +3627,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720883</v>
+        <v>720876</v>
       </c>
       <c r="R28" t="n">
-        <v>6382941</v>
+        <v>6382966</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126192194</v>
+        <v>126192237</v>
       </c>
       <c r="B29" t="n">
-        <v>98270</v>
+        <v>105387</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3716,26 +3716,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>223591</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3749,13 +3749,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720755</v>
+        <v>720884</v>
       </c>
       <c r="R29" t="n">
-        <v>6382837</v>
+        <v>6382932</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126192237</v>
+        <v>126192210</v>
       </c>
       <c r="B30" t="n">
-        <v>105387</v>
+        <v>99393</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3827,46 +3827,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>222662</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720884</v>
+        <v>720818</v>
       </c>
       <c r="R30" t="n">
-        <v>6382932</v>
+        <v>6382895</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3909,7 +3900,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3927,10 +3918,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126192210</v>
+        <v>126192194</v>
       </c>
       <c r="B31" t="n">
-        <v>99393</v>
+        <v>98270</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3938,37 +3929,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222662</v>
+        <v>223591</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720818</v>
+        <v>720755</v>
       </c>
       <c r="R31" t="n">
-        <v>6382895</v>
+        <v>6382837</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4372,57 +4372,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126192231</v>
+        <v>126192304</v>
       </c>
       <c r="B35" t="n">
-        <v>98375</v>
+        <v>105947</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720895</v>
+        <v>720765</v>
       </c>
       <c r="R35" t="n">
-        <v>6382925</v>
+        <v>6382808</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4585,48 +4576,57 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126192304</v>
+        <v>126192231</v>
       </c>
       <c r="B37" t="n">
-        <v>105947</v>
+        <v>98375</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720765</v>
+        <v>720895</v>
       </c>
       <c r="R37" t="n">
-        <v>6382808</v>
+        <v>6382925</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4798,10 +4798,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126192331</v>
+        <v>126192253</v>
       </c>
       <c r="B39" t="n">
-        <v>98375</v>
+        <v>110443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4809,26 +4809,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4836,19 +4836,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720772</v>
+        <v>720863</v>
       </c>
       <c r="R39" t="n">
-        <v>6382868</v>
+        <v>6382976</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4909,10 +4914,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126192253</v>
+        <v>126192331</v>
       </c>
       <c r="B40" t="n">
-        <v>110443</v>
+        <v>98375</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4920,26 +4925,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4947,24 +4952,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>720863</v>
+        <v>720772</v>
       </c>
       <c r="R40" t="n">
-        <v>6382976</v>
+        <v>6382868</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5025,57 +5025,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126192200</v>
+        <v>126192252</v>
       </c>
       <c r="B41" t="n">
-        <v>98375</v>
+        <v>109176</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>720774</v>
+        <v>720863</v>
       </c>
       <c r="R41" t="n">
-        <v>6382882</v>
+        <v>6382976</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5247,48 +5238,57 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126192252</v>
+        <v>126192200</v>
       </c>
       <c r="B43" t="n">
-        <v>109176</v>
+        <v>98375</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720863</v>
+        <v>720774</v>
       </c>
       <c r="R43" t="n">
-        <v>6382976</v>
+        <v>6382882</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5655,10 +5655,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126192199</v>
+        <v>126192330</v>
       </c>
       <c r="B47" t="n">
-        <v>98330</v>
+        <v>98380</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5666,26 +5666,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219798</v>
+        <v>219864</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5699,13 +5699,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720774</v>
+        <v>720772</v>
       </c>
       <c r="R47" t="n">
-        <v>6382882</v>
+        <v>6382868</v>
       </c>
       <c r="S47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5766,10 +5766,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126192219</v>
+        <v>126192199</v>
       </c>
       <c r="B48" t="n">
-        <v>105387</v>
+        <v>98330</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5777,26 +5777,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5810,13 +5810,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720858</v>
+        <v>720774</v>
       </c>
       <c r="R48" t="n">
-        <v>6382930</v>
+        <v>6382882</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5877,10 +5877,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126192330</v>
+        <v>126192254</v>
       </c>
       <c r="B49" t="n">
-        <v>98380</v>
+        <v>98330</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5888,21 +5888,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219864</v>
+        <v>219798</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5915,19 +5915,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>720772</v>
+        <v>720863</v>
       </c>
       <c r="R49" t="n">
-        <v>6382868</v>
+        <v>6382976</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5988,10 +5993,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126192254</v>
+        <v>126192219</v>
       </c>
       <c r="B50" t="n">
-        <v>98330</v>
+        <v>105387</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5999,26 +6004,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6026,21 +6031,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>720863</v>
+        <v>720858</v>
       </c>
       <c r="R50" t="n">
-        <v>6382976</v>
+        <v>6382930</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -6104,37 +6104,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126192195</v>
+        <v>126192207</v>
       </c>
       <c r="B51" t="n">
-        <v>98375</v>
+        <v>105285</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219847</v>
+        <v>221137</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6148,13 +6148,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>720755</v>
+        <v>720818</v>
       </c>
       <c r="R51" t="n">
-        <v>6382837</v>
+        <v>6382895</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6186,6 +6186,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6197,7 +6202,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6215,37 +6220,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126192207</v>
+        <v>126192195</v>
       </c>
       <c r="B52" t="n">
-        <v>105285</v>
+        <v>98375</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221137</v>
+        <v>219847</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6259,13 +6264,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>720818</v>
+        <v>720755</v>
       </c>
       <c r="R52" t="n">
-        <v>6382895</v>
+        <v>6382837</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6297,11 +6302,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6544,7 +6544,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126192260</v>
+        <v>126192222</v>
       </c>
       <c r="B55" t="n">
         <v>105387</v>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6582,24 +6582,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>720835</v>
+        <v>720868</v>
       </c>
       <c r="R55" t="n">
-        <v>6383025</v>
+        <v>6382908</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6629,11 +6624,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Yngre skog mot N, nyröjt?</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6665,7 +6655,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126192222</v>
+        <v>126192260</v>
       </c>
       <c r="B56" t="n">
         <v>105387</v>
@@ -6695,7 +6685,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6703,19 +6693,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>720868</v>
+        <v>720835</v>
       </c>
       <c r="R56" t="n">
-        <v>6382908</v>
+        <v>6383025</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6745,6 +6740,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Yngre skog mot N, nyröjt?</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -1366,48 +1366,62 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126192215</v>
+        <v>126192274</v>
       </c>
       <c r="B8" t="n">
-        <v>109176</v>
+        <v>105387</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720838</v>
+        <v>720757</v>
       </c>
       <c r="R8" t="n">
-        <v>6382930</v>
+        <v>6383073</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1468,54 +1482,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126192192</v>
+        <v>126192215</v>
       </c>
       <c r="B9" t="n">
-        <v>98330</v>
+        <v>109176</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720755</v>
+        <v>720838</v>
       </c>
       <c r="R9" t="n">
-        <v>6382837</v>
+        <v>6382930</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126192274</v>
+        <v>126192192</v>
       </c>
       <c r="B10" t="n">
-        <v>105387</v>
+        <v>98330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1590,26 +1595,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1617,24 +1622,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720757</v>
+        <v>720755</v>
       </c>
       <c r="R10" t="n">
-        <v>6383073</v>
+        <v>6382837</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -3367,10 +3367,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126192239</v>
+        <v>126192221</v>
       </c>
       <c r="B26" t="n">
-        <v>105387</v>
+        <v>98374</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3378,21 +3378,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>219862</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3411,13 +3411,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>720883</v>
+        <v>720865</v>
       </c>
       <c r="R26" t="n">
-        <v>6382941</v>
+        <v>6382912</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3478,10 +3478,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126192221</v>
+        <v>126192250</v>
       </c>
       <c r="B27" t="n">
-        <v>98374</v>
+        <v>98330</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,26 +3489,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3516,19 +3516,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720865</v>
+        <v>720876</v>
       </c>
       <c r="R27" t="n">
-        <v>6382912</v>
+        <v>6382966</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3589,10 +3594,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126192250</v>
+        <v>126192239</v>
       </c>
       <c r="B28" t="n">
-        <v>98330</v>
+        <v>105387</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3600,26 +3605,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3627,24 +3632,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720876</v>
+        <v>720883</v>
       </c>
       <c r="R28" t="n">
-        <v>6382966</v>
+        <v>6382941</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4256,27 +4256,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126192257</v>
+        <v>126192198</v>
       </c>
       <c r="B34" t="n">
-        <v>110443</v>
+        <v>109176</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219711</v>
+        <v>220299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4284,34 +4284,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720869</v>
+        <v>720774</v>
       </c>
       <c r="R34" t="n">
-        <v>6382986</v>
+        <v>6382882</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4372,48 +4358,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126192304</v>
+        <v>126192231</v>
       </c>
       <c r="B35" t="n">
-        <v>105947</v>
+        <v>98375</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720765</v>
+        <v>720895</v>
       </c>
       <c r="R35" t="n">
-        <v>6382808</v>
+        <v>6382925</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4474,27 +4469,27 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126192198</v>
+        <v>126192304</v>
       </c>
       <c r="B36" t="n">
-        <v>109176</v>
+        <v>105947</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4509,10 +4504,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720774</v>
+        <v>720765</v>
       </c>
       <c r="R36" t="n">
-        <v>6382882</v>
+        <v>6382808</v>
       </c>
       <c r="S36" t="n">
         <v>7</v>
@@ -4576,10 +4571,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126192231</v>
+        <v>126192257</v>
       </c>
       <c r="B37" t="n">
-        <v>98375</v>
+        <v>110443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4587,26 +4582,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4614,16 +4609,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720895</v>
+        <v>720869</v>
       </c>
       <c r="R37" t="n">
-        <v>6382925</v>
+        <v>6382986</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -936,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126192356</v>
+        <v>126192244</v>
       </c>
       <c r="B4" t="n">
-        <v>95955</v>
+        <v>98279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,31 +947,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>223591</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720868</v>
+        <v>720876</v>
       </c>
       <c r="R4" t="n">
-        <v>6382908</v>
+        <v>6382945</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
@@ -1026,6 +1026,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1042,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126192244</v>
+        <v>126192356</v>
       </c>
       <c r="B5" t="n">
-        <v>98270</v>
+        <v>95964</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1053,31 +1058,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223591</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1086,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720876</v>
+        <v>720868</v>
       </c>
       <c r="R5" t="n">
-        <v>6382945</v>
+        <v>6382908</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
@@ -1132,11 +1137,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1156,7 +1156,7 @@
         <v>126192233</v>
       </c>
       <c r="B6" t="n">
-        <v>110443</v>
+        <v>110452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>126192220</v>
       </c>
       <c r="B7" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,62 +1366,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126192274</v>
+        <v>126192215</v>
       </c>
       <c r="B8" t="n">
-        <v>105387</v>
+        <v>109185</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720757</v>
+        <v>720838</v>
       </c>
       <c r="R8" t="n">
-        <v>6383073</v>
+        <v>6382930</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1482,48 +1468,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126192215</v>
+        <v>126192274</v>
       </c>
       <c r="B9" t="n">
-        <v>109176</v>
+        <v>105396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720838</v>
+        <v>720757</v>
       </c>
       <c r="R9" t="n">
-        <v>6382930</v>
+        <v>6383073</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>126192192</v>
       </c>
       <c r="B10" t="n">
-        <v>98330</v>
+        <v>98339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,32 +1695,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126192209</v>
+        <v>126192246</v>
       </c>
       <c r="B11" t="n">
-        <v>99027</v>
+        <v>110452</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222322</v>
+        <v>219711</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720818</v>
+        <v>720876</v>
       </c>
       <c r="R11" t="n">
-        <v>6382895</v>
+        <v>6382953</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,11 +1768,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1784,7 +1779,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1802,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126192246</v>
+        <v>126192224</v>
       </c>
       <c r="B12" t="n">
-        <v>110443</v>
+        <v>105396</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,37 +1808,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219711</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720876</v>
+        <v>720878</v>
       </c>
       <c r="R12" t="n">
-        <v>6382953</v>
+        <v>6382913</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1904,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126192224</v>
+        <v>126192228</v>
       </c>
       <c r="B13" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1938,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1948,13 +1952,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720878</v>
+        <v>720883</v>
       </c>
       <c r="R13" t="n">
-        <v>6382913</v>
+        <v>6382912</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2015,57 +2019,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126192228</v>
+        <v>126192209</v>
       </c>
       <c r="B14" t="n">
-        <v>105387</v>
+        <v>99036</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>222322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720883</v>
+        <v>720818</v>
       </c>
       <c r="R14" t="n">
-        <v>6382912</v>
+        <v>6382895</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,6 +2092,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2129,7 +2129,7 @@
         <v>126192229</v>
       </c>
       <c r="B15" t="n">
-        <v>98374</v>
+        <v>98383</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>126192259</v>
       </c>
       <c r="B16" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>126192258</v>
       </c>
       <c r="B17" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>126192243</v>
       </c>
       <c r="B18" t="n">
-        <v>110443</v>
+        <v>110452</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,10 +2590,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126192248</v>
+        <v>126192227</v>
       </c>
       <c r="B19" t="n">
-        <v>98270</v>
+        <v>98339</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,26 +2601,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2634,13 +2634,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720869</v>
+        <v>720883</v>
       </c>
       <c r="R19" t="n">
-        <v>6382960</v>
+        <v>6382912</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126192227</v>
+        <v>126192248</v>
       </c>
       <c r="B20" t="n">
-        <v>98330</v>
+        <v>98279</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,26 +2712,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2745,13 +2745,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720883</v>
+        <v>720869</v>
       </c>
       <c r="R20" t="n">
-        <v>6382912</v>
+        <v>6382960</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>126192216</v>
       </c>
       <c r="B21" t="n">
-        <v>98330</v>
+        <v>98339</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>126192241</v>
       </c>
       <c r="B22" t="n">
-        <v>98374</v>
+        <v>98383</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126192240</v>
+        <v>126192211</v>
       </c>
       <c r="B23" t="n">
-        <v>98375</v>
+        <v>98271</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>223572</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3078,13 +3078,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720883</v>
+        <v>720818</v>
       </c>
       <c r="R23" t="n">
-        <v>6382951</v>
+        <v>6382895</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3145,10 +3145,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126192238</v>
+        <v>126192240</v>
       </c>
       <c r="B24" t="n">
-        <v>98330</v>
+        <v>98384</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3156,21 +3156,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3192,10 +3192,10 @@
         <v>720883</v>
       </c>
       <c r="R24" t="n">
-        <v>6382941</v>
+        <v>6382951</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126192211</v>
+        <v>126192238</v>
       </c>
       <c r="B25" t="n">
-        <v>98262</v>
+        <v>98339</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3267,21 +3267,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223572</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3300,13 +3300,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720818</v>
+        <v>720883</v>
       </c>
       <c r="R25" t="n">
-        <v>6382895</v>
+        <v>6382941</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3370,7 +3370,7 @@
         <v>126192221</v>
       </c>
       <c r="B26" t="n">
-        <v>98374</v>
+        <v>98383</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>126192250</v>
       </c>
       <c r="B27" t="n">
-        <v>98330</v>
+        <v>98339</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>126192239</v>
       </c>
       <c r="B28" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>126192237</v>
       </c>
       <c r="B29" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126192210</v>
+        <v>126192194</v>
       </c>
       <c r="B30" t="n">
-        <v>99393</v>
+        <v>98279</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3827,37 +3827,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222662</v>
+        <v>223591</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720818</v>
+        <v>720755</v>
       </c>
       <c r="R30" t="n">
-        <v>6382895</v>
+        <v>6382837</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3900,7 +3909,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3918,10 +3927,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126192194</v>
+        <v>126192210</v>
       </c>
       <c r="B31" t="n">
-        <v>98270</v>
+        <v>99402</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3929,46 +3938,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223591</v>
+        <v>222662</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720755</v>
+        <v>720818</v>
       </c>
       <c r="R31" t="n">
-        <v>6382837</v>
+        <v>6382895</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4032,7 +4032,7 @@
         <v>126192230</v>
       </c>
       <c r="B32" t="n">
-        <v>98374</v>
+        <v>98383</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>126192271</v>
       </c>
       <c r="B33" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>126192198</v>
       </c>
       <c r="B34" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4358,10 +4358,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126192231</v>
+        <v>126192257</v>
       </c>
       <c r="B35" t="n">
-        <v>98375</v>
+        <v>110452</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4369,26 +4369,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4396,16 +4396,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720895</v>
+        <v>720869</v>
       </c>
       <c r="R35" t="n">
-        <v>6382925</v>
+        <v>6382986</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4469,48 +4474,57 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126192304</v>
+        <v>126192231</v>
       </c>
       <c r="B36" t="n">
-        <v>105947</v>
+        <v>98384</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720765</v>
+        <v>720895</v>
       </c>
       <c r="R36" t="n">
-        <v>6382808</v>
+        <v>6382925</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4571,27 +4585,27 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126192257</v>
+        <v>126192304</v>
       </c>
       <c r="B37" t="n">
-        <v>110443</v>
+        <v>105956</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219711</v>
+        <v>220785</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4599,34 +4613,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720869</v>
+        <v>720765</v>
       </c>
       <c r="R37" t="n">
-        <v>6382986</v>
+        <v>6382808</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>126192203</v>
       </c>
       <c r="B38" t="n">
-        <v>98374</v>
+        <v>98383</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4798,10 +4798,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126192253</v>
+        <v>126192331</v>
       </c>
       <c r="B39" t="n">
-        <v>110443</v>
+        <v>98384</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4809,26 +4809,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4836,24 +4836,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720863</v>
+        <v>720772</v>
       </c>
       <c r="R39" t="n">
-        <v>6382976</v>
+        <v>6382868</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4914,10 +4909,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126192331</v>
+        <v>126192253</v>
       </c>
       <c r="B40" t="n">
-        <v>98375</v>
+        <v>110452</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4925,26 +4920,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4952,19 +4947,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>720772</v>
+        <v>720863</v>
       </c>
       <c r="R40" t="n">
-        <v>6382868</v>
+        <v>6382976</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5025,48 +5025,57 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126192252</v>
+        <v>126192200</v>
       </c>
       <c r="B41" t="n">
-        <v>109176</v>
+        <v>98384</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>720863</v>
+        <v>720774</v>
       </c>
       <c r="R41" t="n">
-        <v>6382976</v>
+        <v>6382882</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5127,10 +5136,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126192249</v>
+        <v>126192252</v>
       </c>
       <c r="B42" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5155,29 +5164,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>720876</v>
+        <v>720863</v>
       </c>
       <c r="R42" t="n">
-        <v>6382966</v>
+        <v>6382976</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5238,37 +5238,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126192200</v>
+        <v>126192249</v>
       </c>
       <c r="B43" t="n">
-        <v>98375</v>
+        <v>109185</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5282,13 +5282,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720774</v>
+        <v>720876</v>
       </c>
       <c r="R43" t="n">
-        <v>6382882</v>
+        <v>6382966</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>126192214</v>
       </c>
       <c r="B44" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>126192202</v>
       </c>
       <c r="B45" t="n">
-        <v>98330</v>
+        <v>98339</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>126192242</v>
       </c>
       <c r="B46" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5655,10 +5655,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126192330</v>
+        <v>126192219</v>
       </c>
       <c r="B47" t="n">
-        <v>98380</v>
+        <v>105396</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5666,26 +5666,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219864</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5699,13 +5699,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720772</v>
+        <v>720858</v>
       </c>
       <c r="R47" t="n">
-        <v>6382868</v>
+        <v>6382930</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5766,10 +5766,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126192199</v>
+        <v>126192330</v>
       </c>
       <c r="B48" t="n">
-        <v>98330</v>
+        <v>98389</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5777,26 +5777,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219798</v>
+        <v>219864</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5810,13 +5810,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720774</v>
+        <v>720772</v>
       </c>
       <c r="R48" t="n">
-        <v>6382882</v>
+        <v>6382868</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5877,10 +5877,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126192254</v>
+        <v>126192199</v>
       </c>
       <c r="B49" t="n">
-        <v>98330</v>
+        <v>98339</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5915,24 +5915,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>720863</v>
+        <v>720774</v>
       </c>
       <c r="R49" t="n">
-        <v>6382976</v>
+        <v>6382882</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5993,10 +5988,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126192219</v>
+        <v>126192254</v>
       </c>
       <c r="B50" t="n">
-        <v>105387</v>
+        <v>98339</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6004,26 +5999,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6031,16 +6026,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>720858</v>
+        <v>720863</v>
       </c>
       <c r="R50" t="n">
-        <v>6382930</v>
+        <v>6382976</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -6104,37 +6104,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126192207</v>
+        <v>126192195</v>
       </c>
       <c r="B51" t="n">
-        <v>105285</v>
+        <v>98384</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221137</v>
+        <v>219847</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6148,13 +6148,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>720818</v>
+        <v>720755</v>
       </c>
       <c r="R51" t="n">
-        <v>6382895</v>
+        <v>6382837</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6186,11 +6186,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6202,7 +6197,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6220,37 +6215,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126192195</v>
+        <v>126192207</v>
       </c>
       <c r="B52" t="n">
-        <v>98375</v>
+        <v>105294</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219847</v>
+        <v>221137</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6264,13 +6259,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>720755</v>
+        <v>720818</v>
       </c>
       <c r="R52" t="n">
-        <v>6382837</v>
+        <v>6382895</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6302,6 +6297,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6334,7 +6334,7 @@
         <v>126192213</v>
       </c>
       <c r="B53" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6442,48 +6442,57 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126192268</v>
+        <v>126192222</v>
       </c>
       <c r="B54" t="n">
-        <v>109176</v>
+        <v>105396</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220299</v>
+        <v>221144</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>720800</v>
+        <v>720868</v>
       </c>
       <c r="R54" t="n">
-        <v>6383077</v>
+        <v>6382908</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6544,10 +6553,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126192222</v>
+        <v>126192260</v>
       </c>
       <c r="B55" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6574,7 +6583,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6582,19 +6591,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>720868</v>
+        <v>720835</v>
       </c>
       <c r="R55" t="n">
-        <v>6382908</v>
+        <v>6383025</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6624,6 +6638,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Yngre skog mot N, nyröjt?</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6655,62 +6674,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126192260</v>
+        <v>126192268</v>
       </c>
       <c r="B56" t="n">
-        <v>105387</v>
+        <v>109185</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>220299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>720835</v>
+        <v>720800</v>
       </c>
       <c r="R56" t="n">
-        <v>6383025</v>
+        <v>6383077</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6740,11 +6745,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Yngre skog mot N, nyröjt?</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -1468,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126192274</v>
+        <v>126192192</v>
       </c>
       <c r="B9" t="n">
-        <v>105396</v>
+        <v>98339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,26 +1479,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1506,24 +1506,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720757</v>
+        <v>720755</v>
       </c>
       <c r="R9" t="n">
-        <v>6383073</v>
+        <v>6382837</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1584,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126192192</v>
+        <v>126192274</v>
       </c>
       <c r="B10" t="n">
-        <v>98339</v>
+        <v>105396</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,26 +1590,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1622,19 +1617,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720755</v>
+        <v>720757</v>
       </c>
       <c r="R10" t="n">
-        <v>6382837</v>
+        <v>6383073</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126192194</v>
+        <v>126192210</v>
       </c>
       <c r="B30" t="n">
-        <v>98279</v>
+        <v>99402</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3827,46 +3827,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>223591</v>
+        <v>222662</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720755</v>
+        <v>720818</v>
       </c>
       <c r="R30" t="n">
-        <v>6382837</v>
+        <v>6382895</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3909,7 +3900,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3927,10 +3918,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126192210</v>
+        <v>126192194</v>
       </c>
       <c r="B31" t="n">
-        <v>99402</v>
+        <v>98279</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3938,37 +3929,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222662</v>
+        <v>223591</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720818</v>
+        <v>720755</v>
       </c>
       <c r="R31" t="n">
-        <v>6382895</v>
+        <v>6382837</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -5655,10 +5655,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126192219</v>
+        <v>126192330</v>
       </c>
       <c r="B47" t="n">
-        <v>105396</v>
+        <v>98389</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5666,26 +5666,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>219864</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5699,13 +5699,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720858</v>
+        <v>720772</v>
       </c>
       <c r="R47" t="n">
-        <v>6382930</v>
+        <v>6382868</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5766,10 +5766,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126192330</v>
+        <v>126192199</v>
       </c>
       <c r="B48" t="n">
-        <v>98389</v>
+        <v>98339</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5777,26 +5777,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219864</v>
+        <v>219798</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5810,13 +5810,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720772</v>
+        <v>720774</v>
       </c>
       <c r="R48" t="n">
-        <v>6382868</v>
+        <v>6382882</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126192199</v>
+        <v>126192254</v>
       </c>
       <c r="B49" t="n">
         <v>98339</v>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5915,19 +5915,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>720774</v>
+        <v>720863</v>
       </c>
       <c r="R49" t="n">
-        <v>6382882</v>
+        <v>6382976</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5988,10 +5993,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126192254</v>
+        <v>126192219</v>
       </c>
       <c r="B50" t="n">
-        <v>98339</v>
+        <v>105396</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5999,26 +6004,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6026,21 +6031,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>720863</v>
+        <v>720858</v>
       </c>
       <c r="R50" t="n">
-        <v>6382976</v>
+        <v>6382930</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -936,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126192244</v>
+        <v>126192356</v>
       </c>
       <c r="B4" t="n">
-        <v>98279</v>
+        <v>95964</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,31 +947,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223591</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720876</v>
+        <v>720868</v>
       </c>
       <c r="R4" t="n">
-        <v>6382945</v>
+        <v>6382908</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
@@ -1026,11 +1026,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1047,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126192356</v>
+        <v>126192244</v>
       </c>
       <c r="B5" t="n">
-        <v>95964</v>
+        <v>98279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,31 +1053,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>223591</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1091,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720868</v>
+        <v>720876</v>
       </c>
       <c r="R5" t="n">
-        <v>6382908</v>
+        <v>6382945</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
@@ -1137,6 +1132,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1366,45 +1366,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126192215</v>
+        <v>126192192</v>
       </c>
       <c r="B8" t="n">
-        <v>109185</v>
+        <v>98339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720838</v>
+        <v>720755</v>
       </c>
       <c r="R8" t="n">
-        <v>6382930</v>
+        <v>6382837</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1468,54 +1477,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126192192</v>
+        <v>126192215</v>
       </c>
       <c r="B9" t="n">
-        <v>98339</v>
+        <v>109185</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720755</v>
+        <v>720838</v>
       </c>
       <c r="R9" t="n">
-        <v>6382837</v>
+        <v>6382930</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1797,57 +1797,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126192224</v>
+        <v>126192209</v>
       </c>
       <c r="B12" t="n">
-        <v>105396</v>
+        <v>99036</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>222322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720878</v>
+        <v>720818</v>
       </c>
       <c r="R12" t="n">
-        <v>6382913</v>
+        <v>6382895</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1879,6 +1870,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1890,7 +1886,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1908,7 +1904,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126192228</v>
+        <v>126192224</v>
       </c>
       <c r="B13" t="n">
         <v>105396</v>
@@ -1938,7 +1934,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1952,13 +1948,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720883</v>
+        <v>720878</v>
       </c>
       <c r="R13" t="n">
-        <v>6382912</v>
+        <v>6382913</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2019,48 +2015,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126192209</v>
+        <v>126192228</v>
       </c>
       <c r="B14" t="n">
-        <v>99036</v>
+        <v>105396</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222322</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720818</v>
+        <v>720883</v>
       </c>
       <c r="R14" t="n">
-        <v>6382895</v>
+        <v>6382912</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2092,11 +2097,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126192211</v>
+        <v>126192240</v>
       </c>
       <c r="B23" t="n">
-        <v>98271</v>
+        <v>98384</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>223572</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3078,13 +3078,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720818</v>
+        <v>720883</v>
       </c>
       <c r="R23" t="n">
-        <v>6382895</v>
+        <v>6382951</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3145,10 +3145,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126192240</v>
+        <v>126192238</v>
       </c>
       <c r="B24" t="n">
-        <v>98384</v>
+        <v>98339</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3156,21 +3156,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3192,10 +3192,10 @@
         <v>720883</v>
       </c>
       <c r="R24" t="n">
-        <v>6382951</v>
+        <v>6382941</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126192238</v>
+        <v>126192211</v>
       </c>
       <c r="B25" t="n">
-        <v>98339</v>
+        <v>98271</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3267,21 +3267,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>223572</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3300,13 +3300,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720883</v>
+        <v>720818</v>
       </c>
       <c r="R25" t="n">
-        <v>6382941</v>
+        <v>6382895</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126192237</v>
+        <v>126192210</v>
       </c>
       <c r="B29" t="n">
-        <v>105396</v>
+        <v>99402</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3716,46 +3716,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>222662</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720884</v>
+        <v>720818</v>
       </c>
       <c r="R29" t="n">
-        <v>6382932</v>
+        <v>6382895</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3798,7 +3789,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Källmyrslik myr; blött i körspår centralt..</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3816,10 +3807,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126192210</v>
+        <v>126192194</v>
       </c>
       <c r="B30" t="n">
-        <v>99402</v>
+        <v>98279</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3827,37 +3818,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222662</v>
+        <v>223591</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720818</v>
+        <v>720755</v>
       </c>
       <c r="R30" t="n">
-        <v>6382895</v>
+        <v>6382837</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Källmyrslik myr; blött i körspår centralt..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3918,10 +3918,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126192194</v>
+        <v>126192237</v>
       </c>
       <c r="B31" t="n">
-        <v>98279</v>
+        <v>105396</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3929,26 +3929,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223591</v>
+        <v>221144</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3962,13 +3962,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720755</v>
+        <v>720884</v>
       </c>
       <c r="R31" t="n">
-        <v>6382837</v>
+        <v>6382932</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4256,27 +4256,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126192198</v>
+        <v>126192257</v>
       </c>
       <c r="B34" t="n">
-        <v>109185</v>
+        <v>110452</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220299</v>
+        <v>219711</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4284,20 +4284,34 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720774</v>
+        <v>720869</v>
       </c>
       <c r="R34" t="n">
-        <v>6382882</v>
+        <v>6382986</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4358,10 +4372,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126192257</v>
+        <v>126192231</v>
       </c>
       <c r="B35" t="n">
-        <v>110452</v>
+        <v>98384</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4369,26 +4383,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4396,21 +4410,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720869</v>
+        <v>720895</v>
       </c>
       <c r="R35" t="n">
-        <v>6382986</v>
+        <v>6382925</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4474,57 +4483,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126192231</v>
+        <v>126192198</v>
       </c>
       <c r="B36" t="n">
-        <v>98384</v>
+        <v>109185</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720895</v>
+        <v>720774</v>
       </c>
       <c r="R36" t="n">
-        <v>6382925</v>
+        <v>6382882</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -6442,57 +6442,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126192222</v>
+        <v>126192268</v>
       </c>
       <c r="B54" t="n">
-        <v>105396</v>
+        <v>109185</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221144</v>
+        <v>220299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>720868</v>
+        <v>720800</v>
       </c>
       <c r="R54" t="n">
-        <v>6382908</v>
+        <v>6383077</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6553,7 +6544,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126192260</v>
+        <v>126192222</v>
       </c>
       <c r="B55" t="n">
         <v>105396</v>
@@ -6583,7 +6574,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6591,24 +6582,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>720835</v>
+        <v>720868</v>
       </c>
       <c r="R55" t="n">
-        <v>6383025</v>
+        <v>6382908</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6638,11 +6624,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Yngre skog mot N, nyröjt?</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6674,48 +6655,62 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126192268</v>
+        <v>126192260</v>
       </c>
       <c r="B56" t="n">
-        <v>109185</v>
+        <v>105396</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220299</v>
+        <v>221144</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>720800</v>
+        <v>720835</v>
       </c>
       <c r="R56" t="n">
-        <v>6383077</v>
+        <v>6383025</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6745,6 +6740,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Yngre skog mot N, nyröjt?</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6774,6 +6774,7279 @@
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>126603939</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98272</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>223578</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Äkta ängsnycklar</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>720921</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6382848</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Kalkgräsmyr i skog.</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126603960</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>720779</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6382857</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>126603997</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>720879</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6382802</v>
+      </c>
+      <c r="S59" t="n">
+        <v>8</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126603993</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98384</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>720877</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6382811</v>
+      </c>
+      <c r="S60" t="n">
+        <v>8</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126603959</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>720779</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6382857</v>
+      </c>
+      <c r="S61" t="n">
+        <v>3</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126604006</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98397</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>720893</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6382800</v>
+      </c>
+      <c r="S62" t="n">
+        <v>7</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>126603947</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>720833</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6382931</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126603945</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>720880</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6382875</v>
+      </c>
+      <c r="S64" t="n">
+        <v>8</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>126603964</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98384</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>720805</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6382844</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>126603956</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98384</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>720778</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6382885</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk; solbelyst glänta..</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>126603987</v>
+      </c>
+      <c r="B67" t="n">
+        <v>98384</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>720880</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6382825</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>126603990</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98384</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>720893</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6382817</v>
+      </c>
+      <c r="S68" t="n">
+        <v>8</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>126604001</v>
+      </c>
+      <c r="B69" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>720893</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6382800</v>
+      </c>
+      <c r="S69" t="n">
+        <v>7</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>126603957</v>
+      </c>
+      <c r="B70" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>720778</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6382885</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk; solbelyst glänta..</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>126603971</v>
+      </c>
+      <c r="B71" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>720851</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6382814</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>126604004</v>
+      </c>
+      <c r="B72" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>720893</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6382800</v>
+      </c>
+      <c r="S72" t="n">
+        <v>7</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>126603975</v>
+      </c>
+      <c r="B73" t="n">
+        <v>98383</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>720861</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6382781</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>126603972</v>
+      </c>
+      <c r="B74" t="n">
+        <v>98398</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>720851</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6382814</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>126603952</v>
+      </c>
+      <c r="B75" t="n">
+        <v>98397</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>720769</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6382920</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>126603999</v>
+      </c>
+      <c r="B76" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>720879</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6382802</v>
+      </c>
+      <c r="S76" t="n">
+        <v>8</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>126603995</v>
+      </c>
+      <c r="B77" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>720877</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6382811</v>
+      </c>
+      <c r="S77" t="n">
+        <v>8</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>126603970</v>
+      </c>
+      <c r="B78" t="n">
+        <v>98398</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>720808</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6382832</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>126603985</v>
+      </c>
+      <c r="B79" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>720870</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6382807</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>126603946</v>
+      </c>
+      <c r="B80" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>720880</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6382875</v>
+      </c>
+      <c r="S80" t="n">
+        <v>8</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>126603966</v>
+      </c>
+      <c r="B81" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>720805</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6382844</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>126603967</v>
+      </c>
+      <c r="B82" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>720805</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6382844</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>126603981</v>
+      </c>
+      <c r="B83" t="n">
+        <v>107243</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>720861</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6382807</v>
+      </c>
+      <c r="S83" t="n">
+        <v>3</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>126603963</v>
+      </c>
+      <c r="B84" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>720785</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6382836</v>
+      </c>
+      <c r="S84" t="n">
+        <v>8</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>126603951</v>
+      </c>
+      <c r="B85" t="n">
+        <v>98383</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>720769</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6382920</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>126603986</v>
+      </c>
+      <c r="B86" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>720880</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6382825</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>126603992</v>
+      </c>
+      <c r="B87" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>720893</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6382817</v>
+      </c>
+      <c r="S87" t="n">
+        <v>8</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>126603953</v>
+      </c>
+      <c r="B88" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>720769</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6382920</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>126603994</v>
+      </c>
+      <c r="B89" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>720877</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6382811</v>
+      </c>
+      <c r="S89" t="n">
+        <v>8</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>126603962</v>
+      </c>
+      <c r="B90" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>720785</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6382836</v>
+      </c>
+      <c r="S90" t="n">
+        <v>8</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>126603943</v>
+      </c>
+      <c r="B91" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>720887</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6382881</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>126603984</v>
+      </c>
+      <c r="B92" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>720870</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6382807</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>126603983</v>
+      </c>
+      <c r="B93" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>720861</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6382807</v>
+      </c>
+      <c r="S93" t="n">
+        <v>3</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>126603903</v>
+      </c>
+      <c r="B94" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>720852</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6382893</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Lundstarr ses ej i området.</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>Tallskog, fuktig glänta.</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>126603954</v>
+      </c>
+      <c r="B95" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>720769</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6382920</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>126603961</v>
+      </c>
+      <c r="B96" t="n">
+        <v>98336</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>720785</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6382836</v>
+      </c>
+      <c r="S96" t="n">
+        <v>8</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>126603996</v>
+      </c>
+      <c r="B97" t="n">
+        <v>110452</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>720879</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6382802</v>
+      </c>
+      <c r="S97" t="n">
+        <v>8</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>126603904</v>
+      </c>
+      <c r="B98" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>720778</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6382885</v>
+      </c>
+      <c r="S98" t="n">
+        <v>5</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Lundstarr ses ej i området.</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk; solbelyst glänta..</t>
+        </is>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>126603938</v>
+      </c>
+      <c r="B99" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>720921</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6382848</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>Kalkgräsmyr i skog.</t>
+        </is>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>126603902</v>
+      </c>
+      <c r="B100" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>720950</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6382850</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Även väddnatfjäril ev. Lundstarr sågs ej. Vid stor sten i NO-hörn av våtmark.</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>Tallskog, kant av fuktig glänta.</t>
+        </is>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>126603998</v>
+      </c>
+      <c r="B101" t="n">
+        <v>107243</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>720879</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6382802</v>
+      </c>
+      <c r="S101" t="n">
+        <v>8</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>126603969</v>
+      </c>
+      <c r="B102" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>720808</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6382832</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>126603948</v>
+      </c>
+      <c r="B103" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>720833</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6382931</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>126604000</v>
+      </c>
+      <c r="B104" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>720879</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6382802</v>
+      </c>
+      <c r="S104" t="n">
+        <v>8</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>126603977</v>
+      </c>
+      <c r="B105" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>720852</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6382793</v>
+      </c>
+      <c r="S105" t="n">
+        <v>3</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>126603980</v>
+      </c>
+      <c r="B106" t="n">
+        <v>98383</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>720861</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6382807</v>
+      </c>
+      <c r="S106" t="n">
+        <v>3</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>126603989</v>
+      </c>
+      <c r="B107" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>720880</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6382825</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>126603982</v>
+      </c>
+      <c r="B108" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>720861</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6382807</v>
+      </c>
+      <c r="S108" t="n">
+        <v>3</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>126603991</v>
+      </c>
+      <c r="B109" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>720893</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6382817</v>
+      </c>
+      <c r="S109" t="n">
+        <v>8</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>126603944</v>
+      </c>
+      <c r="B110" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>720887</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6382881</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>126603949</v>
+      </c>
+      <c r="B111" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>720829</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6382943</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>126603965</v>
+      </c>
+      <c r="B112" t="n">
+        <v>98336</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>720805</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6382844</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>126603976</v>
+      </c>
+      <c r="B113" t="n">
+        <v>98336</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>720861</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6382781</v>
+      </c>
+      <c r="S113" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>126603968</v>
+      </c>
+      <c r="B114" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>720808</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6382832</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>126603988</v>
+      </c>
+      <c r="B115" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>720880</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6382825</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>126603978</v>
+      </c>
+      <c r="B116" t="n">
+        <v>98398</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>720852</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6382793</v>
+      </c>
+      <c r="S116" t="n">
+        <v>3</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>126603974</v>
+      </c>
+      <c r="B117" t="n">
+        <v>98398</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>720861</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6382781</v>
+      </c>
+      <c r="S117" t="n">
+        <v>5</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>126603937</v>
+      </c>
+      <c r="B118" t="n">
+        <v>105294</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>720921</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6382848</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>Kalkgräsmyr i skog.</t>
+        </is>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>126603955</v>
+      </c>
+      <c r="B119" t="n">
+        <v>98398</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>720778</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6382885</v>
+      </c>
+      <c r="S119" t="n">
+        <v>5</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk; solbelyst glänta..</t>
+        </is>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>126603958</v>
+      </c>
+      <c r="B120" t="n">
+        <v>105956</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>720779</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6382857</v>
+      </c>
+      <c r="S120" t="n">
+        <v>3</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>126603950</v>
+      </c>
+      <c r="B121" t="n">
+        <v>98398</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>720829</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6382943</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>126603973</v>
+      </c>
+      <c r="B122" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>720861</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6382781</v>
+      </c>
+      <c r="S122" t="n">
+        <v>5</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -2479,10 +2479,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126192243</v>
+        <v>126192248</v>
       </c>
       <c r="B18" t="n">
-        <v>110452</v>
+        <v>98279</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2490,26 +2490,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219711</v>
+        <v>223591</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720876</v>
+        <v>720869</v>
       </c>
       <c r="R18" t="n">
-        <v>6382945</v>
+        <v>6382960</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2590,10 +2590,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126192227</v>
+        <v>126192243</v>
       </c>
       <c r="B19" t="n">
-        <v>98339</v>
+        <v>110452</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,26 +2601,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2634,13 +2634,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720883</v>
+        <v>720876</v>
       </c>
       <c r="R19" t="n">
-        <v>6382912</v>
+        <v>6382945</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126192248</v>
+        <v>126192227</v>
       </c>
       <c r="B20" t="n">
-        <v>98279</v>
+        <v>98339</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,26 +2712,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2745,13 +2745,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720869</v>
+        <v>720883</v>
       </c>
       <c r="R20" t="n">
-        <v>6382960</v>
+        <v>6382912</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3367,10 +3367,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126192221</v>
+        <v>126192239</v>
       </c>
       <c r="B26" t="n">
-        <v>98383</v>
+        <v>105396</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3378,21 +3378,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219862</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3411,13 +3411,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>720865</v>
+        <v>720883</v>
       </c>
       <c r="R26" t="n">
-        <v>6382912</v>
+        <v>6382941</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3478,10 +3478,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126192250</v>
+        <v>126192221</v>
       </c>
       <c r="B27" t="n">
-        <v>98339</v>
+        <v>98383</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,26 +3489,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3516,24 +3516,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720876</v>
+        <v>720865</v>
       </c>
       <c r="R27" t="n">
-        <v>6382966</v>
+        <v>6382912</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3594,10 +3589,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126192239</v>
+        <v>126192250</v>
       </c>
       <c r="B28" t="n">
-        <v>105396</v>
+        <v>98339</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3605,26 +3600,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3632,19 +3627,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720883</v>
+        <v>720876</v>
       </c>
       <c r="R28" t="n">
-        <v>6382941</v>
+        <v>6382966</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4256,27 +4256,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126192257</v>
+        <v>126192304</v>
       </c>
       <c r="B34" t="n">
-        <v>110452</v>
+        <v>105956</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219711</v>
+        <v>220785</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4284,34 +4284,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720869</v>
+        <v>720765</v>
       </c>
       <c r="R34" t="n">
-        <v>6382986</v>
+        <v>6382808</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4372,10 +4358,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126192231</v>
+        <v>126192257</v>
       </c>
       <c r="B35" t="n">
-        <v>98384</v>
+        <v>110452</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4383,26 +4369,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4410,16 +4396,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720895</v>
+        <v>720869</v>
       </c>
       <c r="R35" t="n">
-        <v>6382925</v>
+        <v>6382986</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4483,48 +4474,57 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126192198</v>
+        <v>126192231</v>
       </c>
       <c r="B36" t="n">
-        <v>109185</v>
+        <v>98384</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720774</v>
+        <v>720895</v>
       </c>
       <c r="R36" t="n">
-        <v>6382882</v>
+        <v>6382925</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4585,27 +4585,27 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126192304</v>
+        <v>126192198</v>
       </c>
       <c r="B37" t="n">
-        <v>105956</v>
+        <v>109185</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720765</v>
+        <v>720774</v>
       </c>
       <c r="R37" t="n">
-        <v>6382808</v>
+        <v>6382882</v>
       </c>
       <c r="S37" t="n">
         <v>7</v>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -6776,10 +6776,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126603939</v>
+        <v>126603993</v>
       </c>
       <c r="B57" t="n">
-        <v>98272</v>
+        <v>98459</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6787,22 +6787,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>223578</v>
+        <v>219847</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6816,13 +6820,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>720921</v>
+        <v>720877</v>
       </c>
       <c r="R57" t="n">
-        <v>6382848</v>
+        <v>6382811</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6865,7 +6869,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr i skog.</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6883,10 +6887,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126603997</v>
+        <v>126603939</v>
       </c>
       <c r="B58" t="n">
-        <v>98279</v>
+        <v>98347</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6894,26 +6898,22 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>223591</v>
+        <v>223578</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6927,13 +6927,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>720879</v>
+        <v>720921</v>
       </c>
       <c r="R58" t="n">
-        <v>6382802</v>
+        <v>6382848</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkgräsmyr i skog.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -6994,10 +6994,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126603993</v>
+        <v>126603997</v>
       </c>
       <c r="B59" t="n">
-        <v>98384</v>
+        <v>98354</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7005,26 +7005,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7038,10 +7038,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>720877</v>
+        <v>720879</v>
       </c>
       <c r="R59" t="n">
-        <v>6382811</v>
+        <v>6382802</v>
       </c>
       <c r="S59" t="n">
         <v>8</v>
@@ -7108,7 +7108,7 @@
         <v>126603960</v>
       </c>
       <c r="B60" t="n">
-        <v>98279</v>
+        <v>98354</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7216,10 +7216,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126603959</v>
+        <v>126604006</v>
       </c>
       <c r="B61" t="n">
-        <v>98339</v>
+        <v>98472</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7227,26 +7227,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219798</v>
+        <v>223621</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7260,13 +7260,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>720779</v>
+        <v>720893</v>
       </c>
       <c r="R61" t="n">
-        <v>6382857</v>
+        <v>6382800</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7327,10 +7327,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126604006</v>
+        <v>126603959</v>
       </c>
       <c r="B62" t="n">
-        <v>98397</v>
+        <v>98414</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7338,26 +7338,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>223621</v>
+        <v>219798</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7371,13 +7371,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>720893</v>
+        <v>720779</v>
       </c>
       <c r="R62" t="n">
-        <v>6382800</v>
+        <v>6382857</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>126603947</v>
       </c>
       <c r="B63" t="n">
-        <v>98279</v>
+        <v>98354</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>126603964</v>
       </c>
       <c r="B64" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>126603945</v>
       </c>
       <c r="B65" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7771,57 +7771,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126603956</v>
+        <v>126604001</v>
       </c>
       <c r="B66" t="n">
-        <v>98384</v>
+        <v>109260</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>720778</v>
+        <v>720893</v>
       </c>
       <c r="R66" t="n">
-        <v>6382885</v>
+        <v>6382800</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7864,7 +7855,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk; solbelyst glänta..</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7882,10 +7873,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126603987</v>
+        <v>126603956</v>
       </c>
       <c r="B67" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7912,7 +7903,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7926,13 +7917,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>720880</v>
+        <v>720778</v>
       </c>
       <c r="R67" t="n">
-        <v>6382825</v>
+        <v>6382885</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7975,7 +7966,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkbarrskog, frisk; solbelyst glänta..</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7993,48 +7984,57 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126604001</v>
+        <v>126603987</v>
       </c>
       <c r="B68" t="n">
-        <v>109185</v>
+        <v>98459</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>720893</v>
+        <v>720880</v>
       </c>
       <c r="R68" t="n">
-        <v>6382800</v>
+        <v>6382825</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>126603990</v>
       </c>
       <c r="B69" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8206,10 +8206,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126603972</v>
+        <v>126603952</v>
       </c>
       <c r="B70" t="n">
-        <v>98398</v>
+        <v>98472</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8217,21 +8217,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219875</v>
+        <v>223621</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8250,10 +8250,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>720851</v>
+        <v>720769</v>
       </c>
       <c r="R70" t="n">
-        <v>6382814</v>
+        <v>6382920</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8320,7 +8320,7 @@
         <v>126603957</v>
       </c>
       <c r="B71" t="n">
-        <v>98279</v>
+        <v>98354</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8428,10 +8428,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126603975</v>
+        <v>126604004</v>
       </c>
       <c r="B72" t="n">
-        <v>98383</v>
+        <v>98354</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8439,21 +8439,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219862</v>
+        <v>223591</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8466,24 +8466,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>720861</v>
+        <v>720893</v>
       </c>
       <c r="R72" t="n">
-        <v>6382781</v>
+        <v>6382800</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8544,10 +8539,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126603952</v>
+        <v>126603971</v>
       </c>
       <c r="B73" t="n">
-        <v>98397</v>
+        <v>98354</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8555,21 +8550,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>223621</v>
+        <v>223591</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8588,10 +8583,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>720769</v>
+        <v>720851</v>
       </c>
       <c r="R73" t="n">
-        <v>6382920</v>
+        <v>6382814</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8655,10 +8650,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126604004</v>
+        <v>126603972</v>
       </c>
       <c r="B74" t="n">
-        <v>98279</v>
+        <v>98473</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8666,21 +8661,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>223591</v>
+        <v>219875</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8699,13 +8694,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>720893</v>
+        <v>720851</v>
       </c>
       <c r="R74" t="n">
-        <v>6382800</v>
+        <v>6382814</v>
       </c>
       <c r="S74" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8766,10 +8761,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126603971</v>
+        <v>126603975</v>
       </c>
       <c r="B75" t="n">
-        <v>98279</v>
+        <v>98458</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8777,21 +8772,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>223591</v>
+        <v>219862</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -8804,19 +8799,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>720851</v>
+        <v>720861</v>
       </c>
       <c r="R75" t="n">
-        <v>6382814</v>
+        <v>6382781</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8877,32 +8877,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126603999</v>
+        <v>126603995</v>
       </c>
       <c r="B76" t="n">
-        <v>109185</v>
+        <v>98354</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8912,10 +8912,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>720879</v>
+        <v>720877</v>
       </c>
       <c r="R76" t="n">
-        <v>6382802</v>
+        <v>6382811</v>
       </c>
       <c r="S76" t="n">
         <v>8</v>
@@ -8979,32 +8979,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126603995</v>
+        <v>126603999</v>
       </c>
       <c r="B77" t="n">
-        <v>98279</v>
+        <v>109260</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9014,10 +9014,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>720877</v>
+        <v>720879</v>
       </c>
       <c r="R77" t="n">
-        <v>6382811</v>
+        <v>6382802</v>
       </c>
       <c r="S77" t="n">
         <v>8</v>
@@ -9084,7 +9084,7 @@
         <v>126603970</v>
       </c>
       <c r="B78" t="n">
-        <v>98398</v>
+        <v>98473</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9192,10 +9192,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126603946</v>
+        <v>126603966</v>
       </c>
       <c r="B79" t="n">
-        <v>98279</v>
+        <v>98414</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9203,21 +9203,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -9236,13 +9236,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>720880</v>
+        <v>720805</v>
       </c>
       <c r="R79" t="n">
-        <v>6382875</v>
+        <v>6382844</v>
       </c>
       <c r="S79" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9303,10 +9303,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126603966</v>
+        <v>126603946</v>
       </c>
       <c r="B80" t="n">
-        <v>98339</v>
+        <v>98354</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9314,21 +9314,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9347,13 +9347,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>720805</v>
+        <v>720880</v>
       </c>
       <c r="R80" t="n">
-        <v>6382844</v>
+        <v>6382875</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9414,10 +9414,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126603985</v>
+        <v>126603967</v>
       </c>
       <c r="B81" t="n">
-        <v>98279</v>
+        <v>98354</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9458,10 +9458,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>720870</v>
+        <v>720805</v>
       </c>
       <c r="R81" t="n">
-        <v>6382807</v>
+        <v>6382844</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9525,10 +9525,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126603967</v>
+        <v>126603985</v>
       </c>
       <c r="B82" t="n">
-        <v>98279</v>
+        <v>98354</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9569,10 +9569,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>720805</v>
+        <v>720870</v>
       </c>
       <c r="R82" t="n">
-        <v>6382844</v>
+        <v>6382807</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9636,57 +9636,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126603963</v>
+        <v>126603986</v>
       </c>
       <c r="B83" t="n">
-        <v>98279</v>
+        <v>109260</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>720785</v>
+        <v>720880</v>
       </c>
       <c r="R83" t="n">
-        <v>6382836</v>
+        <v>6382825</v>
       </c>
       <c r="S83" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9750,7 +9741,7 @@
         <v>126603951</v>
       </c>
       <c r="B84" t="n">
-        <v>98383</v>
+        <v>98458</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9858,10 +9849,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126603986</v>
+        <v>126603981</v>
       </c>
       <c r="B85" t="n">
-        <v>109185</v>
+        <v>107318</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9869,37 +9860,46 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>720880</v>
+        <v>720861</v>
       </c>
       <c r="R85" t="n">
-        <v>6382825</v>
+        <v>6382807</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9960,37 +9960,37 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126603981</v>
+        <v>126603963</v>
       </c>
       <c r="B86" t="n">
-        <v>107243</v>
+        <v>98354</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220079</v>
+        <v>223591</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10004,13 +10004,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>720861</v>
+        <v>720785</v>
       </c>
       <c r="R86" t="n">
-        <v>6382807</v>
+        <v>6382836</v>
       </c>
       <c r="S86" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10071,10 +10071,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126603953</v>
+        <v>126603962</v>
       </c>
       <c r="B87" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10115,13 +10115,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>720769</v>
+        <v>720785</v>
       </c>
       <c r="R87" t="n">
-        <v>6382920</v>
+        <v>6382836</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10182,10 +10182,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126603943</v>
+        <v>126603992</v>
       </c>
       <c r="B88" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10226,13 +10226,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>720887</v>
+        <v>720893</v>
       </c>
       <c r="R88" t="n">
-        <v>6382881</v>
+        <v>6382817</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10293,10 +10293,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126603962</v>
+        <v>126603953</v>
       </c>
       <c r="B89" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10337,13 +10337,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>720785</v>
+        <v>720769</v>
       </c>
       <c r="R89" t="n">
-        <v>6382836</v>
+        <v>6382920</v>
       </c>
       <c r="S89" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10404,10 +10404,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126603992</v>
+        <v>126603943</v>
       </c>
       <c r="B90" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10448,13 +10448,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>720893</v>
+        <v>720887</v>
       </c>
       <c r="R90" t="n">
-        <v>6382817</v>
+        <v>6382881</v>
       </c>
       <c r="S90" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>126603994</v>
       </c>
       <c r="B91" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>126603984</v>
       </c>
       <c r="B92" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10737,42 +10737,52 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126603954</v>
+        <v>126603903</v>
       </c>
       <c r="B93" t="n">
-        <v>98279</v>
+        <v>43228</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>223591</v>
+        <v>101242</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10781,10 +10791,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>720769</v>
+        <v>720852</v>
       </c>
       <c r="R93" t="n">
-        <v>6382920</v>
+        <v>6382893</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10819,6 +10829,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Lundstarr ses ej i området.</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
@@ -10830,7 +10845,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Tallskog, fuktig glänta.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -10851,7 +10866,7 @@
         <v>126603961</v>
       </c>
       <c r="B94" t="n">
-        <v>98336</v>
+        <v>98411</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10959,52 +10974,42 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126603903</v>
+        <v>126603983</v>
       </c>
       <c r="B95" t="n">
-        <v>43228</v>
+        <v>98354</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>101242</v>
+        <v>223591</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -11013,13 +11018,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>720852</v>
+        <v>720861</v>
       </c>
       <c r="R95" t="n">
-        <v>6382893</v>
+        <v>6382807</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11051,11 +11056,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Lundstarr ses ej i området.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>Tallskog, fuktig glänta.</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11085,10 +11085,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126603983</v>
+        <v>126603954</v>
       </c>
       <c r="B96" t="n">
-        <v>98279</v>
+        <v>98354</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11129,13 +11129,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>720861</v>
+        <v>720769</v>
       </c>
       <c r="R96" t="n">
-        <v>6382807</v>
+        <v>6382920</v>
       </c>
       <c r="S96" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>126603996</v>
       </c>
       <c r="B97" t="n">
-        <v>110452</v>
+        <v>110527</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126603904</v>
+        <v>126603902</v>
       </c>
       <c r="B98" t="n">
         <v>43228</v>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11352,13 +11352,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>720778</v>
+        <v>720950</v>
       </c>
       <c r="R98" t="n">
-        <v>6382885</v>
+        <v>6382850</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Lundstarr ses ej i området.</t>
+          <t>Även väddnatfjäril ev. Lundstarr sågs ej. Vid stor sten i NO-hörn av våtmark.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk; solbelyst glänta..</t>
+          <t>Tallskog, kant av fuktig glänta.</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11424,10 +11424,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126603998</v>
+        <v>126603904</v>
       </c>
       <c r="B99" t="n">
-        <v>107243</v>
+        <v>43228</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11435,31 +11435,41 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220079</v>
+        <v>101242</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11468,13 +11478,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>720879</v>
+        <v>720778</v>
       </c>
       <c r="R99" t="n">
-        <v>6382802</v>
+        <v>6382885</v>
       </c>
       <c r="S99" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11506,6 +11516,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Lundstarr ses ej i området.</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -11517,7 +11532,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkbarrskog, frisk; solbelyst glänta..</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -11535,10 +11550,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126603902</v>
+        <v>126603998</v>
       </c>
       <c r="B100" t="n">
-        <v>43228</v>
+        <v>107318</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11546,41 +11561,31 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>101242</v>
+        <v>220079</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11589,13 +11594,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>720950</v>
+        <v>720879</v>
       </c>
       <c r="R100" t="n">
-        <v>6382850</v>
+        <v>6382802</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11627,11 +11632,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Även väddnatfjäril ev. Lundstarr sågs ej. Vid stor sten i NO-hörn av våtmark.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Tallskog, kant av fuktig glänta.</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11664,7 +11664,7 @@
         <v>126603938</v>
       </c>
       <c r="B101" t="n">
-        <v>98279</v>
+        <v>98354</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>126603969</v>
       </c>
       <c r="B102" t="n">
-        <v>98279</v>
+        <v>98354</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>126603977</v>
       </c>
       <c r="B103" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>126604000</v>
       </c>
       <c r="B104" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>126603980</v>
       </c>
       <c r="B105" t="n">
-        <v>98383</v>
+        <v>98458</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>126603948</v>
       </c>
       <c r="B106" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12309,10 +12309,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126603989</v>
+        <v>126603991</v>
       </c>
       <c r="B107" t="n">
-        <v>98279</v>
+        <v>98354</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -12353,13 +12353,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>720880</v>
+        <v>720893</v>
       </c>
       <c r="R107" t="n">
-        <v>6382825</v>
+        <v>6382817</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12420,10 +12420,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126603991</v>
+        <v>126603989</v>
       </c>
       <c r="B108" t="n">
-        <v>98279</v>
+        <v>98354</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -12464,13 +12464,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>720893</v>
+        <v>720880</v>
       </c>
       <c r="R108" t="n">
-        <v>6382817</v>
+        <v>6382825</v>
       </c>
       <c r="S108" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>126603982</v>
       </c>
       <c r="B109" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12642,54 +12642,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126603944</v>
+        <v>126603949</v>
       </c>
       <c r="B110" t="n">
-        <v>98279</v>
+        <v>109260</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>720887</v>
+        <v>720829</v>
       </c>
       <c r="R110" t="n">
-        <v>6382881</v>
+        <v>6382943</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12756,7 +12747,7 @@
         <v>126603965</v>
       </c>
       <c r="B111" t="n">
-        <v>98336</v>
+        <v>98411</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12864,45 +12855,54 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126603949</v>
+        <v>126603944</v>
       </c>
       <c r="B112" t="n">
-        <v>109185</v>
+        <v>98354</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>720829</v>
+        <v>720887</v>
       </c>
       <c r="R112" t="n">
-        <v>6382943</v>
+        <v>6382881</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12969,7 +12969,7 @@
         <v>126603976</v>
       </c>
       <c r="B113" t="n">
-        <v>98336</v>
+        <v>98411</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>126603968</v>
       </c>
       <c r="B114" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>126603988</v>
       </c>
       <c r="B115" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13294,48 +13294,57 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126603937</v>
+        <v>126603974</v>
       </c>
       <c r="B116" t="n">
-        <v>105294</v>
+        <v>98473</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221137</v>
+        <v>219875</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>720921</v>
+        <v>720861</v>
       </c>
       <c r="R116" t="n">
-        <v>6382848</v>
+        <v>6382781</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13367,11 +13376,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -13383,7 +13387,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr i skog.</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -13404,7 +13408,7 @@
         <v>126603955</v>
       </c>
       <c r="B117" t="n">
-        <v>98398</v>
+        <v>98473</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13512,45 +13516,54 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126603958</v>
+        <v>126603978</v>
       </c>
       <c r="B118" t="n">
-        <v>105956</v>
+        <v>98473</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220785</v>
+        <v>219875</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>720779</v>
+        <v>720852</v>
       </c>
       <c r="R118" t="n">
-        <v>6382857</v>
+        <v>6382793</v>
       </c>
       <c r="S118" t="n">
         <v>3</v>
@@ -13614,57 +13627,48 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126603978</v>
+        <v>126603937</v>
       </c>
       <c r="B119" t="n">
-        <v>98398</v>
+        <v>105369</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219875</v>
+        <v>221137</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>720852</v>
+        <v>720921</v>
       </c>
       <c r="R119" t="n">
-        <v>6382793</v>
+        <v>6382848</v>
       </c>
       <c r="S119" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13696,6 +13700,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -13707,7 +13716,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkgräsmyr i skog.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -13725,57 +13734,48 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126603974</v>
+        <v>126603958</v>
       </c>
       <c r="B120" t="n">
-        <v>98398</v>
+        <v>106031</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219875</v>
+        <v>220785</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>720861</v>
+        <v>720779</v>
       </c>
       <c r="R120" t="n">
-        <v>6382781</v>
+        <v>6382857</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>126603973</v>
       </c>
       <c r="B121" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>126603950</v>
       </c>
       <c r="B122" t="n">
-        <v>98398</v>
+        <v>98473</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -6779,7 +6779,7 @@
         <v>126603993</v>
       </c>
       <c r="B57" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>126603939</v>
       </c>
       <c r="B58" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>126603997</v>
       </c>
       <c r="B59" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>126603960</v>
       </c>
       <c r="B60" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7216,10 +7216,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126604006</v>
+        <v>126603959</v>
       </c>
       <c r="B61" t="n">
-        <v>98472</v>
+        <v>98420</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7227,26 +7227,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>223621</v>
+        <v>219798</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7260,13 +7260,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>720893</v>
+        <v>720779</v>
       </c>
       <c r="R61" t="n">
-        <v>6382800</v>
+        <v>6382857</v>
       </c>
       <c r="S61" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7327,10 +7327,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126603959</v>
+        <v>126604006</v>
       </c>
       <c r="B62" t="n">
-        <v>98414</v>
+        <v>98478</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7338,26 +7338,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219798</v>
+        <v>223621</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7371,13 +7371,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>720779</v>
+        <v>720893</v>
       </c>
       <c r="R62" t="n">
-        <v>6382857</v>
+        <v>6382800</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7438,10 +7438,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126603947</v>
+        <v>126603945</v>
       </c>
       <c r="B63" t="n">
-        <v>98354</v>
+        <v>98420</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7449,26 +7449,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7482,13 +7482,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>720833</v>
+        <v>720880</v>
       </c>
       <c r="R63" t="n">
-        <v>6382931</v>
+        <v>6382875</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>126603964</v>
       </c>
       <c r="B64" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7660,10 +7660,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126603945</v>
+        <v>126603947</v>
       </c>
       <c r="B65" t="n">
-        <v>98414</v>
+        <v>98360</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7671,26 +7671,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7704,13 +7704,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>720880</v>
+        <v>720833</v>
       </c>
       <c r="R65" t="n">
-        <v>6382875</v>
+        <v>6382931</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>126604001</v>
       </c>
       <c r="B66" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7873,10 +7873,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126603956</v>
+        <v>126603987</v>
       </c>
       <c r="B67" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7917,13 +7917,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>720778</v>
+        <v>720880</v>
       </c>
       <c r="R67" t="n">
-        <v>6382885</v>
+        <v>6382825</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk; solbelyst glänta..</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7984,10 +7984,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126603987</v>
+        <v>126603956</v>
       </c>
       <c r="B68" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>720880</v>
+        <v>720778</v>
       </c>
       <c r="R68" t="n">
-        <v>6382825</v>
+        <v>6382885</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkbarrskog, frisk; solbelyst glänta..</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8098,7 +8098,7 @@
         <v>126603990</v>
       </c>
       <c r="B69" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>126603952</v>
       </c>
       <c r="B70" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>126603957</v>
       </c>
       <c r="B71" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>126604004</v>
       </c>
       <c r="B72" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>126603971</v>
       </c>
       <c r="B73" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>126603972</v>
       </c>
       <c r="B74" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>126603975</v>
       </c>
       <c r="B75" t="n">
-        <v>98458</v>
+        <v>98464</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8877,32 +8877,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126603995</v>
+        <v>126603999</v>
       </c>
       <c r="B76" t="n">
-        <v>98354</v>
+        <v>109266</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8912,10 +8912,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>720877</v>
+        <v>720879</v>
       </c>
       <c r="R76" t="n">
-        <v>6382811</v>
+        <v>6382802</v>
       </c>
       <c r="S76" t="n">
         <v>8</v>
@@ -8979,32 +8979,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126603999</v>
+        <v>126603995</v>
       </c>
       <c r="B77" t="n">
-        <v>109260</v>
+        <v>98360</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9014,10 +9014,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>720879</v>
+        <v>720877</v>
       </c>
       <c r="R77" t="n">
-        <v>6382802</v>
+        <v>6382811</v>
       </c>
       <c r="S77" t="n">
         <v>8</v>
@@ -9084,7 +9084,7 @@
         <v>126603970</v>
       </c>
       <c r="B78" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>126603966</v>
       </c>
       <c r="B79" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>126603946</v>
       </c>
       <c r="B80" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>126603967</v>
       </c>
       <c r="B81" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>126603985</v>
       </c>
       <c r="B82" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9636,45 +9636,54 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126603986</v>
+        <v>126603951</v>
       </c>
       <c r="B83" t="n">
-        <v>109260</v>
+        <v>98464</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>720880</v>
+        <v>720769</v>
       </c>
       <c r="R83" t="n">
-        <v>6382825</v>
+        <v>6382920</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9738,10 +9747,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126603951</v>
+        <v>126603963</v>
       </c>
       <c r="B84" t="n">
-        <v>98458</v>
+        <v>98360</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9749,26 +9758,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219862</v>
+        <v>223591</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9782,13 +9791,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>720769</v>
+        <v>720785</v>
       </c>
       <c r="R84" t="n">
-        <v>6382920</v>
+        <v>6382836</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9852,7 +9861,7 @@
         <v>126603981</v>
       </c>
       <c r="B85" t="n">
-        <v>107318</v>
+        <v>107324</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9960,57 +9969,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126603963</v>
+        <v>126603986</v>
       </c>
       <c r="B86" t="n">
-        <v>98354</v>
+        <v>109266</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>720785</v>
+        <v>720880</v>
       </c>
       <c r="R86" t="n">
-        <v>6382836</v>
+        <v>6382825</v>
       </c>
       <c r="S86" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10071,10 +10071,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126603962</v>
+        <v>126603943</v>
       </c>
       <c r="B87" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10115,13 +10115,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>720785</v>
+        <v>720887</v>
       </c>
       <c r="R87" t="n">
-        <v>6382836</v>
+        <v>6382881</v>
       </c>
       <c r="S87" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>126603992</v>
       </c>
       <c r="B88" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>126603953</v>
       </c>
       <c r="B89" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10404,10 +10404,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126603943</v>
+        <v>126603962</v>
       </c>
       <c r="B90" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10448,13 +10448,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>720887</v>
+        <v>720785</v>
       </c>
       <c r="R90" t="n">
-        <v>6382881</v>
+        <v>6382836</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>126603994</v>
       </c>
       <c r="B91" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>126603984</v>
       </c>
       <c r="B92" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10863,10 +10863,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126603961</v>
+        <v>126603983</v>
       </c>
       <c r="B94" t="n">
-        <v>98411</v>
+        <v>98360</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10874,26 +10874,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219797</v>
+        <v>223591</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -10907,13 +10907,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>720785</v>
+        <v>720861</v>
       </c>
       <c r="R94" t="n">
-        <v>6382836</v>
+        <v>6382807</v>
       </c>
       <c r="S94" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126603983</v>
+        <v>126603954</v>
       </c>
       <c r="B95" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11018,13 +11018,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>720861</v>
+        <v>720769</v>
       </c>
       <c r="R95" t="n">
-        <v>6382807</v>
+        <v>6382920</v>
       </c>
       <c r="S95" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11085,10 +11085,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126603954</v>
+        <v>126603961</v>
       </c>
       <c r="B96" t="n">
-        <v>98354</v>
+        <v>98417</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11096,26 +11096,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>223591</v>
+        <v>219797</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11129,13 +11129,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>720769</v>
+        <v>720785</v>
       </c>
       <c r="R96" t="n">
-        <v>6382920</v>
+        <v>6382836</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>126603996</v>
       </c>
       <c r="B97" t="n">
-        <v>110527</v>
+        <v>110533</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11550,37 +11550,37 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126603998</v>
+        <v>126603938</v>
       </c>
       <c r="B100" t="n">
-        <v>107318</v>
+        <v>98360</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220079</v>
+        <v>223591</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -11594,13 +11594,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>720879</v>
+        <v>720921</v>
       </c>
       <c r="R100" t="n">
-        <v>6382802</v>
+        <v>6382848</v>
       </c>
       <c r="S100" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkgräsmyr i skog.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11661,37 +11661,37 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126603938</v>
+        <v>126603998</v>
       </c>
       <c r="B101" t="n">
-        <v>98354</v>
+        <v>107324</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>223591</v>
+        <v>220079</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -11705,13 +11705,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>720921</v>
+        <v>720879</v>
       </c>
       <c r="R101" t="n">
-        <v>6382848</v>
+        <v>6382802</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr i skog.</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11775,7 +11775,7 @@
         <v>126603969</v>
       </c>
       <c r="B102" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11883,48 +11883,57 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126603977</v>
+        <v>126604000</v>
       </c>
       <c r="B103" t="n">
-        <v>109260</v>
+        <v>98420</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>720852</v>
+        <v>720879</v>
       </c>
       <c r="R103" t="n">
-        <v>6382793</v>
+        <v>6382802</v>
       </c>
       <c r="S103" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11985,10 +11994,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126604000</v>
+        <v>126603980</v>
       </c>
       <c r="B104" t="n">
-        <v>98414</v>
+        <v>98464</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11996,26 +12005,26 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12029,13 +12038,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>720879</v>
+        <v>720861</v>
       </c>
       <c r="R104" t="n">
-        <v>6382802</v>
+        <v>6382807</v>
       </c>
       <c r="S104" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12096,54 +12105,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126603980</v>
+        <v>126603977</v>
       </c>
       <c r="B105" t="n">
-        <v>98458</v>
+        <v>109266</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>720861</v>
+        <v>720852</v>
       </c>
       <c r="R105" t="n">
-        <v>6382807</v>
+        <v>6382793</v>
       </c>
       <c r="S105" t="n">
         <v>3</v>
@@ -12210,7 +12210,7 @@
         <v>126603948</v>
       </c>
       <c r="B106" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12309,10 +12309,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126603991</v>
+        <v>126603982</v>
       </c>
       <c r="B107" t="n">
-        <v>98354</v>
+        <v>98420</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12320,26 +12320,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -12353,13 +12353,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>720893</v>
+        <v>720861</v>
       </c>
       <c r="R107" t="n">
-        <v>6382817</v>
+        <v>6382807</v>
       </c>
       <c r="S107" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12420,10 +12420,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126603989</v>
+        <v>126603991</v>
       </c>
       <c r="B108" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -12464,13 +12464,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>720880</v>
+        <v>720893</v>
       </c>
       <c r="R108" t="n">
-        <v>6382825</v>
+        <v>6382817</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12531,10 +12531,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126603982</v>
+        <v>126603989</v>
       </c>
       <c r="B109" t="n">
-        <v>98414</v>
+        <v>98360</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12542,21 +12542,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -12575,13 +12575,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>720861</v>
+        <v>720880</v>
       </c>
       <c r="R109" t="n">
-        <v>6382807</v>
+        <v>6382825</v>
       </c>
       <c r="S109" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12642,45 +12642,54 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126603949</v>
+        <v>126603965</v>
       </c>
       <c r="B110" t="n">
-        <v>109260</v>
+        <v>98417</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>720829</v>
+        <v>720805</v>
       </c>
       <c r="R110" t="n">
-        <v>6382943</v>
+        <v>6382844</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12744,54 +12753,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126603965</v>
+        <v>126603949</v>
       </c>
       <c r="B111" t="n">
-        <v>98411</v>
+        <v>109266</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>720805</v>
+        <v>720829</v>
       </c>
       <c r="R111" t="n">
-        <v>6382844</v>
+        <v>6382943</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12858,7 +12858,7 @@
         <v>126603944</v>
       </c>
       <c r="B112" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>126603976</v>
       </c>
       <c r="B113" t="n">
-        <v>98411</v>
+        <v>98417</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>126603968</v>
       </c>
       <c r="B114" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>126603988</v>
       </c>
       <c r="B115" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>126603974</v>
       </c>
       <c r="B116" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>126603955</v>
       </c>
       <c r="B117" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>126603978</v>
       </c>
       <c r="B118" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13627,27 +13627,27 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126603937</v>
+        <v>126603958</v>
       </c>
       <c r="B119" t="n">
-        <v>105369</v>
+        <v>106037</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>221137</v>
+        <v>220785</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -13662,13 +13662,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>720921</v>
+        <v>720779</v>
       </c>
       <c r="R119" t="n">
-        <v>6382848</v>
+        <v>6382857</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13700,11 +13700,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -13716,7 +13711,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr i skog.</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -13734,27 +13729,27 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126603958</v>
+        <v>126603937</v>
       </c>
       <c r="B120" t="n">
-        <v>106031</v>
+        <v>105375</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220785</v>
+        <v>221137</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -13769,13 +13764,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>720779</v>
+        <v>720921</v>
       </c>
       <c r="R120" t="n">
-        <v>6382857</v>
+        <v>6382848</v>
       </c>
       <c r="S120" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13807,6 +13802,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -13818,7 +13818,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkgräsmyr i skog.</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -13836,48 +13836,57 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126603973</v>
+        <v>126603950</v>
       </c>
       <c r="B121" t="n">
-        <v>109260</v>
+        <v>98479</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220299</v>
+        <v>219875</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>720861</v>
+        <v>720829</v>
       </c>
       <c r="R121" t="n">
-        <v>6382781</v>
+        <v>6382943</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13938,57 +13947,48 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126603950</v>
+        <v>126603973</v>
       </c>
       <c r="B122" t="n">
-        <v>98473</v>
+        <v>109266</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219875</v>
+        <v>220299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>720829</v>
+        <v>720861</v>
       </c>
       <c r="R122" t="n">
-        <v>6382943</v>
+        <v>6382781</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -7438,10 +7438,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126603945</v>
+        <v>126603964</v>
       </c>
       <c r="B63" t="n">
-        <v>98420</v>
+        <v>98465</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7449,26 +7449,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7482,13 +7482,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>720880</v>
+        <v>720805</v>
       </c>
       <c r="R63" t="n">
-        <v>6382875</v>
+        <v>6382844</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7549,10 +7549,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126603964</v>
+        <v>126603945</v>
       </c>
       <c r="B64" t="n">
-        <v>98465</v>
+        <v>98420</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7560,26 +7560,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7593,13 +7593,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>720805</v>
+        <v>720880</v>
       </c>
       <c r="R64" t="n">
-        <v>6382844</v>
+        <v>6382875</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126603987</v>
+        <v>126603956</v>
       </c>
       <c r="B67" t="n">
         <v>98465</v>
@@ -7903,7 +7903,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7917,13 +7917,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>720880</v>
+        <v>720778</v>
       </c>
       <c r="R67" t="n">
-        <v>6382825</v>
+        <v>6382885</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkbarrskog, frisk; solbelyst glänta..</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7984,7 +7984,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126603956</v>
+        <v>126603987</v>
       </c>
       <c r="B68" t="n">
         <v>98465</v>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>720778</v>
+        <v>720880</v>
       </c>
       <c r="R68" t="n">
-        <v>6382885</v>
+        <v>6382825</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk; solbelyst glänta..</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9636,54 +9636,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126603951</v>
+        <v>126603986</v>
       </c>
       <c r="B83" t="n">
-        <v>98464</v>
+        <v>109266</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>720769</v>
+        <v>720880</v>
       </c>
       <c r="R83" t="n">
-        <v>6382920</v>
+        <v>6382825</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9747,10 +9738,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126603963</v>
+        <v>126603951</v>
       </c>
       <c r="B84" t="n">
-        <v>98360</v>
+        <v>98464</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9758,26 +9749,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>223591</v>
+        <v>219862</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9791,13 +9782,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>720785</v>
+        <v>720769</v>
       </c>
       <c r="R84" t="n">
-        <v>6382836</v>
+        <v>6382920</v>
       </c>
       <c r="S84" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9969,48 +9960,57 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126603986</v>
+        <v>126603963</v>
       </c>
       <c r="B86" t="n">
-        <v>109266</v>
+        <v>98360</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>720880</v>
+        <v>720785</v>
       </c>
       <c r="R86" t="n">
-        <v>6382825</v>
+        <v>6382836</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126603943</v>
+        <v>126603962</v>
       </c>
       <c r="B87" t="n">
         <v>98420</v>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10115,13 +10115,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>720887</v>
+        <v>720785</v>
       </c>
       <c r="R87" t="n">
-        <v>6382881</v>
+        <v>6382836</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126603962</v>
+        <v>126603943</v>
       </c>
       <c r="B90" t="n">
         <v>98420</v>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10448,13 +10448,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>720785</v>
+        <v>720887</v>
       </c>
       <c r="R90" t="n">
-        <v>6382836</v>
+        <v>6382881</v>
       </c>
       <c r="S90" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11298,10 +11298,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126603902</v>
+        <v>126603998</v>
       </c>
       <c r="B98" t="n">
-        <v>43228</v>
+        <v>107324</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11309,41 +11309,31 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>101242</v>
+        <v>220079</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -11352,13 +11342,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>720950</v>
+        <v>720879</v>
       </c>
       <c r="R98" t="n">
-        <v>6382850</v>
+        <v>6382802</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11390,11 +11380,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Även väddnatfjäril ev. Lundstarr sågs ej. Vid stor sten i NO-hörn av våtmark.</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -11406,7 +11391,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>Tallskog, kant av fuktig glänta.</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11424,32 +11409,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126603904</v>
+        <v>126603938</v>
       </c>
       <c r="B99" t="n">
-        <v>43228</v>
+        <v>98360</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>101242</v>
+        <v>223591</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -11459,17 +11444,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11478,13 +11453,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>720778</v>
+        <v>720921</v>
       </c>
       <c r="R99" t="n">
-        <v>6382885</v>
+        <v>6382848</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11516,11 +11491,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Lundstarr ses ej i området.</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -11532,7 +11502,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk; solbelyst glänta..</t>
+          <t>Kalkgräsmyr i skog.</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -11550,42 +11520,52 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126603938</v>
+        <v>126603902</v>
       </c>
       <c r="B100" t="n">
-        <v>98360</v>
+        <v>43228</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>223591</v>
+        <v>101242</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11594,10 +11574,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>720921</v>
+        <v>720950</v>
       </c>
       <c r="R100" t="n">
-        <v>6382848</v>
+        <v>6382850</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11632,6 +11612,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Även väddnatfjäril ev. Lundstarr sågs ej. Vid stor sten i NO-hörn av våtmark.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11643,7 +11628,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr i skog.</t>
+          <t>Tallskog, kant av fuktig glänta.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11661,10 +11646,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126603998</v>
+        <v>126603904</v>
       </c>
       <c r="B101" t="n">
-        <v>107324</v>
+        <v>43228</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11672,31 +11657,41 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220079</v>
+        <v>101242</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -11705,13 +11700,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>720879</v>
+        <v>720778</v>
       </c>
       <c r="R101" t="n">
-        <v>6382802</v>
+        <v>6382885</v>
       </c>
       <c r="S101" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11743,6 +11738,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Lundstarr ses ej i området.</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkbarrskog, frisk; solbelyst glänta..</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11883,57 +11883,48 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126604000</v>
+        <v>126603977</v>
       </c>
       <c r="B103" t="n">
-        <v>98420</v>
+        <v>109266</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>720879</v>
+        <v>720852</v>
       </c>
       <c r="R103" t="n">
-        <v>6382802</v>
+        <v>6382793</v>
       </c>
       <c r="S103" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11994,10 +11985,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126603980</v>
+        <v>126604000</v>
       </c>
       <c r="B104" t="n">
-        <v>98464</v>
+        <v>98420</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12005,26 +11996,26 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12038,13 +12029,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>720861</v>
+        <v>720879</v>
       </c>
       <c r="R104" t="n">
-        <v>6382807</v>
+        <v>6382802</v>
       </c>
       <c r="S104" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12105,45 +12096,54 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126603977</v>
+        <v>126603980</v>
       </c>
       <c r="B105" t="n">
-        <v>109266</v>
+        <v>98464</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>720852</v>
+        <v>720861</v>
       </c>
       <c r="R105" t="n">
-        <v>6382793</v>
+        <v>6382807</v>
       </c>
       <c r="S105" t="n">
         <v>3</v>
@@ -12642,10 +12642,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126603965</v>
+        <v>126603944</v>
       </c>
       <c r="B110" t="n">
-        <v>98417</v>
+        <v>98360</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12653,26 +12653,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219797</v>
+        <v>223591</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -12686,10 +12686,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>720805</v>
+        <v>720887</v>
       </c>
       <c r="R110" t="n">
-        <v>6382844</v>
+        <v>6382881</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12855,10 +12855,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126603944</v>
+        <v>126603965</v>
       </c>
       <c r="B112" t="n">
-        <v>98360</v>
+        <v>98417</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12866,26 +12866,26 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>223591</v>
+        <v>219797</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -12899,10 +12899,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>720887</v>
+        <v>720805</v>
       </c>
       <c r="R112" t="n">
-        <v>6382881</v>
+        <v>6382844</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13627,27 +13627,27 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126603958</v>
+        <v>126603937</v>
       </c>
       <c r="B119" t="n">
-        <v>106037</v>
+        <v>105375</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220785</v>
+        <v>221137</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -13662,13 +13662,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>720779</v>
+        <v>720921</v>
       </c>
       <c r="R119" t="n">
-        <v>6382857</v>
+        <v>6382848</v>
       </c>
       <c r="S119" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13700,6 +13700,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -13711,7 +13716,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkgräsmyr i skog.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -13729,27 +13734,27 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126603937</v>
+        <v>126603958</v>
       </c>
       <c r="B120" t="n">
-        <v>105375</v>
+        <v>106037</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221137</v>
+        <v>220785</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -13764,13 +13769,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>720921</v>
+        <v>720779</v>
       </c>
       <c r="R120" t="n">
-        <v>6382848</v>
+        <v>6382857</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13802,11 +13807,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -13818,7 +13818,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr i skog.</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -13836,57 +13836,48 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126603950</v>
+        <v>126603973</v>
       </c>
       <c r="B121" t="n">
-        <v>98479</v>
+        <v>109266</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>219875</v>
+        <v>220299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>720829</v>
+        <v>720861</v>
       </c>
       <c r="R121" t="n">
-        <v>6382943</v>
+        <v>6382781</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13947,48 +13938,57 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126603973</v>
+        <v>126603950</v>
       </c>
       <c r="B122" t="n">
-        <v>109266</v>
+        <v>98479</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220299</v>
+        <v>219875</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>720861</v>
+        <v>720829</v>
       </c>
       <c r="R122" t="n">
-        <v>6382781</v>
+        <v>6382943</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -8979,10 +8979,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126603995</v>
+        <v>126603970</v>
       </c>
       <c r="B77" t="n">
-        <v>98360</v>
+        <v>98479</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8990,37 +8990,46 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>223591</v>
+        <v>219875</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>720877</v>
+        <v>720808</v>
       </c>
       <c r="R77" t="n">
-        <v>6382811</v>
+        <v>6382832</v>
       </c>
       <c r="S77" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9081,10 +9090,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126603970</v>
+        <v>126603995</v>
       </c>
       <c r="B78" t="n">
-        <v>98479</v>
+        <v>98360</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9092,46 +9101,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219875</v>
+        <v>223591</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gothem Suderbys 1:11 (5), Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>720808</v>
+        <v>720877</v>
       </c>
       <c r="R78" t="n">
-        <v>6382832</v>
+        <v>6382811</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10863,10 +10863,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126603983</v>
+        <v>126603961</v>
       </c>
       <c r="B94" t="n">
-        <v>98360</v>
+        <v>98417</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10874,26 +10874,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>223591</v>
+        <v>219797</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -10907,13 +10907,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>720861</v>
+        <v>720785</v>
       </c>
       <c r="R94" t="n">
-        <v>6382807</v>
+        <v>6382836</v>
       </c>
       <c r="S94" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126603954</v>
+        <v>126603983</v>
       </c>
       <c r="B95" t="n">
         <v>98360</v>
@@ -11004,7 +11004,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11018,13 +11018,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>720769</v>
+        <v>720861</v>
       </c>
       <c r="R95" t="n">
-        <v>6382920</v>
+        <v>6382807</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11085,10 +11085,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126603961</v>
+        <v>126603954</v>
       </c>
       <c r="B96" t="n">
-        <v>98417</v>
+        <v>98360</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11096,26 +11096,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219797</v>
+        <v>223591</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11129,13 +11129,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>720785</v>
+        <v>720769</v>
       </c>
       <c r="R96" t="n">
-        <v>6382836</v>
+        <v>6382920</v>
       </c>
       <c r="S96" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11298,10 +11298,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126603998</v>
+        <v>126603902</v>
       </c>
       <c r="B98" t="n">
-        <v>107324</v>
+        <v>43228</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11309,31 +11309,41 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220079</v>
+        <v>101242</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -11342,13 +11352,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>720879</v>
+        <v>720950</v>
       </c>
       <c r="R98" t="n">
-        <v>6382802</v>
+        <v>6382850</v>
       </c>
       <c r="S98" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11380,6 +11390,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Även väddnatfjäril ev. Lundstarr sågs ej. Vid stor sten i NO-hörn av våtmark.</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -11391,7 +11406,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Tallskog, kant av fuktig glänta.</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11409,32 +11424,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126603938</v>
+        <v>126603904</v>
       </c>
       <c r="B99" t="n">
-        <v>98360</v>
+        <v>43228</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>223591</v>
+        <v>101242</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -11444,7 +11459,17 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11453,13 +11478,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>720921</v>
+        <v>720778</v>
       </c>
       <c r="R99" t="n">
-        <v>6382848</v>
+        <v>6382885</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11491,6 +11516,11 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Lundstarr ses ej i området.</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -11502,7 +11532,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr i skog.</t>
+          <t>Kalkbarrskog, frisk; solbelyst glänta..</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -11520,10 +11550,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126603902</v>
+        <v>126603998</v>
       </c>
       <c r="B100" t="n">
-        <v>43228</v>
+        <v>107324</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11531,41 +11561,31 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>101242</v>
+        <v>220079</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11574,13 +11594,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>720950</v>
+        <v>720879</v>
       </c>
       <c r="R100" t="n">
-        <v>6382850</v>
+        <v>6382802</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11612,11 +11632,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Även väddnatfjäril ev. Lundstarr sågs ej. Vid stor sten i NO-hörn av våtmark.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11628,7 +11643,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Tallskog, kant av fuktig glänta.</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11646,32 +11661,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126603904</v>
+        <v>126603938</v>
       </c>
       <c r="B101" t="n">
-        <v>43228</v>
+        <v>98360</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>101242</v>
+        <v>223591</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -11681,17 +11696,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -11700,13 +11705,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>720778</v>
+        <v>720921</v>
       </c>
       <c r="R101" t="n">
-        <v>6382885</v>
+        <v>6382848</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11738,11 +11743,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Lundstarr ses ej i området.</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk; solbelyst glänta..</t>
+          <t>Kalkgräsmyr i skog.</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY122"/>
+  <dimension ref="A1:AY168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14047,6 +14047,5072 @@
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>128362631</v>
+      </c>
+      <c r="B123" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>720861</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6382950</v>
+      </c>
+      <c r="S123" t="n">
+        <v>3</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>128362625</v>
+      </c>
+      <c r="B124" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>720854</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6382954</v>
+      </c>
+      <c r="S124" t="n">
+        <v>3</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>128362610</v>
+      </c>
+      <c r="B125" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>720820</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6382977</v>
+      </c>
+      <c r="S125" t="n">
+        <v>3</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>128362609</v>
+      </c>
+      <c r="B126" t="n">
+        <v>109300</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>720820</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6382977</v>
+      </c>
+      <c r="S126" t="n">
+        <v>3</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>128362595</v>
+      </c>
+      <c r="B127" t="n">
+        <v>109300</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>720898</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6382990</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>128362622</v>
+      </c>
+      <c r="B128" t="n">
+        <v>98495</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>720854</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6382954</v>
+      </c>
+      <c r="S128" t="n">
+        <v>3</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128362604</v>
+      </c>
+      <c r="B129" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>720857</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6382943</v>
+      </c>
+      <c r="S129" t="n">
+        <v>5</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128362638</v>
+      </c>
+      <c r="B130" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>720872</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6382941</v>
+      </c>
+      <c r="S130" t="n">
+        <v>5</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>128362627</v>
+      </c>
+      <c r="B131" t="n">
+        <v>98391</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>720870</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6382959</v>
+      </c>
+      <c r="S131" t="n">
+        <v>3</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>128362619</v>
+      </c>
+      <c r="B132" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>720859</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6382986</v>
+      </c>
+      <c r="S132" t="n">
+        <v>3</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>128362671</v>
+      </c>
+      <c r="B133" t="n">
+        <v>109300</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2044, Gtl</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>720992</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6382917</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>128362632</v>
+      </c>
+      <c r="B134" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>720866</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6382946</v>
+      </c>
+      <c r="S134" t="n">
+        <v>3</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>128362630</v>
+      </c>
+      <c r="B135" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>720870</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6382959</v>
+      </c>
+      <c r="S135" t="n">
+        <v>3</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>128362598</v>
+      </c>
+      <c r="B136" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>720886</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6382981</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>128362642</v>
+      </c>
+      <c r="B137" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>720889</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6382907</v>
+      </c>
+      <c r="S137" t="n">
+        <v>5</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Bild på svamp på koordinat.</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>128362640</v>
+      </c>
+      <c r="B138" t="n">
+        <v>109300</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>720889</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6382907</v>
+      </c>
+      <c r="S138" t="n">
+        <v>5</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>128362758</v>
+      </c>
+      <c r="B139" t="n">
+        <v>96075</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>720904</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6382940</v>
+      </c>
+      <c r="S139" t="n">
+        <v>6</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>128362639</v>
+      </c>
+      <c r="B140" t="n">
+        <v>106071</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>720889</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6382907</v>
+      </c>
+      <c r="S140" t="n">
+        <v>5</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>128362635</v>
+      </c>
+      <c r="B141" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>720875</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6382945</v>
+      </c>
+      <c r="S141" t="n">
+        <v>5</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>128362661</v>
+      </c>
+      <c r="B142" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>720921</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6382942</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>128362628</v>
+      </c>
+      <c r="B143" t="n">
+        <v>109300</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>720870</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6382959</v>
+      </c>
+      <c r="S143" t="n">
+        <v>3</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>128362615</v>
+      </c>
+      <c r="B144" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>720854</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6382995</v>
+      </c>
+      <c r="S144" t="n">
+        <v>3</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>128362656</v>
+      </c>
+      <c r="B145" t="n">
+        <v>109300</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>720904</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6382940</v>
+      </c>
+      <c r="S145" t="n">
+        <v>6</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>128362611</v>
+      </c>
+      <c r="B146" t="n">
+        <v>99224</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>720854</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6383001</v>
+      </c>
+      <c r="S146" t="n">
+        <v>3</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>128362612</v>
+      </c>
+      <c r="B147" t="n">
+        <v>98391</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2097, Gtl</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>720854</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6383001</v>
+      </c>
+      <c r="S147" t="n">
+        <v>3</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>128362597</v>
+      </c>
+      <c r="B148" t="n">
+        <v>109300</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>720886</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6382981</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>128362594</v>
+      </c>
+      <c r="B149" t="n">
+        <v>98391</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2112, Gtl</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>720898</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6382990</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>128362657</v>
+      </c>
+      <c r="B150" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>720904</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6382940</v>
+      </c>
+      <c r="S150" t="n">
+        <v>6</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>128362655</v>
+      </c>
+      <c r="B151" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>720897</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6382932</v>
+      </c>
+      <c r="S151" t="n">
+        <v>3</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>128362668</v>
+      </c>
+      <c r="B152" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>720954</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6382931</v>
+      </c>
+      <c r="S152" t="n">
+        <v>5</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>128362600</v>
+      </c>
+      <c r="B153" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>720876</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6382976</v>
+      </c>
+      <c r="S153" t="n">
+        <v>7</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>128362665</v>
+      </c>
+      <c r="B154" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>720967</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6382919</v>
+      </c>
+      <c r="S154" t="n">
+        <v>10</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>128362626</v>
+      </c>
+      <c r="B155" t="n">
+        <v>98495</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>720870</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6382959</v>
+      </c>
+      <c r="S155" t="n">
+        <v>3</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>128362652</v>
+      </c>
+      <c r="B156" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>720884</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6382924</v>
+      </c>
+      <c r="S156" t="n">
+        <v>7</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>128362596</v>
+      </c>
+      <c r="B157" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>720898</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6382990</v>
+      </c>
+      <c r="S157" t="n">
+        <v>10</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>128362607</v>
+      </c>
+      <c r="B158" t="n">
+        <v>107358</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2097, Gtl</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>720820</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6382977</v>
+      </c>
+      <c r="S158" t="n">
+        <v>3</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>128362621</v>
+      </c>
+      <c r="B159" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>720851</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6382971</v>
+      </c>
+      <c r="S159" t="n">
+        <v>3</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>128362659</v>
+      </c>
+      <c r="B160" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>720910</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6382934</v>
+      </c>
+      <c r="S160" t="n">
+        <v>7</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>128362623</v>
+      </c>
+      <c r="B161" t="n">
+        <v>98391</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>720854</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6382954</v>
+      </c>
+      <c r="S161" t="n">
+        <v>3</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>128362663</v>
+      </c>
+      <c r="B162" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>720937</v>
+      </c>
+      <c r="R162" t="n">
+        <v>6382946</v>
+      </c>
+      <c r="S162" t="n">
+        <v>5</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>128362670</v>
+      </c>
+      <c r="B163" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>720947</v>
+      </c>
+      <c r="R163" t="n">
+        <v>6382934</v>
+      </c>
+      <c r="S163" t="n">
+        <v>8</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>128362666</v>
+      </c>
+      <c r="B164" t="n">
+        <v>107358</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>720954</v>
+      </c>
+      <c r="R164" t="n">
+        <v>6382931</v>
+      </c>
+      <c r="S164" t="n">
+        <v>5</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>128362617</v>
+      </c>
+      <c r="B165" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>720861</v>
+      </c>
+      <c r="R165" t="n">
+        <v>6383000</v>
+      </c>
+      <c r="S165" t="n">
+        <v>5</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>128362672</v>
+      </c>
+      <c r="B166" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>720992</v>
+      </c>
+      <c r="R166" t="n">
+        <v>6382917</v>
+      </c>
+      <c r="S166" t="n">
+        <v>10</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>128362614</v>
+      </c>
+      <c r="B167" t="n">
+        <v>98451</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>720854</v>
+      </c>
+      <c r="R167" t="n">
+        <v>6383001</v>
+      </c>
+      <c r="S167" t="n">
+        <v>3</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>128362644</v>
+      </c>
+      <c r="B168" t="n">
+        <v>98495</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>720889</v>
+      </c>
+      <c r="R168" t="n">
+        <v>6382907</v>
+      </c>
+      <c r="S168" t="n">
+        <v>5</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -14049,10 +14049,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128362631</v>
+        <v>128362610</v>
       </c>
       <c r="B123" t="n">
-        <v>98451</v>
+        <v>98456</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -14093,10 +14093,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>720861</v>
+        <v>720820</v>
       </c>
       <c r="R123" t="n">
-        <v>6382950</v>
+        <v>6382977</v>
       </c>
       <c r="S123" t="n">
         <v>3</v>
@@ -14163,7 +14163,7 @@
         <v>128362625</v>
       </c>
       <c r="B124" t="n">
-        <v>98451</v>
+        <v>98456</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14271,10 +14271,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128362610</v>
+        <v>128362631</v>
       </c>
       <c r="B125" t="n">
-        <v>98451</v>
+        <v>98456</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14315,10 +14315,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>720820</v>
+        <v>720861</v>
       </c>
       <c r="R125" t="n">
-        <v>6382977</v>
+        <v>6382950</v>
       </c>
       <c r="S125" t="n">
         <v>3</v>
@@ -14385,7 +14385,7 @@
         <v>128362609</v>
       </c>
       <c r="B126" t="n">
-        <v>109300</v>
+        <v>109305</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14493,48 +14493,57 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128362595</v>
+        <v>128362604</v>
       </c>
       <c r="B127" t="n">
-        <v>109300</v>
+        <v>98456</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>720898</v>
+        <v>720857</v>
       </c>
       <c r="R127" t="n">
-        <v>6382990</v>
+        <v>6382943</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14595,10 +14604,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128362622</v>
+        <v>128362638</v>
       </c>
       <c r="B128" t="n">
-        <v>98495</v>
+        <v>98456</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14606,26 +14615,26 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14635,17 +14644,17 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>720854</v>
+        <v>720872</v>
       </c>
       <c r="R128" t="n">
-        <v>6382954</v>
+        <v>6382941</v>
       </c>
       <c r="S128" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14706,10 +14715,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128362604</v>
+        <v>128362622</v>
       </c>
       <c r="B129" t="n">
-        <v>98451</v>
+        <v>98500</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14717,26 +14726,26 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14746,17 +14755,17 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>720857</v>
+        <v>720854</v>
       </c>
       <c r="R129" t="n">
-        <v>6382943</v>
+        <v>6382954</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14817,57 +14826,48 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128362638</v>
+        <v>128362595</v>
       </c>
       <c r="B130" t="n">
-        <v>98451</v>
+        <v>109305</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>720872</v>
+        <v>720898</v>
       </c>
       <c r="R130" t="n">
-        <v>6382941</v>
+        <v>6382990</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>128362627</v>
       </c>
       <c r="B131" t="n">
-        <v>98391</v>
+        <v>98396</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>128362619</v>
       </c>
       <c r="B132" t="n">
-        <v>98451</v>
+        <v>98456</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>128362671</v>
       </c>
       <c r="B133" t="n">
-        <v>109300</v>
+        <v>109305</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15255,7 +15255,7 @@
         <v>128362632</v>
       </c>
       <c r="B134" t="n">
-        <v>98451</v>
+        <v>98456</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15363,10 +15363,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128362630</v>
+        <v>128362598</v>
       </c>
       <c r="B135" t="n">
-        <v>98451</v>
+        <v>98456</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15407,13 +15407,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>720870</v>
+        <v>720886</v>
       </c>
       <c r="R135" t="n">
-        <v>6382959</v>
+        <v>6382981</v>
       </c>
       <c r="S135" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15474,10 +15474,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128362598</v>
+        <v>128362630</v>
       </c>
       <c r="B136" t="n">
-        <v>98451</v>
+        <v>98456</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15518,13 +15518,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>720886</v>
+        <v>720870</v>
       </c>
       <c r="R136" t="n">
-        <v>6382981</v>
+        <v>6382959</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15585,10 +15585,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128362642</v>
+        <v>128362758</v>
       </c>
       <c r="B137" t="n">
-        <v>98451</v>
+        <v>96080</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15596,46 +15596,46 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>219798</v>
+        <v>2180</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>720889</v>
+        <v>720904</v>
       </c>
       <c r="R137" t="n">
-        <v>6382907</v>
+        <v>6382940</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15667,11 +15667,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Bild på svamp på koordinat.</t>
-        </is>
-      </c>
       <c r="AD137" t="b">
         <v>0</v>
       </c>
@@ -15683,7 +15678,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15701,37 +15696,37 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128362640</v>
+        <v>128362647</v>
       </c>
       <c r="B138" t="n">
-        <v>109300</v>
+        <v>98456</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15741,7 +15736,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
@@ -15812,32 +15807,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128362758</v>
+        <v>128362639</v>
       </c>
       <c r="B139" t="n">
-        <v>96075</v>
+        <v>106076</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2180</v>
+        <v>220785</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -15847,22 +15842,22 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>720904</v>
+        <v>720889</v>
       </c>
       <c r="R139" t="n">
-        <v>6382940</v>
+        <v>6382907</v>
       </c>
       <c r="S139" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15905,7 +15900,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -15923,27 +15918,27 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128362639</v>
+        <v>128362640</v>
       </c>
       <c r="B140" t="n">
-        <v>106071</v>
+        <v>109305</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -15963,7 +15958,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
@@ -16034,10 +16029,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128362635</v>
+        <v>128362661</v>
       </c>
       <c r="B141" t="n">
-        <v>98451</v>
+        <v>98456</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16064,7 +16059,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -16078,13 +16073,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>720875</v>
+        <v>720921</v>
       </c>
       <c r="R141" t="n">
-        <v>6382945</v>
+        <v>6382942</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16145,10 +16140,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128362661</v>
+        <v>128362635</v>
       </c>
       <c r="B142" t="n">
-        <v>98451</v>
+        <v>98456</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16175,7 +16170,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -16189,13 +16184,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>720921</v>
+        <v>720875</v>
       </c>
       <c r="R142" t="n">
-        <v>6382942</v>
+        <v>6382945</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16256,45 +16251,54 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128362628</v>
+        <v>128362615</v>
       </c>
       <c r="B143" t="n">
-        <v>109300</v>
+        <v>98456</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>720870</v>
+        <v>720854</v>
       </c>
       <c r="R143" t="n">
-        <v>6382959</v>
+        <v>6382995</v>
       </c>
       <c r="S143" t="n">
         <v>3</v>
@@ -16358,54 +16362,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128362615</v>
+        <v>128362628</v>
       </c>
       <c r="B144" t="n">
-        <v>98451</v>
+        <v>109305</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>720854</v>
+        <v>720870</v>
       </c>
       <c r="R144" t="n">
-        <v>6382995</v>
+        <v>6382959</v>
       </c>
       <c r="S144" t="n">
         <v>3</v>
@@ -16472,7 +16467,7 @@
         <v>128362656</v>
       </c>
       <c r="B145" t="n">
-        <v>109300</v>
+        <v>109305</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16574,7 +16569,7 @@
         <v>128362611</v>
       </c>
       <c r="B146" t="n">
-        <v>99224</v>
+        <v>99229</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16685,7 +16680,7 @@
         <v>128362612</v>
       </c>
       <c r="B147" t="n">
-        <v>98391</v>
+        <v>98396</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16796,7 +16791,7 @@
         <v>128362597</v>
       </c>
       <c r="B148" t="n">
-        <v>109300</v>
+        <v>109305</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16895,10 +16890,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128362594</v>
+        <v>128362657</v>
       </c>
       <c r="B149" t="n">
-        <v>98391</v>
+        <v>98456</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16906,26 +16901,26 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -16935,17 +16930,17 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2112, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>720898</v>
+        <v>720904</v>
       </c>
       <c r="R149" t="n">
-        <v>6382990</v>
+        <v>6382940</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17006,10 +17001,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128362657</v>
+        <v>128362655</v>
       </c>
       <c r="B150" t="n">
-        <v>98451</v>
+        <v>98456</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17036,7 +17031,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -17050,13 +17045,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>720904</v>
+        <v>720897</v>
       </c>
       <c r="R150" t="n">
-        <v>6382940</v>
+        <v>6382932</v>
       </c>
       <c r="S150" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17117,10 +17112,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128362655</v>
+        <v>128362594</v>
       </c>
       <c r="B151" t="n">
-        <v>98451</v>
+        <v>98396</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17128,26 +17123,26 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -17157,17 +17152,17 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2112, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>720897</v>
+        <v>720898</v>
       </c>
       <c r="R151" t="n">
-        <v>6382932</v>
+        <v>6382990</v>
       </c>
       <c r="S151" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17231,7 +17226,7 @@
         <v>128362668</v>
       </c>
       <c r="B152" t="n">
-        <v>98451</v>
+        <v>98456</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17339,10 +17334,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128362600</v>
+        <v>128362665</v>
       </c>
       <c r="B153" t="n">
-        <v>98451</v>
+        <v>98456</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17369,7 +17364,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -17383,13 +17378,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>720876</v>
+        <v>720967</v>
       </c>
       <c r="R153" t="n">
-        <v>6382976</v>
+        <v>6382919</v>
       </c>
       <c r="S153" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17450,10 +17445,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128362665</v>
+        <v>128362600</v>
       </c>
       <c r="B154" t="n">
-        <v>98451</v>
+        <v>98456</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17480,7 +17475,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -17494,13 +17489,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>720967</v>
+        <v>720876</v>
       </c>
       <c r="R154" t="n">
-        <v>6382919</v>
+        <v>6382976</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17561,37 +17556,37 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128362626</v>
+        <v>128362607</v>
       </c>
       <c r="B155" t="n">
-        <v>98495</v>
+        <v>107363</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -17601,14 +17596,14 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2097, Gtl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>720870</v>
+        <v>720820</v>
       </c>
       <c r="R155" t="n">
-        <v>6382959</v>
+        <v>6382977</v>
       </c>
       <c r="S155" t="n">
         <v>3</v>
@@ -17675,7 +17670,7 @@
         <v>128362652</v>
       </c>
       <c r="B156" t="n">
-        <v>98451</v>
+        <v>98456</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17783,10 +17778,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128362596</v>
+        <v>128362626</v>
       </c>
       <c r="B157" t="n">
-        <v>98451</v>
+        <v>98500</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17794,26 +17789,26 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -17823,17 +17818,17 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>720898</v>
+        <v>720870</v>
       </c>
       <c r="R157" t="n">
-        <v>6382990</v>
+        <v>6382959</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17894,37 +17889,37 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128362607</v>
+        <v>128362596</v>
       </c>
       <c r="B158" t="n">
-        <v>107358</v>
+        <v>98456</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -17934,17 +17929,17 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2097, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>720820</v>
+        <v>720898</v>
       </c>
       <c r="R158" t="n">
-        <v>6382977</v>
+        <v>6382990</v>
       </c>
       <c r="S158" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18008,7 +18003,7 @@
         <v>128362621</v>
       </c>
       <c r="B159" t="n">
-        <v>98451</v>
+        <v>98456</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18119,7 +18114,7 @@
         <v>128362659</v>
       </c>
       <c r="B160" t="n">
-        <v>98451</v>
+        <v>98456</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18230,7 +18225,7 @@
         <v>128362623</v>
       </c>
       <c r="B161" t="n">
-        <v>98391</v>
+        <v>98396</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18341,7 +18336,7 @@
         <v>128362663</v>
       </c>
       <c r="B162" t="n">
-        <v>98451</v>
+        <v>98456</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18452,7 +18447,7 @@
         <v>128362670</v>
       </c>
       <c r="B163" t="n">
-        <v>98451</v>
+        <v>98456</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18560,37 +18555,37 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128362666</v>
+        <v>128362644</v>
       </c>
       <c r="B164" t="n">
-        <v>107358</v>
+        <v>98500</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -18600,14 +18595,14 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>720954</v>
+        <v>720889</v>
       </c>
       <c r="R164" t="n">
-        <v>6382931</v>
+        <v>6382907</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -18671,10 +18666,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128362617</v>
+        <v>128362614</v>
       </c>
       <c r="B165" t="n">
-        <v>98451</v>
+        <v>98456</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18701,7 +18696,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -18715,13 +18710,13 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>720861</v>
+        <v>720854</v>
       </c>
       <c r="R165" t="n">
-        <v>6383000</v>
+        <v>6383001</v>
       </c>
       <c r="S165" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18785,7 +18780,7 @@
         <v>128362672</v>
       </c>
       <c r="B166" t="n">
-        <v>98451</v>
+        <v>98456</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18893,10 +18888,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128362614</v>
+        <v>128362617</v>
       </c>
       <c r="B167" t="n">
-        <v>98451</v>
+        <v>98456</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18923,7 +18918,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18937,13 +18932,13 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>720854</v>
+        <v>720861</v>
       </c>
       <c r="R167" t="n">
-        <v>6383001</v>
+        <v>6383000</v>
       </c>
       <c r="S167" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -19004,37 +18999,37 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128362644</v>
+        <v>128362666</v>
       </c>
       <c r="B168" t="n">
-        <v>98495</v>
+        <v>107363</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -19044,14 +19039,14 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>720889</v>
+        <v>720954</v>
       </c>
       <c r="R168" t="n">
-        <v>6382907</v>
+        <v>6382931</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -14052,7 +14052,7 @@
         <v>128362610</v>
       </c>
       <c r="B123" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>128362625</v>
       </c>
       <c r="B124" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>128362631</v>
       </c>
       <c r="B125" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         <v>128362609</v>
       </c>
       <c r="B126" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>128362604</v>
       </c>
       <c r="B127" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>128362638</v>
       </c>
       <c r="B128" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>128362622</v>
       </c>
       <c r="B129" t="n">
-        <v>98500</v>
+        <v>98593</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>128362595</v>
       </c>
       <c r="B130" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>128362627</v>
       </c>
       <c r="B131" t="n">
-        <v>98396</v>
+        <v>98489</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>128362619</v>
       </c>
       <c r="B132" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>128362671</v>
       </c>
       <c r="B133" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15255,7 +15255,7 @@
         <v>128362632</v>
       </c>
       <c r="B134" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>128362598</v>
       </c>
       <c r="B135" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>128362630</v>
       </c>
       <c r="B136" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15585,10 +15585,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128362758</v>
+        <v>128362647</v>
       </c>
       <c r="B137" t="n">
-        <v>96080</v>
+        <v>98549</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15596,46 +15596,46 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2180</v>
+        <v>219798</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>720904</v>
+        <v>720889</v>
       </c>
       <c r="R137" t="n">
-        <v>6382940</v>
+        <v>6382907</v>
       </c>
       <c r="S137" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15696,37 +15696,37 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128362647</v>
+        <v>128362640</v>
       </c>
       <c r="B138" t="n">
-        <v>98456</v>
+        <v>109398</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
@@ -15810,7 +15810,7 @@
         <v>128362639</v>
       </c>
       <c r="B139" t="n">
-        <v>106076</v>
+        <v>106169</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15918,32 +15918,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128362640</v>
+        <v>128362758</v>
       </c>
       <c r="B140" t="n">
-        <v>109305</v>
+        <v>96173</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220299</v>
+        <v>2180</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -15953,22 +15953,22 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>720889</v>
+        <v>720904</v>
       </c>
       <c r="R140" t="n">
-        <v>6382907</v>
+        <v>6382940</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -16032,7 +16032,7 @@
         <v>128362661</v>
       </c>
       <c r="B141" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>128362635</v>
       </c>
       <c r="B142" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16251,37 +16251,37 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128362615</v>
+        <v>128362611</v>
       </c>
       <c r="B143" t="n">
-        <v>98456</v>
+        <v>99322</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>219798</v>
+        <v>222361</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -16291,14 +16291,14 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
         <v>720854</v>
       </c>
       <c r="R143" t="n">
-        <v>6382995</v>
+        <v>6383001</v>
       </c>
       <c r="S143" t="n">
         <v>3</v>
@@ -16365,7 +16365,7 @@
         <v>128362628</v>
       </c>
       <c r="B144" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>128362656</v>
       </c>
       <c r="B145" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16566,37 +16566,37 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128362611</v>
+        <v>128362615</v>
       </c>
       <c r="B146" t="n">
-        <v>99229</v>
+        <v>98549</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>222361</v>
+        <v>219798</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -16606,14 +16606,14 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
         <v>720854</v>
       </c>
       <c r="R146" t="n">
-        <v>6383001</v>
+        <v>6382995</v>
       </c>
       <c r="S146" t="n">
         <v>3</v>
@@ -16680,7 +16680,7 @@
         <v>128362612</v>
       </c>
       <c r="B147" t="n">
-        <v>98396</v>
+        <v>98489</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>128362597</v>
       </c>
       <c r="B148" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16890,10 +16890,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128362657</v>
+        <v>128362594</v>
       </c>
       <c r="B149" t="n">
-        <v>98456</v>
+        <v>98489</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16901,26 +16901,26 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -16930,17 +16930,17 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2112, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>720904</v>
+        <v>720898</v>
       </c>
       <c r="R149" t="n">
-        <v>6382940</v>
+        <v>6382990</v>
       </c>
       <c r="S149" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17001,10 +17001,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128362655</v>
+        <v>128362657</v>
       </c>
       <c r="B150" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -17045,13 +17045,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>720897</v>
+        <v>720904</v>
       </c>
       <c r="R150" t="n">
-        <v>6382932</v>
+        <v>6382940</v>
       </c>
       <c r="S150" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17112,10 +17112,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128362594</v>
+        <v>128362655</v>
       </c>
       <c r="B151" t="n">
-        <v>98396</v>
+        <v>98549</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17123,26 +17123,26 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -17152,17 +17152,17 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2112, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>720898</v>
+        <v>720897</v>
       </c>
       <c r="R151" t="n">
-        <v>6382990</v>
+        <v>6382932</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>128362668</v>
       </c>
       <c r="B152" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>128362665</v>
       </c>
       <c r="B153" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>128362600</v>
       </c>
       <c r="B154" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>128362607</v>
       </c>
       <c r="B155" t="n">
-        <v>107363</v>
+        <v>107456</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>128362652</v>
       </c>
       <c r="B156" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>128362626</v>
       </c>
       <c r="B157" t="n">
-        <v>98500</v>
+        <v>98593</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>128362596</v>
       </c>
       <c r="B158" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>128362621</v>
       </c>
       <c r="B159" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>128362659</v>
       </c>
       <c r="B160" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>128362623</v>
       </c>
       <c r="B161" t="n">
-        <v>98396</v>
+        <v>98489</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>128362663</v>
       </c>
       <c r="B162" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18447,7 +18447,7 @@
         <v>128362670</v>
       </c>
       <c r="B163" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>128362644</v>
       </c>
       <c r="B164" t="n">
-        <v>98500</v>
+        <v>98593</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>128362614</v>
       </c>
       <c r="B165" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18780,7 +18780,7 @@
         <v>128362672</v>
       </c>
       <c r="B166" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>128362617</v>
       </c>
       <c r="B167" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>128362666</v>
       </c>
       <c r="B168" t="n">
-        <v>107363</v>
+        <v>107456</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -14493,10 +14493,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128362604</v>
+        <v>128362627</v>
       </c>
       <c r="B127" t="n">
-        <v>98549</v>
+        <v>98489</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14504,26 +14504,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14533,17 +14533,17 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>720857</v>
+        <v>720870</v>
       </c>
       <c r="R127" t="n">
-        <v>6382943</v>
+        <v>6382959</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128362638</v>
+        <v>128362604</v>
       </c>
       <c r="B128" t="n">
         <v>98549</v>
@@ -14634,7 +14634,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14648,10 +14648,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>720872</v>
+        <v>720857</v>
       </c>
       <c r="R128" t="n">
-        <v>6382941</v>
+        <v>6382943</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14715,10 +14715,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128362622</v>
+        <v>128362638</v>
       </c>
       <c r="B129" t="n">
-        <v>98593</v>
+        <v>98549</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14726,26 +14726,26 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14755,17 +14755,17 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>720854</v>
+        <v>720872</v>
       </c>
       <c r="R129" t="n">
-        <v>6382954</v>
+        <v>6382941</v>
       </c>
       <c r="S129" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14826,48 +14826,57 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128362595</v>
+        <v>128362622</v>
       </c>
       <c r="B130" t="n">
-        <v>109398</v>
+        <v>98593</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>720898</v>
+        <v>720854</v>
       </c>
       <c r="R130" t="n">
-        <v>6382990</v>
+        <v>6382954</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14928,57 +14937,48 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128362627</v>
+        <v>128362595</v>
       </c>
       <c r="B131" t="n">
-        <v>98489</v>
+        <v>109398</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>720870</v>
+        <v>720898</v>
       </c>
       <c r="R131" t="n">
-        <v>6382959</v>
+        <v>6382990</v>
       </c>
       <c r="S131" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15585,37 +15585,37 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128362647</v>
+        <v>128362639</v>
       </c>
       <c r="B137" t="n">
-        <v>98549</v>
+        <v>106169</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15625,7 +15625,7 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
@@ -15696,37 +15696,37 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128362640</v>
+        <v>128362647</v>
       </c>
       <c r="B138" t="n">
-        <v>109398</v>
+        <v>98549</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
@@ -15807,27 +15807,27 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128362639</v>
+        <v>128362640</v>
       </c>
       <c r="B139" t="n">
-        <v>106169</v>
+        <v>109398</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -15847,7 +15847,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
@@ -16251,10 +16251,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128362611</v>
+        <v>128362628</v>
       </c>
       <c r="B143" t="n">
-        <v>99322</v>
+        <v>109398</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16262,16 +16262,16 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>222361</v>
+        <v>220299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -16279,26 +16279,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>720854</v>
+        <v>720870</v>
       </c>
       <c r="R143" t="n">
-        <v>6383001</v>
+        <v>6382959</v>
       </c>
       <c r="S143" t="n">
         <v>3</v>
@@ -16362,7 +16353,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128362628</v>
+        <v>128362656</v>
       </c>
       <c r="B144" t="n">
         <v>109398</v>
@@ -16393,17 +16384,17 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>720870</v>
+        <v>720904</v>
       </c>
       <c r="R144" t="n">
-        <v>6382959</v>
+        <v>6382940</v>
       </c>
       <c r="S144" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16464,48 +16455,57 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128362656</v>
+        <v>128362615</v>
       </c>
       <c r="B145" t="n">
-        <v>109398</v>
+        <v>98549</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>720904</v>
+        <v>720854</v>
       </c>
       <c r="R145" t="n">
-        <v>6382940</v>
+        <v>6382995</v>
       </c>
       <c r="S145" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16566,37 +16566,37 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128362615</v>
+        <v>128362611</v>
       </c>
       <c r="B146" t="n">
-        <v>98549</v>
+        <v>99322</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>219798</v>
+        <v>222361</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -16606,14 +16606,14 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
         <v>720854</v>
       </c>
       <c r="R146" t="n">
-        <v>6382995</v>
+        <v>6383001</v>
       </c>
       <c r="S146" t="n">
         <v>3</v>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -15585,32 +15585,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128362639</v>
+        <v>128362758</v>
       </c>
       <c r="B137" t="n">
-        <v>106169</v>
+        <v>96173</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220785</v>
+        <v>2180</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -15620,22 +15620,22 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>720889</v>
+        <v>720904</v>
       </c>
       <c r="R137" t="n">
-        <v>6382907</v>
+        <v>6382940</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15807,27 +15807,27 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128362640</v>
+        <v>128362639</v>
       </c>
       <c r="B139" t="n">
-        <v>109398</v>
+        <v>106169</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -15847,7 +15847,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
@@ -15918,32 +15918,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128362758</v>
+        <v>128362640</v>
       </c>
       <c r="B140" t="n">
-        <v>96173</v>
+        <v>109398</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2180</v>
+        <v>220299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -15953,22 +15953,22 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>720904</v>
+        <v>720889</v>
       </c>
       <c r="R140" t="n">
-        <v>6382940</v>
+        <v>6382907</v>
       </c>
       <c r="S140" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -16251,45 +16251,54 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128362628</v>
+        <v>128362615</v>
       </c>
       <c r="B143" t="n">
-        <v>109398</v>
+        <v>98549</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>720870</v>
+        <v>720854</v>
       </c>
       <c r="R143" t="n">
-        <v>6382959</v>
+        <v>6382995</v>
       </c>
       <c r="S143" t="n">
         <v>3</v>
@@ -16353,10 +16362,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128362656</v>
+        <v>128362611</v>
       </c>
       <c r="B144" t="n">
-        <v>109398</v>
+        <v>99322</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16364,16 +16373,16 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220299</v>
+        <v>222361</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -16381,20 +16390,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>720904</v>
+        <v>720854</v>
       </c>
       <c r="R144" t="n">
-        <v>6382940</v>
+        <v>6383001</v>
       </c>
       <c r="S144" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16455,54 +16473,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128362615</v>
+        <v>128362628</v>
       </c>
       <c r="B145" t="n">
-        <v>98549</v>
+        <v>109398</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>720854</v>
+        <v>720870</v>
       </c>
       <c r="R145" t="n">
-        <v>6382995</v>
+        <v>6382959</v>
       </c>
       <c r="S145" t="n">
         <v>3</v>
@@ -16566,10 +16575,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128362611</v>
+        <v>128362656</v>
       </c>
       <c r="B146" t="n">
-        <v>99322</v>
+        <v>109398</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16577,16 +16586,16 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>222361</v>
+        <v>220299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -16594,29 +16603,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>720854</v>
+        <v>720904</v>
       </c>
       <c r="R146" t="n">
-        <v>6383001</v>
+        <v>6382940</v>
       </c>
       <c r="S146" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -18111,10 +18111,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128362659</v>
+        <v>128362623</v>
       </c>
       <c r="B160" t="n">
-        <v>98549</v>
+        <v>98489</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18122,26 +18122,26 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -18151,17 +18151,17 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>720910</v>
+        <v>720854</v>
       </c>
       <c r="R160" t="n">
-        <v>6382934</v>
+        <v>6382954</v>
       </c>
       <c r="S160" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18222,10 +18222,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128362623</v>
+        <v>128362659</v>
       </c>
       <c r="B161" t="n">
-        <v>98489</v>
+        <v>98549</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18233,26 +18233,26 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -18262,17 +18262,17 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>720854</v>
+        <v>720910</v>
       </c>
       <c r="R161" t="n">
-        <v>6382954</v>
+        <v>6382934</v>
       </c>
       <c r="S161" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -804,12 +804,7 @@
         <v>105082160</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -850,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720809.1541196827</v>
+        <v>720809</v>
       </c>
       <c r="R3" t="n">
-        <v>6382765.247689249</v>
+        <v>6382765</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,19 +878,9 @@
           <t>1992-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1996-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -15039,57 +15024,48 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128362619</v>
+        <v>128362671</v>
       </c>
       <c r="B132" t="n">
-        <v>98549</v>
+        <v>109398</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2044, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>720859</v>
+        <v>720992</v>
       </c>
       <c r="R132" t="n">
-        <v>6382986</v>
+        <v>6382917</v>
       </c>
       <c r="S132" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15150,48 +15126,57 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128362671</v>
+        <v>128362619</v>
       </c>
       <c r="B133" t="n">
-        <v>109398</v>
+        <v>98549</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2044, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>720992</v>
+        <v>720859</v>
       </c>
       <c r="R133" t="n">
-        <v>6382917</v>
+        <v>6382986</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15585,10 +15570,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128362758</v>
+        <v>128362647</v>
       </c>
       <c r="B137" t="n">
-        <v>96173</v>
+        <v>98549</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15596,46 +15581,46 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2180</v>
+        <v>219798</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>720904</v>
+        <v>720889</v>
       </c>
       <c r="R137" t="n">
-        <v>6382940</v>
+        <v>6382907</v>
       </c>
       <c r="S137" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15678,7 +15663,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15696,37 +15681,37 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128362647</v>
+        <v>128362639</v>
       </c>
       <c r="B138" t="n">
-        <v>98549</v>
+        <v>106169</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15736,7 +15721,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
@@ -15807,27 +15792,27 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128362639</v>
+        <v>128362640</v>
       </c>
       <c r="B139" t="n">
-        <v>106169</v>
+        <v>109398</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -15847,7 +15832,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
@@ -15918,32 +15903,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128362640</v>
+        <v>128362758</v>
       </c>
       <c r="B140" t="n">
-        <v>109398</v>
+        <v>96173</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220299</v>
+        <v>2180</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -15953,22 +15938,22 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>720889</v>
+        <v>720904</v>
       </c>
       <c r="R140" t="n">
-        <v>6382907</v>
+        <v>6382940</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16011,7 +15996,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>105082160</v>
       </c>
       <c r="B3" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>128362610</v>
       </c>
       <c r="B123" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>128362625</v>
       </c>
       <c r="B124" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>128362631</v>
       </c>
       <c r="B125" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>128362609</v>
       </c>
       <c r="B126" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14481,7 +14481,7 @@
         <v>128362627</v>
       </c>
       <c r="B127" t="n">
-        <v>98489</v>
+        <v>98503</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>128362604</v>
       </c>
       <c r="B128" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>128362638</v>
       </c>
       <c r="B129" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>128362622</v>
       </c>
       <c r="B130" t="n">
-        <v>98593</v>
+        <v>98607</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>128362595</v>
       </c>
       <c r="B131" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15024,48 +15024,57 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128362671</v>
+        <v>128362619</v>
       </c>
       <c r="B132" t="n">
-        <v>109398</v>
+        <v>98563</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2044, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>720992</v>
+        <v>720859</v>
       </c>
       <c r="R132" t="n">
-        <v>6382917</v>
+        <v>6382986</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15126,57 +15135,48 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128362619</v>
+        <v>128362671</v>
       </c>
       <c r="B133" t="n">
-        <v>98549</v>
+        <v>109422</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2044, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>720859</v>
+        <v>720992</v>
       </c>
       <c r="R133" t="n">
-        <v>6382986</v>
+        <v>6382917</v>
       </c>
       <c r="S133" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>128362632</v>
       </c>
       <c r="B134" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>128362598</v>
       </c>
       <c r="B135" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>128362630</v>
       </c>
       <c r="B136" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15570,10 +15570,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128362647</v>
+        <v>128362758</v>
       </c>
       <c r="B137" t="n">
-        <v>98549</v>
+        <v>96185</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15581,46 +15581,46 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>219798</v>
+        <v>2180</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>720889</v>
+        <v>720904</v>
       </c>
       <c r="R137" t="n">
-        <v>6382907</v>
+        <v>6382940</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15684,7 +15684,7 @@
         <v>128362639</v>
       </c>
       <c r="B138" t="n">
-        <v>106169</v>
+        <v>106190</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>128362640</v>
       </c>
       <c r="B139" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15903,10 +15903,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128362758</v>
+        <v>128362647</v>
       </c>
       <c r="B140" t="n">
-        <v>96173</v>
+        <v>98563</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15914,46 +15914,46 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2180</v>
+        <v>219798</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>720904</v>
+        <v>720889</v>
       </c>
       <c r="R140" t="n">
-        <v>6382940</v>
+        <v>6382907</v>
       </c>
       <c r="S140" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -16017,7 +16017,7 @@
         <v>128362661</v>
       </c>
       <c r="B141" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>128362635</v>
       </c>
       <c r="B142" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16236,37 +16236,37 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128362615</v>
+        <v>128362611</v>
       </c>
       <c r="B143" t="n">
-        <v>98549</v>
+        <v>99336</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>219798</v>
+        <v>222361</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -16276,14 +16276,14 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
         <v>720854</v>
       </c>
       <c r="R143" t="n">
-        <v>6382995</v>
+        <v>6383001</v>
       </c>
       <c r="S143" t="n">
         <v>3</v>
@@ -16347,37 +16347,37 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128362611</v>
+        <v>128362615</v>
       </c>
       <c r="B144" t="n">
-        <v>99322</v>
+        <v>98563</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>222361</v>
+        <v>219798</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -16387,14 +16387,14 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q144" t="n">
         <v>720854</v>
       </c>
       <c r="R144" t="n">
-        <v>6383001</v>
+        <v>6382995</v>
       </c>
       <c r="S144" t="n">
         <v>3</v>
@@ -16461,7 +16461,7 @@
         <v>128362628</v>
       </c>
       <c r="B145" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>128362656</v>
       </c>
       <c r="B146" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>128362612</v>
       </c>
       <c r="B147" t="n">
-        <v>98489</v>
+        <v>98503</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>128362597</v>
       </c>
       <c r="B148" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>128362594</v>
       </c>
       <c r="B149" t="n">
-        <v>98489</v>
+        <v>98503</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>128362657</v>
       </c>
       <c r="B150" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>128362655</v>
       </c>
       <c r="B151" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>128362668</v>
       </c>
       <c r="B152" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>128362665</v>
       </c>
       <c r="B153" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>128362600</v>
       </c>
       <c r="B154" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>128362607</v>
       </c>
       <c r="B155" t="n">
-        <v>107456</v>
+        <v>107479</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17655,7 +17655,7 @@
         <v>128362652</v>
       </c>
       <c r="B156" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>128362626</v>
       </c>
       <c r="B157" t="n">
-        <v>98593</v>
+        <v>98607</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>128362596</v>
       </c>
       <c r="B158" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>128362621</v>
       </c>
       <c r="B159" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128362623</v>
+        <v>128362659</v>
       </c>
       <c r="B160" t="n">
-        <v>98489</v>
+        <v>98563</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18107,26 +18107,26 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -18136,17 +18136,17 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>720854</v>
+        <v>720910</v>
       </c>
       <c r="R160" t="n">
-        <v>6382954</v>
+        <v>6382934</v>
       </c>
       <c r="S160" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18207,10 +18207,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128362659</v>
+        <v>128362623</v>
       </c>
       <c r="B161" t="n">
-        <v>98549</v>
+        <v>98503</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18218,26 +18218,26 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -18247,17 +18247,17 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>720910</v>
+        <v>720854</v>
       </c>
       <c r="R161" t="n">
-        <v>6382934</v>
+        <v>6382954</v>
       </c>
       <c r="S161" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>128362663</v>
       </c>
       <c r="B162" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>128362670</v>
       </c>
       <c r="B163" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>128362644</v>
       </c>
       <c r="B164" t="n">
-        <v>98593</v>
+        <v>98607</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>128362614</v>
       </c>
       <c r="B165" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>128362672</v>
       </c>
       <c r="B166" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>128362617</v>
       </c>
       <c r="B167" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>128362666</v>
       </c>
       <c r="B168" t="n">
-        <v>107456</v>
+        <v>107479</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -14478,57 +14478,48 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128362627</v>
+        <v>128362595</v>
       </c>
       <c r="B127" t="n">
-        <v>98503</v>
+        <v>109422</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>720870</v>
+        <v>720898</v>
       </c>
       <c r="R127" t="n">
-        <v>6382959</v>
+        <v>6382990</v>
       </c>
       <c r="S127" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14922,48 +14913,57 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128362595</v>
+        <v>128362627</v>
       </c>
       <c r="B131" t="n">
-        <v>109422</v>
+        <v>98503</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>720898</v>
+        <v>720870</v>
       </c>
       <c r="R131" t="n">
-        <v>6382990</v>
+        <v>6382959</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15681,37 +15681,37 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128362639</v>
+        <v>128362647</v>
       </c>
       <c r="B138" t="n">
-        <v>106190</v>
+        <v>98563</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
@@ -15792,27 +15792,27 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128362640</v>
+        <v>128362639</v>
       </c>
       <c r="B139" t="n">
-        <v>109422</v>
+        <v>106190</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -15832,7 +15832,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
@@ -15903,37 +15903,37 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128362647</v>
+        <v>128362640</v>
       </c>
       <c r="B140" t="n">
-        <v>98563</v>
+        <v>109422</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15943,7 +15943,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
@@ -16236,37 +16236,37 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128362611</v>
+        <v>128362615</v>
       </c>
       <c r="B143" t="n">
-        <v>99336</v>
+        <v>98563</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>222361</v>
+        <v>219798</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -16276,14 +16276,14 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
         <v>720854</v>
       </c>
       <c r="R143" t="n">
-        <v>6383001</v>
+        <v>6382995</v>
       </c>
       <c r="S143" t="n">
         <v>3</v>
@@ -16347,54 +16347,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128362615</v>
+        <v>128362628</v>
       </c>
       <c r="B144" t="n">
-        <v>98563</v>
+        <v>109422</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>720854</v>
+        <v>720870</v>
       </c>
       <c r="R144" t="n">
-        <v>6382995</v>
+        <v>6382959</v>
       </c>
       <c r="S144" t="n">
         <v>3</v>
@@ -16458,7 +16449,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128362628</v>
+        <v>128362656</v>
       </c>
       <c r="B145" t="n">
         <v>109422</v>
@@ -16489,17 +16480,17 @@
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>720870</v>
+        <v>720904</v>
       </c>
       <c r="R145" t="n">
-        <v>6382959</v>
+        <v>6382940</v>
       </c>
       <c r="S145" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16560,10 +16551,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128362656</v>
+        <v>128362611</v>
       </c>
       <c r="B146" t="n">
-        <v>109422</v>
+        <v>99336</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16571,16 +16562,16 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220299</v>
+        <v>222361</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -16588,20 +16579,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>720904</v>
+        <v>720854</v>
       </c>
       <c r="R146" t="n">
-        <v>6382940</v>
+        <v>6383001</v>
       </c>
       <c r="S146" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>105082160</v>
       </c>
       <c r="B3" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -14034,10 +14034,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128362610</v>
+        <v>128362631</v>
       </c>
       <c r="B123" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -14078,10 +14078,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>720820</v>
+        <v>720861</v>
       </c>
       <c r="R123" t="n">
-        <v>6382977</v>
+        <v>6382950</v>
       </c>
       <c r="S123" t="n">
         <v>3</v>
@@ -14148,7 +14148,7 @@
         <v>128362625</v>
       </c>
       <c r="B124" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14256,10 +14256,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128362631</v>
+        <v>128362610</v>
       </c>
       <c r="B125" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14300,10 +14300,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>720861</v>
+        <v>720820</v>
       </c>
       <c r="R125" t="n">
-        <v>6382950</v>
+        <v>6382977</v>
       </c>
       <c r="S125" t="n">
         <v>3</v>
@@ -14370,7 +14370,7 @@
         <v>128362609</v>
       </c>
       <c r="B126" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14478,48 +14478,57 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128362595</v>
+        <v>128362604</v>
       </c>
       <c r="B127" t="n">
-        <v>109422</v>
+        <v>98566</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>720898</v>
+        <v>720857</v>
       </c>
       <c r="R127" t="n">
-        <v>6382990</v>
+        <v>6382943</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14580,10 +14589,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128362604</v>
+        <v>128362627</v>
       </c>
       <c r="B128" t="n">
-        <v>98563</v>
+        <v>98506</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14591,26 +14600,26 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14620,17 +14629,17 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>720857</v>
+        <v>720870</v>
       </c>
       <c r="R128" t="n">
-        <v>6382943</v>
+        <v>6382959</v>
       </c>
       <c r="S128" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14691,57 +14700,48 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128362638</v>
+        <v>128362595</v>
       </c>
       <c r="B129" t="n">
-        <v>98563</v>
+        <v>109435</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>720872</v>
+        <v>720898</v>
       </c>
       <c r="R129" t="n">
-        <v>6382941</v>
+        <v>6382990</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>128362622</v>
       </c>
       <c r="B130" t="n">
-        <v>98607</v>
+        <v>98610</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14913,10 +14913,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128362627</v>
+        <v>128362638</v>
       </c>
       <c r="B131" t="n">
-        <v>98503</v>
+        <v>98566</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14924,26 +14924,26 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -14953,17 +14953,17 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>720870</v>
+        <v>720872</v>
       </c>
       <c r="R131" t="n">
-        <v>6382959</v>
+        <v>6382941</v>
       </c>
       <c r="S131" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15024,57 +15024,48 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128362619</v>
+        <v>128362671</v>
       </c>
       <c r="B132" t="n">
-        <v>98563</v>
+        <v>109435</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2044, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>720859</v>
+        <v>720992</v>
       </c>
       <c r="R132" t="n">
-        <v>6382986</v>
+        <v>6382917</v>
       </c>
       <c r="S132" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15135,48 +15126,57 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128362671</v>
+        <v>128362619</v>
       </c>
       <c r="B133" t="n">
-        <v>109422</v>
+        <v>98566</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2044, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>720992</v>
+        <v>720859</v>
       </c>
       <c r="R133" t="n">
-        <v>6382917</v>
+        <v>6382986</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>128362632</v>
       </c>
       <c r="B134" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15348,10 +15348,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128362598</v>
+        <v>128362630</v>
       </c>
       <c r="B135" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15392,13 +15392,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>720886</v>
+        <v>720870</v>
       </c>
       <c r="R135" t="n">
-        <v>6382981</v>
+        <v>6382959</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15459,10 +15459,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128362630</v>
+        <v>128362598</v>
       </c>
       <c r="B136" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15503,13 +15503,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>720870</v>
+        <v>720886</v>
       </c>
       <c r="R136" t="n">
-        <v>6382959</v>
+        <v>6382981</v>
       </c>
       <c r="S136" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>128362758</v>
       </c>
       <c r="B137" t="n">
-        <v>96185</v>
+        <v>96187</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15681,37 +15681,37 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128362647</v>
+        <v>128362639</v>
       </c>
       <c r="B138" t="n">
-        <v>98563</v>
+        <v>106202</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
@@ -15792,27 +15792,27 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128362639</v>
+        <v>128362640</v>
       </c>
       <c r="B139" t="n">
-        <v>106190</v>
+        <v>109435</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -15832,7 +15832,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
@@ -15903,37 +15903,37 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128362640</v>
+        <v>128362642</v>
       </c>
       <c r="B140" t="n">
-        <v>109422</v>
+        <v>98566</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15943,7 +15943,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
@@ -15983,6 +15983,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Bild på svamp på koordinat.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16014,10 +16019,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128362661</v>
+        <v>128362635</v>
       </c>
       <c r="B141" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16044,7 +16049,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -16058,13 +16063,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>720921</v>
+        <v>720875</v>
       </c>
       <c r="R141" t="n">
-        <v>6382942</v>
+        <v>6382945</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16125,10 +16130,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128362635</v>
+        <v>128362661</v>
       </c>
       <c r="B142" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16155,7 +16160,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -16169,13 +16174,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>720875</v>
+        <v>720921</v>
       </c>
       <c r="R142" t="n">
-        <v>6382945</v>
+        <v>6382942</v>
       </c>
       <c r="S142" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16236,37 +16241,37 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128362615</v>
+        <v>128362611</v>
       </c>
       <c r="B143" t="n">
-        <v>98563</v>
+        <v>99339</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>219798</v>
+        <v>222361</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -16276,14 +16281,14 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
         <v>720854</v>
       </c>
       <c r="R143" t="n">
-        <v>6382995</v>
+        <v>6383001</v>
       </c>
       <c r="S143" t="n">
         <v>3</v>
@@ -16350,7 +16355,7 @@
         <v>128362628</v>
       </c>
       <c r="B144" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16452,7 +16457,7 @@
         <v>128362656</v>
       </c>
       <c r="B145" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16551,37 +16556,37 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128362611</v>
+        <v>128362615</v>
       </c>
       <c r="B146" t="n">
-        <v>99336</v>
+        <v>98566</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>222361</v>
+        <v>219798</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -16591,14 +16596,14 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
         <v>720854</v>
       </c>
       <c r="R146" t="n">
-        <v>6383001</v>
+        <v>6382995</v>
       </c>
       <c r="S146" t="n">
         <v>3</v>
@@ -16665,7 +16670,7 @@
         <v>128362612</v>
       </c>
       <c r="B147" t="n">
-        <v>98503</v>
+        <v>98506</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16776,7 +16781,7 @@
         <v>128362597</v>
       </c>
       <c r="B148" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16875,10 +16880,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128362594</v>
+        <v>128362657</v>
       </c>
       <c r="B149" t="n">
-        <v>98503</v>
+        <v>98566</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16886,26 +16891,26 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -16915,17 +16920,17 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2112, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>720898</v>
+        <v>720904</v>
       </c>
       <c r="R149" t="n">
-        <v>6382990</v>
+        <v>6382940</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16986,10 +16991,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128362657</v>
+        <v>128362655</v>
       </c>
       <c r="B150" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17016,7 +17021,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -17030,13 +17035,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>720904</v>
+        <v>720897</v>
       </c>
       <c r="R150" t="n">
-        <v>6382940</v>
+        <v>6382932</v>
       </c>
       <c r="S150" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17097,10 +17102,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128362655</v>
+        <v>128362594</v>
       </c>
       <c r="B151" t="n">
-        <v>98563</v>
+        <v>98506</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17108,26 +17113,26 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -17137,17 +17142,17 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2112, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>720897</v>
+        <v>720898</v>
       </c>
       <c r="R151" t="n">
-        <v>6382932</v>
+        <v>6382990</v>
       </c>
       <c r="S151" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17211,7 +17216,7 @@
         <v>128362668</v>
       </c>
       <c r="B152" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17319,10 +17324,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128362665</v>
+        <v>128362600</v>
       </c>
       <c r="B153" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17349,7 +17354,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -17363,13 +17368,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>720967</v>
+        <v>720876</v>
       </c>
       <c r="R153" t="n">
-        <v>6382919</v>
+        <v>6382976</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17430,10 +17435,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128362600</v>
+        <v>128362665</v>
       </c>
       <c r="B154" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17460,7 +17465,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -17474,13 +17479,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>720876</v>
+        <v>720967</v>
       </c>
       <c r="R154" t="n">
-        <v>6382976</v>
+        <v>6382919</v>
       </c>
       <c r="S154" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17541,37 +17546,37 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128362607</v>
+        <v>128362626</v>
       </c>
       <c r="B155" t="n">
-        <v>107479</v>
+        <v>98610</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -17581,14 +17586,14 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2097, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>720820</v>
+        <v>720870</v>
       </c>
       <c r="R155" t="n">
-        <v>6382977</v>
+        <v>6382959</v>
       </c>
       <c r="S155" t="n">
         <v>3</v>
@@ -17655,7 +17660,7 @@
         <v>128362652</v>
       </c>
       <c r="B156" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17763,10 +17768,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128362626</v>
+        <v>128362596</v>
       </c>
       <c r="B157" t="n">
-        <v>98607</v>
+        <v>98566</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17774,26 +17779,26 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -17803,17 +17808,17 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>720870</v>
+        <v>720898</v>
       </c>
       <c r="R157" t="n">
-        <v>6382959</v>
+        <v>6382990</v>
       </c>
       <c r="S157" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17874,37 +17879,37 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128362596</v>
+        <v>128362607</v>
       </c>
       <c r="B158" t="n">
-        <v>98563</v>
+        <v>107491</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>219798</v>
+        <v>220079</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -17914,17 +17919,17 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2097, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>720898</v>
+        <v>720820</v>
       </c>
       <c r="R158" t="n">
-        <v>6382990</v>
+        <v>6382977</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17988,7 +17993,7 @@
         <v>128362621</v>
       </c>
       <c r="B159" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18099,7 +18104,7 @@
         <v>128362659</v>
       </c>
       <c r="B160" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18210,7 +18215,7 @@
         <v>128362623</v>
       </c>
       <c r="B161" t="n">
-        <v>98503</v>
+        <v>98506</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18321,7 +18326,7 @@
         <v>128362663</v>
       </c>
       <c r="B162" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18432,7 +18437,7 @@
         <v>128362670</v>
       </c>
       <c r="B163" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18540,37 +18545,37 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128362644</v>
+        <v>128362666</v>
       </c>
       <c r="B164" t="n">
-        <v>98607</v>
+        <v>107491</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -18580,14 +18585,14 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>720889</v>
+        <v>720954</v>
       </c>
       <c r="R164" t="n">
-        <v>6382907</v>
+        <v>6382931</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -18651,10 +18656,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128362614</v>
+        <v>128362617</v>
       </c>
       <c r="B165" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18681,7 +18686,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -18695,13 +18700,13 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>720854</v>
+        <v>720861</v>
       </c>
       <c r="R165" t="n">
-        <v>6383001</v>
+        <v>6383000</v>
       </c>
       <c r="S165" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18765,7 +18770,7 @@
         <v>128362672</v>
       </c>
       <c r="B166" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18873,10 +18878,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128362617</v>
+        <v>128362614</v>
       </c>
       <c r="B167" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18903,7 +18908,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18917,13 +18922,13 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>720861</v>
+        <v>720854</v>
       </c>
       <c r="R167" t="n">
-        <v>6383000</v>
+        <v>6383001</v>
       </c>
       <c r="S167" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18984,37 +18989,37 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128362666</v>
+        <v>128362644</v>
       </c>
       <c r="B168" t="n">
-        <v>107479</v>
+        <v>98610</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -19024,14 +19029,14 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>720954</v>
+        <v>720889</v>
       </c>
       <c r="R168" t="n">
-        <v>6382931</v>
+        <v>6382907</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>105082160</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -14034,10 +14034,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128362631</v>
+        <v>128362610</v>
       </c>
       <c r="B123" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -14078,10 +14078,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>720861</v>
+        <v>720820</v>
       </c>
       <c r="R123" t="n">
-        <v>6382950</v>
+        <v>6382977</v>
       </c>
       <c r="S123" t="n">
         <v>3</v>
@@ -14148,7 +14148,7 @@
         <v>128362625</v>
       </c>
       <c r="B124" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14256,10 +14256,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128362610</v>
+        <v>128362631</v>
       </c>
       <c r="B125" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14300,10 +14300,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>720820</v>
+        <v>720861</v>
       </c>
       <c r="R125" t="n">
-        <v>6382977</v>
+        <v>6382950</v>
       </c>
       <c r="S125" t="n">
         <v>3</v>
@@ -14370,7 +14370,7 @@
         <v>128362609</v>
       </c>
       <c r="B126" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14478,57 +14478,48 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128362604</v>
+        <v>128362595</v>
       </c>
       <c r="B127" t="n">
-        <v>98566</v>
+        <v>109444</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>720857</v>
+        <v>720898</v>
       </c>
       <c r="R127" t="n">
-        <v>6382943</v>
+        <v>6382990</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14592,7 +14583,7 @@
         <v>128362627</v>
       </c>
       <c r="B128" t="n">
-        <v>98506</v>
+        <v>98509</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14700,48 +14691,57 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128362595</v>
+        <v>128362604</v>
       </c>
       <c r="B129" t="n">
-        <v>109435</v>
+        <v>98569</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>720898</v>
+        <v>720857</v>
       </c>
       <c r="R129" t="n">
-        <v>6382990</v>
+        <v>6382943</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14802,10 +14802,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128362622</v>
+        <v>128362638</v>
       </c>
       <c r="B130" t="n">
-        <v>98610</v>
+        <v>98569</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14813,26 +14813,26 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14842,17 +14842,17 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>720854</v>
+        <v>720872</v>
       </c>
       <c r="R130" t="n">
-        <v>6382954</v>
+        <v>6382941</v>
       </c>
       <c r="S130" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14913,10 +14913,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128362638</v>
+        <v>128362622</v>
       </c>
       <c r="B131" t="n">
-        <v>98566</v>
+        <v>98613</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14924,26 +14924,26 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -14953,17 +14953,17 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>720872</v>
+        <v>720854</v>
       </c>
       <c r="R131" t="n">
-        <v>6382941</v>
+        <v>6382954</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15024,48 +15024,57 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128362671</v>
+        <v>128362619</v>
       </c>
       <c r="B132" t="n">
-        <v>109435</v>
+        <v>98569</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2044, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>720992</v>
+        <v>720859</v>
       </c>
       <c r="R132" t="n">
-        <v>6382917</v>
+        <v>6382986</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15126,57 +15135,48 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128362619</v>
+        <v>128362671</v>
       </c>
       <c r="B133" t="n">
-        <v>98566</v>
+        <v>109444</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2044, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>720859</v>
+        <v>720992</v>
       </c>
       <c r="R133" t="n">
-        <v>6382986</v>
+        <v>6382917</v>
       </c>
       <c r="S133" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>128362632</v>
       </c>
       <c r="B134" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15348,10 +15348,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128362630</v>
+        <v>128362598</v>
       </c>
       <c r="B135" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15392,13 +15392,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>720870</v>
+        <v>720886</v>
       </c>
       <c r="R135" t="n">
-        <v>6382959</v>
+        <v>6382981</v>
       </c>
       <c r="S135" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15459,10 +15459,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128362598</v>
+        <v>128362630</v>
       </c>
       <c r="B136" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15503,13 +15503,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>720886</v>
+        <v>720870</v>
       </c>
       <c r="R136" t="n">
-        <v>6382981</v>
+        <v>6382959</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15570,32 +15570,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128362758</v>
+        <v>128362639</v>
       </c>
       <c r="B137" t="n">
-        <v>96187</v>
+        <v>106211</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2180</v>
+        <v>220785</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -15605,22 +15605,22 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>720904</v>
+        <v>720889</v>
       </c>
       <c r="R137" t="n">
-        <v>6382940</v>
+        <v>6382907</v>
       </c>
       <c r="S137" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15681,27 +15681,27 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128362639</v>
+        <v>128362640</v>
       </c>
       <c r="B138" t="n">
-        <v>106202</v>
+        <v>109444</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
@@ -15792,37 +15792,37 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128362640</v>
+        <v>128362647</v>
       </c>
       <c r="B139" t="n">
-        <v>109435</v>
+        <v>98569</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15832,7 +15832,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
@@ -15903,10 +15903,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128362642</v>
+        <v>128362758</v>
       </c>
       <c r="B140" t="n">
-        <v>98566</v>
+        <v>96187</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15914,46 +15914,46 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>219798</v>
+        <v>2180</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>720889</v>
+        <v>720904</v>
       </c>
       <c r="R140" t="n">
-        <v>6382907</v>
+        <v>6382940</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15985,11 +15985,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Bild på svamp på koordinat.</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -16001,7 +15996,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -16019,10 +16014,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128362635</v>
+        <v>128362661</v>
       </c>
       <c r="B141" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16049,7 +16044,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -16063,13 +16058,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>720875</v>
+        <v>720921</v>
       </c>
       <c r="R141" t="n">
-        <v>6382945</v>
+        <v>6382942</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16130,10 +16125,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128362661</v>
+        <v>128362635</v>
       </c>
       <c r="B142" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16160,7 +16155,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -16174,13 +16169,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>720921</v>
+        <v>720875</v>
       </c>
       <c r="R142" t="n">
-        <v>6382942</v>
+        <v>6382945</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16244,7 +16239,7 @@
         <v>128362611</v>
       </c>
       <c r="B143" t="n">
-        <v>99339</v>
+        <v>99344</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16355,7 +16350,7 @@
         <v>128362628</v>
       </c>
       <c r="B144" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16457,7 +16452,7 @@
         <v>128362656</v>
       </c>
       <c r="B145" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16559,7 +16554,7 @@
         <v>128362615</v>
       </c>
       <c r="B146" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16670,7 +16665,7 @@
         <v>128362612</v>
       </c>
       <c r="B147" t="n">
-        <v>98506</v>
+        <v>98509</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16781,7 +16776,7 @@
         <v>128362597</v>
       </c>
       <c r="B148" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16880,10 +16875,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128362657</v>
+        <v>128362594</v>
       </c>
       <c r="B149" t="n">
-        <v>98566</v>
+        <v>98509</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16891,26 +16886,26 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -16920,17 +16915,17 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2112, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>720904</v>
+        <v>720898</v>
       </c>
       <c r="R149" t="n">
-        <v>6382940</v>
+        <v>6382990</v>
       </c>
       <c r="S149" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16991,10 +16986,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128362655</v>
+        <v>128362657</v>
       </c>
       <c r="B150" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17021,7 +17016,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -17035,13 +17030,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>720897</v>
+        <v>720904</v>
       </c>
       <c r="R150" t="n">
-        <v>6382932</v>
+        <v>6382940</v>
       </c>
       <c r="S150" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17102,10 +17097,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128362594</v>
+        <v>128362655</v>
       </c>
       <c r="B151" t="n">
-        <v>98506</v>
+        <v>98569</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17113,26 +17108,26 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -17142,17 +17137,17 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2112, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>720898</v>
+        <v>720897</v>
       </c>
       <c r="R151" t="n">
-        <v>6382990</v>
+        <v>6382932</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17216,7 +17211,7 @@
         <v>128362668</v>
       </c>
       <c r="B152" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17324,10 +17319,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128362600</v>
+        <v>128362665</v>
       </c>
       <c r="B153" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17354,7 +17349,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -17368,13 +17363,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>720876</v>
+        <v>720967</v>
       </c>
       <c r="R153" t="n">
-        <v>6382976</v>
+        <v>6382919</v>
       </c>
       <c r="S153" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17435,10 +17430,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128362665</v>
+        <v>128362600</v>
       </c>
       <c r="B154" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17465,7 +17460,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -17479,13 +17474,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>720967</v>
+        <v>720876</v>
       </c>
       <c r="R154" t="n">
-        <v>6382919</v>
+        <v>6382976</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17546,37 +17541,37 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128362626</v>
+        <v>128362607</v>
       </c>
       <c r="B155" t="n">
-        <v>98610</v>
+        <v>107500</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -17586,14 +17581,14 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2097, Gtl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>720870</v>
+        <v>720820</v>
       </c>
       <c r="R155" t="n">
-        <v>6382959</v>
+        <v>6382977</v>
       </c>
       <c r="S155" t="n">
         <v>3</v>
@@ -17660,7 +17655,7 @@
         <v>128362652</v>
       </c>
       <c r="B156" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17768,10 +17763,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128362596</v>
+        <v>128362626</v>
       </c>
       <c r="B157" t="n">
-        <v>98566</v>
+        <v>98613</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17779,26 +17774,26 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -17808,17 +17803,17 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>720898</v>
+        <v>720870</v>
       </c>
       <c r="R157" t="n">
-        <v>6382990</v>
+        <v>6382959</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17879,37 +17874,37 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128362607</v>
+        <v>128362596</v>
       </c>
       <c r="B158" t="n">
-        <v>107491</v>
+        <v>98569</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -17919,17 +17914,17 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2097, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>720820</v>
+        <v>720898</v>
       </c>
       <c r="R158" t="n">
-        <v>6382977</v>
+        <v>6382990</v>
       </c>
       <c r="S158" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17993,7 +17988,7 @@
         <v>128362621</v>
       </c>
       <c r="B159" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18101,10 +18096,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128362659</v>
+        <v>128362623</v>
       </c>
       <c r="B160" t="n">
-        <v>98566</v>
+        <v>98509</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18112,26 +18107,26 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -18141,17 +18136,17 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>720910</v>
+        <v>720854</v>
       </c>
       <c r="R160" t="n">
-        <v>6382934</v>
+        <v>6382954</v>
       </c>
       <c r="S160" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18212,10 +18207,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128362623</v>
+        <v>128362659</v>
       </c>
       <c r="B161" t="n">
-        <v>98506</v>
+        <v>98569</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18223,26 +18218,26 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -18252,17 +18247,17 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>720854</v>
+        <v>720910</v>
       </c>
       <c r="R161" t="n">
-        <v>6382954</v>
+        <v>6382934</v>
       </c>
       <c r="S161" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18326,7 +18321,7 @@
         <v>128362663</v>
       </c>
       <c r="B162" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18437,7 +18432,7 @@
         <v>128362670</v>
       </c>
       <c r="B163" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18545,37 +18540,37 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128362666</v>
+        <v>128362644</v>
       </c>
       <c r="B164" t="n">
-        <v>107491</v>
+        <v>98613</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -18585,14 +18580,14 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>720954</v>
+        <v>720889</v>
       </c>
       <c r="R164" t="n">
-        <v>6382931</v>
+        <v>6382907</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -18656,10 +18651,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128362617</v>
+        <v>128362614</v>
       </c>
       <c r="B165" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18686,7 +18681,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -18700,13 +18695,13 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>720861</v>
+        <v>720854</v>
       </c>
       <c r="R165" t="n">
-        <v>6383000</v>
+        <v>6383001</v>
       </c>
       <c r="S165" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18770,7 +18765,7 @@
         <v>128362672</v>
       </c>
       <c r="B166" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18878,10 +18873,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128362614</v>
+        <v>128362617</v>
       </c>
       <c r="B167" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18908,7 +18903,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18922,13 +18917,13 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>720854</v>
+        <v>720861</v>
       </c>
       <c r="R167" t="n">
-        <v>6383001</v>
+        <v>6383000</v>
       </c>
       <c r="S167" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18989,37 +18984,37 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128362644</v>
+        <v>128362666</v>
       </c>
       <c r="B168" t="n">
-        <v>98610</v>
+        <v>107500</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -19029,14 +19024,14 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>720889</v>
+        <v>720954</v>
       </c>
       <c r="R168" t="n">
-        <v>6382907</v>
+        <v>6382931</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -14478,48 +14478,57 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128362595</v>
+        <v>128362627</v>
       </c>
       <c r="B127" t="n">
-        <v>109444</v>
+        <v>98509</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>720898</v>
+        <v>720870</v>
       </c>
       <c r="R127" t="n">
-        <v>6382990</v>
+        <v>6382959</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14580,10 +14589,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128362627</v>
+        <v>128362604</v>
       </c>
       <c r="B128" t="n">
-        <v>98509</v>
+        <v>98569</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14591,26 +14600,26 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14620,17 +14629,17 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>720870</v>
+        <v>720857</v>
       </c>
       <c r="R128" t="n">
-        <v>6382959</v>
+        <v>6382943</v>
       </c>
       <c r="S128" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14691,7 +14700,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128362604</v>
+        <v>128362638</v>
       </c>
       <c r="B129" t="n">
         <v>98569</v>
@@ -14721,7 +14730,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14735,10 +14744,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>720857</v>
+        <v>720872</v>
       </c>
       <c r="R129" t="n">
-        <v>6382943</v>
+        <v>6382941</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -14802,10 +14811,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128362638</v>
+        <v>128362622</v>
       </c>
       <c r="B130" t="n">
-        <v>98569</v>
+        <v>98613</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14813,26 +14822,26 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14842,17 +14851,17 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>720872</v>
+        <v>720854</v>
       </c>
       <c r="R130" t="n">
-        <v>6382941</v>
+        <v>6382954</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14913,57 +14922,48 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128362622</v>
+        <v>128362595</v>
       </c>
       <c r="B131" t="n">
-        <v>98613</v>
+        <v>109444</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>720854</v>
+        <v>720898</v>
       </c>
       <c r="R131" t="n">
-        <v>6382954</v>
+        <v>6382990</v>
       </c>
       <c r="S131" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128362632</v>
+        <v>128362598</v>
       </c>
       <c r="B134" t="n">
         <v>98569</v>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15281,13 +15281,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>720866</v>
+        <v>720886</v>
       </c>
       <c r="R134" t="n">
-        <v>6382946</v>
+        <v>6382981</v>
       </c>
       <c r="S134" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128362598</v>
+        <v>128362632</v>
       </c>
       <c r="B135" t="n">
         <v>98569</v>
@@ -15378,7 +15378,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15392,13 +15392,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>720886</v>
+        <v>720866</v>
       </c>
       <c r="R135" t="n">
-        <v>6382981</v>
+        <v>6382946</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15792,10 +15792,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128362647</v>
+        <v>128362758</v>
       </c>
       <c r="B139" t="n">
-        <v>98569</v>
+        <v>96187</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15803,46 +15803,46 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>219798</v>
+        <v>2180</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>720889</v>
+        <v>720904</v>
       </c>
       <c r="R139" t="n">
-        <v>6382907</v>
+        <v>6382940</v>
       </c>
       <c r="S139" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -15903,10 +15903,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128362758</v>
+        <v>128362647</v>
       </c>
       <c r="B140" t="n">
-        <v>96187</v>
+        <v>98569</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15914,46 +15914,46 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2180</v>
+        <v>219798</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>720904</v>
+        <v>720889</v>
       </c>
       <c r="R140" t="n">
-        <v>6382940</v>
+        <v>6382907</v>
       </c>
       <c r="S140" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -17541,37 +17541,37 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128362607</v>
+        <v>128362652</v>
       </c>
       <c r="B155" t="n">
-        <v>107500</v>
+        <v>98569</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -17581,17 +17581,17 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2097, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>720820</v>
+        <v>720884</v>
       </c>
       <c r="R155" t="n">
-        <v>6382977</v>
+        <v>6382924</v>
       </c>
       <c r="S155" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17652,10 +17652,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128362652</v>
+        <v>128362626</v>
       </c>
       <c r="B156" t="n">
-        <v>98569</v>
+        <v>98613</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17663,26 +17663,26 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -17692,17 +17692,17 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>720884</v>
+        <v>720870</v>
       </c>
       <c r="R156" t="n">
-        <v>6382924</v>
+        <v>6382959</v>
       </c>
       <c r="S156" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17763,37 +17763,37 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128362626</v>
+        <v>128362607</v>
       </c>
       <c r="B157" t="n">
-        <v>98613</v>
+        <v>107500</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -17803,14 +17803,14 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2097, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>720870</v>
+        <v>720820</v>
       </c>
       <c r="R157" t="n">
-        <v>6382959</v>
+        <v>6382977</v>
       </c>
       <c r="S157" t="n">
         <v>3</v>
@@ -18540,37 +18540,37 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128362644</v>
+        <v>128362666</v>
       </c>
       <c r="B164" t="n">
-        <v>98613</v>
+        <v>107500</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -18580,14 +18580,14 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>720889</v>
+        <v>720954</v>
       </c>
       <c r="R164" t="n">
-        <v>6382907</v>
+        <v>6382931</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -18651,10 +18651,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128362614</v>
+        <v>128362644</v>
       </c>
       <c r="B165" t="n">
-        <v>98569</v>
+        <v>98613</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18662,26 +18662,26 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -18691,17 +18691,17 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>720854</v>
+        <v>720889</v>
       </c>
       <c r="R165" t="n">
-        <v>6383001</v>
+        <v>6382907</v>
       </c>
       <c r="S165" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128362672</v>
+        <v>128362614</v>
       </c>
       <c r="B166" t="n">
         <v>98569</v>
@@ -18806,13 +18806,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>720992</v>
+        <v>720854</v>
       </c>
       <c r="R166" t="n">
-        <v>6382917</v>
+        <v>6383001</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128362617</v>
+        <v>128362672</v>
       </c>
       <c r="B167" t="n">
         <v>98569</v>
@@ -18903,7 +18903,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18917,13 +18917,13 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>720861</v>
+        <v>720992</v>
       </c>
       <c r="R167" t="n">
-        <v>6383000</v>
+        <v>6382917</v>
       </c>
       <c r="S167" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18984,32 +18984,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128362666</v>
+        <v>128362617</v>
       </c>
       <c r="B168" t="n">
-        <v>107500</v>
+        <v>98569</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -19024,14 +19024,14 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>720954</v>
+        <v>720861</v>
       </c>
       <c r="R168" t="n">
-        <v>6382931</v>
+        <v>6383000</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY168"/>
+  <dimension ref="A1:AY212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,7 +804,7 @@
         <v>105082160</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>128362610</v>
       </c>
       <c r="B123" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>128362625</v>
       </c>
       <c r="B124" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>128362631</v>
       </c>
       <c r="B125" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>128362609</v>
       </c>
       <c r="B126" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14478,10 +14478,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128362627</v>
+        <v>128362604</v>
       </c>
       <c r="B127" t="n">
-        <v>98509</v>
+        <v>98570</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14489,26 +14489,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14518,17 +14518,17 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>720870</v>
+        <v>720857</v>
       </c>
       <c r="R127" t="n">
-        <v>6382959</v>
+        <v>6382943</v>
       </c>
       <c r="S127" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14589,10 +14589,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128362604</v>
+        <v>128362638</v>
       </c>
       <c r="B128" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14633,10 +14633,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>720857</v>
+        <v>720872</v>
       </c>
       <c r="R128" t="n">
-        <v>6382943</v>
+        <v>6382941</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14700,10 +14700,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128362638</v>
+        <v>128362622</v>
       </c>
       <c r="B129" t="n">
-        <v>98569</v>
+        <v>98614</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14711,26 +14711,26 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14740,17 +14740,17 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>720872</v>
+        <v>720854</v>
       </c>
       <c r="R129" t="n">
-        <v>6382941</v>
+        <v>6382954</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14811,57 +14811,48 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128362622</v>
+        <v>128362595</v>
       </c>
       <c r="B130" t="n">
-        <v>98613</v>
+        <v>109449</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>720854</v>
+        <v>720898</v>
       </c>
       <c r="R130" t="n">
-        <v>6382954</v>
+        <v>6382990</v>
       </c>
       <c r="S130" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14922,48 +14913,57 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128362595</v>
+        <v>128362627</v>
       </c>
       <c r="B131" t="n">
-        <v>109444</v>
+        <v>98510</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>720898</v>
+        <v>720870</v>
       </c>
       <c r="R131" t="n">
-        <v>6382990</v>
+        <v>6382959</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15024,57 +15024,48 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128362619</v>
+        <v>128362671</v>
       </c>
       <c r="B132" t="n">
-        <v>98569</v>
+        <v>109449</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2044, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>720859</v>
+        <v>720992</v>
       </c>
       <c r="R132" t="n">
-        <v>6382986</v>
+        <v>6382917</v>
       </c>
       <c r="S132" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15135,48 +15126,57 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128362671</v>
+        <v>128362619</v>
       </c>
       <c r="B133" t="n">
-        <v>109444</v>
+        <v>98570</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2044, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>720992</v>
+        <v>720859</v>
       </c>
       <c r="R133" t="n">
-        <v>6382917</v>
+        <v>6382986</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15237,10 +15237,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128362598</v>
+        <v>128362632</v>
       </c>
       <c r="B134" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15281,13 +15281,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>720886</v>
+        <v>720866</v>
       </c>
       <c r="R134" t="n">
-        <v>6382981</v>
+        <v>6382946</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15348,10 +15348,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128362632</v>
+        <v>128362598</v>
       </c>
       <c r="B135" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15392,13 +15392,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>720866</v>
+        <v>720886</v>
       </c>
       <c r="R135" t="n">
-        <v>6382946</v>
+        <v>6382981</v>
       </c>
       <c r="S135" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>128362630</v>
       </c>
       <c r="B136" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15570,32 +15570,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128362639</v>
+        <v>128362758</v>
       </c>
       <c r="B137" t="n">
-        <v>106211</v>
+        <v>96188</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220785</v>
+        <v>2180</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -15605,22 +15605,22 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>720889</v>
+        <v>720904</v>
       </c>
       <c r="R137" t="n">
-        <v>6382907</v>
+        <v>6382940</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15681,37 +15681,37 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128362640</v>
+        <v>128362647</v>
       </c>
       <c r="B138" t="n">
-        <v>109444</v>
+        <v>98570</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
@@ -15792,32 +15792,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128362758</v>
+        <v>128362639</v>
       </c>
       <c r="B139" t="n">
-        <v>96187</v>
+        <v>106216</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2180</v>
+        <v>220785</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -15827,22 +15827,22 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>720904</v>
+        <v>720889</v>
       </c>
       <c r="R139" t="n">
-        <v>6382940</v>
+        <v>6382907</v>
       </c>
       <c r="S139" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -15903,37 +15903,37 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128362647</v>
+        <v>128362640</v>
       </c>
       <c r="B140" t="n">
-        <v>98569</v>
+        <v>109449</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15943,7 +15943,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
@@ -16017,7 +16017,7 @@
         <v>128362661</v>
       </c>
       <c r="B141" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>128362635</v>
       </c>
       <c r="B142" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16236,37 +16236,37 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128362611</v>
+        <v>128362615</v>
       </c>
       <c r="B143" t="n">
-        <v>99344</v>
+        <v>98570</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>222361</v>
+        <v>219798</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -16276,14 +16276,14 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
         <v>720854</v>
       </c>
       <c r="R143" t="n">
-        <v>6383001</v>
+        <v>6382995</v>
       </c>
       <c r="S143" t="n">
         <v>3</v>
@@ -16350,7 +16350,7 @@
         <v>128362628</v>
       </c>
       <c r="B144" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>128362656</v>
       </c>
       <c r="B145" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16551,37 +16551,37 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128362615</v>
+        <v>128362611</v>
       </c>
       <c r="B146" t="n">
-        <v>98569</v>
+        <v>99345</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>219798</v>
+        <v>222361</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -16591,14 +16591,14 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
         <v>720854</v>
       </c>
       <c r="R146" t="n">
-        <v>6382995</v>
+        <v>6383001</v>
       </c>
       <c r="S146" t="n">
         <v>3</v>
@@ -16665,7 +16665,7 @@
         <v>128362612</v>
       </c>
       <c r="B147" t="n">
-        <v>98509</v>
+        <v>98510</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>128362597</v>
       </c>
       <c r="B148" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>128362594</v>
       </c>
       <c r="B149" t="n">
-        <v>98509</v>
+        <v>98510</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>128362657</v>
       </c>
       <c r="B150" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>128362655</v>
       </c>
       <c r="B151" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>128362668</v>
       </c>
       <c r="B152" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>128362665</v>
       </c>
       <c r="B153" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>128362600</v>
       </c>
       <c r="B154" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17541,37 +17541,37 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128362652</v>
+        <v>128362607</v>
       </c>
       <c r="B155" t="n">
-        <v>98569</v>
+        <v>107505</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>219798</v>
+        <v>220079</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -17581,17 +17581,17 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2097, Gtl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>720884</v>
+        <v>720820</v>
       </c>
       <c r="R155" t="n">
-        <v>6382924</v>
+        <v>6382977</v>
       </c>
       <c r="S155" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17652,10 +17652,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128362626</v>
+        <v>128362652</v>
       </c>
       <c r="B156" t="n">
-        <v>98613</v>
+        <v>98570</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17663,26 +17663,26 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -17692,17 +17692,17 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>720870</v>
+        <v>720884</v>
       </c>
       <c r="R156" t="n">
-        <v>6382959</v>
+        <v>6382924</v>
       </c>
       <c r="S156" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17763,37 +17763,37 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128362607</v>
+        <v>128362626</v>
       </c>
       <c r="B157" t="n">
-        <v>107500</v>
+        <v>98614</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -17803,14 +17803,14 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2097, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>720820</v>
+        <v>720870</v>
       </c>
       <c r="R157" t="n">
-        <v>6382977</v>
+        <v>6382959</v>
       </c>
       <c r="S157" t="n">
         <v>3</v>
@@ -17877,7 +17877,7 @@
         <v>128362596</v>
       </c>
       <c r="B158" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>128362621</v>
       </c>
       <c r="B159" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128362623</v>
+        <v>128362659</v>
       </c>
       <c r="B160" t="n">
-        <v>98509</v>
+        <v>98570</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18107,26 +18107,26 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -18136,17 +18136,17 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>720854</v>
+        <v>720910</v>
       </c>
       <c r="R160" t="n">
-        <v>6382954</v>
+        <v>6382934</v>
       </c>
       <c r="S160" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18207,10 +18207,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128362659</v>
+        <v>128362623</v>
       </c>
       <c r="B161" t="n">
-        <v>98569</v>
+        <v>98510</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18218,26 +18218,26 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -18247,17 +18247,17 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>720910</v>
+        <v>720854</v>
       </c>
       <c r="R161" t="n">
-        <v>6382934</v>
+        <v>6382954</v>
       </c>
       <c r="S161" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>128362663</v>
       </c>
       <c r="B162" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>128362670</v>
       </c>
       <c r="B163" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18540,37 +18540,37 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128362666</v>
+        <v>128362644</v>
       </c>
       <c r="B164" t="n">
-        <v>107500</v>
+        <v>98614</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -18580,14 +18580,14 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>720954</v>
+        <v>720889</v>
       </c>
       <c r="R164" t="n">
-        <v>6382931</v>
+        <v>6382907</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -18651,10 +18651,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128362644</v>
+        <v>128362614</v>
       </c>
       <c r="B165" t="n">
-        <v>98613</v>
+        <v>98570</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18662,26 +18662,26 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -18691,17 +18691,17 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>720889</v>
+        <v>720854</v>
       </c>
       <c r="R165" t="n">
-        <v>6382907</v>
+        <v>6383001</v>
       </c>
       <c r="S165" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18762,10 +18762,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128362614</v>
+        <v>128362672</v>
       </c>
       <c r="B166" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18806,13 +18806,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>720854</v>
+        <v>720992</v>
       </c>
       <c r="R166" t="n">
-        <v>6383001</v>
+        <v>6382917</v>
       </c>
       <c r="S166" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18873,10 +18873,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128362672</v>
+        <v>128362617</v>
       </c>
       <c r="B167" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18917,13 +18917,13 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>720992</v>
+        <v>720861</v>
       </c>
       <c r="R167" t="n">
-        <v>6382917</v>
+        <v>6383000</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18984,32 +18984,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128362617</v>
+        <v>128362666</v>
       </c>
       <c r="B168" t="n">
-        <v>98569</v>
+        <v>107505</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>219798</v>
+        <v>220079</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -19024,14 +19024,14 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>720861</v>
+        <v>720954</v>
       </c>
       <c r="R168" t="n">
-        <v>6383000</v>
+        <v>6382931</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -19092,6 +19092,4538 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>128808200</v>
+      </c>
+      <c r="B169" t="n">
+        <v>98614</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>720849</v>
+      </c>
+      <c r="R169" t="n">
+        <v>6383016</v>
+      </c>
+      <c r="S169" t="n">
+        <v>10</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>128808204</v>
+      </c>
+      <c r="B170" t="n">
+        <v>107505</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>720903</v>
+      </c>
+      <c r="R170" t="n">
+        <v>6382925</v>
+      </c>
+      <c r="S170" t="n">
+        <v>10</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>128808194</v>
+      </c>
+      <c r="B171" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>720872</v>
+      </c>
+      <c r="R171" t="n">
+        <v>6382981</v>
+      </c>
+      <c r="S171" t="n">
+        <v>10</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF171" t="inlineStr"/>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>128808213</v>
+      </c>
+      <c r="B172" t="n">
+        <v>86890</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>720849</v>
+      </c>
+      <c r="R172" t="n">
+        <v>6383038</v>
+      </c>
+      <c r="S172" t="n">
+        <v>10</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>128811517</v>
+      </c>
+      <c r="B173" t="n">
+        <v>86815</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>442</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Bullspindling</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Cortinarius corrosus</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>720799</v>
+      </c>
+      <c r="R173" t="n">
+        <v>6382978</v>
+      </c>
+      <c r="S173" t="n">
+        <v>10</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT173" t="inlineStr"/>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>128808210</v>
+      </c>
+      <c r="B174" t="n">
+        <v>86815</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>442</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Bullspindling</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Cortinarius corrosus</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>720874</v>
+      </c>
+      <c r="R174" t="n">
+        <v>6382938</v>
+      </c>
+      <c r="S174" t="n">
+        <v>10</v>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Negativ KOH hattkant och bulbkant.</t>
+        </is>
+      </c>
+      <c r="AD174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF174" t="inlineStr"/>
+      <c r="AG174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT174" t="inlineStr"/>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>128808201</v>
+      </c>
+      <c r="B175" t="n">
+        <v>92221</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>720882</v>
+      </c>
+      <c r="R175" t="n">
+        <v>6382914</v>
+      </c>
+      <c r="S175" t="n">
+        <v>10</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF175" t="inlineStr"/>
+      <c r="AG175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT175" t="inlineStr"/>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>128808203</v>
+      </c>
+      <c r="B176" t="n">
+        <v>105641</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>720949</v>
+      </c>
+      <c r="R176" t="n">
+        <v>6382867</v>
+      </c>
+      <c r="S176" t="n">
+        <v>10</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT176" t="inlineStr"/>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>128808205</v>
+      </c>
+      <c r="B177" t="n">
+        <v>107505</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>720773</v>
+      </c>
+      <c r="R177" t="n">
+        <v>6383077</v>
+      </c>
+      <c r="S177" t="n">
+        <v>10</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT177" t="inlineStr"/>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>128808208</v>
+      </c>
+      <c r="B178" t="n">
+        <v>86815</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>442</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Bullspindling</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Cortinarius corrosus</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>720873</v>
+      </c>
+      <c r="R178" t="n">
+        <v>6382935</v>
+      </c>
+      <c r="S178" t="n">
+        <v>10</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>1 fk</t>
+        </is>
+      </c>
+      <c r="AD178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT178" t="inlineStr"/>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>128811515</v>
+      </c>
+      <c r="B179" t="n">
+        <v>86984</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>433</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>720871</v>
+      </c>
+      <c r="R179" t="n">
+        <v>6382781</v>
+      </c>
+      <c r="S179" t="n">
+        <v>10</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT179" t="inlineStr"/>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>128811516</v>
+      </c>
+      <c r="B180" t="n">
+        <v>86815</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>442</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Bullspindling</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Cortinarius corrosus</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>720793</v>
+      </c>
+      <c r="R180" t="n">
+        <v>6382789</v>
+      </c>
+      <c r="S180" t="n">
+        <v>10</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT180" t="inlineStr"/>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>128811522</v>
+      </c>
+      <c r="B181" t="n">
+        <v>86890</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>720847</v>
+      </c>
+      <c r="R181" t="n">
+        <v>6383038</v>
+      </c>
+      <c r="S181" t="n">
+        <v>10</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>128808197</v>
+      </c>
+      <c r="B182" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>720926</v>
+      </c>
+      <c r="R182" t="n">
+        <v>6382874</v>
+      </c>
+      <c r="S182" t="n">
+        <v>10</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF182" t="inlineStr"/>
+      <c r="AG182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT182" t="inlineStr"/>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>128811505</v>
+      </c>
+      <c r="B183" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>720776</v>
+      </c>
+      <c r="R183" t="n">
+        <v>6382965</v>
+      </c>
+      <c r="S183" t="n">
+        <v>10</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF183" t="inlineStr"/>
+      <c r="AG183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT183" t="inlineStr"/>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>128811513</v>
+      </c>
+      <c r="B184" t="n">
+        <v>90928</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>720914</v>
+      </c>
+      <c r="R184" t="n">
+        <v>6382786</v>
+      </c>
+      <c r="S184" t="n">
+        <v>10</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>128811501</v>
+      </c>
+      <c r="B185" t="n">
+        <v>86729</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>720786</v>
+      </c>
+      <c r="R185" t="n">
+        <v>6383069</v>
+      </c>
+      <c r="S185" t="n">
+        <v>10</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>128811502</v>
+      </c>
+      <c r="B186" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>720958</v>
+      </c>
+      <c r="R186" t="n">
+        <v>6382920</v>
+      </c>
+      <c r="S186" t="n">
+        <v>10</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF186" t="inlineStr"/>
+      <c r="AG186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>128808198</v>
+      </c>
+      <c r="B187" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>720928</v>
+      </c>
+      <c r="R187" t="n">
+        <v>6382883</v>
+      </c>
+      <c r="S187" t="n">
+        <v>10</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF187" t="inlineStr"/>
+      <c r="AG187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>128808186</v>
+      </c>
+      <c r="B188" t="n">
+        <v>86729</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>720940</v>
+      </c>
+      <c r="R188" t="n">
+        <v>6382871</v>
+      </c>
+      <c r="S188" t="n">
+        <v>10</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF188" t="inlineStr"/>
+      <c r="AG188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT188" t="inlineStr"/>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>128811503</v>
+      </c>
+      <c r="B189" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>720839</v>
+      </c>
+      <c r="R189" t="n">
+        <v>6382829</v>
+      </c>
+      <c r="S189" t="n">
+        <v>10</v>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF189" t="inlineStr"/>
+      <c r="AG189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT189" t="inlineStr"/>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>128811496</v>
+      </c>
+      <c r="B190" t="n">
+        <v>86775</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>424</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>720807</v>
+      </c>
+      <c r="R190" t="n">
+        <v>6382962</v>
+      </c>
+      <c r="S190" t="n">
+        <v>10</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT190" t="inlineStr"/>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>128811498</v>
+      </c>
+      <c r="B191" t="n">
+        <v>92785</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>720831</v>
+      </c>
+      <c r="R191" t="n">
+        <v>6383010</v>
+      </c>
+      <c r="S191" t="n">
+        <v>10</v>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT191" t="inlineStr"/>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>128811497</v>
+      </c>
+      <c r="B192" t="n">
+        <v>92785</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>720815</v>
+      </c>
+      <c r="R192" t="n">
+        <v>6382996</v>
+      </c>
+      <c r="S192" t="n">
+        <v>10</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT192" t="inlineStr"/>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>128811511</v>
+      </c>
+      <c r="B193" t="n">
+        <v>107505</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>720728</v>
+      </c>
+      <c r="R193" t="n">
+        <v>6382877</v>
+      </c>
+      <c r="S193" t="n">
+        <v>10</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT193" t="inlineStr"/>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>128811512</v>
+      </c>
+      <c r="B194" t="n">
+        <v>86843</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>720762</v>
+      </c>
+      <c r="R194" t="n">
+        <v>6382917</v>
+      </c>
+      <c r="S194" t="n">
+        <v>10</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT194" t="inlineStr"/>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>128811507</v>
+      </c>
+      <c r="B195" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>720812</v>
+      </c>
+      <c r="R195" t="n">
+        <v>6382982</v>
+      </c>
+      <c r="S195" t="n">
+        <v>10</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF195" t="inlineStr"/>
+      <c r="AG195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>128811521</v>
+      </c>
+      <c r="B196" t="n">
+        <v>86890</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>720848</v>
+      </c>
+      <c r="R196" t="n">
+        <v>6382975</v>
+      </c>
+      <c r="S196" t="n">
+        <v>10</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>128811509</v>
+      </c>
+      <c r="B197" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>720782</v>
+      </c>
+      <c r="R197" t="n">
+        <v>6383068</v>
+      </c>
+      <c r="S197" t="n">
+        <v>10</v>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF197" t="inlineStr"/>
+      <c r="AG197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT197" t="inlineStr"/>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>128808191</v>
+      </c>
+      <c r="B198" t="n">
+        <v>92749</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>720923</v>
+      </c>
+      <c r="R198" t="n">
+        <v>6382884</v>
+      </c>
+      <c r="S198" t="n">
+        <v>10</v>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT198" t="inlineStr"/>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>128811508</v>
+      </c>
+      <c r="B199" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>720828</v>
+      </c>
+      <c r="R199" t="n">
+        <v>6383032</v>
+      </c>
+      <c r="S199" t="n">
+        <v>10</v>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF199" t="inlineStr"/>
+      <c r="AG199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT199" t="inlineStr"/>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>128808196</v>
+      </c>
+      <c r="B200" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>720882</v>
+      </c>
+      <c r="R200" t="n">
+        <v>6382944</v>
+      </c>
+      <c r="S200" t="n">
+        <v>10</v>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF200" t="inlineStr"/>
+      <c r="AG200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT200" t="inlineStr"/>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>128811514</v>
+      </c>
+      <c r="B201" t="n">
+        <v>90928</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>720775</v>
+      </c>
+      <c r="R201" t="n">
+        <v>6382814</v>
+      </c>
+      <c r="S201" t="n">
+        <v>10</v>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT201" t="inlineStr"/>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>128808209</v>
+      </c>
+      <c r="B202" t="n">
+        <v>86775</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>424</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>720782</v>
+      </c>
+      <c r="R202" t="n">
+        <v>6383065</v>
+      </c>
+      <c r="S202" t="n">
+        <v>10</v>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>3 fk bild</t>
+        </is>
+      </c>
+      <c r="AD202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT202" t="inlineStr"/>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>128811506</v>
+      </c>
+      <c r="B203" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>720791</v>
+      </c>
+      <c r="R203" t="n">
+        <v>6382968</v>
+      </c>
+      <c r="S203" t="n">
+        <v>10</v>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF203" t="inlineStr"/>
+      <c r="AG203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT203" t="inlineStr"/>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>128808207</v>
+      </c>
+      <c r="B204" t="n">
+        <v>90928</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>720854</v>
+      </c>
+      <c r="R204" t="n">
+        <v>6382963</v>
+      </c>
+      <c r="S204" t="n">
+        <v>10</v>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT204" t="inlineStr"/>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>128808192</v>
+      </c>
+      <c r="B205" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>720870</v>
+      </c>
+      <c r="R205" t="n">
+        <v>6382928</v>
+      </c>
+      <c r="S205" t="n">
+        <v>10</v>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF205" t="inlineStr"/>
+      <c r="AG205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT205" t="inlineStr"/>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>128812128</v>
+      </c>
+      <c r="B206" t="n">
+        <v>105641</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>720940</v>
+      </c>
+      <c r="R206" t="n">
+        <v>6382871</v>
+      </c>
+      <c r="S206" t="n">
+        <v>10</v>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT206" t="inlineStr"/>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>128808211</v>
+      </c>
+      <c r="B207" t="n">
+        <v>90234</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>245042</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Besk kastanjemusseron</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Tricholoma batschii</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q207" t="n">
+        <v>720816</v>
+      </c>
+      <c r="R207" t="n">
+        <v>6382972</v>
+      </c>
+      <c r="S207" t="n">
+        <v>10</v>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT207" t="inlineStr"/>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>128808206</v>
+      </c>
+      <c r="B208" t="n">
+        <v>90928</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q208" t="n">
+        <v>720877</v>
+      </c>
+      <c r="R208" t="n">
+        <v>6382941</v>
+      </c>
+      <c r="S208" t="n">
+        <v>10</v>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT208" t="inlineStr"/>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>128811499</v>
+      </c>
+      <c r="B209" t="n">
+        <v>92771</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q209" t="n">
+        <v>720831</v>
+      </c>
+      <c r="R209" t="n">
+        <v>6382773</v>
+      </c>
+      <c r="S209" t="n">
+        <v>10</v>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF209" t="inlineStr"/>
+      <c r="AG209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT209" t="inlineStr"/>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>128808212</v>
+      </c>
+      <c r="B210" t="n">
+        <v>106216</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr"/>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q210" t="n">
+        <v>720875</v>
+      </c>
+      <c r="R210" t="n">
+        <v>6382950</v>
+      </c>
+      <c r="S210" t="n">
+        <v>10</v>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT210" t="inlineStr"/>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>128811504</v>
+      </c>
+      <c r="B211" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q211" t="n">
+        <v>720789</v>
+      </c>
+      <c r="R211" t="n">
+        <v>6382798</v>
+      </c>
+      <c r="S211" t="n">
+        <v>10</v>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF211" t="inlineStr"/>
+      <c r="AG211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT211" t="inlineStr"/>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>128811510</v>
+      </c>
+      <c r="B212" t="n">
+        <v>107505</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>720809</v>
+      </c>
+      <c r="R212" t="n">
+        <v>6382787</v>
+      </c>
+      <c r="S212" t="n">
+        <v>10</v>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT212" t="inlineStr"/>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>105082160</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -14478,57 +14478,48 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128362604</v>
+        <v>128362595</v>
       </c>
       <c r="B127" t="n">
-        <v>98570</v>
+        <v>109449</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>720857</v>
+        <v>720898</v>
       </c>
       <c r="R127" t="n">
-        <v>6382943</v>
+        <v>6382990</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14589,7 +14580,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128362638</v>
+        <v>128362604</v>
       </c>
       <c r="B128" t="n">
         <v>98570</v>
@@ -14619,7 +14610,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14633,10 +14624,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>720872</v>
+        <v>720857</v>
       </c>
       <c r="R128" t="n">
-        <v>6382941</v>
+        <v>6382943</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14700,10 +14691,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128362622</v>
+        <v>128362638</v>
       </c>
       <c r="B129" t="n">
-        <v>98614</v>
+        <v>98570</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14711,26 +14702,26 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14740,17 +14731,17 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>720854</v>
+        <v>720872</v>
       </c>
       <c r="R129" t="n">
-        <v>6382954</v>
+        <v>6382941</v>
       </c>
       <c r="S129" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14811,48 +14802,57 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128362595</v>
+        <v>128362622</v>
       </c>
       <c r="B130" t="n">
-        <v>109449</v>
+        <v>98614</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>720898</v>
+        <v>720854</v>
       </c>
       <c r="R130" t="n">
-        <v>6382990</v>
+        <v>6382954</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -16236,54 +16236,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128362615</v>
+        <v>128362628</v>
       </c>
       <c r="B143" t="n">
-        <v>98570</v>
+        <v>109449</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>720854</v>
+        <v>720870</v>
       </c>
       <c r="R143" t="n">
-        <v>6382995</v>
+        <v>6382959</v>
       </c>
       <c r="S143" t="n">
         <v>3</v>
@@ -16347,7 +16338,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128362628</v>
+        <v>128362656</v>
       </c>
       <c r="B144" t="n">
         <v>109449</v>
@@ -16378,17 +16369,17 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>720870</v>
+        <v>720904</v>
       </c>
       <c r="R144" t="n">
-        <v>6382959</v>
+        <v>6382940</v>
       </c>
       <c r="S144" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16449,10 +16440,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128362656</v>
+        <v>128362611</v>
       </c>
       <c r="B145" t="n">
-        <v>109449</v>
+        <v>99345</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16460,16 +16451,16 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220299</v>
+        <v>222361</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -16477,20 +16468,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>720904</v>
+        <v>720854</v>
       </c>
       <c r="R145" t="n">
-        <v>6382940</v>
+        <v>6383001</v>
       </c>
       <c r="S145" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16551,37 +16551,37 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128362611</v>
+        <v>128362615</v>
       </c>
       <c r="B146" t="n">
-        <v>99345</v>
+        <v>98570</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>222361</v>
+        <v>219798</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -16591,14 +16591,14 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
         <v>720854</v>
       </c>
       <c r="R146" t="n">
-        <v>6383001</v>
+        <v>6382995</v>
       </c>
       <c r="S146" t="n">
         <v>3</v>
@@ -16875,10 +16875,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128362594</v>
+        <v>128362657</v>
       </c>
       <c r="B149" t="n">
-        <v>98510</v>
+        <v>98570</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16886,26 +16886,26 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -16915,17 +16915,17 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2112, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>720898</v>
+        <v>720904</v>
       </c>
       <c r="R149" t="n">
-        <v>6382990</v>
+        <v>6382940</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128362657</v>
+        <v>128362655</v>
       </c>
       <c r="B150" t="n">
         <v>98570</v>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -17030,13 +17030,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>720904</v>
+        <v>720897</v>
       </c>
       <c r="R150" t="n">
-        <v>6382940</v>
+        <v>6382932</v>
       </c>
       <c r="S150" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17097,10 +17097,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128362655</v>
+        <v>128362594</v>
       </c>
       <c r="B151" t="n">
-        <v>98570</v>
+        <v>98510</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17108,26 +17108,26 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -17137,17 +17137,17 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2112, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>720897</v>
+        <v>720898</v>
       </c>
       <c r="R151" t="n">
-        <v>6382932</v>
+        <v>6382990</v>
       </c>
       <c r="S151" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>128808200</v>
       </c>
       <c r="B169" t="n">
-        <v>98614</v>
+        <v>98641</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19202,32 +19202,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128808204</v>
+        <v>128811517</v>
       </c>
       <c r="B170" t="n">
-        <v>107505</v>
+        <v>86842</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220079</v>
+        <v>442</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19237,10 +19237,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>720903</v>
+        <v>720799</v>
       </c>
       <c r="R170" t="n">
-        <v>6382925</v>
+        <v>6382978</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19270,19 +19270,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>14:12</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19297,57 +19287,60 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128808194</v>
+        <v>128808210</v>
       </c>
       <c r="B171" t="n">
-        <v>86927</v>
+        <v>86842</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6003295</v>
+        <v>442</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>720872</v>
+        <v>720874</v>
       </c>
       <c r="R171" t="n">
-        <v>6382981</v>
+        <v>6382938</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19379,7 +19372,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19389,7 +19382,12 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Negativ KOH hattkant och bulbkant.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19420,7 +19418,7 @@
         <v>128808213</v>
       </c>
       <c r="B172" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19524,32 +19522,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128811517</v>
+        <v>128808194</v>
       </c>
       <c r="B173" t="n">
-        <v>86815</v>
+        <v>86954</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>442</v>
+        <v>6003295</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19559,10 +19557,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>720799</v>
+        <v>720872</v>
       </c>
       <c r="R173" t="n">
-        <v>6382978</v>
+        <v>6382981</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19592,77 +19590,85 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
       <c r="AE173" t="b">
         <v>0</v>
       </c>
+      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128808210</v>
+        <v>128808204</v>
       </c>
       <c r="B174" t="n">
-        <v>86815</v>
+        <v>107533</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>442</v>
+        <v>220079</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>720874</v>
+        <v>720903</v>
       </c>
       <c r="R174" t="n">
-        <v>6382938</v>
+        <v>6382925</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19694,7 +19700,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19704,12 +19710,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Negativ KOH hattkant och bulbkant.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19718,7 +19719,6 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
-      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -19740,7 +19740,7 @@
         <v>128808201</v>
       </c>
       <c r="B175" t="n">
-        <v>92221</v>
+        <v>92248</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>128808203</v>
       </c>
       <c r="B176" t="n">
-        <v>105641</v>
+        <v>105669</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19955,32 +19955,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128808205</v>
+        <v>128808208</v>
       </c>
       <c r="B177" t="n">
-        <v>107505</v>
+        <v>86842</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220079</v>
+        <v>442</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19990,10 +19990,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>720773</v>
+        <v>720873</v>
       </c>
       <c r="R177" t="n">
-        <v>6383077</v>
+        <v>6382935</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20025,7 +20025,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -20035,7 +20035,12 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>1 fk</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20062,32 +20067,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128808208</v>
+        <v>128808205</v>
       </c>
       <c r="B178" t="n">
-        <v>86815</v>
+        <v>107533</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>442</v>
+        <v>220079</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -20097,10 +20102,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>720873</v>
+        <v>720773</v>
       </c>
       <c r="R178" t="n">
-        <v>6382935</v>
+        <v>6383077</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20132,7 +20137,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -20142,12 +20147,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>1 fk</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20177,7 +20177,7 @@
         <v>128811515</v>
       </c>
       <c r="B179" t="n">
-        <v>86984</v>
+        <v>87011</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>128811516</v>
       </c>
       <c r="B180" t="n">
-        <v>86815</v>
+        <v>86842</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>128811522</v>
       </c>
       <c r="B181" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>128808197</v>
       </c>
       <c r="B182" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>128811505</v>
       </c>
       <c r="B183" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>128811513</v>
       </c>
       <c r="B184" t="n">
-        <v>90928</v>
+        <v>90955</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>128811501</v>
       </c>
       <c r="B185" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20864,10 +20864,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128811502</v>
+        <v>128808198</v>
       </c>
       <c r="B186" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20893,19 +20893,16 @@
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>720958</v>
+        <v>720928</v>
       </c>
       <c r="R186" t="n">
-        <v>6382920</v>
+        <v>6382883</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20935,9 +20932,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20953,22 +20960,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128808198</v>
+        <v>128811502</v>
       </c>
       <c r="B187" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20994,16 +21001,19 @@
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>720928</v>
+        <v>720958</v>
       </c>
       <c r="R187" t="n">
-        <v>6382883</v>
+        <v>6382920</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21033,19 +21043,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21061,12 +21061,12 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
@@ -21076,7 +21076,7 @@
         <v>128808186</v>
       </c>
       <c r="B188" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>128811503</v>
       </c>
       <c r="B189" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>128811496</v>
       </c>
       <c r="B190" t="n">
-        <v>86775</v>
+        <v>86802</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>128811498</v>
       </c>
       <c r="B191" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>128811497</v>
       </c>
       <c r="B192" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21573,32 +21573,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128811511</v>
+        <v>128811512</v>
       </c>
       <c r="B193" t="n">
-        <v>107505</v>
+        <v>86870</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>220079</v>
+        <v>248956</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21608,10 +21608,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>720728</v>
+        <v>720762</v>
       </c>
       <c r="R193" t="n">
-        <v>6382877</v>
+        <v>6382917</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21670,45 +21670,48 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128811512</v>
+        <v>128811507</v>
       </c>
       <c r="B194" t="n">
-        <v>86843</v>
+        <v>86954</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>720762</v>
+        <v>720812</v>
       </c>
       <c r="R194" t="n">
-        <v>6382917</v>
+        <v>6382982</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21749,6 +21752,7 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
+      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
@@ -21767,10 +21771,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128811507</v>
+        <v>128811511</v>
       </c>
       <c r="B195" t="n">
-        <v>86927</v>
+        <v>107533</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21778,37 +21782,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>720812</v>
+        <v>720728</v>
       </c>
       <c r="R195" t="n">
-        <v>6382982</v>
+        <v>6382877</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21849,7 +21850,6 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -21871,7 +21871,7 @@
         <v>128811521</v>
       </c>
       <c r="B196" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>128811509</v>
       </c>
       <c r="B197" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>128808191</v>
       </c>
       <c r="B198" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>128811508</v>
       </c>
       <c r="B199" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22274,10 +22274,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128808196</v>
+        <v>128811514</v>
       </c>
       <c r="B200" t="n">
-        <v>86927</v>
+        <v>90955</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22285,21 +22285,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6003295</v>
+        <v>3286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22309,10 +22309,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>720882</v>
+        <v>720775</v>
       </c>
       <c r="R200" t="n">
-        <v>6382944</v>
+        <v>6382814</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22342,72 +22342,61 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AD200" t="b">
         <v>0</v>
       </c>
       <c r="AE200" t="b">
         <v>0</v>
       </c>
-      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128811514</v>
+        <v>128808209</v>
       </c>
       <c r="B201" t="n">
-        <v>90928</v>
+        <v>86802</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>3286</v>
+        <v>424</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -22417,10 +22406,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>720775</v>
+        <v>720782</v>
       </c>
       <c r="R201" t="n">
-        <v>6382814</v>
+        <v>6383065</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22450,9 +22439,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>3 fk bild</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22467,44 +22471,44 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128808209</v>
+        <v>128808196</v>
       </c>
       <c r="B202" t="n">
-        <v>86775</v>
+        <v>86954</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -22514,10 +22518,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>720782</v>
+        <v>720882</v>
       </c>
       <c r="R202" t="n">
-        <v>6383065</v>
+        <v>6382944</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22549,7 +22553,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -22559,12 +22563,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>3 fk bild</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22573,6 +22572,7 @@
       <c r="AE202" t="b">
         <v>0</v>
       </c>
+      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
@@ -22591,10 +22591,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128811506</v>
+        <v>128808207</v>
       </c>
       <c r="B203" t="n">
-        <v>86927</v>
+        <v>90955</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22602,37 +22602,34 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6003295</v>
+        <v>3286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>720791</v>
+        <v>720854</v>
       </c>
       <c r="R203" t="n">
-        <v>6382968</v>
+        <v>6382963</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22662,40 +22659,49 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AD203" t="b">
         <v>0</v>
       </c>
       <c r="AE203" t="b">
         <v>0</v>
       </c>
-      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
       </c>
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128808207</v>
+        <v>128808192</v>
       </c>
       <c r="B204" t="n">
-        <v>90928</v>
+        <v>86954</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22703,21 +22709,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>3286</v>
+        <v>6003295</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -22727,10 +22733,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>720854</v>
+        <v>720870</v>
       </c>
       <c r="R204" t="n">
-        <v>6382963</v>
+        <v>6382928</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22762,7 +22768,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -22772,7 +22778,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22781,6 +22787,7 @@
       <c r="AE204" t="b">
         <v>0</v>
       </c>
+      <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="b">
         <v>0</v>
       </c>
@@ -22799,32 +22806,32 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128808192</v>
+        <v>128812128</v>
       </c>
       <c r="B205" t="n">
-        <v>86927</v>
+        <v>105669</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6003295</v>
+        <v>224098</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -22834,10 +22841,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>720870</v>
+        <v>720940</v>
       </c>
       <c r="R205" t="n">
-        <v>6382928</v>
+        <v>6382871</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22869,7 +22876,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22879,7 +22886,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22888,7 +22895,6 @@
       <c r="AE205" t="b">
         <v>0</v>
       </c>
-      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
       </c>
@@ -22907,45 +22913,48 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128812128</v>
+        <v>128811506</v>
       </c>
       <c r="B206" t="n">
-        <v>105641</v>
+        <v>86954</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>720940</v>
+        <v>720791</v>
       </c>
       <c r="R206" t="n">
-        <v>6382871</v>
+        <v>6382968</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22975,39 +22984,30 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AD206" t="b">
         <v>0</v>
       </c>
       <c r="AE206" t="b">
         <v>0</v>
       </c>
+      <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="b">
         <v>0</v>
       </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
@@ -23017,7 +23017,7 @@
         <v>128808211</v>
       </c>
       <c r="B207" t="n">
-        <v>90234</v>
+        <v>90261</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>128808206</v>
       </c>
       <c r="B208" t="n">
-        <v>90928</v>
+        <v>90955</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>128811499</v>
       </c>
       <c r="B209" t="n">
-        <v>92771</v>
+        <v>92798</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>128808212</v>
       </c>
       <c r="B210" t="n">
-        <v>106216</v>
+        <v>106244</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23429,10 +23429,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128811504</v>
+        <v>128811510</v>
       </c>
       <c r="B211" t="n">
-        <v>86927</v>
+        <v>107533</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23440,37 +23440,34 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>720789</v>
+        <v>720809</v>
       </c>
       <c r="R211" t="n">
-        <v>6382798</v>
+        <v>6382787</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23511,7 +23508,6 @@
       <c r="AE211" t="b">
         <v>0</v>
       </c>
-      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
@@ -23530,10 +23526,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128811510</v>
+        <v>128811504</v>
       </c>
       <c r="B212" t="n">
-        <v>107505</v>
+        <v>86954</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23541,34 +23537,37 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>720809</v>
+        <v>720789</v>
       </c>
       <c r="R212" t="n">
-        <v>6382787</v>
+        <v>6382798</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23609,6 +23608,7 @@
       <c r="AE212" t="b">
         <v>0</v>
       </c>
+      <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -14037,7 +14037,7 @@
         <v>128362610</v>
       </c>
       <c r="B123" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>128362625</v>
       </c>
       <c r="B124" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>128362631</v>
       </c>
       <c r="B125" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>128362609</v>
       </c>
       <c r="B126" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14478,48 +14478,57 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128362595</v>
+        <v>128362627</v>
       </c>
       <c r="B127" t="n">
-        <v>109449</v>
+        <v>98537</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>720898</v>
+        <v>720870</v>
       </c>
       <c r="R127" t="n">
-        <v>6382990</v>
+        <v>6382959</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14583,7 +14592,7 @@
         <v>128362604</v>
       </c>
       <c r="B128" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14694,7 +14703,7 @@
         <v>128362638</v>
       </c>
       <c r="B129" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14805,7 +14814,7 @@
         <v>128362622</v>
       </c>
       <c r="B130" t="n">
-        <v>98614</v>
+        <v>98641</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14913,57 +14922,48 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128362627</v>
+        <v>128362595</v>
       </c>
       <c r="B131" t="n">
-        <v>98510</v>
+        <v>109477</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>720870</v>
+        <v>720898</v>
       </c>
       <c r="R131" t="n">
-        <v>6382959</v>
+        <v>6382990</v>
       </c>
       <c r="S131" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15024,48 +15024,57 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128362671</v>
+        <v>128362619</v>
       </c>
       <c r="B132" t="n">
-        <v>109449</v>
+        <v>98597</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2044, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>720992</v>
+        <v>720859</v>
       </c>
       <c r="R132" t="n">
-        <v>6382917</v>
+        <v>6382986</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15126,57 +15135,48 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128362619</v>
+        <v>128362671</v>
       </c>
       <c r="B133" t="n">
-        <v>98570</v>
+        <v>109477</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2044, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>720859</v>
+        <v>720992</v>
       </c>
       <c r="R133" t="n">
-        <v>6382986</v>
+        <v>6382917</v>
       </c>
       <c r="S133" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>128362632</v>
       </c>
       <c r="B134" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>128362598</v>
       </c>
       <c r="B135" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>128362630</v>
       </c>
       <c r="B136" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>128362758</v>
       </c>
       <c r="B137" t="n">
-        <v>96188</v>
+        <v>96215</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15681,37 +15681,37 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128362647</v>
+        <v>128362639</v>
       </c>
       <c r="B138" t="n">
-        <v>98570</v>
+        <v>106244</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
@@ -15792,37 +15792,37 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128362639</v>
+        <v>128362647</v>
       </c>
       <c r="B139" t="n">
-        <v>106216</v>
+        <v>98597</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15832,7 +15832,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
@@ -15906,7 +15906,7 @@
         <v>128362640</v>
       </c>
       <c r="B140" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>128362661</v>
       </c>
       <c r="B141" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>128362635</v>
       </c>
       <c r="B142" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>128362628</v>
       </c>
       <c r="B143" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16338,10 +16338,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128362656</v>
+        <v>128362611</v>
       </c>
       <c r="B144" t="n">
-        <v>109449</v>
+        <v>99372</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16349,16 +16349,16 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220299</v>
+        <v>222361</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -16366,20 +16366,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>720904</v>
+        <v>720854</v>
       </c>
       <c r="R144" t="n">
-        <v>6382940</v>
+        <v>6383001</v>
       </c>
       <c r="S144" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16440,10 +16449,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128362611</v>
+        <v>128362656</v>
       </c>
       <c r="B145" t="n">
-        <v>99345</v>
+        <v>109477</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16451,16 +16460,16 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>222361</v>
+        <v>220299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -16468,29 +16477,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>720854</v>
+        <v>720904</v>
       </c>
       <c r="R145" t="n">
-        <v>6383001</v>
+        <v>6382940</v>
       </c>
       <c r="S145" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>128362615</v>
       </c>
       <c r="B146" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>128362612</v>
       </c>
       <c r="B147" t="n">
-        <v>98510</v>
+        <v>98537</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>128362597</v>
       </c>
       <c r="B148" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16875,10 +16875,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128362657</v>
+        <v>128362594</v>
       </c>
       <c r="B149" t="n">
-        <v>98570</v>
+        <v>98537</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16886,26 +16886,26 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -16915,17 +16915,17 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2112, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>720904</v>
+        <v>720898</v>
       </c>
       <c r="R149" t="n">
-        <v>6382940</v>
+        <v>6382990</v>
       </c>
       <c r="S149" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16986,10 +16986,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128362655</v>
+        <v>128362657</v>
       </c>
       <c r="B150" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -17030,13 +17030,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>720897</v>
+        <v>720904</v>
       </c>
       <c r="R150" t="n">
-        <v>6382932</v>
+        <v>6382940</v>
       </c>
       <c r="S150" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17097,10 +17097,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128362594</v>
+        <v>128362655</v>
       </c>
       <c r="B151" t="n">
-        <v>98510</v>
+        <v>98597</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17108,26 +17108,26 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -17137,17 +17137,17 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2112, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>720898</v>
+        <v>720897</v>
       </c>
       <c r="R151" t="n">
-        <v>6382990</v>
+        <v>6382932</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>128362668</v>
       </c>
       <c r="B152" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>128362665</v>
       </c>
       <c r="B153" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>128362600</v>
       </c>
       <c r="B154" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>128362607</v>
       </c>
       <c r="B155" t="n">
-        <v>107505</v>
+        <v>107533</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17655,7 +17655,7 @@
         <v>128362652</v>
       </c>
       <c r="B156" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>128362626</v>
       </c>
       <c r="B157" t="n">
-        <v>98614</v>
+        <v>98641</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>128362596</v>
       </c>
       <c r="B158" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>128362621</v>
       </c>
       <c r="B159" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128362659</v>
+        <v>128362623</v>
       </c>
       <c r="B160" t="n">
-        <v>98570</v>
+        <v>98537</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18107,26 +18107,26 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -18136,17 +18136,17 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>720910</v>
+        <v>720854</v>
       </c>
       <c r="R160" t="n">
-        <v>6382934</v>
+        <v>6382954</v>
       </c>
       <c r="S160" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18207,10 +18207,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128362623</v>
+        <v>128362659</v>
       </c>
       <c r="B161" t="n">
-        <v>98510</v>
+        <v>98597</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18218,26 +18218,26 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -18247,17 +18247,17 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>720854</v>
+        <v>720910</v>
       </c>
       <c r="R161" t="n">
-        <v>6382954</v>
+        <v>6382934</v>
       </c>
       <c r="S161" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>128362663</v>
       </c>
       <c r="B162" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>128362670</v>
       </c>
       <c r="B163" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>128362644</v>
       </c>
       <c r="B164" t="n">
-        <v>98614</v>
+        <v>98641</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>128362614</v>
       </c>
       <c r="B165" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>128362672</v>
       </c>
       <c r="B166" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>128362617</v>
       </c>
       <c r="B167" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>128362666</v>
       </c>
       <c r="B168" t="n">
-        <v>107505</v>
+        <v>107533</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19202,32 +19202,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128811517</v>
+        <v>128808213</v>
       </c>
       <c r="B170" t="n">
-        <v>86842</v>
+        <v>86917</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>442</v>
+        <v>3674</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19237,10 +19237,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>720799</v>
+        <v>720849</v>
       </c>
       <c r="R170" t="n">
-        <v>6382978</v>
+        <v>6383038</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19270,9 +19270,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19287,60 +19297,57 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128808210</v>
+        <v>128808194</v>
       </c>
       <c r="B171" t="n">
-        <v>86842</v>
+        <v>86954</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>442</v>
+        <v>6003295</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>720874</v>
+        <v>720872</v>
       </c>
       <c r="R171" t="n">
-        <v>6382938</v>
+        <v>6382981</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19372,7 +19379,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19382,12 +19389,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Negativ KOH hattkant och bulbkant.</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19415,32 +19417,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128808213</v>
+        <v>128811517</v>
       </c>
       <c r="B172" t="n">
-        <v>86917</v>
+        <v>86842</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3674</v>
+        <v>442</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -19450,10 +19452,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>720849</v>
+        <v>720799</v>
       </c>
       <c r="R172" t="n">
-        <v>6383038</v>
+        <v>6382978</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19483,19 +19485,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>13:42</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19510,57 +19502,60 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128808194</v>
+        <v>128808210</v>
       </c>
       <c r="B173" t="n">
-        <v>86954</v>
+        <v>86842</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6003295</v>
+        <v>442</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>720872</v>
+        <v>720874</v>
       </c>
       <c r="R173" t="n">
-        <v>6382981</v>
+        <v>6382938</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19592,7 +19587,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19602,7 +19597,12 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>Negativ KOH hattkant och bulbkant.</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19737,48 +19737,45 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128808201</v>
+        <v>128808203</v>
       </c>
       <c r="B175" t="n">
-        <v>92248</v>
+        <v>105669</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>232138</v>
+        <v>224098</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>720882</v>
+        <v>720949</v>
       </c>
       <c r="R175" t="n">
-        <v>6382914</v>
+        <v>6382867</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19810,7 +19807,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19820,7 +19817,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19829,7 +19826,6 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -19848,45 +19844,48 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128808203</v>
+        <v>128808201</v>
       </c>
       <c r="B176" t="n">
-        <v>105669</v>
+        <v>92248</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>224098</v>
+        <v>232138</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>720949</v>
+        <v>720882</v>
       </c>
       <c r="R176" t="n">
-        <v>6382867</v>
+        <v>6382914</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19918,7 +19917,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19928,7 +19927,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19937,6 +19936,7 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -19955,32 +19955,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128808208</v>
+        <v>128808205</v>
       </c>
       <c r="B177" t="n">
-        <v>86842</v>
+        <v>107533</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>442</v>
+        <v>220079</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19990,10 +19990,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>720873</v>
+        <v>720773</v>
       </c>
       <c r="R177" t="n">
-        <v>6382935</v>
+        <v>6383077</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20025,7 +20025,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -20035,12 +20035,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>1 fk</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20067,32 +20062,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128808205</v>
+        <v>128808208</v>
       </c>
       <c r="B178" t="n">
-        <v>107533</v>
+        <v>86842</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>220079</v>
+        <v>442</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -20102,10 +20097,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>720773</v>
+        <v>720873</v>
       </c>
       <c r="R178" t="n">
-        <v>6383077</v>
+        <v>6382935</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20137,7 +20132,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -20147,7 +20142,12 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>1 fk</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20267,32 +20267,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128811516</v>
+        <v>128811522</v>
       </c>
       <c r="B180" t="n">
-        <v>86842</v>
+        <v>86917</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>442</v>
+        <v>3674</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20302,10 +20302,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>720793</v>
+        <v>720847</v>
       </c>
       <c r="R180" t="n">
-        <v>6382789</v>
+        <v>6383038</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20364,32 +20364,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128811522</v>
+        <v>128811516</v>
       </c>
       <c r="B181" t="n">
-        <v>86917</v>
+        <v>86842</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>3674</v>
+        <v>442</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -20399,10 +20399,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>720847</v>
+        <v>720793</v>
       </c>
       <c r="R181" t="n">
-        <v>6383038</v>
+        <v>6382789</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20767,32 +20767,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128811501</v>
+        <v>128808198</v>
       </c>
       <c r="B185" t="n">
-        <v>86756</v>
+        <v>86954</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20802,10 +20802,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>720786</v>
+        <v>720928</v>
       </c>
       <c r="R185" t="n">
-        <v>6383069</v>
+        <v>6382883</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20835,36 +20835,47 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AD185" t="b">
         <v>0</v>
       </c>
       <c r="AE185" t="b">
         <v>0</v>
       </c>
+      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128808198</v>
+        <v>128811502</v>
       </c>
       <c r="B186" t="n">
         <v>86954</v>
@@ -20893,16 +20904,19 @@
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>720928</v>
+        <v>720958</v>
       </c>
       <c r="R186" t="n">
-        <v>6382883</v>
+        <v>6382920</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20932,19 +20946,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20960,60 +20964,57 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128811502</v>
+        <v>128811501</v>
       </c>
       <c r="B187" t="n">
-        <v>86954</v>
+        <v>86756</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>720958</v>
+        <v>720786</v>
       </c>
       <c r="R187" t="n">
-        <v>6382920</v>
+        <v>6383069</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21054,7 +21055,6 @@
       <c r="AE187" t="b">
         <v>0</v>
       </c>
-      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
       </c>
@@ -21073,45 +21073,48 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128808186</v>
+        <v>128811503</v>
       </c>
       <c r="B188" t="n">
-        <v>86756</v>
+        <v>86954</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>720940</v>
+        <v>720839</v>
       </c>
       <c r="R188" t="n">
-        <v>6382871</v>
+        <v>6382829</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21141,19 +21144,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21169,60 +21162,57 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128811503</v>
+        <v>128808186</v>
       </c>
       <c r="B189" t="n">
-        <v>86954</v>
+        <v>86756</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>720839</v>
+        <v>720940</v>
       </c>
       <c r="R189" t="n">
-        <v>6382829</v>
+        <v>6382871</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21252,9 +21242,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21270,12 +21270,12 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
@@ -21573,32 +21573,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128811512</v>
+        <v>128811511</v>
       </c>
       <c r="B193" t="n">
-        <v>86870</v>
+        <v>107533</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>248956</v>
+        <v>220079</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21608,10 +21608,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>720762</v>
+        <v>720728</v>
       </c>
       <c r="R193" t="n">
-        <v>6382917</v>
+        <v>6382877</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21670,48 +21670,45 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128811507</v>
+        <v>128811512</v>
       </c>
       <c r="B194" t="n">
-        <v>86954</v>
+        <v>86870</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>720812</v>
+        <v>720762</v>
       </c>
       <c r="R194" t="n">
-        <v>6382982</v>
+        <v>6382917</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21752,7 +21749,6 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
-      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
@@ -21771,10 +21767,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128811511</v>
+        <v>128811507</v>
       </c>
       <c r="B195" t="n">
-        <v>107533</v>
+        <v>86954</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21782,34 +21778,37 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>720728</v>
+        <v>720812</v>
       </c>
       <c r="R195" t="n">
-        <v>6382877</v>
+        <v>6382982</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21850,6 +21849,7 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
+      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -22698,32 +22698,32 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128808192</v>
+        <v>128812128</v>
       </c>
       <c r="B204" t="n">
-        <v>86954</v>
+        <v>105669</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6003295</v>
+        <v>224098</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -22733,10 +22733,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>720870</v>
+        <v>720940</v>
       </c>
       <c r="R204" t="n">
-        <v>6382928</v>
+        <v>6382871</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22768,7 +22768,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -22778,7 +22778,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22787,7 +22787,6 @@
       <c r="AE204" t="b">
         <v>0</v>
       </c>
-      <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="b">
         <v>0</v>
       </c>
@@ -22806,32 +22805,32 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128812128</v>
+        <v>128808192</v>
       </c>
       <c r="B205" t="n">
-        <v>105669</v>
+        <v>86954</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -22841,10 +22840,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>720940</v>
+        <v>720870</v>
       </c>
       <c r="R205" t="n">
-        <v>6382871</v>
+        <v>6382928</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22876,7 +22875,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22886,7 +22885,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22895,6 +22894,7 @@
       <c r="AE205" t="b">
         <v>0</v>
       </c>
+      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
       </c>
@@ -23014,32 +23014,32 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128808211</v>
+        <v>128808206</v>
       </c>
       <c r="B207" t="n">
-        <v>90261</v>
+        <v>90955</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>245042</v>
+        <v>3286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -23049,10 +23049,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>720816</v>
+        <v>720877</v>
       </c>
       <c r="R207" t="n">
-        <v>6382972</v>
+        <v>6382941</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23084,7 +23084,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -23094,7 +23094,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23121,32 +23121,32 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128808206</v>
+        <v>128808211</v>
       </c>
       <c r="B208" t="n">
-        <v>90955</v>
+        <v>90261</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>3286</v>
+        <v>245042</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -23156,10 +23156,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>720877</v>
+        <v>720816</v>
       </c>
       <c r="R208" t="n">
-        <v>6382941</v>
+        <v>6382972</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23191,7 +23191,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -23201,7 +23201,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23322,32 +23322,32 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128808212</v>
+        <v>128811510</v>
       </c>
       <c r="B210" t="n">
-        <v>106244</v>
+        <v>107533</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>220785</v>
+        <v>220079</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -23357,10 +23357,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>720875</v>
+        <v>720809</v>
       </c>
       <c r="R210" t="n">
-        <v>6382950</v>
+        <v>6382787</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23390,19 +23390,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23417,44 +23407,44 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128811510</v>
+        <v>128808212</v>
       </c>
       <c r="B211" t="n">
-        <v>107533</v>
+        <v>106244</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>220079</v>
+        <v>220785</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23464,10 +23454,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>720809</v>
+        <v>720875</v>
       </c>
       <c r="R211" t="n">
-        <v>6382787</v>
+        <v>6382950</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23497,9 +23487,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23514,12 +23514,12 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>105082160</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -14478,57 +14478,48 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128362627</v>
+        <v>128362595</v>
       </c>
       <c r="B127" t="n">
-        <v>98537</v>
+        <v>109477</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>720870</v>
+        <v>720898</v>
       </c>
       <c r="R127" t="n">
-        <v>6382959</v>
+        <v>6382990</v>
       </c>
       <c r="S127" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14922,48 +14913,57 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128362595</v>
+        <v>128362627</v>
       </c>
       <c r="B131" t="n">
-        <v>109477</v>
+        <v>98537</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>720898</v>
+        <v>720870</v>
       </c>
       <c r="R131" t="n">
-        <v>6382990</v>
+        <v>6382959</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15024,57 +15024,48 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128362619</v>
+        <v>128362671</v>
       </c>
       <c r="B132" t="n">
-        <v>98597</v>
+        <v>109477</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2044, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>720859</v>
+        <v>720992</v>
       </c>
       <c r="R132" t="n">
-        <v>6382986</v>
+        <v>6382917</v>
       </c>
       <c r="S132" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15135,48 +15126,57 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128362671</v>
+        <v>128362619</v>
       </c>
       <c r="B133" t="n">
-        <v>109477</v>
+        <v>98597</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2044, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>720992</v>
+        <v>720859</v>
       </c>
       <c r="R133" t="n">
-        <v>6382917</v>
+        <v>6382986</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15681,37 +15681,37 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128362639</v>
+        <v>128362647</v>
       </c>
       <c r="B138" t="n">
-        <v>106244</v>
+        <v>98597</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
@@ -15792,37 +15792,37 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128362647</v>
+        <v>128362639</v>
       </c>
       <c r="B139" t="n">
-        <v>98597</v>
+        <v>106244</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15832,7 +15832,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
@@ -16338,10 +16338,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128362611</v>
+        <v>128362656</v>
       </c>
       <c r="B144" t="n">
-        <v>99372</v>
+        <v>109477</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16349,16 +16349,16 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>222361</v>
+        <v>220299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -16366,29 +16366,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>720854</v>
+        <v>720904</v>
       </c>
       <c r="R144" t="n">
-        <v>6383001</v>
+        <v>6382940</v>
       </c>
       <c r="S144" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16449,48 +16440,57 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128362656</v>
+        <v>128362615</v>
       </c>
       <c r="B145" t="n">
-        <v>109477</v>
+        <v>98597</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>720904</v>
+        <v>720854</v>
       </c>
       <c r="R145" t="n">
-        <v>6382940</v>
+        <v>6382995</v>
       </c>
       <c r="S145" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16551,37 +16551,37 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128362615</v>
+        <v>128362611</v>
       </c>
       <c r="B146" t="n">
-        <v>98597</v>
+        <v>99372</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>219798</v>
+        <v>222361</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -16591,14 +16591,14 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
         <v>720854</v>
       </c>
       <c r="R146" t="n">
-        <v>6382995</v>
+        <v>6383001</v>
       </c>
       <c r="S146" t="n">
         <v>3</v>
@@ -16875,10 +16875,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128362594</v>
+        <v>128362657</v>
       </c>
       <c r="B149" t="n">
-        <v>98537</v>
+        <v>98597</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16886,26 +16886,26 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -16915,17 +16915,17 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2112, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>720898</v>
+        <v>720904</v>
       </c>
       <c r="R149" t="n">
-        <v>6382990</v>
+        <v>6382940</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128362657</v>
+        <v>128362655</v>
       </c>
       <c r="B150" t="n">
         <v>98597</v>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -17030,13 +17030,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>720904</v>
+        <v>720897</v>
       </c>
       <c r="R150" t="n">
-        <v>6382940</v>
+        <v>6382932</v>
       </c>
       <c r="S150" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17097,10 +17097,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128362655</v>
+        <v>128362594</v>
       </c>
       <c r="B151" t="n">
-        <v>98597</v>
+        <v>98537</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17108,26 +17108,26 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -17137,17 +17137,17 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2112, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>720897</v>
+        <v>720898</v>
       </c>
       <c r="R151" t="n">
-        <v>6382932</v>
+        <v>6382990</v>
       </c>
       <c r="S151" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17541,37 +17541,37 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128362607</v>
+        <v>128362652</v>
       </c>
       <c r="B155" t="n">
-        <v>107533</v>
+        <v>98597</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -17581,17 +17581,17 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2097, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>720820</v>
+        <v>720884</v>
       </c>
       <c r="R155" t="n">
-        <v>6382977</v>
+        <v>6382924</v>
       </c>
       <c r="S155" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17652,10 +17652,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128362652</v>
+        <v>128362626</v>
       </c>
       <c r="B156" t="n">
-        <v>98597</v>
+        <v>98641</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17663,26 +17663,26 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -17692,17 +17692,17 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>720884</v>
+        <v>720870</v>
       </c>
       <c r="R156" t="n">
-        <v>6382924</v>
+        <v>6382959</v>
       </c>
       <c r="S156" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17763,10 +17763,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128362626</v>
+        <v>128362596</v>
       </c>
       <c r="B157" t="n">
-        <v>98641</v>
+        <v>98597</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17774,26 +17774,26 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -17803,17 +17803,17 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>720870</v>
+        <v>720898</v>
       </c>
       <c r="R157" t="n">
-        <v>6382959</v>
+        <v>6382990</v>
       </c>
       <c r="S157" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17874,37 +17874,37 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128362596</v>
+        <v>128362607</v>
       </c>
       <c r="B158" t="n">
-        <v>98597</v>
+        <v>107533</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>219798</v>
+        <v>220079</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -17914,17 +17914,17 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2097, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>720898</v>
+        <v>720820</v>
       </c>
       <c r="R158" t="n">
-        <v>6382990</v>
+        <v>6382977</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18540,37 +18540,37 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128362644</v>
+        <v>128362666</v>
       </c>
       <c r="B164" t="n">
-        <v>98641</v>
+        <v>107533</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -18580,14 +18580,14 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>720889</v>
+        <v>720954</v>
       </c>
       <c r="R164" t="n">
-        <v>6382907</v>
+        <v>6382931</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -18651,10 +18651,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128362614</v>
+        <v>128362644</v>
       </c>
       <c r="B165" t="n">
-        <v>98597</v>
+        <v>98641</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18662,26 +18662,26 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -18691,17 +18691,17 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>720854</v>
+        <v>720889</v>
       </c>
       <c r="R165" t="n">
-        <v>6383001</v>
+        <v>6382907</v>
       </c>
       <c r="S165" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128362672</v>
+        <v>128362614</v>
       </c>
       <c r="B166" t="n">
         <v>98597</v>
@@ -18806,13 +18806,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>720992</v>
+        <v>720854</v>
       </c>
       <c r="R166" t="n">
-        <v>6382917</v>
+        <v>6383001</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128362617</v>
+        <v>128362672</v>
       </c>
       <c r="B167" t="n">
         <v>98597</v>
@@ -18903,7 +18903,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18917,13 +18917,13 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>720861</v>
+        <v>720992</v>
       </c>
       <c r="R167" t="n">
-        <v>6383000</v>
+        <v>6382917</v>
       </c>
       <c r="S167" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18984,32 +18984,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128362666</v>
+        <v>128362617</v>
       </c>
       <c r="B168" t="n">
-        <v>107533</v>
+        <v>98597</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -19024,14 +19024,14 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>720954</v>
+        <v>720861</v>
       </c>
       <c r="R168" t="n">
-        <v>6382931</v>
+        <v>6383000</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -19098,7 +19098,7 @@
         <v>128808200</v>
       </c>
       <c r="B169" t="n">
-        <v>98641</v>
+        <v>98647</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19202,32 +19202,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128808213</v>
+        <v>128808204</v>
       </c>
       <c r="B170" t="n">
-        <v>86917</v>
+        <v>107539</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3674</v>
+        <v>220079</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19237,10 +19237,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>720849</v>
+        <v>720903</v>
       </c>
       <c r="R170" t="n">
-        <v>6383038</v>
+        <v>6382925</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19272,7 +19272,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -19282,7 +19282,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19312,7 +19312,7 @@
         <v>128808194</v>
       </c>
       <c r="B171" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>128811517</v>
       </c>
       <c r="B172" t="n">
-        <v>86842</v>
+        <v>86846</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>128808210</v>
       </c>
       <c r="B173" t="n">
-        <v>86842</v>
+        <v>86846</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19630,32 +19630,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128808204</v>
+        <v>128808213</v>
       </c>
       <c r="B174" t="n">
-        <v>107533</v>
+        <v>86921</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>220079</v>
+        <v>3674</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19665,10 +19665,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>720903</v>
+        <v>720849</v>
       </c>
       <c r="R174" t="n">
-        <v>6382925</v>
+        <v>6383038</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19700,7 +19700,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19710,7 +19710,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19737,45 +19737,48 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128808203</v>
+        <v>128808201</v>
       </c>
       <c r="B175" t="n">
-        <v>105669</v>
+        <v>92253</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>224098</v>
+        <v>232138</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>720949</v>
+        <v>720882</v>
       </c>
       <c r="R175" t="n">
-        <v>6382867</v>
+        <v>6382914</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19807,7 +19810,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19817,7 +19820,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19826,6 +19829,7 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
+      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -19844,48 +19848,45 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128808201</v>
+        <v>128808203</v>
       </c>
       <c r="B176" t="n">
-        <v>92248</v>
+        <v>105675</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>232138</v>
+        <v>224098</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>720882</v>
+        <v>720949</v>
       </c>
       <c r="R176" t="n">
-        <v>6382914</v>
+        <v>6382867</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19917,7 +19918,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19927,7 +19928,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19936,7 +19937,6 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -19955,32 +19955,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128808205</v>
+        <v>128808208</v>
       </c>
       <c r="B177" t="n">
-        <v>107533</v>
+        <v>86846</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220079</v>
+        <v>442</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19990,10 +19990,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>720773</v>
+        <v>720873</v>
       </c>
       <c r="R177" t="n">
-        <v>6383077</v>
+        <v>6382935</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20025,7 +20025,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -20035,7 +20035,12 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>1 fk</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20062,32 +20067,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128808208</v>
+        <v>128808205</v>
       </c>
       <c r="B178" t="n">
-        <v>86842</v>
+        <v>107539</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>442</v>
+        <v>220079</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -20097,10 +20102,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>720873</v>
+        <v>720773</v>
       </c>
       <c r="R178" t="n">
-        <v>6382935</v>
+        <v>6383077</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20132,7 +20137,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -20142,12 +20147,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>1 fk</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20177,7 +20177,7 @@
         <v>128811515</v>
       </c>
       <c r="B179" t="n">
-        <v>87011</v>
+        <v>87015</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20267,32 +20267,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128811522</v>
+        <v>128811516</v>
       </c>
       <c r="B180" t="n">
-        <v>86917</v>
+        <v>86846</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>3674</v>
+        <v>442</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20302,10 +20302,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>720847</v>
+        <v>720793</v>
       </c>
       <c r="R180" t="n">
-        <v>6383038</v>
+        <v>6382789</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20364,32 +20364,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128811516</v>
+        <v>128811522</v>
       </c>
       <c r="B181" t="n">
-        <v>86842</v>
+        <v>86921</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>442</v>
+        <v>3674</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -20399,10 +20399,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>720793</v>
+        <v>720847</v>
       </c>
       <c r="R181" t="n">
-        <v>6382789</v>
+        <v>6383038</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20464,7 +20464,7 @@
         <v>128808197</v>
       </c>
       <c r="B182" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>128811505</v>
       </c>
       <c r="B183" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>128811513</v>
       </c>
       <c r="B184" t="n">
-        <v>90955</v>
+        <v>90960</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20767,32 +20767,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128808198</v>
+        <v>128811501</v>
       </c>
       <c r="B185" t="n">
-        <v>86954</v>
+        <v>86760</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20802,10 +20802,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>720928</v>
+        <v>720786</v>
       </c>
       <c r="R185" t="n">
-        <v>6382883</v>
+        <v>6383069</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20835,50 +20835,39 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AD185" t="b">
         <v>0</v>
       </c>
       <c r="AE185" t="b">
         <v>0</v>
       </c>
-      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128811502</v>
+        <v>128808198</v>
       </c>
       <c r="B186" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20904,19 +20893,16 @@
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>720958</v>
+        <v>720928</v>
       </c>
       <c r="R186" t="n">
-        <v>6382920</v>
+        <v>6382883</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20946,9 +20932,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20964,57 +20960,60 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128811501</v>
+        <v>128811502</v>
       </c>
       <c r="B187" t="n">
-        <v>86756</v>
+        <v>86958</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>720786</v>
+        <v>720958</v>
       </c>
       <c r="R187" t="n">
-        <v>6383069</v>
+        <v>6382920</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21055,6 +21054,7 @@
       <c r="AE187" t="b">
         <v>0</v>
       </c>
+      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
       </c>
@@ -21073,48 +21073,45 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128811503</v>
+        <v>128808186</v>
       </c>
       <c r="B188" t="n">
-        <v>86954</v>
+        <v>86760</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>720839</v>
+        <v>720940</v>
       </c>
       <c r="R188" t="n">
-        <v>6382829</v>
+        <v>6382871</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21144,9 +21141,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21162,57 +21169,60 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128808186</v>
+        <v>128811503</v>
       </c>
       <c r="B189" t="n">
-        <v>86756</v>
+        <v>86958</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>720940</v>
+        <v>720839</v>
       </c>
       <c r="R189" t="n">
-        <v>6382871</v>
+        <v>6382829</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21242,19 +21252,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21270,44 +21270,44 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128811496</v>
+        <v>128811498</v>
       </c>
       <c r="B190" t="n">
-        <v>86802</v>
+        <v>92817</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>424</v>
+        <v>5449</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -21317,10 +21317,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>720807</v>
+        <v>720831</v>
       </c>
       <c r="R190" t="n">
-        <v>6382962</v>
+        <v>6383010</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21379,32 +21379,32 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128811498</v>
+        <v>128811496</v>
       </c>
       <c r="B191" t="n">
-        <v>92812</v>
+        <v>86806</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5449</v>
+        <v>424</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -21414,10 +21414,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>720831</v>
+        <v>720807</v>
       </c>
       <c r="R191" t="n">
-        <v>6383010</v>
+        <v>6382962</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21479,7 +21479,7 @@
         <v>128811497</v>
       </c>
       <c r="B192" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21573,32 +21573,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128811511</v>
+        <v>128811512</v>
       </c>
       <c r="B193" t="n">
-        <v>107533</v>
+        <v>86874</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>220079</v>
+        <v>248956</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21608,10 +21608,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>720728</v>
+        <v>720762</v>
       </c>
       <c r="R193" t="n">
-        <v>6382877</v>
+        <v>6382917</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21670,45 +21670,48 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128811512</v>
+        <v>128811507</v>
       </c>
       <c r="B194" t="n">
-        <v>86870</v>
+        <v>86958</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>720762</v>
+        <v>720812</v>
       </c>
       <c r="R194" t="n">
-        <v>6382917</v>
+        <v>6382982</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21749,6 +21752,7 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
+      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
@@ -21767,10 +21771,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128811507</v>
+        <v>128811511</v>
       </c>
       <c r="B195" t="n">
-        <v>86954</v>
+        <v>107539</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21778,37 +21782,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>720812</v>
+        <v>720728</v>
       </c>
       <c r="R195" t="n">
-        <v>6382982</v>
+        <v>6382877</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21849,7 +21850,6 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -21871,7 +21871,7 @@
         <v>128811521</v>
       </c>
       <c r="B196" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>128811509</v>
       </c>
       <c r="B197" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>128808191</v>
       </c>
       <c r="B198" t="n">
-        <v>92776</v>
+        <v>92781</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>128811508</v>
       </c>
       <c r="B199" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>128811514</v>
       </c>
       <c r="B200" t="n">
-        <v>90955</v>
+        <v>90960</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>128808209</v>
       </c>
       <c r="B201" t="n">
-        <v>86802</v>
+        <v>86806</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>128808196</v>
       </c>
       <c r="B202" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>128808207</v>
       </c>
       <c r="B203" t="n">
-        <v>90955</v>
+        <v>90960</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>128812128</v>
       </c>
       <c r="B204" t="n">
-        <v>105669</v>
+        <v>105675</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>128808192</v>
       </c>
       <c r="B205" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>128811506</v>
       </c>
       <c r="B206" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23017,7 +23017,7 @@
         <v>128808206</v>
       </c>
       <c r="B207" t="n">
-        <v>90955</v>
+        <v>90960</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>128808211</v>
       </c>
       <c r="B208" t="n">
-        <v>90261</v>
+        <v>90266</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>128811499</v>
       </c>
       <c r="B209" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23322,10 +23322,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128811510</v>
+        <v>128811504</v>
       </c>
       <c r="B210" t="n">
-        <v>107533</v>
+        <v>86958</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23333,34 +23333,37 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>720809</v>
+        <v>720789</v>
       </c>
       <c r="R210" t="n">
-        <v>6382787</v>
+        <v>6382798</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23401,6 +23404,7 @@
       <c r="AE210" t="b">
         <v>0</v>
       </c>
+      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
@@ -23419,32 +23423,32 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128808212</v>
+        <v>128811510</v>
       </c>
       <c r="B211" t="n">
-        <v>106244</v>
+        <v>107539</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>220785</v>
+        <v>220079</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23454,10 +23458,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>720875</v>
+        <v>720809</v>
       </c>
       <c r="R211" t="n">
-        <v>6382950</v>
+        <v>6382787</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23487,19 +23491,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z211" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB211" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23514,60 +23508,57 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128811504</v>
+        <v>128808212</v>
       </c>
       <c r="B212" t="n">
-        <v>86954</v>
+        <v>106250</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6003295</v>
+        <v>220785</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>720789</v>
+        <v>720875</v>
       </c>
       <c r="R212" t="n">
-        <v>6382798</v>
+        <v>6382950</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23597,30 +23588,39 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AD212" t="b">
         <v>0</v>
       </c>
       <c r="AE212" t="b">
         <v>0</v>
       </c>
-      <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="b">
         <v>0</v>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY212"/>
+  <dimension ref="A1:AY213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,7 +804,7 @@
         <v>105082160</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>128362610</v>
       </c>
       <c r="B123" t="n">
-        <v>98597</v>
+        <v>98610</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>128362625</v>
       </c>
       <c r="B124" t="n">
-        <v>98597</v>
+        <v>98610</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>128362631</v>
       </c>
       <c r="B125" t="n">
-        <v>98597</v>
+        <v>98610</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>128362609</v>
       </c>
       <c r="B126" t="n">
-        <v>109477</v>
+        <v>109490</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14478,48 +14478,57 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128362595</v>
+        <v>128362627</v>
       </c>
       <c r="B127" t="n">
-        <v>109477</v>
+        <v>98550</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>720898</v>
+        <v>720870</v>
       </c>
       <c r="R127" t="n">
-        <v>6382990</v>
+        <v>6382959</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14583,7 +14592,7 @@
         <v>128362604</v>
       </c>
       <c r="B128" t="n">
-        <v>98597</v>
+        <v>98610</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14694,7 +14703,7 @@
         <v>128362638</v>
       </c>
       <c r="B129" t="n">
-        <v>98597</v>
+        <v>98610</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14805,7 +14814,7 @@
         <v>128362622</v>
       </c>
       <c r="B130" t="n">
-        <v>98641</v>
+        <v>98654</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14913,57 +14922,48 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128362627</v>
+        <v>128362595</v>
       </c>
       <c r="B131" t="n">
-        <v>98537</v>
+        <v>109490</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>720870</v>
+        <v>720898</v>
       </c>
       <c r="R131" t="n">
-        <v>6382959</v>
+        <v>6382990</v>
       </c>
       <c r="S131" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15024,48 +15024,57 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128362671</v>
+        <v>128362619</v>
       </c>
       <c r="B132" t="n">
-        <v>109477</v>
+        <v>98610</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2044, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>720992</v>
+        <v>720859</v>
       </c>
       <c r="R132" t="n">
-        <v>6382917</v>
+        <v>6382986</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15126,57 +15135,48 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128362619</v>
+        <v>128362671</v>
       </c>
       <c r="B133" t="n">
-        <v>98597</v>
+        <v>109490</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2044, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>720859</v>
+        <v>720992</v>
       </c>
       <c r="R133" t="n">
-        <v>6382986</v>
+        <v>6382917</v>
       </c>
       <c r="S133" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15237,10 +15237,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128362632</v>
+        <v>128362598</v>
       </c>
       <c r="B134" t="n">
-        <v>98597</v>
+        <v>98610</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15281,13 +15281,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>720866</v>
+        <v>720886</v>
       </c>
       <c r="R134" t="n">
-        <v>6382946</v>
+        <v>6382981</v>
       </c>
       <c r="S134" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15348,10 +15348,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128362598</v>
+        <v>128362632</v>
       </c>
       <c r="B135" t="n">
-        <v>98597</v>
+        <v>98610</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15392,13 +15392,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>720886</v>
+        <v>720866</v>
       </c>
       <c r="R135" t="n">
-        <v>6382981</v>
+        <v>6382946</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>128362630</v>
       </c>
       <c r="B136" t="n">
-        <v>98597</v>
+        <v>98610</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>128362758</v>
       </c>
       <c r="B137" t="n">
-        <v>96215</v>
+        <v>96228</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15681,37 +15681,37 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128362647</v>
+        <v>128362639</v>
       </c>
       <c r="B138" t="n">
-        <v>98597</v>
+        <v>106257</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
@@ -15792,37 +15792,37 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128362639</v>
+        <v>128362647</v>
       </c>
       <c r="B139" t="n">
-        <v>106244</v>
+        <v>98610</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15832,7 +15832,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
@@ -15906,7 +15906,7 @@
         <v>128362640</v>
       </c>
       <c r="B140" t="n">
-        <v>109477</v>
+        <v>109490</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>128362661</v>
       </c>
       <c r="B141" t="n">
-        <v>98597</v>
+        <v>98610</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>128362635</v>
       </c>
       <c r="B142" t="n">
-        <v>98597</v>
+        <v>98610</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16236,45 +16236,54 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128362628</v>
+        <v>128362615</v>
       </c>
       <c r="B143" t="n">
-        <v>109477</v>
+        <v>98610</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>720870</v>
+        <v>720854</v>
       </c>
       <c r="R143" t="n">
-        <v>6382959</v>
+        <v>6382995</v>
       </c>
       <c r="S143" t="n">
         <v>3</v>
@@ -16338,10 +16347,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128362656</v>
+        <v>128362628</v>
       </c>
       <c r="B144" t="n">
-        <v>109477</v>
+        <v>109490</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16369,17 +16378,17 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>720904</v>
+        <v>720870</v>
       </c>
       <c r="R144" t="n">
-        <v>6382940</v>
+        <v>6382959</v>
       </c>
       <c r="S144" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16440,57 +16449,48 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128362615</v>
+        <v>128362656</v>
       </c>
       <c r="B145" t="n">
-        <v>98597</v>
+        <v>109490</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>720854</v>
+        <v>720904</v>
       </c>
       <c r="R145" t="n">
-        <v>6382995</v>
+        <v>6382940</v>
       </c>
       <c r="S145" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>128362611</v>
       </c>
       <c r="B146" t="n">
-        <v>99372</v>
+        <v>99385</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>128362612</v>
       </c>
       <c r="B147" t="n">
-        <v>98537</v>
+        <v>98550</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>128362597</v>
       </c>
       <c r="B148" t="n">
-        <v>109477</v>
+        <v>109490</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>128362657</v>
       </c>
       <c r="B149" t="n">
-        <v>98597</v>
+        <v>98610</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>128362655</v>
       </c>
       <c r="B150" t="n">
-        <v>98597</v>
+        <v>98610</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>128362594</v>
       </c>
       <c r="B151" t="n">
-        <v>98537</v>
+        <v>98550</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>128362668</v>
       </c>
       <c r="B152" t="n">
-        <v>98597</v>
+        <v>98610</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>128362665</v>
       </c>
       <c r="B153" t="n">
-        <v>98597</v>
+        <v>98610</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>128362600</v>
       </c>
       <c r="B154" t="n">
-        <v>98597</v>
+        <v>98610</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17541,37 +17541,37 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128362652</v>
+        <v>128362607</v>
       </c>
       <c r="B155" t="n">
-        <v>98597</v>
+        <v>107546</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>219798</v>
+        <v>220079</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -17581,17 +17581,17 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2097, Gtl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>720884</v>
+        <v>720820</v>
       </c>
       <c r="R155" t="n">
-        <v>6382924</v>
+        <v>6382977</v>
       </c>
       <c r="S155" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17652,10 +17652,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128362626</v>
+        <v>128362652</v>
       </c>
       <c r="B156" t="n">
-        <v>98641</v>
+        <v>98610</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17663,26 +17663,26 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -17692,17 +17692,17 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>720870</v>
+        <v>720884</v>
       </c>
       <c r="R156" t="n">
-        <v>6382959</v>
+        <v>6382924</v>
       </c>
       <c r="S156" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17763,10 +17763,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128362596</v>
+        <v>128362626</v>
       </c>
       <c r="B157" t="n">
-        <v>98597</v>
+        <v>98654</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17774,26 +17774,26 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -17803,17 +17803,17 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>720898</v>
+        <v>720870</v>
       </c>
       <c r="R157" t="n">
-        <v>6382990</v>
+        <v>6382959</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17874,37 +17874,37 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128362607</v>
+        <v>128362596</v>
       </c>
       <c r="B158" t="n">
-        <v>107533</v>
+        <v>98610</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -17914,17 +17914,17 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2097, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>720820</v>
+        <v>720898</v>
       </c>
       <c r="R158" t="n">
-        <v>6382977</v>
+        <v>6382990</v>
       </c>
       <c r="S158" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>128362621</v>
       </c>
       <c r="B159" t="n">
-        <v>98597</v>
+        <v>98610</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128362623</v>
+        <v>128362659</v>
       </c>
       <c r="B160" t="n">
-        <v>98537</v>
+        <v>98610</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18107,26 +18107,26 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -18136,17 +18136,17 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>720854</v>
+        <v>720910</v>
       </c>
       <c r="R160" t="n">
-        <v>6382954</v>
+        <v>6382934</v>
       </c>
       <c r="S160" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18207,10 +18207,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128362659</v>
+        <v>128362623</v>
       </c>
       <c r="B161" t="n">
-        <v>98597</v>
+        <v>98550</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18218,26 +18218,26 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -18247,17 +18247,17 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>720910</v>
+        <v>720854</v>
       </c>
       <c r="R161" t="n">
-        <v>6382934</v>
+        <v>6382954</v>
       </c>
       <c r="S161" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>128362663</v>
       </c>
       <c r="B162" t="n">
-        <v>98597</v>
+        <v>98610</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>128362670</v>
       </c>
       <c r="B163" t="n">
-        <v>98597</v>
+        <v>98610</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18540,37 +18540,37 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128362666</v>
+        <v>128362644</v>
       </c>
       <c r="B164" t="n">
-        <v>107533</v>
+        <v>98654</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -18580,14 +18580,14 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>720954</v>
+        <v>720889</v>
       </c>
       <c r="R164" t="n">
-        <v>6382931</v>
+        <v>6382907</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -18651,10 +18651,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128362644</v>
+        <v>128362614</v>
       </c>
       <c r="B165" t="n">
-        <v>98641</v>
+        <v>98610</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18662,26 +18662,26 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -18691,17 +18691,17 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>720889</v>
+        <v>720854</v>
       </c>
       <c r="R165" t="n">
-        <v>6382907</v>
+        <v>6383001</v>
       </c>
       <c r="S165" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18762,10 +18762,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128362614</v>
+        <v>128362672</v>
       </c>
       <c r="B166" t="n">
-        <v>98597</v>
+        <v>98610</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18806,13 +18806,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>720854</v>
+        <v>720992</v>
       </c>
       <c r="R166" t="n">
-        <v>6383001</v>
+        <v>6382917</v>
       </c>
       <c r="S166" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18873,10 +18873,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128362672</v>
+        <v>128362617</v>
       </c>
       <c r="B167" t="n">
-        <v>98597</v>
+        <v>98610</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18917,13 +18917,13 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>720992</v>
+        <v>720861</v>
       </c>
       <c r="R167" t="n">
-        <v>6382917</v>
+        <v>6383000</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18984,32 +18984,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128362617</v>
+        <v>128362666</v>
       </c>
       <c r="B168" t="n">
-        <v>98597</v>
+        <v>107546</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>219798</v>
+        <v>220079</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -19024,14 +19024,14 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>720861</v>
+        <v>720954</v>
       </c>
       <c r="R168" t="n">
-        <v>6383000</v>
+        <v>6382931</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -19098,7 +19098,7 @@
         <v>128808200</v>
       </c>
       <c r="B169" t="n">
-        <v>98647</v>
+        <v>98654</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19202,32 +19202,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128808204</v>
+        <v>128811517</v>
       </c>
       <c r="B170" t="n">
-        <v>107539</v>
+        <v>86846</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220079</v>
+        <v>442</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19237,10 +19237,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>720903</v>
+        <v>720799</v>
       </c>
       <c r="R170" t="n">
-        <v>6382925</v>
+        <v>6382978</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19270,19 +19270,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>14:12</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19297,57 +19287,60 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128808194</v>
+        <v>128808210</v>
       </c>
       <c r="B171" t="n">
-        <v>86958</v>
+        <v>86846</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6003295</v>
+        <v>442</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>720872</v>
+        <v>720874</v>
       </c>
       <c r="R171" t="n">
-        <v>6382981</v>
+        <v>6382938</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19379,7 +19372,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19389,7 +19382,12 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Negativ KOH hattkant och bulbkant.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19417,32 +19415,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128811517</v>
+        <v>128808213</v>
       </c>
       <c r="B172" t="n">
-        <v>86846</v>
+        <v>86922</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>442</v>
+        <v>3674</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -19452,10 +19450,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>720799</v>
+        <v>720849</v>
       </c>
       <c r="R172" t="n">
-        <v>6382978</v>
+        <v>6383038</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19485,9 +19483,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19502,60 +19510,57 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128808210</v>
+        <v>128808204</v>
       </c>
       <c r="B173" t="n">
-        <v>86846</v>
+        <v>107546</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>442</v>
+        <v>220079</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>720874</v>
+        <v>720903</v>
       </c>
       <c r="R173" t="n">
-        <v>6382938</v>
+        <v>6382925</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19587,7 +19592,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19597,12 +19602,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Negativ KOH hattkant och bulbkant.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19611,7 +19611,6 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -19630,32 +19629,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128808213</v>
+        <v>128808194</v>
       </c>
       <c r="B174" t="n">
-        <v>86921</v>
+        <v>86959</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19665,10 +19664,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>720849</v>
+        <v>720872</v>
       </c>
       <c r="R174" t="n">
-        <v>6383038</v>
+        <v>6382981</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19700,7 +19699,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19710,7 +19709,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19719,6 +19718,7 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
+      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -19740,7 +19740,7 @@
         <v>128808201</v>
       </c>
       <c r="B175" t="n">
-        <v>92253</v>
+        <v>92258</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>128808203</v>
       </c>
       <c r="B176" t="n">
-        <v>105675</v>
+        <v>105682</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19955,32 +19955,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128808208</v>
+        <v>128808205</v>
       </c>
       <c r="B177" t="n">
-        <v>86846</v>
+        <v>107546</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>442</v>
+        <v>220079</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19990,10 +19990,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>720873</v>
+        <v>720773</v>
       </c>
       <c r="R177" t="n">
-        <v>6382935</v>
+        <v>6383077</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20025,7 +20025,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -20035,12 +20035,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>1 fk</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20067,32 +20062,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128808205</v>
+        <v>128808208</v>
       </c>
       <c r="B178" t="n">
-        <v>107539</v>
+        <v>86846</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>220079</v>
+        <v>442</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -20102,10 +20097,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>720773</v>
+        <v>720873</v>
       </c>
       <c r="R178" t="n">
-        <v>6383077</v>
+        <v>6382935</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20137,7 +20132,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -20147,7 +20142,12 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>1 fk</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20177,7 +20177,7 @@
         <v>128811515</v>
       </c>
       <c r="B179" t="n">
-        <v>87015</v>
+        <v>87016</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>128811522</v>
       </c>
       <c r="B181" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>128808197</v>
       </c>
       <c r="B182" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>128811505</v>
       </c>
       <c r="B183" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>128811513</v>
       </c>
       <c r="B184" t="n">
-        <v>90960</v>
+        <v>90965</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>128808198</v>
       </c>
       <c r="B186" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>128811502</v>
       </c>
       <c r="B187" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>128811503</v>
       </c>
       <c r="B189" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>128811498</v>
       </c>
       <c r="B190" t="n">
-        <v>92817</v>
+        <v>92823</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21295,21 +21295,12 @@
       <c r="E190" t="n">
         <v>5449</v>
       </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
@@ -21476,10 +21467,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128811497</v>
+        <v>128811511</v>
       </c>
       <c r="B192" t="n">
-        <v>92817</v>
+        <v>107546</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21487,21 +21478,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5449</v>
+        <v>220079</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -21511,10 +21502,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>720815</v>
+        <v>720728</v>
       </c>
       <c r="R192" t="n">
-        <v>6382996</v>
+        <v>6382877</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21573,45 +21564,48 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128811512</v>
+        <v>128811507</v>
       </c>
       <c r="B193" t="n">
-        <v>86874</v>
+        <v>86959</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>720762</v>
+        <v>720812</v>
       </c>
       <c r="R193" t="n">
-        <v>6382917</v>
+        <v>6382982</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21652,6 +21646,7 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -21670,10 +21665,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128811507</v>
+        <v>128811497</v>
       </c>
       <c r="B194" t="n">
-        <v>86958</v>
+        <v>92823</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21681,37 +21676,25 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6003295</v>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>Odörspindling</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>720812</v>
+        <v>720815</v>
       </c>
       <c r="R194" t="n">
-        <v>6382982</v>
+        <v>6382996</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21752,7 +21735,6 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
-      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
@@ -21771,32 +21753,32 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128811511</v>
+        <v>128811512</v>
       </c>
       <c r="B195" t="n">
-        <v>107539</v>
+        <v>86875</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>220079</v>
+        <v>248956</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -21806,10 +21788,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>720728</v>
+        <v>720762</v>
       </c>
       <c r="R195" t="n">
-        <v>6382877</v>
+        <v>6382917</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21871,7 +21853,7 @@
         <v>128811521</v>
       </c>
       <c r="B196" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21968,7 +21950,7 @@
         <v>128811509</v>
       </c>
       <c r="B197" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22069,7 +22051,7 @@
         <v>128808191</v>
       </c>
       <c r="B198" t="n">
-        <v>92781</v>
+        <v>92786</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22176,7 +22158,7 @@
         <v>128811508</v>
       </c>
       <c r="B199" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22274,32 +22256,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128811514</v>
+        <v>128808209</v>
       </c>
       <c r="B200" t="n">
-        <v>90960</v>
+        <v>86806</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>3286</v>
+        <v>424</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22309,10 +22291,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>720775</v>
+        <v>720782</v>
       </c>
       <c r="R200" t="n">
-        <v>6382814</v>
+        <v>6383065</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22342,9 +22324,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>3 fk bild</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22359,44 +22356,44 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128808209</v>
+        <v>128811514</v>
       </c>
       <c r="B201" t="n">
-        <v>86806</v>
+        <v>90965</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>424</v>
+        <v>3286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -22406,10 +22403,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>720782</v>
+        <v>720775</v>
       </c>
       <c r="R201" t="n">
-        <v>6383065</v>
+        <v>6382814</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22439,24 +22436,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>3 fk bild</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22471,12 +22453,12 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
@@ -22486,7 +22468,7 @@
         <v>128808196</v>
       </c>
       <c r="B202" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22591,32 +22573,32 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128808207</v>
+        <v>128812128</v>
       </c>
       <c r="B203" t="n">
-        <v>90960</v>
+        <v>105682</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>3286</v>
+        <v>224098</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -22626,10 +22608,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>720854</v>
+        <v>720940</v>
       </c>
       <c r="R203" t="n">
-        <v>6382963</v>
+        <v>6382871</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22661,7 +22643,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -22671,7 +22653,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22698,32 +22680,32 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128812128</v>
+        <v>128808192</v>
       </c>
       <c r="B204" t="n">
-        <v>105675</v>
+        <v>86959</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -22733,10 +22715,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>720940</v>
+        <v>720870</v>
       </c>
       <c r="R204" t="n">
-        <v>6382871</v>
+        <v>6382928</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22768,7 +22750,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -22778,7 +22760,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22787,6 +22769,7 @@
       <c r="AE204" t="b">
         <v>0</v>
       </c>
+      <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="b">
         <v>0</v>
       </c>
@@ -22805,10 +22788,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128808192</v>
+        <v>128811506</v>
       </c>
       <c r="B205" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22834,16 +22817,19 @@
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>720870</v>
+        <v>720791</v>
       </c>
       <c r="R205" t="n">
-        <v>6382928</v>
+        <v>6382968</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22873,19 +22859,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>14:47</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22901,22 +22877,22 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128811506</v>
+        <v>128808207</v>
       </c>
       <c r="B206" t="n">
-        <v>86958</v>
+        <v>90965</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22924,37 +22900,34 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6003295</v>
+        <v>3286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>720791</v>
+        <v>720854</v>
       </c>
       <c r="R206" t="n">
-        <v>6382968</v>
+        <v>6382963</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22984,62 +22957,71 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AD206" t="b">
         <v>0</v>
       </c>
       <c r="AE206" t="b">
         <v>0</v>
       </c>
-      <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="b">
         <v>0</v>
       </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128808206</v>
+        <v>128808211</v>
       </c>
       <c r="B207" t="n">
-        <v>90960</v>
+        <v>90271</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>3286</v>
+        <v>245042</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -23049,10 +23031,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>720877</v>
+        <v>720816</v>
       </c>
       <c r="R207" t="n">
-        <v>6382941</v>
+        <v>6382972</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23084,7 +23066,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -23094,7 +23076,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23121,32 +23103,32 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128808211</v>
+        <v>128808206</v>
       </c>
       <c r="B208" t="n">
-        <v>90266</v>
+        <v>90965</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>245042</v>
+        <v>3286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -23156,10 +23138,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>720816</v>
+        <v>720877</v>
       </c>
       <c r="R208" t="n">
-        <v>6382972</v>
+        <v>6382941</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23191,7 +23173,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -23201,7 +23183,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23231,7 +23213,7 @@
         <v>128811499</v>
       </c>
       <c r="B209" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23322,10 +23304,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128811504</v>
+        <v>128811510</v>
       </c>
       <c r="B210" t="n">
-        <v>86958</v>
+        <v>107546</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23333,37 +23315,34 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>720789</v>
+        <v>720809</v>
       </c>
       <c r="R210" t="n">
-        <v>6382798</v>
+        <v>6382787</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23404,7 +23383,6 @@
       <c r="AE210" t="b">
         <v>0</v>
       </c>
-      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
@@ -23423,32 +23401,32 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128811510</v>
+        <v>128808212</v>
       </c>
       <c r="B211" t="n">
-        <v>107539</v>
+        <v>106257</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>220079</v>
+        <v>220785</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23458,10 +23436,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>720809</v>
+        <v>720875</v>
       </c>
       <c r="R211" t="n">
-        <v>6382787</v>
+        <v>6382950</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23491,9 +23469,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23508,57 +23496,60 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128808212</v>
+        <v>128811504</v>
       </c>
       <c r="B212" t="n">
-        <v>106250</v>
+        <v>86959</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>220785</v>
+        <v>6003295</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>720875</v>
+        <v>720789</v>
       </c>
       <c r="R212" t="n">
-        <v>6382950</v>
+        <v>6382798</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23588,42 +23579,149 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AD212" t="b">
         <v>0</v>
       </c>
       <c r="AE212" t="b">
         <v>0</v>
       </c>
+      <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="b">
         <v>0</v>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>128808187</v>
+      </c>
+      <c r="B213" t="n">
+        <v>86960</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>467</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Rostspindling</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Cortinarius russus</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>720934</v>
+      </c>
+      <c r="R213" t="n">
+        <v>6382872</v>
+      </c>
+      <c r="S213" t="n">
+        <v>10</v>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>Stor Med Vita Riftar. Invid tall. Gran 3m bort. Inga uppenbara ädellöv. Klen ek 30cm bort.</t>
+        </is>
+      </c>
+      <c r="AD213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF213" t="inlineStr"/>
+      <c r="AG213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT213" t="inlineStr"/>
+      <c r="AW213" t="inlineStr">
+        <is>
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AX212" t="inlineStr">
+      <c r="AX213" t="inlineStr">
         <is>
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY212" t="inlineStr"/>
+      <c r="AY213" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -14478,10 +14478,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128362627</v>
+        <v>128362604</v>
       </c>
       <c r="B127" t="n">
-        <v>98550</v>
+        <v>98610</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14489,26 +14489,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14518,17 +14518,17 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>720870</v>
+        <v>720857</v>
       </c>
       <c r="R127" t="n">
-        <v>6382959</v>
+        <v>6382943</v>
       </c>
       <c r="S127" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128362604</v>
+        <v>128362638</v>
       </c>
       <c r="B128" t="n">
         <v>98610</v>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14633,10 +14633,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>720857</v>
+        <v>720872</v>
       </c>
       <c r="R128" t="n">
-        <v>6382943</v>
+        <v>6382941</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14700,10 +14700,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128362638</v>
+        <v>128362622</v>
       </c>
       <c r="B129" t="n">
-        <v>98610</v>
+        <v>98654</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14711,26 +14711,26 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14740,17 +14740,17 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>720872</v>
+        <v>720854</v>
       </c>
       <c r="R129" t="n">
-        <v>6382941</v>
+        <v>6382954</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14811,10 +14811,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128362622</v>
+        <v>128362627</v>
       </c>
       <c r="B130" t="n">
-        <v>98654</v>
+        <v>98550</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14822,26 +14822,26 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219862</v>
+        <v>223591</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14851,14 +14851,14 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>720854</v>
+        <v>720870</v>
       </c>
       <c r="R130" t="n">
-        <v>6382954</v>
+        <v>6382959</v>
       </c>
       <c r="S130" t="n">
         <v>3</v>
@@ -15024,57 +15024,48 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128362619</v>
+        <v>128362671</v>
       </c>
       <c r="B132" t="n">
-        <v>98610</v>
+        <v>109490</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2044, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>720859</v>
+        <v>720992</v>
       </c>
       <c r="R132" t="n">
-        <v>6382986</v>
+        <v>6382917</v>
       </c>
       <c r="S132" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15135,48 +15126,57 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128362671</v>
+        <v>128362619</v>
       </c>
       <c r="B133" t="n">
-        <v>109490</v>
+        <v>98610</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2044, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>720992</v>
+        <v>720859</v>
       </c>
       <c r="R133" t="n">
-        <v>6382917</v>
+        <v>6382986</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128362598</v>
+        <v>128362632</v>
       </c>
       <c r="B134" t="n">
         <v>98610</v>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15281,13 +15281,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>720886</v>
+        <v>720866</v>
       </c>
       <c r="R134" t="n">
-        <v>6382981</v>
+        <v>6382946</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128362632</v>
+        <v>128362598</v>
       </c>
       <c r="B135" t="n">
         <v>98610</v>
@@ -15378,7 +15378,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15392,13 +15392,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>720866</v>
+        <v>720886</v>
       </c>
       <c r="R135" t="n">
-        <v>6382946</v>
+        <v>6382981</v>
       </c>
       <c r="S135" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15570,10 +15570,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128362758</v>
+        <v>128362647</v>
       </c>
       <c r="B137" t="n">
-        <v>96228</v>
+        <v>98610</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15581,46 +15581,46 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2180</v>
+        <v>219798</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>720904</v>
+        <v>720889</v>
       </c>
       <c r="R137" t="n">
-        <v>6382940</v>
+        <v>6382907</v>
       </c>
       <c r="S137" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15681,32 +15681,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128362639</v>
+        <v>128362758</v>
       </c>
       <c r="B138" t="n">
-        <v>106257</v>
+        <v>96228</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220785</v>
+        <v>2180</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -15716,22 +15716,22 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>720889</v>
+        <v>720904</v>
       </c>
       <c r="R138" t="n">
-        <v>6382907</v>
+        <v>6382940</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -15792,37 +15792,37 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128362647</v>
+        <v>128362639</v>
       </c>
       <c r="B139" t="n">
-        <v>98610</v>
+        <v>106257</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15832,7 +15832,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
@@ -16347,10 +16347,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128362628</v>
+        <v>128362611</v>
       </c>
       <c r="B144" t="n">
-        <v>109490</v>
+        <v>99385</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16358,16 +16358,16 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220299</v>
+        <v>222361</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -16375,17 +16375,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>720870</v>
+        <v>720854</v>
       </c>
       <c r="R144" t="n">
-        <v>6382959</v>
+        <v>6383001</v>
       </c>
       <c r="S144" t="n">
         <v>3</v>
@@ -16551,10 +16560,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128362611</v>
+        <v>128362628</v>
       </c>
       <c r="B146" t="n">
-        <v>99385</v>
+        <v>109490</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16562,16 +16571,16 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>222361</v>
+        <v>220299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -16579,26 +16588,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>720854</v>
+        <v>720870</v>
       </c>
       <c r="R146" t="n">
-        <v>6383001</v>
+        <v>6382959</v>
       </c>
       <c r="S146" t="n">
         <v>3</v>
@@ -18540,37 +18540,37 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128362644</v>
+        <v>128362666</v>
       </c>
       <c r="B164" t="n">
-        <v>98654</v>
+        <v>107546</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -18580,14 +18580,14 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>720889</v>
+        <v>720954</v>
       </c>
       <c r="R164" t="n">
-        <v>6382907</v>
+        <v>6382931</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -18651,10 +18651,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128362614</v>
+        <v>128362644</v>
       </c>
       <c r="B165" t="n">
-        <v>98610</v>
+        <v>98654</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18662,26 +18662,26 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -18691,17 +18691,17 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>720854</v>
+        <v>720889</v>
       </c>
       <c r="R165" t="n">
-        <v>6383001</v>
+        <v>6382907</v>
       </c>
       <c r="S165" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128362672</v>
+        <v>128362614</v>
       </c>
       <c r="B166" t="n">
         <v>98610</v>
@@ -18806,13 +18806,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>720992</v>
+        <v>720854</v>
       </c>
       <c r="R166" t="n">
-        <v>6382917</v>
+        <v>6383001</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128362617</v>
+        <v>128362672</v>
       </c>
       <c r="B167" t="n">
         <v>98610</v>
@@ -18903,7 +18903,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18917,13 +18917,13 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>720861</v>
+        <v>720992</v>
       </c>
       <c r="R167" t="n">
-        <v>6383000</v>
+        <v>6382917</v>
       </c>
       <c r="S167" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18984,32 +18984,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128362666</v>
+        <v>128362617</v>
       </c>
       <c r="B168" t="n">
-        <v>107546</v>
+        <v>98610</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -19024,14 +19024,14 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>720954</v>
+        <v>720861</v>
       </c>
       <c r="R168" t="n">
-        <v>6382931</v>
+        <v>6383000</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -19202,32 +19202,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128811517</v>
+        <v>128808213</v>
       </c>
       <c r="B170" t="n">
-        <v>86846</v>
+        <v>86922</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>442</v>
+        <v>3674</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19237,10 +19237,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>720799</v>
+        <v>720849</v>
       </c>
       <c r="R170" t="n">
-        <v>6382978</v>
+        <v>6383038</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19270,9 +19270,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19287,19 +19297,19 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128808210</v>
+        <v>128811517</v>
       </c>
       <c r="B171" t="n">
         <v>86846</v>
@@ -19328,19 +19338,16 @@
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>720874</v>
+        <v>720799</v>
       </c>
       <c r="R171" t="n">
-        <v>6382938</v>
+        <v>6382978</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19370,90 +19377,77 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Negativ KOH hattkant och bulbkant.</t>
-        </is>
-      </c>
       <c r="AD171" t="b">
         <v>0</v>
       </c>
       <c r="AE171" t="b">
         <v>0</v>
       </c>
-      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128808213</v>
+        <v>128808210</v>
       </c>
       <c r="B172" t="n">
-        <v>86922</v>
+        <v>86846</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3674</v>
+        <v>442</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>720849</v>
+        <v>720874</v>
       </c>
       <c r="R172" t="n">
-        <v>6383038</v>
+        <v>6382938</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19485,7 +19479,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19495,7 +19489,12 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>Negativ KOH hattkant och bulbkant.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19504,6 +19503,7 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -19737,48 +19737,45 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128808201</v>
+        <v>128808203</v>
       </c>
       <c r="B175" t="n">
-        <v>92258</v>
+        <v>105682</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>232138</v>
+        <v>224098</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>720882</v>
+        <v>720949</v>
       </c>
       <c r="R175" t="n">
-        <v>6382914</v>
+        <v>6382867</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19810,7 +19807,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19820,7 +19817,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19829,7 +19826,6 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -19848,45 +19844,48 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128808203</v>
+        <v>128808201</v>
       </c>
       <c r="B176" t="n">
-        <v>105682</v>
+        <v>92258</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>224098</v>
+        <v>232138</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>720949</v>
+        <v>720882</v>
       </c>
       <c r="R176" t="n">
-        <v>6382867</v>
+        <v>6382914</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19918,7 +19917,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19928,7 +19927,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19937,6 +19936,7 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -19955,32 +19955,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128808205</v>
+        <v>128808208</v>
       </c>
       <c r="B177" t="n">
-        <v>107546</v>
+        <v>86846</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220079</v>
+        <v>442</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19990,10 +19990,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>720773</v>
+        <v>720873</v>
       </c>
       <c r="R177" t="n">
-        <v>6383077</v>
+        <v>6382935</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20025,7 +20025,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -20035,7 +20035,12 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>1 fk</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20062,32 +20067,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128808208</v>
+        <v>128808205</v>
       </c>
       <c r="B178" t="n">
-        <v>86846</v>
+        <v>107546</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>442</v>
+        <v>220079</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -20097,10 +20102,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>720873</v>
+        <v>720773</v>
       </c>
       <c r="R178" t="n">
-        <v>6382935</v>
+        <v>6383077</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20132,7 +20137,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -20142,12 +20147,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>1 fk</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21073,45 +21073,48 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128808186</v>
+        <v>128811503</v>
       </c>
       <c r="B188" t="n">
-        <v>86760</v>
+        <v>86959</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>720940</v>
+        <v>720839</v>
       </c>
       <c r="R188" t="n">
-        <v>6382871</v>
+        <v>6382829</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21141,19 +21144,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21169,60 +21162,57 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128811503</v>
+        <v>128808186</v>
       </c>
       <c r="B189" t="n">
-        <v>86959</v>
+        <v>86760</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>720839</v>
+        <v>720940</v>
       </c>
       <c r="R189" t="n">
-        <v>6382829</v>
+        <v>6382871</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21252,9 +21242,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21270,12 +21270,12 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
@@ -21467,10 +21467,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128811511</v>
+        <v>128811497</v>
       </c>
       <c r="B192" t="n">
-        <v>107546</v>
+        <v>92823</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21478,23 +21478,14 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220079</v>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>Jordtistel</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
@@ -21502,10 +21493,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>720728</v>
+        <v>720815</v>
       </c>
       <c r="R192" t="n">
-        <v>6382877</v>
+        <v>6382996</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21564,48 +21555,45 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128811507</v>
+        <v>128811512</v>
       </c>
       <c r="B193" t="n">
-        <v>86959</v>
+        <v>86875</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>720812</v>
+        <v>720762</v>
       </c>
       <c r="R193" t="n">
-        <v>6382982</v>
+        <v>6382917</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21646,7 +21634,6 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -21665,10 +21652,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128811497</v>
+        <v>128811511</v>
       </c>
       <c r="B194" t="n">
-        <v>92823</v>
+        <v>107546</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21676,14 +21663,23 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>5449</v>
+        <v>220079</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr"/>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
@@ -21691,10 +21687,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>720815</v>
+        <v>720728</v>
       </c>
       <c r="R194" t="n">
-        <v>6382996</v>
+        <v>6382877</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21753,45 +21749,48 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128811512</v>
+        <v>128811507</v>
       </c>
       <c r="B195" t="n">
-        <v>86875</v>
+        <v>86959</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>720762</v>
+        <v>720812</v>
       </c>
       <c r="R195" t="n">
-        <v>6382917</v>
+        <v>6382982</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21832,6 +21831,7 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
+      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -22256,32 +22256,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128808209</v>
+        <v>128811514</v>
       </c>
       <c r="B200" t="n">
-        <v>86806</v>
+        <v>90965</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>424</v>
+        <v>3286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22291,10 +22291,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>720782</v>
+        <v>720775</v>
       </c>
       <c r="R200" t="n">
-        <v>6383065</v>
+        <v>6382814</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22324,24 +22324,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>3 fk bild</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22356,44 +22341,44 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128811514</v>
+        <v>128808209</v>
       </c>
       <c r="B201" t="n">
-        <v>90965</v>
+        <v>86806</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>3286</v>
+        <v>424</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -22403,10 +22388,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>720775</v>
+        <v>720782</v>
       </c>
       <c r="R201" t="n">
-        <v>6382814</v>
+        <v>6383065</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22436,9 +22421,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>3 fk bild</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22453,12 +22453,12 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -15024,48 +15024,57 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128362671</v>
+        <v>128362619</v>
       </c>
       <c r="B132" t="n">
-        <v>109490</v>
+        <v>98610</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2044, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>720992</v>
+        <v>720859</v>
       </c>
       <c r="R132" t="n">
-        <v>6382917</v>
+        <v>6382986</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15126,57 +15135,48 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128362619</v>
+        <v>128362671</v>
       </c>
       <c r="B133" t="n">
-        <v>98610</v>
+        <v>109490</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2044, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>720859</v>
+        <v>720992</v>
       </c>
       <c r="R133" t="n">
-        <v>6382986</v>
+        <v>6382917</v>
       </c>
       <c r="S133" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15570,10 +15570,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128362647</v>
+        <v>128362758</v>
       </c>
       <c r="B137" t="n">
-        <v>98610</v>
+        <v>96228</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15581,46 +15581,46 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>219798</v>
+        <v>2180</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>720889</v>
+        <v>720904</v>
       </c>
       <c r="R137" t="n">
-        <v>6382907</v>
+        <v>6382940</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15681,10 +15681,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128362758</v>
+        <v>128362647</v>
       </c>
       <c r="B138" t="n">
-        <v>96228</v>
+        <v>98610</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15692,46 +15692,46 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2180</v>
+        <v>219798</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>720904</v>
+        <v>720889</v>
       </c>
       <c r="R138" t="n">
-        <v>6382940</v>
+        <v>6382907</v>
       </c>
       <c r="S138" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -17541,37 +17541,37 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128362607</v>
+        <v>128362652</v>
       </c>
       <c r="B155" t="n">
-        <v>107546</v>
+        <v>98610</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -17581,17 +17581,17 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2097, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>720820</v>
+        <v>720884</v>
       </c>
       <c r="R155" t="n">
-        <v>6382977</v>
+        <v>6382924</v>
       </c>
       <c r="S155" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17652,10 +17652,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128362652</v>
+        <v>128362626</v>
       </c>
       <c r="B156" t="n">
-        <v>98610</v>
+        <v>98654</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17663,26 +17663,26 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -17692,17 +17692,17 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>720884</v>
+        <v>720870</v>
       </c>
       <c r="R156" t="n">
-        <v>6382924</v>
+        <v>6382959</v>
       </c>
       <c r="S156" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17763,10 +17763,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128362626</v>
+        <v>128362596</v>
       </c>
       <c r="B157" t="n">
-        <v>98654</v>
+        <v>98610</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17774,26 +17774,26 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -17803,17 +17803,17 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>720870</v>
+        <v>720898</v>
       </c>
       <c r="R157" t="n">
-        <v>6382959</v>
+        <v>6382990</v>
       </c>
       <c r="S157" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17874,37 +17874,37 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128362596</v>
+        <v>128362607</v>
       </c>
       <c r="B158" t="n">
-        <v>98610</v>
+        <v>107546</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>219798</v>
+        <v>220079</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -17914,17 +17914,17 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2097, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>720898</v>
+        <v>720820</v>
       </c>
       <c r="R158" t="n">
-        <v>6382990</v>
+        <v>6382977</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18540,37 +18540,37 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128362666</v>
+        <v>128362644</v>
       </c>
       <c r="B164" t="n">
-        <v>107546</v>
+        <v>98654</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -18580,14 +18580,14 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>720954</v>
+        <v>720889</v>
       </c>
       <c r="R164" t="n">
-        <v>6382931</v>
+        <v>6382907</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -18651,10 +18651,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128362644</v>
+        <v>128362614</v>
       </c>
       <c r="B165" t="n">
-        <v>98654</v>
+        <v>98610</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18662,26 +18662,26 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -18691,17 +18691,17 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>720889</v>
+        <v>720854</v>
       </c>
       <c r="R165" t="n">
-        <v>6382907</v>
+        <v>6383001</v>
       </c>
       <c r="S165" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128362614</v>
+        <v>128362672</v>
       </c>
       <c r="B166" t="n">
         <v>98610</v>
@@ -18806,13 +18806,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>720854</v>
+        <v>720992</v>
       </c>
       <c r="R166" t="n">
-        <v>6383001</v>
+        <v>6382917</v>
       </c>
       <c r="S166" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128362672</v>
+        <v>128362617</v>
       </c>
       <c r="B167" t="n">
         <v>98610</v>
@@ -18903,7 +18903,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18917,13 +18917,13 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>720992</v>
+        <v>720861</v>
       </c>
       <c r="R167" t="n">
-        <v>6382917</v>
+        <v>6383000</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18984,32 +18984,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128362617</v>
+        <v>128362666</v>
       </c>
       <c r="B168" t="n">
-        <v>98610</v>
+        <v>107546</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>219798</v>
+        <v>220079</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -19024,14 +19024,14 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>720861</v>
+        <v>720954</v>
       </c>
       <c r="R168" t="n">
-        <v>6383000</v>
+        <v>6382931</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -19309,32 +19309,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128811517</v>
+        <v>128808204</v>
       </c>
       <c r="B171" t="n">
-        <v>86846</v>
+        <v>107546</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>442</v>
+        <v>220079</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19344,10 +19344,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>720799</v>
+        <v>720903</v>
       </c>
       <c r="R171" t="n">
-        <v>6382978</v>
+        <v>6382925</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19377,9 +19377,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19394,60 +19404,57 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128808210</v>
+        <v>128808194</v>
       </c>
       <c r="B172" t="n">
-        <v>86846</v>
+        <v>86959</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>442</v>
+        <v>6003295</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>720874</v>
+        <v>720872</v>
       </c>
       <c r="R172" t="n">
-        <v>6382938</v>
+        <v>6382981</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19479,7 +19486,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19489,12 +19496,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>Negativ KOH hattkant och bulbkant.</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19522,32 +19524,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128808204</v>
+        <v>128811517</v>
       </c>
       <c r="B173" t="n">
-        <v>107546</v>
+        <v>86846</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>220079</v>
+        <v>442</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19557,10 +19559,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>720903</v>
+        <v>720799</v>
       </c>
       <c r="R173" t="n">
-        <v>6382925</v>
+        <v>6382978</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19590,19 +19592,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>14:12</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19617,57 +19609,60 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128808194</v>
+        <v>128808210</v>
       </c>
       <c r="B174" t="n">
-        <v>86959</v>
+        <v>86846</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6003295</v>
+        <v>442</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>720872</v>
+        <v>720874</v>
       </c>
       <c r="R174" t="n">
-        <v>6382981</v>
+        <v>6382938</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19699,7 +19694,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19709,7 +19704,12 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Negativ KOH hattkant och bulbkant.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19737,45 +19737,48 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128808203</v>
+        <v>128808201</v>
       </c>
       <c r="B175" t="n">
-        <v>105682</v>
+        <v>92258</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>224098</v>
+        <v>232138</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>720949</v>
+        <v>720882</v>
       </c>
       <c r="R175" t="n">
-        <v>6382867</v>
+        <v>6382914</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19807,7 +19810,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19817,7 +19820,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19826,6 +19829,7 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
+      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -19844,48 +19848,45 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128808201</v>
+        <v>128808203</v>
       </c>
       <c r="B176" t="n">
-        <v>92258</v>
+        <v>105682</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>232138</v>
+        <v>224098</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>720882</v>
+        <v>720949</v>
       </c>
       <c r="R176" t="n">
-        <v>6382914</v>
+        <v>6382867</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19917,7 +19918,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19927,7 +19928,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19936,7 +19937,6 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -21073,48 +21073,45 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128811503</v>
+        <v>128808186</v>
       </c>
       <c r="B188" t="n">
-        <v>86959</v>
+        <v>86760</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>720839</v>
+        <v>720940</v>
       </c>
       <c r="R188" t="n">
-        <v>6382829</v>
+        <v>6382871</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21144,9 +21141,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21162,57 +21169,60 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128808186</v>
+        <v>128811503</v>
       </c>
       <c r="B189" t="n">
-        <v>86760</v>
+        <v>86959</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>720940</v>
+        <v>720839</v>
       </c>
       <c r="R189" t="n">
-        <v>6382871</v>
+        <v>6382829</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21242,19 +21252,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21270,37 +21270,46 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128811498</v>
+        <v>128811496</v>
       </c>
       <c r="B190" t="n">
-        <v>92823</v>
+        <v>86806</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>5449</v>
+        <v>424</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
@@ -21308,10 +21317,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>720831</v>
+        <v>720807</v>
       </c>
       <c r="R190" t="n">
-        <v>6383010</v>
+        <v>6382962</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21370,34 +21379,25 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128811496</v>
+        <v>128811498</v>
       </c>
       <c r="B191" t="n">
-        <v>86806</v>
+        <v>92823</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>424</v>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>Svartgrön spindling</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
@@ -21405,10 +21405,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>720807</v>
+        <v>720831</v>
       </c>
       <c r="R191" t="n">
-        <v>6382962</v>
+        <v>6383010</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21467,10 +21467,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128811497</v>
+        <v>128811511</v>
       </c>
       <c r="B192" t="n">
-        <v>92823</v>
+        <v>107546</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21478,14 +21478,23 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5449</v>
+        <v>220079</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr"/>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
@@ -21493,10 +21502,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>720815</v>
+        <v>720728</v>
       </c>
       <c r="R192" t="n">
-        <v>6382996</v>
+        <v>6382877</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21652,10 +21661,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128811511</v>
+        <v>128811507</v>
       </c>
       <c r="B194" t="n">
-        <v>107546</v>
+        <v>86959</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21663,34 +21672,37 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>720728</v>
+        <v>720812</v>
       </c>
       <c r="R194" t="n">
-        <v>6382877</v>
+        <v>6382982</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21731,6 +21743,7 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
+      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
@@ -21749,10 +21762,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128811507</v>
+        <v>128811497</v>
       </c>
       <c r="B195" t="n">
-        <v>86959</v>
+        <v>92823</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21760,37 +21773,25 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6003295</v>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>Odörspindling</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>720812</v>
+        <v>720815</v>
       </c>
       <c r="R195" t="n">
-        <v>6382982</v>
+        <v>6382996</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21831,7 +21832,6 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -22256,10 +22256,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128811514</v>
+        <v>128808196</v>
       </c>
       <c r="B200" t="n">
-        <v>90965</v>
+        <v>86959</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22267,21 +22267,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>3286</v>
+        <v>6003295</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22291,10 +22291,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>720775</v>
+        <v>720882</v>
       </c>
       <c r="R200" t="n">
-        <v>6382814</v>
+        <v>6382944</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22324,29 +22324,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AD200" t="b">
         <v>0</v>
       </c>
       <c r="AE200" t="b">
         <v>0</v>
       </c>
+      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
@@ -22465,10 +22476,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128808196</v>
+        <v>128811514</v>
       </c>
       <c r="B202" t="n">
-        <v>86959</v>
+        <v>90965</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22476,21 +22487,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6003295</v>
+        <v>3286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -22500,10 +22511,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>720882</v>
+        <v>720775</v>
       </c>
       <c r="R202" t="n">
-        <v>6382944</v>
+        <v>6382814</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22533,72 +22544,61 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AD202" t="b">
         <v>0</v>
       </c>
       <c r="AE202" t="b">
         <v>0</v>
       </c>
-      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128812128</v>
+        <v>128808207</v>
       </c>
       <c r="B203" t="n">
-        <v>105682</v>
+        <v>90965</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>224098</v>
+        <v>3286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -22608,10 +22608,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>720940</v>
+        <v>720854</v>
       </c>
       <c r="R203" t="n">
-        <v>6382871</v>
+        <v>6382963</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22643,7 +22643,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -22653,7 +22653,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22889,32 +22889,32 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128808207</v>
+        <v>128812128</v>
       </c>
       <c r="B206" t="n">
-        <v>90965</v>
+        <v>105682</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>3286</v>
+        <v>224098</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -22924,10 +22924,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>720854</v>
+        <v>720940</v>
       </c>
       <c r="R206" t="n">
-        <v>6382963</v>
+        <v>6382871</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22959,7 +22959,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -22969,7 +22969,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22996,32 +22996,32 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128808211</v>
+        <v>128808206</v>
       </c>
       <c r="B207" t="n">
-        <v>90271</v>
+        <v>90965</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>245042</v>
+        <v>3286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -23031,10 +23031,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>720816</v>
+        <v>720877</v>
       </c>
       <c r="R207" t="n">
-        <v>6382972</v>
+        <v>6382941</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23066,7 +23066,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -23076,7 +23076,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23103,32 +23103,32 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128808206</v>
+        <v>128808211</v>
       </c>
       <c r="B208" t="n">
-        <v>90965</v>
+        <v>90271</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>3286</v>
+        <v>245042</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -23138,10 +23138,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>720877</v>
+        <v>720816</v>
       </c>
       <c r="R208" t="n">
-        <v>6382941</v>
+        <v>6382972</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23173,7 +23173,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -23183,7 +23183,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD208" t="b">

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>105082160</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -14478,57 +14478,48 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128362604</v>
+        <v>128362595</v>
       </c>
       <c r="B127" t="n">
-        <v>98610</v>
+        <v>109490</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>720857</v>
+        <v>720898</v>
       </c>
       <c r="R127" t="n">
-        <v>6382943</v>
+        <v>6382990</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14589,10 +14580,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128362638</v>
+        <v>128362627</v>
       </c>
       <c r="B128" t="n">
-        <v>98610</v>
+        <v>98550</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14600,26 +14591,26 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14629,17 +14620,17 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>720872</v>
+        <v>720870</v>
       </c>
       <c r="R128" t="n">
-        <v>6382941</v>
+        <v>6382959</v>
       </c>
       <c r="S128" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14700,10 +14691,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128362622</v>
+        <v>128362604</v>
       </c>
       <c r="B129" t="n">
-        <v>98654</v>
+        <v>98610</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14711,26 +14702,26 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14740,17 +14731,17 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>720854</v>
+        <v>720857</v>
       </c>
       <c r="R129" t="n">
-        <v>6382954</v>
+        <v>6382943</v>
       </c>
       <c r="S129" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14811,10 +14802,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128362627</v>
+        <v>128362638</v>
       </c>
       <c r="B130" t="n">
-        <v>98550</v>
+        <v>98610</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14822,26 +14813,26 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14851,17 +14842,17 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>720870</v>
+        <v>720872</v>
       </c>
       <c r="R130" t="n">
-        <v>6382959</v>
+        <v>6382941</v>
       </c>
       <c r="S130" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14922,48 +14913,57 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128362595</v>
+        <v>128362622</v>
       </c>
       <c r="B131" t="n">
-        <v>109490</v>
+        <v>98654</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>720898</v>
+        <v>720854</v>
       </c>
       <c r="R131" t="n">
-        <v>6382990</v>
+        <v>6382954</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15570,10 +15570,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128362758</v>
+        <v>128362647</v>
       </c>
       <c r="B137" t="n">
-        <v>96228</v>
+        <v>98610</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15581,46 +15581,46 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2180</v>
+        <v>219798</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>720904</v>
+        <v>720889</v>
       </c>
       <c r="R137" t="n">
-        <v>6382940</v>
+        <v>6382907</v>
       </c>
       <c r="S137" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15681,37 +15681,37 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128362647</v>
+        <v>128362639</v>
       </c>
       <c r="B138" t="n">
-        <v>98610</v>
+        <v>106257</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
@@ -15792,27 +15792,27 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128362639</v>
+        <v>128362640</v>
       </c>
       <c r="B139" t="n">
-        <v>106257</v>
+        <v>109490</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -15832,7 +15832,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
@@ -15903,32 +15903,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128362640</v>
+        <v>128362758</v>
       </c>
       <c r="B140" t="n">
-        <v>109490</v>
+        <v>96228</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220299</v>
+        <v>2180</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -15938,22 +15938,22 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>720889</v>
+        <v>720904</v>
       </c>
       <c r="R140" t="n">
-        <v>6382907</v>
+        <v>6382940</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -16347,10 +16347,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128362611</v>
+        <v>128362628</v>
       </c>
       <c r="B144" t="n">
-        <v>99385</v>
+        <v>109490</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16358,16 +16358,16 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>222361</v>
+        <v>220299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -16375,26 +16375,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>720854</v>
+        <v>720870</v>
       </c>
       <c r="R144" t="n">
-        <v>6383001</v>
+        <v>6382959</v>
       </c>
       <c r="S144" t="n">
         <v>3</v>
@@ -16560,10 +16551,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128362628</v>
+        <v>128362611</v>
       </c>
       <c r="B146" t="n">
-        <v>109490</v>
+        <v>99385</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16571,16 +16562,16 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220299</v>
+        <v>222361</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -16588,17 +16579,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2098, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>720870</v>
+        <v>720854</v>
       </c>
       <c r="R146" t="n">
-        <v>6382959</v>
+        <v>6383001</v>
       </c>
       <c r="S146" t="n">
         <v>3</v>
@@ -16875,10 +16875,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128362657</v>
+        <v>128362594</v>
       </c>
       <c r="B149" t="n">
-        <v>98610</v>
+        <v>98550</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16886,26 +16886,26 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -16915,17 +16915,17 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2112, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>720904</v>
+        <v>720898</v>
       </c>
       <c r="R149" t="n">
-        <v>6382940</v>
+        <v>6382990</v>
       </c>
       <c r="S149" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128362655</v>
+        <v>128362657</v>
       </c>
       <c r="B150" t="n">
         <v>98610</v>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -17030,13 +17030,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>720897</v>
+        <v>720904</v>
       </c>
       <c r="R150" t="n">
-        <v>6382932</v>
+        <v>6382940</v>
       </c>
       <c r="S150" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17097,10 +17097,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128362594</v>
+        <v>128362655</v>
       </c>
       <c r="B151" t="n">
-        <v>98550</v>
+        <v>98610</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17108,26 +17108,26 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -17137,17 +17137,17 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2112, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>720898</v>
+        <v>720897</v>
       </c>
       <c r="R151" t="n">
-        <v>6382990</v>
+        <v>6382932</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17541,37 +17541,37 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128362652</v>
+        <v>128362607</v>
       </c>
       <c r="B155" t="n">
-        <v>98610</v>
+        <v>107546</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>219798</v>
+        <v>220079</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -17581,17 +17581,17 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2097, Gtl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>720884</v>
+        <v>720820</v>
       </c>
       <c r="R155" t="n">
-        <v>6382924</v>
+        <v>6382977</v>
       </c>
       <c r="S155" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17652,10 +17652,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128362626</v>
+        <v>128362652</v>
       </c>
       <c r="B156" t="n">
-        <v>98654</v>
+        <v>98610</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17663,26 +17663,26 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -17692,17 +17692,17 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>720870</v>
+        <v>720884</v>
       </c>
       <c r="R156" t="n">
-        <v>6382959</v>
+        <v>6382924</v>
       </c>
       <c r="S156" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17763,10 +17763,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128362596</v>
+        <v>128362626</v>
       </c>
       <c r="B157" t="n">
-        <v>98610</v>
+        <v>98654</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17774,26 +17774,26 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -17803,17 +17803,17 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>720898</v>
+        <v>720870</v>
       </c>
       <c r="R157" t="n">
-        <v>6382990</v>
+        <v>6382959</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17874,37 +17874,37 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128362607</v>
+        <v>128362596</v>
       </c>
       <c r="B158" t="n">
-        <v>107546</v>
+        <v>98610</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -17914,17 +17914,17 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2097, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>720820</v>
+        <v>720898</v>
       </c>
       <c r="R158" t="n">
-        <v>6382977</v>
+        <v>6382990</v>
       </c>
       <c r="S158" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18540,37 +18540,37 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128362644</v>
+        <v>128362666</v>
       </c>
       <c r="B164" t="n">
-        <v>98654</v>
+        <v>107546</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -18580,14 +18580,14 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>720889</v>
+        <v>720954</v>
       </c>
       <c r="R164" t="n">
-        <v>6382907</v>
+        <v>6382931</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -18651,10 +18651,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128362614</v>
+        <v>128362644</v>
       </c>
       <c r="B165" t="n">
-        <v>98610</v>
+        <v>98654</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18662,26 +18662,26 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -18691,17 +18691,17 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>720854</v>
+        <v>720889</v>
       </c>
       <c r="R165" t="n">
-        <v>6383001</v>
+        <v>6382907</v>
       </c>
       <c r="S165" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128362672</v>
+        <v>128362614</v>
       </c>
       <c r="B166" t="n">
         <v>98610</v>
@@ -18806,13 +18806,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>720992</v>
+        <v>720854</v>
       </c>
       <c r="R166" t="n">
-        <v>6382917</v>
+        <v>6383001</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128362617</v>
+        <v>128362672</v>
       </c>
       <c r="B167" t="n">
         <v>98610</v>
@@ -18903,7 +18903,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18917,13 +18917,13 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>720861</v>
+        <v>720992</v>
       </c>
       <c r="R167" t="n">
-        <v>6383000</v>
+        <v>6382917</v>
       </c>
       <c r="S167" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18984,32 +18984,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128362666</v>
+        <v>128362617</v>
       </c>
       <c r="B168" t="n">
-        <v>107546</v>
+        <v>98610</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -19024,14 +19024,14 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>720954</v>
+        <v>720861</v>
       </c>
       <c r="R168" t="n">
-        <v>6382931</v>
+        <v>6383000</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -19098,7 +19098,7 @@
         <v>128808200</v>
       </c>
       <c r="B169" t="n">
-        <v>98654</v>
+        <v>98658</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19202,32 +19202,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128808213</v>
+        <v>128811517</v>
       </c>
       <c r="B170" t="n">
-        <v>86922</v>
+        <v>86850</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3674</v>
+        <v>442</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19237,10 +19237,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>720849</v>
+        <v>720799</v>
       </c>
       <c r="R170" t="n">
-        <v>6383038</v>
+        <v>6382978</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19270,19 +19270,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>13:42</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19297,57 +19287,60 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128808204</v>
+        <v>128808210</v>
       </c>
       <c r="B171" t="n">
-        <v>107546</v>
+        <v>86850</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>220079</v>
+        <v>442</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>720903</v>
+        <v>720874</v>
       </c>
       <c r="R171" t="n">
-        <v>6382925</v>
+        <v>6382938</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19379,7 +19372,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19389,7 +19382,12 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Negativ KOH hattkant och bulbkant.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19398,6 +19396,7 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -19416,32 +19415,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128808194</v>
+        <v>128808213</v>
       </c>
       <c r="B172" t="n">
-        <v>86959</v>
+        <v>86926</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -19451,10 +19450,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>720872</v>
+        <v>720849</v>
       </c>
       <c r="R172" t="n">
-        <v>6382981</v>
+        <v>6383038</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19486,7 +19485,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19496,7 +19495,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19505,7 +19504,6 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
-      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -19524,32 +19522,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128811517</v>
+        <v>128808204</v>
       </c>
       <c r="B173" t="n">
-        <v>86846</v>
+        <v>107550</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>442</v>
+        <v>220079</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19559,10 +19557,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>720799</v>
+        <v>720903</v>
       </c>
       <c r="R173" t="n">
-        <v>6382978</v>
+        <v>6382925</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19592,9 +19590,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19609,60 +19617,57 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128808210</v>
+        <v>128808194</v>
       </c>
       <c r="B174" t="n">
-        <v>86846</v>
+        <v>86963</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>442</v>
+        <v>6003295</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>720874</v>
+        <v>720872</v>
       </c>
       <c r="R174" t="n">
-        <v>6382938</v>
+        <v>6382981</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19694,7 +19699,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19704,12 +19709,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Negativ KOH hattkant och bulbkant.</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19737,48 +19737,45 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128808201</v>
+        <v>128808203</v>
       </c>
       <c r="B175" t="n">
-        <v>92258</v>
+        <v>105686</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>232138</v>
+        <v>224098</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>720882</v>
+        <v>720949</v>
       </c>
       <c r="R175" t="n">
-        <v>6382914</v>
+        <v>6382867</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19810,7 +19807,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19820,7 +19817,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19829,7 +19826,6 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -19848,45 +19844,48 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128808203</v>
+        <v>128808201</v>
       </c>
       <c r="B176" t="n">
-        <v>105682</v>
+        <v>92262</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>224098</v>
+        <v>232138</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>720949</v>
+        <v>720882</v>
       </c>
       <c r="R176" t="n">
-        <v>6382867</v>
+        <v>6382914</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19918,7 +19917,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19928,7 +19927,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19937,6 +19936,7 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -19958,7 +19958,7 @@
         <v>128808208</v>
       </c>
       <c r="B177" t="n">
-        <v>86846</v>
+        <v>86850</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>128808205</v>
       </c>
       <c r="B178" t="n">
-        <v>107546</v>
+        <v>107550</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>128811515</v>
       </c>
       <c r="B179" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20267,32 +20267,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128811516</v>
+        <v>128811522</v>
       </c>
       <c r="B180" t="n">
-        <v>86846</v>
+        <v>86926</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>442</v>
+        <v>3674</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20302,10 +20302,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>720793</v>
+        <v>720847</v>
       </c>
       <c r="R180" t="n">
-        <v>6382789</v>
+        <v>6383038</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20364,32 +20364,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128811522</v>
+        <v>128811516</v>
       </c>
       <c r="B181" t="n">
-        <v>86922</v>
+        <v>86850</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>3674</v>
+        <v>442</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -20399,10 +20399,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>720847</v>
+        <v>720793</v>
       </c>
       <c r="R181" t="n">
-        <v>6383038</v>
+        <v>6382789</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20464,7 +20464,7 @@
         <v>128808197</v>
       </c>
       <c r="B182" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>128811505</v>
       </c>
       <c r="B183" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20670,32 +20670,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128811513</v>
+        <v>128811501</v>
       </c>
       <c r="B184" t="n">
-        <v>90965</v>
+        <v>86764</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>3286</v>
+        <v>3762</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -20705,10 +20705,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>720914</v>
+        <v>720786</v>
       </c>
       <c r="R184" t="n">
-        <v>6382786</v>
+        <v>6383069</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20767,32 +20767,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128811501</v>
+        <v>128811513</v>
       </c>
       <c r="B185" t="n">
-        <v>86760</v>
+        <v>90969</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>3762</v>
+        <v>3286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20802,10 +20802,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>720786</v>
+        <v>720914</v>
       </c>
       <c r="R185" t="n">
-        <v>6383069</v>
+        <v>6382786</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20867,7 +20867,7 @@
         <v>128808198</v>
       </c>
       <c r="B186" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>128811502</v>
       </c>
       <c r="B187" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21073,45 +21073,48 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128808186</v>
+        <v>128811503</v>
       </c>
       <c r="B188" t="n">
-        <v>86760</v>
+        <v>86963</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>720940</v>
+        <v>720839</v>
       </c>
       <c r="R188" t="n">
-        <v>6382871</v>
+        <v>6382829</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21141,19 +21144,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21169,60 +21162,57 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128811503</v>
+        <v>128808186</v>
       </c>
       <c r="B189" t="n">
-        <v>86959</v>
+        <v>86764</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>720839</v>
+        <v>720940</v>
       </c>
       <c r="R189" t="n">
-        <v>6382829</v>
+        <v>6382871</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21252,9 +21242,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21270,12 +21270,12 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
@@ -21285,7 +21285,7 @@
         <v>128811496</v>
       </c>
       <c r="B190" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>128811498</v>
       </c>
       <c r="B191" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21467,10 +21467,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128811511</v>
+        <v>128811497</v>
       </c>
       <c r="B192" t="n">
-        <v>107546</v>
+        <v>92827</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21478,23 +21478,14 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220079</v>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>Jordtistel</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
@@ -21502,10 +21493,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>720728</v>
+        <v>720815</v>
       </c>
       <c r="R192" t="n">
-        <v>6382877</v>
+        <v>6382996</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21564,45 +21555,48 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128811512</v>
+        <v>128811507</v>
       </c>
       <c r="B193" t="n">
-        <v>86875</v>
+        <v>86963</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>720762</v>
+        <v>720812</v>
       </c>
       <c r="R193" t="n">
-        <v>6382917</v>
+        <v>6382982</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21643,6 +21637,7 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -21661,48 +21656,45 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128811507</v>
+        <v>128811512</v>
       </c>
       <c r="B194" t="n">
-        <v>86959</v>
+        <v>86879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>720812</v>
+        <v>720762</v>
       </c>
       <c r="R194" t="n">
-        <v>6382982</v>
+        <v>6382917</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21743,7 +21735,6 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
-      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
@@ -21762,10 +21753,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128811497</v>
+        <v>128811511</v>
       </c>
       <c r="B195" t="n">
-        <v>92823</v>
+        <v>107550</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21773,14 +21764,23 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5449</v>
+        <v>220079</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr"/>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
@@ -21788,10 +21788,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>720815</v>
+        <v>720728</v>
       </c>
       <c r="R195" t="n">
-        <v>6382996</v>
+        <v>6382877</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21853,7 +21853,7 @@
         <v>128811521</v>
       </c>
       <c r="B196" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>128811509</v>
       </c>
       <c r="B197" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>128808191</v>
       </c>
       <c r="B198" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>128811508</v>
       </c>
       <c r="B199" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>128808196</v>
       </c>
       <c r="B200" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>128808209</v>
       </c>
       <c r="B201" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>128811514</v>
       </c>
       <c r="B202" t="n">
-        <v>90965</v>
+        <v>90969</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22576,7 +22576,7 @@
         <v>128808207</v>
       </c>
       <c r="B203" t="n">
-        <v>90965</v>
+        <v>90969</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22680,32 +22680,32 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128808192</v>
+        <v>128812128</v>
       </c>
       <c r="B204" t="n">
-        <v>86959</v>
+        <v>105686</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6003295</v>
+        <v>224098</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -22715,10 +22715,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>720870</v>
+        <v>720940</v>
       </c>
       <c r="R204" t="n">
-        <v>6382928</v>
+        <v>6382871</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22750,7 +22750,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -22760,7 +22760,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22769,7 +22769,6 @@
       <c r="AE204" t="b">
         <v>0</v>
       </c>
-      <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="b">
         <v>0</v>
       </c>
@@ -22788,10 +22787,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128811506</v>
+        <v>128808192</v>
       </c>
       <c r="B205" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22817,19 +22816,16 @@
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>720791</v>
+        <v>720870</v>
       </c>
       <c r="R205" t="n">
-        <v>6382968</v>
+        <v>6382928</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22859,9 +22855,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22877,57 +22883,60 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128812128</v>
+        <v>128811506</v>
       </c>
       <c r="B206" t="n">
-        <v>105682</v>
+        <v>86963</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>720940</v>
+        <v>720791</v>
       </c>
       <c r="R206" t="n">
-        <v>6382871</v>
+        <v>6382968</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22957,39 +22966,30 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AD206" t="b">
         <v>0</v>
       </c>
       <c r="AE206" t="b">
         <v>0</v>
       </c>
+      <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="b">
         <v>0</v>
       </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
@@ -22999,7 +22999,7 @@
         <v>128808206</v>
       </c>
       <c r="B207" t="n">
-        <v>90965</v>
+        <v>90969</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>128808211</v>
       </c>
       <c r="B208" t="n">
-        <v>90271</v>
+        <v>90275</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>128811499</v>
       </c>
       <c r="B209" t="n">
-        <v>92808</v>
+        <v>92812</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23304,32 +23304,32 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128811510</v>
+        <v>128808212</v>
       </c>
       <c r="B210" t="n">
-        <v>107546</v>
+        <v>106261</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>220079</v>
+        <v>220785</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -23339,10 +23339,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>720809</v>
+        <v>720875</v>
       </c>
       <c r="R210" t="n">
-        <v>6382787</v>
+        <v>6382950</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23372,9 +23372,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23389,44 +23399,44 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128808212</v>
+        <v>128811510</v>
       </c>
       <c r="B211" t="n">
-        <v>106257</v>
+        <v>107550</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>220785</v>
+        <v>220079</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23436,10 +23446,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>720875</v>
+        <v>720809</v>
       </c>
       <c r="R211" t="n">
-        <v>6382950</v>
+        <v>6382787</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23469,19 +23479,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z211" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB211" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23496,12 +23496,12 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
@@ -23511,7 +23511,7 @@
         <v>128811504</v>
       </c>
       <c r="B212" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>128808187</v>
       </c>
       <c r="B213" t="n">
-        <v>86960</v>
+        <v>86964</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -14037,7 +14037,7 @@
         <v>128362610</v>
       </c>
       <c r="B123" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>128362625</v>
       </c>
       <c r="B124" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>128362631</v>
       </c>
       <c r="B125" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>128362609</v>
       </c>
       <c r="B126" t="n">
-        <v>109490</v>
+        <v>109494</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14478,48 +14478,57 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128362595</v>
+        <v>128362627</v>
       </c>
       <c r="B127" t="n">
-        <v>109490</v>
+        <v>98554</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>720898</v>
+        <v>720870</v>
       </c>
       <c r="R127" t="n">
-        <v>6382990</v>
+        <v>6382959</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14580,10 +14589,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128362627</v>
+        <v>128362604</v>
       </c>
       <c r="B128" t="n">
-        <v>98550</v>
+        <v>98614</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14591,26 +14600,26 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14620,17 +14629,17 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>720870</v>
+        <v>720857</v>
       </c>
       <c r="R128" t="n">
-        <v>6382959</v>
+        <v>6382943</v>
       </c>
       <c r="S128" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14691,10 +14700,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128362604</v>
+        <v>128362638</v>
       </c>
       <c r="B129" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14721,7 +14730,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14735,10 +14744,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>720857</v>
+        <v>720872</v>
       </c>
       <c r="R129" t="n">
-        <v>6382943</v>
+        <v>6382941</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -14802,10 +14811,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128362638</v>
+        <v>128362622</v>
       </c>
       <c r="B130" t="n">
-        <v>98610</v>
+        <v>98658</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14813,26 +14822,26 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14842,17 +14851,17 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>720872</v>
+        <v>720854</v>
       </c>
       <c r="R130" t="n">
-        <v>6382941</v>
+        <v>6382954</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14913,57 +14922,48 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128362622</v>
+        <v>128362595</v>
       </c>
       <c r="B131" t="n">
-        <v>98654</v>
+        <v>109494</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2083, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>720854</v>
+        <v>720898</v>
       </c>
       <c r="R131" t="n">
-        <v>6382954</v>
+        <v>6382990</v>
       </c>
       <c r="S131" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>128362619</v>
       </c>
       <c r="B132" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>128362671</v>
       </c>
       <c r="B133" t="n">
-        <v>109490</v>
+        <v>109494</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>128362632</v>
       </c>
       <c r="B134" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>128362598</v>
       </c>
       <c r="B135" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>128362630</v>
       </c>
       <c r="B136" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15570,37 +15570,37 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128362647</v>
+        <v>128362639</v>
       </c>
       <c r="B137" t="n">
-        <v>98610</v>
+        <v>106261</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15610,7 +15610,7 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
@@ -15681,32 +15681,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128362639</v>
+        <v>128362758</v>
       </c>
       <c r="B138" t="n">
-        <v>106257</v>
+        <v>96232</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220785</v>
+        <v>2180</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -15716,22 +15716,22 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>720889</v>
+        <v>720904</v>
       </c>
       <c r="R138" t="n">
-        <v>6382907</v>
+        <v>6382940</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -15792,37 +15792,37 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128362640</v>
+        <v>128362647</v>
       </c>
       <c r="B139" t="n">
-        <v>109490</v>
+        <v>98614</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15832,7 +15832,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
@@ -15903,32 +15903,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128362758</v>
+        <v>128362640</v>
       </c>
       <c r="B140" t="n">
-        <v>96228</v>
+        <v>109494</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2180</v>
+        <v>220299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -15938,22 +15938,22 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>720904</v>
+        <v>720889</v>
       </c>
       <c r="R140" t="n">
-        <v>6382940</v>
+        <v>6382907</v>
       </c>
       <c r="S140" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -16017,7 +16017,7 @@
         <v>128362661</v>
       </c>
       <c r="B141" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>128362635</v>
       </c>
       <c r="B142" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16236,54 +16236,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128362615</v>
+        <v>128362628</v>
       </c>
       <c r="B143" t="n">
-        <v>98610</v>
+        <v>109494</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>720854</v>
+        <v>720870</v>
       </c>
       <c r="R143" t="n">
-        <v>6382995</v>
+        <v>6382959</v>
       </c>
       <c r="S143" t="n">
         <v>3</v>
@@ -16347,10 +16338,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128362628</v>
+        <v>128362656</v>
       </c>
       <c r="B144" t="n">
-        <v>109490</v>
+        <v>109494</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16378,17 +16369,17 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2081, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>720870</v>
+        <v>720904</v>
       </c>
       <c r="R144" t="n">
-        <v>6382959</v>
+        <v>6382940</v>
       </c>
       <c r="S144" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16449,48 +16440,57 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128362656</v>
+        <v>128362615</v>
       </c>
       <c r="B145" t="n">
-        <v>109490</v>
+        <v>98614</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>720904</v>
+        <v>720854</v>
       </c>
       <c r="R145" t="n">
-        <v>6382940</v>
+        <v>6382995</v>
       </c>
       <c r="S145" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>128362611</v>
       </c>
       <c r="B146" t="n">
-        <v>99385</v>
+        <v>99389</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>128362612</v>
       </c>
       <c r="B147" t="n">
-        <v>98550</v>
+        <v>98554</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>128362597</v>
       </c>
       <c r="B148" t="n">
-        <v>109490</v>
+        <v>109494</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>128362594</v>
       </c>
       <c r="B149" t="n">
-        <v>98550</v>
+        <v>98554</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>128362657</v>
       </c>
       <c r="B150" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>128362655</v>
       </c>
       <c r="B151" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>128362668</v>
       </c>
       <c r="B152" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>128362665</v>
       </c>
       <c r="B153" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>128362600</v>
       </c>
       <c r="B154" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>128362607</v>
       </c>
       <c r="B155" t="n">
-        <v>107546</v>
+        <v>107550</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17655,7 +17655,7 @@
         <v>128362652</v>
       </c>
       <c r="B156" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>128362626</v>
       </c>
       <c r="B157" t="n">
-        <v>98654</v>
+        <v>98658</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>128362596</v>
       </c>
       <c r="B158" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>128362621</v>
       </c>
       <c r="B159" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
         <v>128362659</v>
       </c>
       <c r="B160" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>128362623</v>
       </c>
       <c r="B161" t="n">
-        <v>98550</v>
+        <v>98554</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>128362663</v>
       </c>
       <c r="B162" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>128362670</v>
       </c>
       <c r="B163" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18540,37 +18540,37 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128362666</v>
+        <v>128362644</v>
       </c>
       <c r="B164" t="n">
-        <v>107546</v>
+        <v>98658</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -18580,14 +18580,14 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>720954</v>
+        <v>720889</v>
       </c>
       <c r="R164" t="n">
-        <v>6382931</v>
+        <v>6382907</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -18651,10 +18651,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128362644</v>
+        <v>128362614</v>
       </c>
       <c r="B165" t="n">
-        <v>98654</v>
+        <v>98614</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18662,26 +18662,26 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -18691,17 +18691,17 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2064, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>720889</v>
+        <v>720854</v>
       </c>
       <c r="R165" t="n">
-        <v>6382907</v>
+        <v>6383001</v>
       </c>
       <c r="S165" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18762,10 +18762,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128362614</v>
+        <v>128362672</v>
       </c>
       <c r="B166" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18806,13 +18806,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>720854</v>
+        <v>720992</v>
       </c>
       <c r="R166" t="n">
-        <v>6383001</v>
+        <v>6382917</v>
       </c>
       <c r="S166" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18873,10 +18873,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128362672</v>
+        <v>128362617</v>
       </c>
       <c r="B167" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18917,13 +18917,13 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>720992</v>
+        <v>720861</v>
       </c>
       <c r="R167" t="n">
-        <v>6382917</v>
+        <v>6383000</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18984,32 +18984,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128362617</v>
+        <v>128362666</v>
       </c>
       <c r="B168" t="n">
-        <v>98610</v>
+        <v>107550</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>219798</v>
+        <v>220079</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -19024,14 +19024,14 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2049, Gtl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>720861</v>
+        <v>720954</v>
       </c>
       <c r="R168" t="n">
-        <v>6383000</v>
+        <v>6382931</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -19737,45 +19737,48 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128808203</v>
+        <v>128808201</v>
       </c>
       <c r="B175" t="n">
-        <v>105686</v>
+        <v>92262</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>224098</v>
+        <v>232138</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>720949</v>
+        <v>720882</v>
       </c>
       <c r="R175" t="n">
-        <v>6382867</v>
+        <v>6382914</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19807,7 +19810,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19817,7 +19820,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19826,6 +19829,7 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
+      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -19844,48 +19848,45 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128808201</v>
+        <v>128808203</v>
       </c>
       <c r="B176" t="n">
-        <v>92262</v>
+        <v>105686</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>232138</v>
+        <v>224098</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>720882</v>
+        <v>720949</v>
       </c>
       <c r="R176" t="n">
-        <v>6382914</v>
+        <v>6382867</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19917,7 +19918,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19927,7 +19928,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19936,7 +19937,6 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -20267,32 +20267,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128811522</v>
+        <v>128811516</v>
       </c>
       <c r="B180" t="n">
-        <v>86926</v>
+        <v>86850</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>3674</v>
+        <v>442</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20302,10 +20302,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>720847</v>
+        <v>720793</v>
       </c>
       <c r="R180" t="n">
-        <v>6383038</v>
+        <v>6382789</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20364,32 +20364,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128811516</v>
+        <v>128811522</v>
       </c>
       <c r="B181" t="n">
-        <v>86850</v>
+        <v>86926</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>442</v>
+        <v>3674</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -20399,10 +20399,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>720793</v>
+        <v>720847</v>
       </c>
       <c r="R181" t="n">
-        <v>6382789</v>
+        <v>6383038</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20670,32 +20670,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128811501</v>
+        <v>128811513</v>
       </c>
       <c r="B184" t="n">
-        <v>86764</v>
+        <v>90969</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>3762</v>
+        <v>3286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -20705,10 +20705,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>720786</v>
+        <v>720914</v>
       </c>
       <c r="R184" t="n">
-        <v>6383069</v>
+        <v>6382786</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20767,10 +20767,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128811513</v>
+        <v>128808198</v>
       </c>
       <c r="B185" t="n">
-        <v>90969</v>
+        <v>86963</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20778,21 +20778,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>3286</v>
+        <v>6003295</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20802,10 +20802,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>720914</v>
+        <v>720928</v>
       </c>
       <c r="R185" t="n">
-        <v>6382786</v>
+        <v>6382883</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20835,36 +20835,47 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AD185" t="b">
         <v>0</v>
       </c>
       <c r="AE185" t="b">
         <v>0</v>
       </c>
+      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128808198</v>
+        <v>128811502</v>
       </c>
       <c r="B186" t="n">
         <v>86963</v>
@@ -20893,16 +20904,19 @@
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>720928</v>
+        <v>720958</v>
       </c>
       <c r="R186" t="n">
-        <v>6382883</v>
+        <v>6382920</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20932,19 +20946,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20960,60 +20964,57 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128811502</v>
+        <v>128811501</v>
       </c>
       <c r="B187" t="n">
-        <v>86963</v>
+        <v>86764</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>720958</v>
+        <v>720786</v>
       </c>
       <c r="R187" t="n">
-        <v>6382920</v>
+        <v>6383069</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21054,7 +21055,6 @@
       <c r="AE187" t="b">
         <v>0</v>
       </c>
-      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
       </c>
@@ -21073,48 +21073,45 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128811503</v>
+        <v>128808186</v>
       </c>
       <c r="B188" t="n">
-        <v>86963</v>
+        <v>86764</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>720839</v>
+        <v>720940</v>
       </c>
       <c r="R188" t="n">
-        <v>6382829</v>
+        <v>6382871</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21144,9 +21141,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21162,57 +21169,60 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128808186</v>
+        <v>128811503</v>
       </c>
       <c r="B189" t="n">
-        <v>86764</v>
+        <v>86963</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>720940</v>
+        <v>720839</v>
       </c>
       <c r="R189" t="n">
-        <v>6382871</v>
+        <v>6382829</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21242,19 +21252,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21270,12 +21270,12 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
@@ -21467,10 +21467,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128811497</v>
+        <v>128811511</v>
       </c>
       <c r="B192" t="n">
-        <v>92827</v>
+        <v>107550</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21478,14 +21478,23 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5449</v>
+        <v>220079</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr"/>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
@@ -21493,10 +21502,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>720815</v>
+        <v>720728</v>
       </c>
       <c r="R192" t="n">
-        <v>6382996</v>
+        <v>6382877</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21753,10 +21762,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128811511</v>
+        <v>128811497</v>
       </c>
       <c r="B195" t="n">
-        <v>107550</v>
+        <v>92827</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21764,23 +21773,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>220079</v>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>Jordtistel</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
@@ -21788,10 +21788,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>720728</v>
+        <v>720815</v>
       </c>
       <c r="R195" t="n">
-        <v>6382877</v>
+        <v>6382996</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22048,10 +22048,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128808191</v>
+        <v>128811508</v>
       </c>
       <c r="B198" t="n">
-        <v>92790</v>
+        <v>86963</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22059,34 +22059,37 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>4361</v>
+        <v>6003295</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>720923</v>
+        <v>720828</v>
       </c>
       <c r="R198" t="n">
-        <v>6382884</v>
+        <v>6383032</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22116,49 +22119,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AD198" t="b">
         <v>0</v>
       </c>
       <c r="AE198" t="b">
         <v>0</v>
       </c>
+      <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
       </c>
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>128811508</v>
+        <v>128808191</v>
       </c>
       <c r="B199" t="n">
-        <v>86963</v>
+        <v>92790</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22166,37 +22160,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6003295</v>
+        <v>4361</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>720828</v>
+        <v>720923</v>
       </c>
       <c r="R199" t="n">
-        <v>6383032</v>
+        <v>6382884</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22226,30 +22217,39 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AD199" t="b">
         <v>0</v>
       </c>
       <c r="AE199" t="b">
         <v>0</v>
       </c>
-      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
@@ -23304,32 +23304,32 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128808212</v>
+        <v>128811510</v>
       </c>
       <c r="B210" t="n">
-        <v>106261</v>
+        <v>107550</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>220785</v>
+        <v>220079</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -23339,10 +23339,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>720875</v>
+        <v>720809</v>
       </c>
       <c r="R210" t="n">
-        <v>6382950</v>
+        <v>6382787</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23372,19 +23372,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23399,44 +23389,44 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128811510</v>
+        <v>128808212</v>
       </c>
       <c r="B211" t="n">
-        <v>107550</v>
+        <v>106261</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>220079</v>
+        <v>220785</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23446,10 +23436,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>720809</v>
+        <v>720875</v>
       </c>
       <c r="R211" t="n">
-        <v>6382787</v>
+        <v>6382950</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23479,9 +23469,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23496,12 +23496,12 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -15570,32 +15570,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128362639</v>
+        <v>128362758</v>
       </c>
       <c r="B137" t="n">
-        <v>106261</v>
+        <v>96232</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220785</v>
+        <v>2180</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -15605,22 +15605,22 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>720889</v>
+        <v>720904</v>
       </c>
       <c r="R137" t="n">
-        <v>6382907</v>
+        <v>6382940</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, frisk.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15681,32 +15681,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128362758</v>
+        <v>128362639</v>
       </c>
       <c r="B138" t="n">
-        <v>96232</v>
+        <v>106261</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2180</v>
+        <v>220785</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -15716,22 +15716,22 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2046, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2069, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>720904</v>
+        <v>720889</v>
       </c>
       <c r="R138" t="n">
-        <v>6382940</v>
+        <v>6382907</v>
       </c>
       <c r="S138" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -16875,10 +16875,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128362594</v>
+        <v>128362657</v>
       </c>
       <c r="B149" t="n">
-        <v>98554</v>
+        <v>98614</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16886,26 +16886,26 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -16915,17 +16915,17 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2112, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>720898</v>
+        <v>720904</v>
       </c>
       <c r="R149" t="n">
-        <v>6382990</v>
+        <v>6382940</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128362657</v>
+        <v>128362655</v>
       </c>
       <c r="B150" t="n">
         <v>98614</v>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -17030,13 +17030,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>720904</v>
+        <v>720897</v>
       </c>
       <c r="R150" t="n">
-        <v>6382940</v>
+        <v>6382932</v>
       </c>
       <c r="S150" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17097,10 +17097,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128362655</v>
+        <v>128362594</v>
       </c>
       <c r="B151" t="n">
-        <v>98614</v>
+        <v>98554</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17108,26 +17108,26 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -17137,17 +17137,17 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2112, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>720897</v>
+        <v>720898</v>
       </c>
       <c r="R151" t="n">
-        <v>6382932</v>
+        <v>6382990</v>
       </c>
       <c r="S151" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128362659</v>
+        <v>128362623</v>
       </c>
       <c r="B160" t="n">
-        <v>98614</v>
+        <v>98554</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18107,26 +18107,26 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -18136,17 +18136,17 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>720910</v>
+        <v>720854</v>
       </c>
       <c r="R160" t="n">
-        <v>6382934</v>
+        <v>6382954</v>
       </c>
       <c r="S160" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18207,10 +18207,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128362623</v>
+        <v>128362659</v>
       </c>
       <c r="B161" t="n">
-        <v>98554</v>
+        <v>98614</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18218,26 +18218,26 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -18247,17 +18247,17 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Gothem Suderbys 1:11 (5) A 10780-2082, Gtl</t>
+          <t>Gothem Suderbys 1:11 (5) A 10780-2042, Gtl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>720854</v>
+        <v>720910</v>
       </c>
       <c r="R161" t="n">
-        <v>6382954</v>
+        <v>6382934</v>
       </c>
       <c r="S161" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -20670,32 +20670,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128811513</v>
+        <v>128811501</v>
       </c>
       <c r="B184" t="n">
-        <v>90969</v>
+        <v>86764</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>3286</v>
+        <v>3762</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -20705,10 +20705,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>720914</v>
+        <v>720786</v>
       </c>
       <c r="R184" t="n">
-        <v>6382786</v>
+        <v>6383069</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20767,10 +20767,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128808198</v>
+        <v>128811513</v>
       </c>
       <c r="B185" t="n">
-        <v>86963</v>
+        <v>90969</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20778,21 +20778,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6003295</v>
+        <v>3286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20802,10 +20802,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>720928</v>
+        <v>720914</v>
       </c>
       <c r="R185" t="n">
-        <v>6382883</v>
+        <v>6382786</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20835,40 +20835,29 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AD185" t="b">
         <v>0</v>
       </c>
       <c r="AE185" t="b">
         <v>0</v>
       </c>
-      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
@@ -20976,32 +20965,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128811501</v>
+        <v>128808198</v>
       </c>
       <c r="B187" t="n">
-        <v>86764</v>
+        <v>86963</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -21011,10 +21000,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>720786</v>
+        <v>720928</v>
       </c>
       <c r="R187" t="n">
-        <v>6383069</v>
+        <v>6382883</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21044,29 +21033,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AD187" t="b">
         <v>0</v>
       </c>
       <c r="AE187" t="b">
         <v>0</v>
       </c>
+      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
@@ -21467,10 +21467,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128811511</v>
+        <v>128811497</v>
       </c>
       <c r="B192" t="n">
-        <v>107550</v>
+        <v>92827</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21478,23 +21478,14 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220079</v>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>Jordtistel</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
@@ -21502,10 +21493,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>720728</v>
+        <v>720815</v>
       </c>
       <c r="R192" t="n">
-        <v>6382877</v>
+        <v>6382996</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21564,10 +21555,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128811507</v>
+        <v>128811511</v>
       </c>
       <c r="B193" t="n">
-        <v>86963</v>
+        <v>107550</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21575,37 +21566,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>720812</v>
+        <v>720728</v>
       </c>
       <c r="R193" t="n">
-        <v>6382982</v>
+        <v>6382877</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21646,7 +21634,6 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -21762,10 +21749,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128811497</v>
+        <v>128811507</v>
       </c>
       <c r="B195" t="n">
-        <v>92827</v>
+        <v>86963</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21773,25 +21760,37 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5449</v>
+        <v>6003295</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>720815</v>
+        <v>720812</v>
       </c>
       <c r="R195" t="n">
-        <v>6382996</v>
+        <v>6382982</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21832,6 +21831,7 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
+      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -22256,32 +22256,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128808196</v>
+        <v>128808209</v>
       </c>
       <c r="B200" t="n">
-        <v>86963</v>
+        <v>86810</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22291,10 +22291,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>720882</v>
+        <v>720782</v>
       </c>
       <c r="R200" t="n">
-        <v>6382944</v>
+        <v>6383065</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22326,7 +22326,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22336,7 +22336,12 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>3 fk bild</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22345,7 +22350,6 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
-      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
@@ -22364,32 +22368,32 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128808209</v>
+        <v>128811514</v>
       </c>
       <c r="B201" t="n">
-        <v>86810</v>
+        <v>90969</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>424</v>
+        <v>3286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -22399,10 +22403,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>720782</v>
+        <v>720775</v>
       </c>
       <c r="R201" t="n">
-        <v>6383065</v>
+        <v>6382814</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22432,24 +22436,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>3 fk bild</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22464,22 +22453,22 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128811514</v>
+        <v>128808196</v>
       </c>
       <c r="B202" t="n">
-        <v>90969</v>
+        <v>86963</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22487,21 +22476,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>3286</v>
+        <v>6003295</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -22511,10 +22500,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>720775</v>
+        <v>720882</v>
       </c>
       <c r="R202" t="n">
-        <v>6382814</v>
+        <v>6382944</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22544,39 +22533,50 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AD202" t="b">
         <v>0</v>
       </c>
       <c r="AE202" t="b">
         <v>0</v>
       </c>
+      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128808207</v>
+        <v>128811506</v>
       </c>
       <c r="B203" t="n">
-        <v>90969</v>
+        <v>86963</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22584,34 +22584,37 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>3286</v>
+        <v>6003295</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>720854</v>
+        <v>720791</v>
       </c>
       <c r="R203" t="n">
-        <v>6382963</v>
+        <v>6382968</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22641,71 +22644,62 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AD203" t="b">
         <v>0</v>
       </c>
       <c r="AE203" t="b">
         <v>0</v>
       </c>
+      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
       </c>
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128812128</v>
+        <v>128808192</v>
       </c>
       <c r="B204" t="n">
-        <v>105686</v>
+        <v>86963</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -22715,10 +22709,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>720940</v>
+        <v>720870</v>
       </c>
       <c r="R204" t="n">
-        <v>6382871</v>
+        <v>6382928</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22750,7 +22744,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -22760,7 +22754,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22769,6 +22763,7 @@
       <c r="AE204" t="b">
         <v>0</v>
       </c>
+      <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="b">
         <v>0</v>
       </c>
@@ -22787,10 +22782,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128808192</v>
+        <v>128808207</v>
       </c>
       <c r="B205" t="n">
-        <v>86963</v>
+        <v>90969</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22798,21 +22793,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6003295</v>
+        <v>3286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -22822,10 +22817,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>720870</v>
+        <v>720854</v>
       </c>
       <c r="R205" t="n">
-        <v>6382928</v>
+        <v>6382963</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22857,7 +22852,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22867,7 +22862,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22876,7 +22871,6 @@
       <c r="AE205" t="b">
         <v>0</v>
       </c>
-      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
       </c>
@@ -22895,48 +22889,45 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128811506</v>
+        <v>128812128</v>
       </c>
       <c r="B206" t="n">
-        <v>86963</v>
+        <v>105686</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6003295</v>
+        <v>224098</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>720791</v>
+        <v>720940</v>
       </c>
       <c r="R206" t="n">
-        <v>6382968</v>
+        <v>6382871</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22966,62 +22957,71 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AD206" t="b">
         <v>0</v>
       </c>
       <c r="AE206" t="b">
         <v>0</v>
       </c>
-      <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="b">
         <v>0</v>
       </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128808206</v>
+        <v>128808211</v>
       </c>
       <c r="B207" t="n">
-        <v>90969</v>
+        <v>90275</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>3286</v>
+        <v>245042</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -23031,10 +23031,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>720877</v>
+        <v>720816</v>
       </c>
       <c r="R207" t="n">
-        <v>6382941</v>
+        <v>6382972</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23066,7 +23066,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -23076,7 +23076,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23103,32 +23103,32 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128808211</v>
+        <v>128808206</v>
       </c>
       <c r="B208" t="n">
-        <v>90275</v>
+        <v>90969</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>245042</v>
+        <v>3286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -23138,10 +23138,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>720816</v>
+        <v>720877</v>
       </c>
       <c r="R208" t="n">
-        <v>6382972</v>
+        <v>6382941</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23173,7 +23173,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -23183,7 +23183,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23304,10 +23304,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128811510</v>
+        <v>128811504</v>
       </c>
       <c r="B210" t="n">
-        <v>107550</v>
+        <v>86963</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23315,34 +23315,37 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>720809</v>
+        <v>720789</v>
       </c>
       <c r="R210" t="n">
-        <v>6382787</v>
+        <v>6382798</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23383,6 +23386,7 @@
       <c r="AE210" t="b">
         <v>0</v>
       </c>
+      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
@@ -23401,32 +23405,32 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128808212</v>
+        <v>128811510</v>
       </c>
       <c r="B211" t="n">
-        <v>106261</v>
+        <v>107550</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>220785</v>
+        <v>220079</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23436,10 +23440,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>720875</v>
+        <v>720809</v>
       </c>
       <c r="R211" t="n">
-        <v>6382950</v>
+        <v>6382787</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23469,19 +23473,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z211" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB211" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23496,60 +23490,57 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128811504</v>
+        <v>128808212</v>
       </c>
       <c r="B212" t="n">
-        <v>86963</v>
+        <v>106261</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6003295</v>
+        <v>220785</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>720789</v>
+        <v>720875</v>
       </c>
       <c r="R212" t="n">
-        <v>6382798</v>
+        <v>6382950</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23579,30 +23570,39 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AD212" t="b">
         <v>0</v>
       </c>
       <c r="AE212" t="b">
         <v>0</v>
       </c>
-      <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="b">
         <v>0</v>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>105082160</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>128808200</v>
       </c>
       <c r="B169" t="n">
-        <v>98658</v>
+        <v>98665</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19202,32 +19202,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128811517</v>
+        <v>128808213</v>
       </c>
       <c r="B170" t="n">
-        <v>86850</v>
+        <v>86931</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>442</v>
+        <v>3674</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19237,10 +19237,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>720799</v>
+        <v>720849</v>
       </c>
       <c r="R170" t="n">
-        <v>6382978</v>
+        <v>6383038</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19270,9 +19270,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19287,22 +19297,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128808210</v>
+        <v>128811517</v>
       </c>
       <c r="B171" t="n">
-        <v>86850</v>
+        <v>86855</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19328,19 +19338,16 @@
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>720874</v>
+        <v>720799</v>
       </c>
       <c r="R171" t="n">
-        <v>6382938</v>
+        <v>6382978</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19370,90 +19377,77 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Negativ KOH hattkant och bulbkant.</t>
-        </is>
-      </c>
       <c r="AD171" t="b">
         <v>0</v>
       </c>
       <c r="AE171" t="b">
         <v>0</v>
       </c>
-      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128808213</v>
+        <v>128808210</v>
       </c>
       <c r="B172" t="n">
-        <v>86926</v>
+        <v>86855</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3674</v>
+        <v>442</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>720849</v>
+        <v>720874</v>
       </c>
       <c r="R172" t="n">
-        <v>6383038</v>
+        <v>6382938</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19485,7 +19479,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19495,7 +19489,12 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>Negativ KOH hattkant och bulbkant.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19504,6 +19503,7 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -19525,7 +19525,7 @@
         <v>128808204</v>
       </c>
       <c r="B173" t="n">
-        <v>107550</v>
+        <v>107558</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>128808194</v>
       </c>
       <c r="B174" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19737,48 +19737,45 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128808201</v>
+        <v>128808203</v>
       </c>
       <c r="B175" t="n">
-        <v>92262</v>
+        <v>105693</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>232138</v>
+        <v>224098</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>720882</v>
+        <v>720949</v>
       </c>
       <c r="R175" t="n">
-        <v>6382914</v>
+        <v>6382867</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19810,7 +19807,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19820,7 +19817,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19829,7 +19826,6 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -19848,45 +19844,48 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128808203</v>
+        <v>128808201</v>
       </c>
       <c r="B176" t="n">
-        <v>105686</v>
+        <v>92267</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>224098</v>
+        <v>232138</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>720949</v>
+        <v>720882</v>
       </c>
       <c r="R176" t="n">
-        <v>6382867</v>
+        <v>6382914</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19918,7 +19917,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19928,7 +19927,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19937,6 +19936,7 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -19958,7 +19958,7 @@
         <v>128808208</v>
       </c>
       <c r="B177" t="n">
-        <v>86850</v>
+        <v>86855</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>128808205</v>
       </c>
       <c r="B178" t="n">
-        <v>107550</v>
+        <v>107558</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>128811515</v>
       </c>
       <c r="B179" t="n">
-        <v>87020</v>
+        <v>87025</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20267,32 +20267,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128811516</v>
+        <v>128811522</v>
       </c>
       <c r="B180" t="n">
-        <v>86850</v>
+        <v>86931</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>442</v>
+        <v>3674</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20302,10 +20302,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>720793</v>
+        <v>720847</v>
       </c>
       <c r="R180" t="n">
-        <v>6382789</v>
+        <v>6383038</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20364,32 +20364,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128811522</v>
+        <v>128811516</v>
       </c>
       <c r="B181" t="n">
-        <v>86926</v>
+        <v>86855</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>3674</v>
+        <v>442</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -20399,10 +20399,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>720847</v>
+        <v>720793</v>
       </c>
       <c r="R181" t="n">
-        <v>6383038</v>
+        <v>6382789</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20464,7 +20464,7 @@
         <v>128808197</v>
       </c>
       <c r="B182" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>128811505</v>
       </c>
       <c r="B183" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20670,32 +20670,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128811501</v>
+        <v>128811513</v>
       </c>
       <c r="B184" t="n">
-        <v>86764</v>
+        <v>90974</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>3762</v>
+        <v>3286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -20705,10 +20705,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>720786</v>
+        <v>720914</v>
       </c>
       <c r="R184" t="n">
-        <v>6383069</v>
+        <v>6382786</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20767,32 +20767,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128811513</v>
+        <v>128811501</v>
       </c>
       <c r="B185" t="n">
-        <v>90969</v>
+        <v>86769</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>3286</v>
+        <v>3762</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20802,10 +20802,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>720914</v>
+        <v>720786</v>
       </c>
       <c r="R185" t="n">
-        <v>6382786</v>
+        <v>6383069</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20864,10 +20864,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128811502</v>
+        <v>128808198</v>
       </c>
       <c r="B186" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20893,19 +20893,16 @@
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>720958</v>
+        <v>720928</v>
       </c>
       <c r="R186" t="n">
-        <v>6382920</v>
+        <v>6382883</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20935,9 +20932,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20953,22 +20960,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128808198</v>
+        <v>128811502</v>
       </c>
       <c r="B187" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20994,16 +21001,19 @@
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>720928</v>
+        <v>720958</v>
       </c>
       <c r="R187" t="n">
-        <v>6382883</v>
+        <v>6382920</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21033,19 +21043,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21061,12 +21061,12 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
@@ -21076,7 +21076,7 @@
         <v>128808186</v>
       </c>
       <c r="B188" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>128811503</v>
       </c>
       <c r="B189" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>128811496</v>
       </c>
       <c r="B190" t="n">
-        <v>86810</v>
+        <v>86815</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>128811498</v>
       </c>
       <c r="B191" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>128811497</v>
       </c>
       <c r="B192" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21555,32 +21555,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128811511</v>
+        <v>128811512</v>
       </c>
       <c r="B193" t="n">
-        <v>107550</v>
+        <v>86884</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>220079</v>
+        <v>248956</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21590,10 +21590,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>720728</v>
+        <v>720762</v>
       </c>
       <c r="R193" t="n">
-        <v>6382877</v>
+        <v>6382917</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21652,45 +21652,48 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128811512</v>
+        <v>128811507</v>
       </c>
       <c r="B194" t="n">
-        <v>86879</v>
+        <v>86968</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>720762</v>
+        <v>720812</v>
       </c>
       <c r="R194" t="n">
-        <v>6382917</v>
+        <v>6382982</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21731,6 +21734,7 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
+      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
@@ -21749,10 +21753,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128811507</v>
+        <v>128811511</v>
       </c>
       <c r="B195" t="n">
-        <v>86963</v>
+        <v>107558</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21760,37 +21764,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>720812</v>
+        <v>720728</v>
       </c>
       <c r="R195" t="n">
-        <v>6382982</v>
+        <v>6382877</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21831,7 +21832,6 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -21853,7 +21853,7 @@
         <v>128811521</v>
       </c>
       <c r="B196" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>128811509</v>
       </c>
       <c r="B197" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22048,10 +22048,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128811508</v>
+        <v>128808191</v>
       </c>
       <c r="B198" t="n">
-        <v>86963</v>
+        <v>92795</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22059,37 +22059,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6003295</v>
+        <v>4361</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>720828</v>
+        <v>720923</v>
       </c>
       <c r="R198" t="n">
-        <v>6383032</v>
+        <v>6382884</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22119,40 +22116,49 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AD198" t="b">
         <v>0</v>
       </c>
       <c r="AE198" t="b">
         <v>0</v>
       </c>
-      <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
       </c>
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>128808191</v>
+        <v>128811508</v>
       </c>
       <c r="B199" t="n">
-        <v>92790</v>
+        <v>86968</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22160,34 +22166,37 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>4361</v>
+        <v>6003295</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>720923</v>
+        <v>720828</v>
       </c>
       <c r="R199" t="n">
-        <v>6382884</v>
+        <v>6383032</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22217,39 +22226,30 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AD199" t="b">
         <v>0</v>
       </c>
       <c r="AE199" t="b">
         <v>0</v>
       </c>
+      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
@@ -22259,7 +22259,7 @@
         <v>128808209</v>
       </c>
       <c r="B200" t="n">
-        <v>86810</v>
+        <v>86815</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>128811514</v>
       </c>
       <c r="B201" t="n">
-        <v>90969</v>
+        <v>90974</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>128808196</v>
       </c>
       <c r="B202" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22573,10 +22573,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128811506</v>
+        <v>128808207</v>
       </c>
       <c r="B203" t="n">
-        <v>86963</v>
+        <v>90974</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22584,37 +22584,34 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6003295</v>
+        <v>3286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>720791</v>
+        <v>720854</v>
       </c>
       <c r="R203" t="n">
-        <v>6382968</v>
+        <v>6382963</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22644,30 +22641,39 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AD203" t="b">
         <v>0</v>
       </c>
       <c r="AE203" t="b">
         <v>0</v>
       </c>
-      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
       </c>
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
@@ -22677,7 +22683,7 @@
         <v>128808192</v>
       </c>
       <c r="B204" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22782,10 +22788,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128808207</v>
+        <v>128811506</v>
       </c>
       <c r="B205" t="n">
-        <v>90969</v>
+        <v>86968</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22793,34 +22799,37 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>3286</v>
+        <v>6003295</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>720854</v>
+        <v>720791</v>
       </c>
       <c r="R205" t="n">
-        <v>6382963</v>
+        <v>6382968</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22850,39 +22859,30 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AD205" t="b">
         <v>0</v>
       </c>
       <c r="AE205" t="b">
         <v>0</v>
       </c>
+      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
       </c>
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
@@ -22892,7 +22892,7 @@
         <v>128812128</v>
       </c>
       <c r="B206" t="n">
-        <v>105686</v>
+        <v>105693</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22996,32 +22996,32 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128808211</v>
+        <v>128808206</v>
       </c>
       <c r="B207" t="n">
-        <v>90275</v>
+        <v>90974</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>245042</v>
+        <v>3286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -23031,10 +23031,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>720816</v>
+        <v>720877</v>
       </c>
       <c r="R207" t="n">
-        <v>6382972</v>
+        <v>6382941</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23066,7 +23066,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -23076,7 +23076,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23103,32 +23103,32 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128808206</v>
+        <v>128808211</v>
       </c>
       <c r="B208" t="n">
-        <v>90969</v>
+        <v>90280</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>3286</v>
+        <v>245042</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -23138,10 +23138,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>720877</v>
+        <v>720816</v>
       </c>
       <c r="R208" t="n">
-        <v>6382941</v>
+        <v>6382972</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23173,7 +23173,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -23183,7 +23183,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23213,7 +23213,7 @@
         <v>128811499</v>
       </c>
       <c r="B209" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23304,10 +23304,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128811504</v>
+        <v>128811510</v>
       </c>
       <c r="B210" t="n">
-        <v>86963</v>
+        <v>107558</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23315,37 +23315,34 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>720789</v>
+        <v>720809</v>
       </c>
       <c r="R210" t="n">
-        <v>6382798</v>
+        <v>6382787</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23386,7 +23383,6 @@
       <c r="AE210" t="b">
         <v>0</v>
       </c>
-      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
@@ -23405,32 +23401,32 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128811510</v>
+        <v>128808212</v>
       </c>
       <c r="B211" t="n">
-        <v>107550</v>
+        <v>106268</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>220079</v>
+        <v>220785</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23440,10 +23436,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>720809</v>
+        <v>720875</v>
       </c>
       <c r="R211" t="n">
-        <v>6382787</v>
+        <v>6382950</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23473,9 +23469,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23490,57 +23496,60 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128808212</v>
+        <v>128811504</v>
       </c>
       <c r="B212" t="n">
-        <v>106261</v>
+        <v>86968</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>220785</v>
+        <v>6003295</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>720875</v>
+        <v>720789</v>
       </c>
       <c r="R212" t="n">
-        <v>6382950</v>
+        <v>6382798</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23570,39 +23579,30 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AD212" t="b">
         <v>0</v>
       </c>
       <c r="AE212" t="b">
         <v>0</v>
       </c>
+      <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="b">
         <v>0</v>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
@@ -23612,7 +23612,7 @@
         <v>128808187</v>
       </c>
       <c r="B213" t="n">
-        <v>86964</v>
+        <v>86969</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>105082160</v>
       </c>
       <c r="B3" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -19202,32 +19202,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128811517</v>
+        <v>128808204</v>
       </c>
       <c r="B170" t="n">
-        <v>86862</v>
+        <v>107566</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>442</v>
+        <v>220079</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19237,10 +19237,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>720799</v>
+        <v>720903</v>
       </c>
       <c r="R170" t="n">
-        <v>6382978</v>
+        <v>6382925</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19270,9 +19270,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19287,60 +19297,57 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128808210</v>
+        <v>128808194</v>
       </c>
       <c r="B171" t="n">
-        <v>86862</v>
+        <v>86975</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>442</v>
+        <v>6003295</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>720874</v>
+        <v>720872</v>
       </c>
       <c r="R171" t="n">
-        <v>6382938</v>
+        <v>6382981</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19372,7 +19379,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19382,12 +19389,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Negativ KOH hattkant och bulbkant.</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19415,32 +19417,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128808204</v>
+        <v>128808213</v>
       </c>
       <c r="B172" t="n">
-        <v>107566</v>
+        <v>86938</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220079</v>
+        <v>3674</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -19450,10 +19452,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>720903</v>
+        <v>720849</v>
       </c>
       <c r="R172" t="n">
-        <v>6382925</v>
+        <v>6383038</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19485,7 +19487,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19495,7 +19497,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19522,32 +19524,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128808194</v>
+        <v>128811517</v>
       </c>
       <c r="B173" t="n">
-        <v>86975</v>
+        <v>86862</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6003295</v>
+        <v>442</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19557,10 +19559,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>720872</v>
+        <v>720799</v>
       </c>
       <c r="R173" t="n">
-        <v>6382981</v>
+        <v>6382978</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19590,85 +19592,77 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128808213</v>
+        <v>128808210</v>
       </c>
       <c r="B174" t="n">
-        <v>86938</v>
+        <v>86862</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>3674</v>
+        <v>442</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>720849</v>
+        <v>720874</v>
       </c>
       <c r="R174" t="n">
-        <v>6383038</v>
+        <v>6382938</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19700,7 +19694,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19710,7 +19704,12 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Negativ KOH hattkant och bulbkant.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19719,6 +19718,7 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
+      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -20670,10 +20670,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128808198</v>
+        <v>128811513</v>
       </c>
       <c r="B184" t="n">
-        <v>86975</v>
+        <v>90981</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20681,21 +20681,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6003295</v>
+        <v>3286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -20705,10 +20705,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>720928</v>
+        <v>720914</v>
       </c>
       <c r="R184" t="n">
-        <v>6382883</v>
+        <v>6382786</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20738,88 +20738,74 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AD184" t="b">
         <v>0</v>
       </c>
       <c r="AE184" t="b">
         <v>0</v>
       </c>
-      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128811502</v>
+        <v>128811501</v>
       </c>
       <c r="B185" t="n">
-        <v>86975</v>
+        <v>86776</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>720958</v>
+        <v>720786</v>
       </c>
       <c r="R185" t="n">
-        <v>6382920</v>
+        <v>6383069</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20860,7 +20846,6 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
-      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
@@ -20879,10 +20864,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128811513</v>
+        <v>128808198</v>
       </c>
       <c r="B186" t="n">
-        <v>90981</v>
+        <v>86975</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20890,21 +20875,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>3286</v>
+        <v>6003295</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -20914,10 +20899,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>720914</v>
+        <v>720928</v>
       </c>
       <c r="R186" t="n">
-        <v>6382786</v>
+        <v>6382883</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20947,74 +20932,88 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AD186" t="b">
         <v>0</v>
       </c>
       <c r="AE186" t="b">
         <v>0</v>
       </c>
+      <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="b">
         <v>0</v>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128811501</v>
+        <v>128811502</v>
       </c>
       <c r="B187" t="n">
-        <v>86776</v>
+        <v>86975</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>720786</v>
+        <v>720958</v>
       </c>
       <c r="R187" t="n">
-        <v>6383069</v>
+        <v>6382920</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21055,6 +21054,7 @@
       <c r="AE187" t="b">
         <v>0</v>
       </c>
+      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
       </c>
@@ -21282,25 +21282,34 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128811498</v>
+        <v>128811496</v>
       </c>
       <c r="B190" t="n">
-        <v>92840</v>
+        <v>86822</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>5449</v>
+        <v>424</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
@@ -21308,10 +21317,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>720831</v>
+        <v>720807</v>
       </c>
       <c r="R190" t="n">
-        <v>6383010</v>
+        <v>6382962</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21370,34 +21379,25 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128811496</v>
+        <v>128811498</v>
       </c>
       <c r="B191" t="n">
-        <v>86822</v>
+        <v>92840</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>424</v>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>Svartgrön spindling</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
@@ -21405,10 +21405,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>720807</v>
+        <v>720831</v>
       </c>
       <c r="R191" t="n">
-        <v>6382962</v>
+        <v>6383010</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21467,10 +21467,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128811511</v>
+        <v>128811507</v>
       </c>
       <c r="B192" t="n">
-        <v>107566</v>
+        <v>86975</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21478,34 +21478,37 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>720728</v>
+        <v>720812</v>
       </c>
       <c r="R192" t="n">
-        <v>6382877</v>
+        <v>6382982</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21546,6 +21549,7 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
+      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
@@ -21564,10 +21568,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128811507</v>
+        <v>128811497</v>
       </c>
       <c r="B193" t="n">
-        <v>86975</v>
+        <v>92840</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21575,37 +21579,25 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6003295</v>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>Odörspindling</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>720812</v>
+        <v>720815</v>
       </c>
       <c r="R193" t="n">
-        <v>6382982</v>
+        <v>6382996</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21646,7 +21638,6 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -21665,10 +21656,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128811497</v>
+        <v>128811511</v>
       </c>
       <c r="B194" t="n">
-        <v>92840</v>
+        <v>107566</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21676,14 +21667,23 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>5449</v>
+        <v>220079</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr"/>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
@@ -21691,10 +21691,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>720815</v>
+        <v>720728</v>
       </c>
       <c r="R194" t="n">
-        <v>6382996</v>
+        <v>6382877</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22256,32 +22256,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128808196</v>
+        <v>128808209</v>
       </c>
       <c r="B200" t="n">
-        <v>86975</v>
+        <v>86822</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22291,10 +22291,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>720882</v>
+        <v>720782</v>
       </c>
       <c r="R200" t="n">
-        <v>6382944</v>
+        <v>6383065</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22326,7 +22326,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22336,7 +22336,12 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>3 fk bild</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22345,7 +22350,6 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
-      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
@@ -22461,32 +22465,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128808209</v>
+        <v>128808196</v>
       </c>
       <c r="B202" t="n">
-        <v>86822</v>
+        <v>86975</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -22496,10 +22500,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>720782</v>
+        <v>720882</v>
       </c>
       <c r="R202" t="n">
-        <v>6383065</v>
+        <v>6382944</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22531,7 +22535,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -22541,12 +22545,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>3 fk bild</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22555,6 +22554,7 @@
       <c r="AE202" t="b">
         <v>0</v>
       </c>
+      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10780-2025 artfynd.xlsx
+++ b/artfynd/A 10780-2025 artfynd.xlsx
@@ -19098,7 +19098,7 @@
         <v>128808200</v>
       </c>
       <c r="B169" t="n">
-        <v>98673</v>
+        <v>98678</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>128808204</v>
       </c>
       <c r="B170" t="n">
-        <v>107566</v>
+        <v>107571</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19309,32 +19309,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128808194</v>
+        <v>128811517</v>
       </c>
       <c r="B171" t="n">
-        <v>86975</v>
+        <v>86865</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6003295</v>
+        <v>442</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19344,10 +19344,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>720872</v>
+        <v>720799</v>
       </c>
       <c r="R171" t="n">
-        <v>6382981</v>
+        <v>6382978</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19377,85 +19377,77 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AD171" t="b">
         <v>0</v>
       </c>
       <c r="AE171" t="b">
         <v>0</v>
       </c>
-      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128808213</v>
+        <v>128808210</v>
       </c>
       <c r="B172" t="n">
-        <v>86938</v>
+        <v>86865</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3674</v>
+        <v>442</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>720849</v>
+        <v>720874</v>
       </c>
       <c r="R172" t="n">
-        <v>6383038</v>
+        <v>6382938</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19487,7 +19479,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19497,7 +19489,12 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>Negativ KOH hattkant och bulbkant.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19506,6 +19503,7 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -19524,32 +19522,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128811517</v>
+        <v>128808213</v>
       </c>
       <c r="B173" t="n">
-        <v>86862</v>
+        <v>86941</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>442</v>
+        <v>3674</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19559,10 +19557,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>720799</v>
+        <v>720849</v>
       </c>
       <c r="R173" t="n">
-        <v>6382978</v>
+        <v>6383038</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19592,9 +19590,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19609,60 +19617,57 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128808210</v>
+        <v>128808194</v>
       </c>
       <c r="B174" t="n">
-        <v>86862</v>
+        <v>86978</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>442</v>
+        <v>6003295</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>720874</v>
+        <v>720872</v>
       </c>
       <c r="R174" t="n">
-        <v>6382938</v>
+        <v>6382981</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19694,7 +19699,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19704,12 +19709,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Negativ KOH hattkant och bulbkant.</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19740,7 +19740,7 @@
         <v>128808201</v>
       </c>
       <c r="B175" t="n">
-        <v>92275</v>
+        <v>92280</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>128808203</v>
       </c>
       <c r="B176" t="n">
-        <v>105701</v>
+        <v>105706</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>128808208</v>
       </c>
       <c r="B177" t="n">
-        <v>86862</v>
+        <v>86865</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>128808205</v>
       </c>
       <c r="B178" t="n">
-        <v>107566</v>
+        <v>107571</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>128811515</v>
       </c>
       <c r="B179" t="n">
-        <v>87032</v>
+        <v>87035</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20267,32 +20267,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128811522</v>
+        <v>128811516</v>
       </c>
       <c r="B180" t="n">
-        <v>86938</v>
+        <v>86865</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>3674</v>
+        <v>442</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20302,10 +20302,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>720847</v>
+        <v>720793</v>
       </c>
       <c r="R180" t="n">
-        <v>6383038</v>
+        <v>6382789</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20364,32 +20364,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128811516</v>
+        <v>128811522</v>
       </c>
       <c r="B181" t="n">
-        <v>86862</v>
+        <v>86941</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>442</v>
+        <v>3674</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -20399,10 +20399,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>720793</v>
+        <v>720847</v>
       </c>
       <c r="R181" t="n">
-        <v>6382789</v>
+        <v>6383038</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20464,7 +20464,7 @@
         <v>128808197</v>
       </c>
       <c r="B182" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>128811505</v>
       </c>
       <c r="B183" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>128811513</v>
       </c>
       <c r="B184" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>128811501</v>
       </c>
       <c r="B185" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>128808198</v>
       </c>
       <c r="B186" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>128811502</v>
       </c>
       <c r="B187" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>128808186</v>
       </c>
       <c r="B188" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>128811503</v>
       </c>
       <c r="B189" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21282,34 +21282,25 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128811496</v>
+        <v>128811498</v>
       </c>
       <c r="B190" t="n">
-        <v>86822</v>
+        <v>92845</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>424</v>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>Svartgrön spindling</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
@@ -21317,10 +21308,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>720807</v>
+        <v>720831</v>
       </c>
       <c r="R190" t="n">
-        <v>6382962</v>
+        <v>6383010</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21379,25 +21370,34 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128811498</v>
+        <v>128811496</v>
       </c>
       <c r="B191" t="n">
-        <v>92840</v>
+        <v>86825</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5449</v>
+        <v>424</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
@@ -21405,10 +21405,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>720831</v>
+        <v>720807</v>
       </c>
       <c r="R191" t="n">
-        <v>6383010</v>
+        <v>6382962</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21467,48 +21467,45 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128811507</v>
+        <v>128811512</v>
       </c>
       <c r="B192" t="n">
-        <v>86975</v>
+        <v>86894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>720812</v>
+        <v>720762</v>
       </c>
       <c r="R192" t="n">
-        <v>6382982</v>
+        <v>6382917</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21549,7 +21546,6 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
-      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
@@ -21571,7 +21567,7 @@
         <v>128811497</v>
       </c>
       <c r="B193" t="n">
-        <v>92840</v>
+        <v>92845</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21659,7 +21655,7 @@
         <v>128811511</v>
       </c>
       <c r="B194" t="n">
-        <v>107566</v>
+        <v>107571</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21753,45 +21749,48 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128811512</v>
+        <v>128811507</v>
       </c>
       <c r="B195" t="n">
-        <v>86891</v>
+        <v>86978</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Gothem Suderbys, Gtl</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>720762</v>
+        <v>720812</v>
       </c>
       <c r="R195" t="n">
-        <v>6382917</v>
+        <v>6382982</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21832,6 +21831,7 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
+      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -21853,7 +21853,7 @@
         <v>128811521</v>
       </c>
       <c r="B196" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>128811509</v>
       </c>
       <c r="B197" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>128808191</v>
       </c>
       <c r="B198" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>128811508</v>
       </c>
       <c r="B199" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22256,32 +22256,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128808209</v>
+        <v>128811514</v>
       </c>
       <c r="B200" t="n">
-        <v>86822</v>
+        <v>90984</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>424</v>
+        <v>3286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22291,10 +22291,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>720782</v>
+        <v>720775</v>
       </c>
       <c r="R200" t="n">
-        <v>6383065</v>
+        <v>6382814</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22324,24 +22324,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>3 fk bild</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22356,44 +22341,44 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128811514</v>
+        <v>128808209</v>
       </c>
       <c r="B201" t="n">
-        <v>90981</v>
+        <v>86825</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>3286</v>
+        <v>424</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -22403,10 +22388,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>720775</v>
+        <v>720782</v>
       </c>
       <c r="R201" t="n">
-        <v>6382814</v>
+        <v>6383065</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22436,9 +22421,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>3 fk bild</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22453,12 +22453,12 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
@@ -22468,7 +22468,7 @@
         <v>128808196</v>
       </c>
       <c r="B202" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22573,32 +22573,32 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128812128</v>
+        <v>128808207</v>
       </c>
       <c r="B203" t="n">
-        <v>105701</v>
+        <v>90984</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>224098</v>
+        <v>3286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -22608,10 +22608,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>720940</v>
+        <v>720854</v>
       </c>
       <c r="R203" t="n">
-        <v>6382871</v>
+        <v>6382963</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22643,7 +22643,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -22653,7 +22653,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22680,32 +22680,32 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128808192</v>
+        <v>128812128</v>
       </c>
       <c r="B204" t="n">
-        <v>86975</v>
+        <v>105706</v>
       </c>
       <c r="D20